--- a/source/bin/excel/audio.xlsx
+++ b/source/bin/excel/audio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1072D70D-6FCC-45B4-994A-FFC18310E563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2527F154-67EF-4DE2-9305-39B6E7250D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="722">
   <si>
     <t>sheet</t>
   </si>
@@ -2425,381 +2425,461 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>fate卡池切换页签</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_lobby/gacha_banner_fate</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_对局bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_养成bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_train_bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_match_bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_activity_enter</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_进入界面</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_ui_open</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_窗口打开（剧情、任务、奖励）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_养成_失败</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_养成_成功</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_养成_大成功</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_train_failure</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_train_success</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_train_great_success</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_event_show</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_事件_出现</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_事件_普通</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_事件_成功</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_事件_大成功</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_event_normal</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_event_success</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_event_great_success</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_等待跳入传送门</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_waiting_enter_match</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_match_begin</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_比赛开始</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_traveling</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_穿越中</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_比赛结束</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_match_over</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀斗_生涯结束</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504quedou_lifetime_over</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>背水_大金火焰</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504beishui_big_fire</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2504beishui_normal_fire</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>背水_中紫火焰</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>music/25xila_duiju.mp3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>优雅格调</t>
+  </si>
+  <si>
+    <t>優雅格調</t>
+  </si>
+  <si>
+    <t>Majestic Elegance</t>
+  </si>
+  <si>
+    <t>우아한 격조</t>
+  </si>
+  <si>
+    <t>2506合成活动bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2506xila_bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>優雅に、格調高く</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>絶景</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ミッドナイトララバイ</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>璃央卡池切换页签</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_lobby/gacha_banner_liyang</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>music/lobby_yiji.mp3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>闲暇炒面</t>
+  </si>
+  <si>
+    <t>閒暇炒麵</t>
+  </si>
+  <si>
+    <t>audio/audio_event/2508hanghai_sea_bird</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2508hanghai_sea_wave</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>航海_环境音_海浪（常驻）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>航海_环境音_海鸥叫（白天）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>航海_环境音_雷雨（雨天）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>航海_抚子_大炮</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>航海_任务、奖励弹窗开启</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2508hanghai_rain</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2508hanghai_boom</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mayo Yakisoba</t>
+  </si>
+  <si>
+    <t>마요 야키소바</t>
+  </si>
+  <si>
+    <t>2508青云之志_普通关循环</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2508qyzz_lobby_normal_loop</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2508青云之志_BOSS关循环</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2508qyzz_lobby_boss_loop</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2508青云之志_进入大厅</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2508qyzz_lobby_in</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2508青云之志_大厅界面_喷火</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2508qyzz_lobby_breathing</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2508青云之志_大厅界面_闪电</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2508qyzz_lobby_lighting</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2508青云之志_大厅界面_射箭</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2508qyzz_lobby_shooting</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2508青云之志_进入关卡列表</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2508qyzz_stage_show</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2508青云之志_进入商店</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2508qyzz_shop_pop</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2508青云之志_fevertime</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2508qyzz_stage_fevertime</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2508青云之志_关卡clear</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2508qyzz_stage_clear</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2508青云之志_游戏结束</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2508qyzz_stage_game_over</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2508青云之志_护身符变形</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2508qyzz_stage_amulet_transform</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">リーヒマ -Piano Version- </t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_mj/effect_liqi_liyang</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_mj/effect_liqi_25summer</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_mj/ron_liyang</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_mj/ron_25summer</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_mj/ron_25yh</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_mj/effect_liqi_25yh</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2510yh_bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2510万事屋_bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2510yh_activity_enter</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2510yh_ui_open</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2510yh_request_success</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2510yh_request_great_success</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2510yh_request_start</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2510yh_hire_employee</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2510yh_pass</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2510yh_charge</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2510万事屋_进入活动</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2510万事屋_打开各界面</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2510万事屋_委托出发摩托滴滴</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2510万事屋_委托_成功</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2510万事屋_委托_大成功</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2510万事屋_雇佣员工</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2510万事屋_通过印章</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2510万事屋_员工充能</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>audio/audio_mj/ron_25hf</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>audio/audio_mj/effect_liqi_25hf</t>
-  </si>
-  <si>
-    <t>fate卡池切换页签</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_lobby/gacha_banner_fate</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_对局bgm</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_养成bgm</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_train_bgm</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_match_bgm</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_activity_enter</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_进入界面</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_ui_open</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_窗口打开（剧情、任务、奖励）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_养成_失败</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_养成_成功</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_养成_大成功</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_train_failure</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_train_success</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_train_great_success</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_event_show</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_事件_出现</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_事件_普通</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_事件_成功</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_事件_大成功</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_event_normal</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_event_success</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_event_great_success</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_等待跳入传送门</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_waiting_enter_match</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_match_begin</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_比赛开始</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_traveling</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_穿越中</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_比赛结束</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_match_over</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雀斗_生涯结束</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504quedou_lifetime_over</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>背水_大金火焰</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504beishui_big_fire</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2504beishui_normal_fire</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>背水_中紫火焰</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>music/25xila_duiju.mp3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>优雅格调</t>
-  </si>
-  <si>
-    <t>優雅格調</t>
-  </si>
-  <si>
-    <t>Majestic Elegance</t>
-  </si>
-  <si>
-    <t>우아한 격조</t>
-  </si>
-  <si>
-    <t>2506合成活动bgm</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2506xila_bgm</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>優雅に、格調高く</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>絶景</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>ミッドナイトララバイ</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>璃央卡池切换页签</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_lobby/gacha_banner_liyang</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>music/lobby_yiji.mp3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>闲暇炒面</t>
-  </si>
-  <si>
-    <t>閒暇炒麵</t>
-  </si>
-  <si>
-    <t>audio/audio_event/2508hanghai_sea_bird</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2508hanghai_sea_wave</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>航海_环境音_海浪（常驻）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>航海_环境音_海鸥叫（白天）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>航海_环境音_雷雨（雨天）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>航海_抚子_大炮</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>航海_任务、奖励弹窗开启</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2508hanghai_rain</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2508hanghai_boom</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mayo Yakisoba</t>
-  </si>
-  <si>
-    <t>마요 야키소바</t>
-  </si>
-  <si>
-    <t>2508青云之志_普通关循环</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2508qyzz_lobby_normal_loop</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2508青云之志_BOSS关循环</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2508qyzz_lobby_boss_loop</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2508青云之志_进入大厅</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2508qyzz_lobby_in</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2508青云之志_大厅界面_喷火</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2508qyzz_lobby_breathing</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2508青云之志_大厅界面_闪电</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2508qyzz_lobby_lighting</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2508青云之志_大厅界面_射箭</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2508qyzz_lobby_shooting</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2508青云之志_进入关卡列表</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2508qyzz_stage_show</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2508青云之志_进入商店</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2508qyzz_shop_pop</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2508青云之志_fevertime</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2508qyzz_stage_fevertime</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2508青云之志_关卡clear</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2508qyzz_stage_clear</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2508青云之志_游戏结束</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2508qyzz_stage_game_over</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2508青云之志_护身符变形</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2508qyzz_stage_amulet_transform</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">リーヒマ -Piano Version- </t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>effect</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_mj/effect_liqi_liyang</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_mj/effect_liqi_25summer</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_mj/ron_liyang</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_mj/ron_25summer</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3116,7 +3196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3226,8 +3306,6 @@
     <xf numFmtId="0" fontId="19" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3560,7 +3638,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E374"/>
+  <dimension ref="A1:E385"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -4261,13 +4339,13 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="15" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B55" s="29">
         <v>154</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D55"/>
       <c r="E55" t="s">
@@ -4276,13 +4354,13 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="15" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B56" s="29">
         <v>155</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D56"/>
       <c r="E56" t="s">
@@ -5232,13 +5310,13 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="15" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B126">
         <v>10000</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D126"/>
       <c r="E126" t="s">
@@ -6932,13 +7010,13 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" s="15" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B238" s="41">
         <v>10313</v>
       </c>
       <c r="C238" s="41" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D238" s="15"/>
       <c r="E238" t="s">
@@ -6947,13 +7025,13 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" s="15" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B239" s="41">
         <v>10314</v>
       </c>
       <c r="C239" s="41" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D239" s="15"/>
       <c r="E239" t="s">
@@ -6962,13 +7040,13 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" s="15" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B240" s="41">
         <v>10315</v>
       </c>
       <c r="C240" s="41" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D240" s="15"/>
       <c r="E240" t="s">
@@ -6977,13 +7055,13 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" s="15" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B241" s="41">
         <v>10316</v>
       </c>
       <c r="C241" s="41" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D241" s="15"/>
       <c r="E241" t="s">
@@ -6992,13 +7070,13 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" s="15" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B242" s="41">
         <v>10317</v>
       </c>
       <c r="C242" s="41" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D242" s="15"/>
       <c r="E242" t="s">
@@ -7007,13 +7085,13 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" s="15" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B243" s="41">
         <v>10318</v>
       </c>
       <c r="C243" s="41" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D243" s="15"/>
       <c r="E243" t="s">
@@ -7022,13 +7100,13 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" s="15" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B244" s="41">
         <v>10319</v>
       </c>
       <c r="C244" s="41" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D244" s="15"/>
       <c r="E244" t="s">
@@ -7037,13 +7115,13 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" s="15" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B245" s="41">
         <v>10320</v>
       </c>
       <c r="C245" s="41" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D245" s="15"/>
       <c r="E245" t="s">
@@ -7052,13 +7130,13 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" s="15" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B246" s="41">
         <v>10321</v>
       </c>
       <c r="C246" s="41" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D246" s="15"/>
       <c r="E246" t="s">
@@ -7067,13 +7145,13 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" s="15" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B247" s="41">
         <v>10322</v>
       </c>
       <c r="C247" s="41" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D247" s="15"/>
       <c r="E247" t="s">
@@ -7082,13 +7160,13 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" s="15" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B248" s="41">
         <v>10323</v>
       </c>
       <c r="C248" s="41" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D248" s="15"/>
       <c r="E248" t="s">
@@ -7097,13 +7175,13 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" s="15" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B249" s="41">
         <v>10324</v>
       </c>
       <c r="C249" s="41" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D249" s="15"/>
       <c r="E249" t="s">
@@ -7112,13 +7190,13 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" s="15" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B250" s="41">
         <v>10325</v>
       </c>
       <c r="C250" s="41" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D250" s="15"/>
       <c r="E250" t="s">
@@ -7127,13 +7205,13 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" s="15" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B251" s="41">
         <v>10326</v>
       </c>
       <c r="C251" s="41" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D251" s="15"/>
       <c r="E251" t="s">
@@ -7142,13 +7220,13 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" s="15" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B252" s="41">
         <v>10327</v>
       </c>
       <c r="C252" s="41" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D252" s="15"/>
       <c r="E252" t="s">
@@ -7157,13 +7235,13 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" s="15" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B253" s="41">
         <v>10328</v>
       </c>
       <c r="C253" s="41" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D253" s="15"/>
       <c r="E253" t="s">
@@ -7172,13 +7250,13 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" s="15" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B254" s="41">
         <v>10329</v>
       </c>
       <c r="C254" s="41" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D254" s="15"/>
       <c r="E254" t="s">
@@ -7187,13 +7265,13 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" s="15" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B255" s="41">
         <v>10330</v>
       </c>
       <c r="C255" s="41" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D255" s="15"/>
       <c r="E255" t="s">
@@ -7202,13 +7280,13 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256" s="15" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B256" s="41">
         <v>10331</v>
       </c>
       <c r="C256" s="41" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D256" s="15">
         <v>60000</v>
@@ -7219,13 +7297,13 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257" s="15" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B257" s="41">
         <v>10332</v>
       </c>
       <c r="C257" s="41" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D257" s="15">
         <v>60000</v>
@@ -7236,13 +7314,13 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" s="15" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B258" s="41">
         <v>10333</v>
       </c>
       <c r="C258" s="41" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D258" s="15"/>
       <c r="E258" t="s">
@@ -7251,13 +7329,13 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" s="15" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B259" s="41">
         <v>10334</v>
       </c>
       <c r="C259" s="41" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D259" s="15"/>
       <c r="E259" t="s">
@@ -7266,13 +7344,13 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" s="15" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B260" s="41">
         <v>10335</v>
       </c>
       <c r="C260" s="41" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D260" s="15"/>
       <c r="E260" t="s">
@@ -7281,13 +7359,13 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" s="15" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B261" s="41">
         <v>10336</v>
       </c>
       <c r="C261" s="41" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D261" s="15"/>
       <c r="E261" t="s">
@@ -7296,13 +7374,13 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" s="15" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B262" s="41">
         <v>10337</v>
       </c>
       <c r="C262" s="41" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D262" s="15"/>
       <c r="E262" t="s">
@@ -7311,13 +7389,13 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" s="15" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B263" s="41">
         <v>10338</v>
       </c>
       <c r="C263" s="41" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D263" s="15"/>
       <c r="E263" t="s">
@@ -7326,13 +7404,13 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" s="15" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B264" s="41">
         <v>10339</v>
       </c>
       <c r="C264" s="41" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D264" s="15"/>
       <c r="E264" t="s">
@@ -7341,13 +7419,13 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" s="15" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B265" s="41">
         <v>10340</v>
       </c>
       <c r="C265" s="41" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D265" s="15"/>
       <c r="E265" t="s">
@@ -7356,13 +7434,13 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" s="15" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B266" s="41">
         <v>10341</v>
       </c>
       <c r="C266" s="41" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D266" s="15"/>
       <c r="E266" t="s">
@@ -7371,13 +7449,13 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" s="15" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B267" s="41">
         <v>10342</v>
       </c>
       <c r="C267" s="41" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D267" s="15"/>
       <c r="E267" s="15" t="s">
@@ -7386,13 +7464,13 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" s="15" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B268" s="41">
         <v>10350</v>
       </c>
       <c r="C268" s="41" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D268" s="15"/>
       <c r="E268" t="s">
@@ -7401,13 +7479,13 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" s="15" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B269" s="41">
         <v>10351</v>
       </c>
       <c r="C269" s="41" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D269" s="15"/>
       <c r="E269" t="s">
@@ -7416,13 +7494,13 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" s="15" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B270" s="41">
         <v>10352</v>
       </c>
       <c r="C270" s="41" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D270" s="15"/>
       <c r="E270" t="s">
@@ -7431,13 +7509,13 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" s="15" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B271" s="41">
         <v>10353</v>
       </c>
       <c r="C271" s="41" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D271" s="15"/>
       <c r="E271" t="s">
@@ -7446,259 +7524,286 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" s="15" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B272" s="41">
         <v>10354</v>
       </c>
       <c r="C272" s="41" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D272" s="15"/>
       <c r="E272" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="273" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B273">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A273" s="15" t="s">
+        <v>703</v>
+      </c>
+      <c r="B273" s="41">
+        <v>10355</v>
+      </c>
+      <c r="C273" s="41" t="s">
+        <v>702</v>
+      </c>
+      <c r="D273" s="15"/>
+      <c r="E273" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A274" s="15" t="s">
+        <v>712</v>
+      </c>
+      <c r="B274" s="41">
+        <v>10356</v>
+      </c>
+      <c r="C274" s="41" t="s">
+        <v>704</v>
+      </c>
+      <c r="D274" s="15"/>
+      <c r="E274" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A275" s="15" t="s">
+        <v>713</v>
+      </c>
+      <c r="B275" s="41">
+        <v>10357</v>
+      </c>
+      <c r="C275" s="41" t="s">
+        <v>705</v>
+      </c>
+      <c r="D275" s="15"/>
+      <c r="E275" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A276" s="15" t="s">
+        <v>714</v>
+      </c>
+      <c r="B276" s="41">
+        <v>10358</v>
+      </c>
+      <c r="C276" s="41" t="s">
+        <v>708</v>
+      </c>
+      <c r="D276" s="15"/>
+      <c r="E276" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A277" s="15" t="s">
+        <v>715</v>
+      </c>
+      <c r="B277" s="41">
+        <v>10359</v>
+      </c>
+      <c r="C277" s="41" t="s">
+        <v>706</v>
+      </c>
+      <c r="D277" s="15"/>
+      <c r="E277" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A278" s="15" t="s">
+        <v>716</v>
+      </c>
+      <c r="B278" s="41">
+        <v>10360</v>
+      </c>
+      <c r="C278" s="41" t="s">
+        <v>707</v>
+      </c>
+      <c r="D278" s="15"/>
+      <c r="E278" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A279" s="15" t="s">
+        <v>718</v>
+      </c>
+      <c r="B279" s="41">
+        <v>10361</v>
+      </c>
+      <c r="C279" s="41" t="s">
+        <v>710</v>
+      </c>
+      <c r="D279" s="15"/>
+      <c r="E279" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A280" s="15" t="s">
+        <v>717</v>
+      </c>
+      <c r="B280" s="41">
+        <v>10362</v>
+      </c>
+      <c r="C280" s="41" t="s">
+        <v>709</v>
+      </c>
+      <c r="D280" s="15"/>
+      <c r="E280" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A281" s="15" t="s">
+        <v>719</v>
+      </c>
+      <c r="B281" s="41">
+        <v>10363</v>
+      </c>
+      <c r="C281" s="41" t="s">
+        <v>711</v>
+      </c>
+      <c r="D281" s="15"/>
+      <c r="E281" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B282">
         <v>305032</v>
       </c>
-      <c r="C273" t="s">
+      <c r="C282" t="s">
         <v>111</v>
       </c>
-      <c r="D273">
+      <c r="D282">
         <v>1314</v>
       </c>
-      <c r="E273" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="274" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B274">
+      <c r="E282" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B283">
         <v>305033</v>
       </c>
-      <c r="C274" t="s">
+      <c r="C283" t="s">
         <v>112</v>
       </c>
-      <c r="D274">
+      <c r="D283">
         <v>1445</v>
       </c>
-      <c r="E274" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="275" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B275">
+      <c r="E283" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B284">
         <v>305034</v>
       </c>
-      <c r="C275" t="s">
+      <c r="C284" t="s">
         <v>113</v>
       </c>
-      <c r="D275">
+      <c r="D284">
         <v>2098</v>
       </c>
-      <c r="E275" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="276" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B276">
+      <c r="E284" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B285">
         <v>305035</v>
       </c>
-      <c r="C276" t="s">
+      <c r="C285" t="s">
         <v>114</v>
       </c>
-      <c r="D276">
+      <c r="D285">
         <v>1523</v>
       </c>
-      <c r="E276" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="277" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B277">
+      <c r="E285" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B286">
         <v>305036</v>
       </c>
-      <c r="C277" s="15" t="s">
+      <c r="C286" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="D277">
+      <c r="D286">
         <v>1915</v>
       </c>
-      <c r="E277" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="278" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B278">
+      <c r="E286" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B287">
         <v>305037</v>
       </c>
-      <c r="C278" t="s">
+      <c r="C287" t="s">
         <v>115</v>
       </c>
-      <c r="D278">
+      <c r="D287">
         <v>1200</v>
       </c>
-      <c r="E278" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="279" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B279">
+      <c r="E287" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B288">
         <v>305038</v>
       </c>
-      <c r="C279" t="s">
+      <c r="C288" t="s">
         <v>116</v>
       </c>
-      <c r="D279">
+      <c r="D288">
         <v>2500</v>
       </c>
-      <c r="E279" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="280" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B280">
-        <v>305039</v>
-      </c>
-      <c r="C280" t="s">
-        <v>117</v>
-      </c>
-      <c r="D280">
-        <v>1200</v>
-      </c>
-      <c r="E280" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="281" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B281">
-        <v>305040</v>
-      </c>
-      <c r="C281" t="s">
-        <v>118</v>
-      </c>
-      <c r="D281">
-        <v>2500</v>
-      </c>
-      <c r="E281" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="282" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B282">
-        <v>305200</v>
-      </c>
-      <c r="C282" t="s">
-        <v>119</v>
-      </c>
-      <c r="D282"/>
-      <c r="E282" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="283" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B283">
-        <v>305201</v>
-      </c>
-      <c r="C283" t="s">
-        <v>120</v>
-      </c>
-      <c r="D283"/>
-      <c r="E283" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="284" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B284">
-        <v>305202</v>
-      </c>
-      <c r="C284" t="s">
-        <v>121</v>
-      </c>
-      <c r="D284"/>
-      <c r="E284" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="285" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B285">
-        <v>305203</v>
-      </c>
-      <c r="C285" t="s">
-        <v>122</v>
-      </c>
-      <c r="D285"/>
-      <c r="E285" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="286" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B286">
-        <v>305204</v>
-      </c>
-      <c r="C286" t="s">
-        <v>123</v>
-      </c>
-      <c r="D286"/>
-      <c r="E286" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="287" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B287">
-        <v>305205</v>
-      </c>
-      <c r="C287" t="s">
-        <v>124</v>
-      </c>
-      <c r="D287"/>
-      <c r="E287" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="288" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B288">
-        <v>305206</v>
-      </c>
-      <c r="C288" t="s">
-        <v>125</v>
-      </c>
-      <c r="D288"/>
       <c r="E288" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="289" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B289">
-        <v>305207</v>
+        <v>305039</v>
       </c>
       <c r="C289" t="s">
-        <v>126</v>
-      </c>
-      <c r="D289"/>
+        <v>117</v>
+      </c>
+      <c r="D289">
+        <v>1200</v>
+      </c>
       <c r="E289" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="290" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B290">
-        <v>305208</v>
+        <v>305040</v>
       </c>
       <c r="C290" t="s">
-        <v>127</v>
-      </c>
-      <c r="D290"/>
+        <v>118</v>
+      </c>
+      <c r="D290">
+        <v>2500</v>
+      </c>
       <c r="E290" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="291" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B291">
-        <v>305209</v>
+        <v>305200</v>
       </c>
       <c r="C291" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D291"/>
       <c r="E291" t="s">
@@ -7707,10 +7812,10 @@
     </row>
     <row r="292" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B292">
-        <v>305210</v>
+        <v>305201</v>
       </c>
       <c r="C292" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D292"/>
       <c r="E292" t="s">
@@ -7719,10 +7824,10 @@
     </row>
     <row r="293" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B293">
-        <v>305211</v>
+        <v>305202</v>
       </c>
       <c r="C293" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D293"/>
       <c r="E293" t="s">
@@ -7731,10 +7836,10 @@
     </row>
     <row r="294" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B294">
-        <v>305212</v>
+        <v>305203</v>
       </c>
       <c r="C294" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D294"/>
       <c r="E294" t="s">
@@ -7743,10 +7848,10 @@
     </row>
     <row r="295" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B295">
-        <v>305213</v>
+        <v>305204</v>
       </c>
       <c r="C295" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D295"/>
       <c r="E295" t="s">
@@ -7755,10 +7860,10 @@
     </row>
     <row r="296" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B296">
-        <v>305214</v>
+        <v>305205</v>
       </c>
       <c r="C296" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D296"/>
       <c r="E296" t="s">
@@ -7767,10 +7872,10 @@
     </row>
     <row r="297" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B297">
-        <v>305215</v>
+        <v>305206</v>
       </c>
       <c r="C297" t="s">
-        <v>207</v>
+        <v>125</v>
       </c>
       <c r="D297"/>
       <c r="E297" t="s">
@@ -7779,10 +7884,10 @@
     </row>
     <row r="298" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B298">
-        <v>305216</v>
+        <v>305207</v>
       </c>
       <c r="C298" t="s">
-        <v>208</v>
+        <v>126</v>
       </c>
       <c r="D298"/>
       <c r="E298" t="s">
@@ -7791,10 +7896,10 @@
     </row>
     <row r="299" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B299">
-        <v>305217</v>
+        <v>305208</v>
       </c>
       <c r="C299" t="s">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="D299"/>
       <c r="E299" t="s">
@@ -7803,10 +7908,10 @@
     </row>
     <row r="300" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B300">
-        <v>305218</v>
+        <v>305209</v>
       </c>
       <c r="C300" t="s">
-        <v>214</v>
+        <v>128</v>
       </c>
       <c r="D300"/>
       <c r="E300" t="s">
@@ -7815,10 +7920,10 @@
     </row>
     <row r="301" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B301">
-        <v>305219</v>
+        <v>305210</v>
       </c>
       <c r="C301" t="s">
-        <v>227</v>
+        <v>129</v>
       </c>
       <c r="D301"/>
       <c r="E301" t="s">
@@ -7827,10 +7932,10 @@
     </row>
     <row r="302" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B302">
-        <v>305220</v>
+        <v>305211</v>
       </c>
       <c r="C302" t="s">
-        <v>229</v>
+        <v>130</v>
       </c>
       <c r="D302"/>
       <c r="E302" t="s">
@@ -7839,10 +7944,10 @@
     </row>
     <row r="303" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B303">
-        <v>305221</v>
-      </c>
-      <c r="C303" s="15" t="s">
-        <v>239</v>
+        <v>305212</v>
+      </c>
+      <c r="C303" t="s">
+        <v>131</v>
       </c>
       <c r="D303"/>
       <c r="E303" t="s">
@@ -7851,10 +7956,10 @@
     </row>
     <row r="304" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B304">
-        <v>305222</v>
-      </c>
-      <c r="C304" s="15" t="s">
-        <v>247</v>
+        <v>305213</v>
+      </c>
+      <c r="C304" t="s">
+        <v>132</v>
       </c>
       <c r="D304"/>
       <c r="E304" t="s">
@@ -7863,10 +7968,10 @@
     </row>
     <row r="305" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B305">
-        <v>305223</v>
+        <v>305214</v>
       </c>
       <c r="C305" t="s">
-        <v>254</v>
+        <v>133</v>
       </c>
       <c r="D305"/>
       <c r="E305" t="s">
@@ -7875,10 +7980,10 @@
     </row>
     <row r="306" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B306">
-        <v>30520001</v>
-      </c>
-      <c r="C306" s="15" t="s">
-        <v>307</v>
+        <v>305215</v>
+      </c>
+      <c r="C306" t="s">
+        <v>207</v>
       </c>
       <c r="D306"/>
       <c r="E306" t="s">
@@ -7887,10 +7992,10 @@
     </row>
     <row r="307" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B307">
-        <v>30520002</v>
-      </c>
-      <c r="C307" s="15" t="s">
-        <v>316</v>
+        <v>305216</v>
+      </c>
+      <c r="C307" t="s">
+        <v>208</v>
       </c>
       <c r="D307"/>
       <c r="E307" t="s">
@@ -7899,10 +8004,10 @@
     </row>
     <row r="308" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B308">
-        <v>30520003</v>
-      </c>
-      <c r="C308" s="15" t="s">
-        <v>326</v>
+        <v>305217</v>
+      </c>
+      <c r="C308" t="s">
+        <v>209</v>
       </c>
       <c r="D308"/>
       <c r="E308" t="s">
@@ -7911,10 +8016,10 @@
     </row>
     <row r="309" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B309">
-        <v>30520004</v>
-      </c>
-      <c r="C309" s="15" t="s">
-        <v>403</v>
+        <v>305218</v>
+      </c>
+      <c r="C309" t="s">
+        <v>214</v>
       </c>
       <c r="D309"/>
       <c r="E309" t="s">
@@ -7923,10 +8028,10 @@
     </row>
     <row r="310" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B310">
-        <v>30520005</v>
-      </c>
-      <c r="C310" s="15" t="s">
-        <v>424</v>
+        <v>305219</v>
+      </c>
+      <c r="C310" t="s">
+        <v>227</v>
       </c>
       <c r="D310"/>
       <c r="E310" t="s">
@@ -7935,10 +8040,10 @@
     </row>
     <row r="311" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B311">
-        <v>30520006</v>
-      </c>
-      <c r="C311" s="15" t="s">
-        <v>425</v>
+        <v>305220</v>
+      </c>
+      <c r="C311" t="s">
+        <v>229</v>
       </c>
       <c r="D311"/>
       <c r="E311" t="s">
@@ -7947,57 +8052,58 @@
     </row>
     <row r="312" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B312">
-        <v>30520007</v>
+        <v>305221</v>
       </c>
       <c r="C312" s="15" t="s">
-        <v>511</v>
+        <v>239</v>
       </c>
       <c r="D312"/>
       <c r="E312" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="313" spans="2:5" s="51" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B313" s="51">
-        <v>30520008</v>
-      </c>
-      <c r="C313" s="52" t="s">
-        <v>552</v>
-      </c>
-      <c r="E313" s="52" t="s">
-        <v>697</v>
+    <row r="313" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B313">
+        <v>305222</v>
+      </c>
+      <c r="C313" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="D313"/>
+      <c r="E313" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="314" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B314" s="17">
-        <v>30520009</v>
-      </c>
-      <c r="C314" s="18" t="s">
-        <v>700</v>
-      </c>
-      <c r="D314" s="17"/>
-      <c r="E314" s="18" t="s">
-        <v>697</v>
+      <c r="B314">
+        <v>305223</v>
+      </c>
+      <c r="C314" t="s">
+        <v>254</v>
+      </c>
+      <c r="D314"/>
+      <c r="E314" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="315" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B315" s="17">
-        <v>30520010</v>
-      </c>
-      <c r="C315" s="18" t="s">
-        <v>701</v>
-      </c>
-      <c r="D315" s="17"/>
-      <c r="E315" s="18" t="s">
-        <v>697</v>
+      <c r="B315">
+        <v>30520001</v>
+      </c>
+      <c r="C315" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="D315"/>
+      <c r="E315" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="316" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B316">
-        <v>305224</v>
-      </c>
-      <c r="C316" t="s">
-        <v>256</v>
+        <v>30520002</v>
+      </c>
+      <c r="C316" s="15" t="s">
+        <v>316</v>
       </c>
       <c r="D316"/>
       <c r="E316" t="s">
@@ -8006,10 +8112,10 @@
     </row>
     <row r="317" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B317">
-        <v>305225</v>
-      </c>
-      <c r="C317" t="s">
-        <v>257</v>
+        <v>30520003</v>
+      </c>
+      <c r="C317" s="15" t="s">
+        <v>326</v>
       </c>
       <c r="D317"/>
       <c r="E317" t="s">
@@ -8018,10 +8124,10 @@
     </row>
     <row r="318" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B318">
-        <v>305226</v>
-      </c>
-      <c r="C318" t="s">
-        <v>258</v>
+        <v>30520004</v>
+      </c>
+      <c r="C318" s="15" t="s">
+        <v>403</v>
       </c>
       <c r="D318"/>
       <c r="E318" t="s">
@@ -8030,10 +8136,10 @@
     </row>
     <row r="319" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B319">
-        <v>305300</v>
-      </c>
-      <c r="C319" t="s">
-        <v>134</v>
+        <v>30520005</v>
+      </c>
+      <c r="C319" s="15" t="s">
+        <v>424</v>
       </c>
       <c r="D319"/>
       <c r="E319" t="s">
@@ -8042,10 +8148,10 @@
     </row>
     <row r="320" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B320">
-        <v>305301</v>
-      </c>
-      <c r="C320" t="s">
-        <v>135</v>
+        <v>30520006</v>
+      </c>
+      <c r="C320" s="15" t="s">
+        <v>425</v>
       </c>
       <c r="D320"/>
       <c r="E320" t="s">
@@ -8054,10 +8160,10 @@
     </row>
     <row r="321" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B321">
-        <v>305302</v>
-      </c>
-      <c r="C321" t="s">
-        <v>136</v>
+        <v>30520007</v>
+      </c>
+      <c r="C321" s="15" t="s">
+        <v>511</v>
       </c>
       <c r="D321"/>
       <c r="E321" t="s">
@@ -8066,46 +8172,46 @@
     </row>
     <row r="322" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B322">
-        <v>305303</v>
-      </c>
-      <c r="C322" t="s">
-        <v>137</v>
+        <v>30520008</v>
+      </c>
+      <c r="C322" s="15" t="s">
+        <v>552</v>
       </c>
       <c r="D322"/>
-      <c r="E322" t="s">
-        <v>74</v>
+      <c r="E322" s="15" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="323" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B323">
-        <v>305304</v>
-      </c>
-      <c r="C323" t="s">
-        <v>138</v>
-      </c>
-      <c r="D323"/>
-      <c r="E323" t="s">
-        <v>74</v>
+      <c r="B323" s="17">
+        <v>30520009</v>
+      </c>
+      <c r="C323" s="18" t="s">
+        <v>698</v>
+      </c>
+      <c r="D323" s="17"/>
+      <c r="E323" s="18" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="324" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B324">
-        <v>305305</v>
-      </c>
-      <c r="C324" t="s">
-        <v>139</v>
-      </c>
-      <c r="D324"/>
-      <c r="E324" t="s">
-        <v>74</v>
+      <c r="B324" s="17">
+        <v>30520010</v>
+      </c>
+      <c r="C324" s="18" t="s">
+        <v>699</v>
+      </c>
+      <c r="D324" s="17"/>
+      <c r="E324" s="18" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="325" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B325">
-        <v>305306</v>
+        <v>305224</v>
       </c>
       <c r="C325" t="s">
-        <v>140</v>
+        <v>256</v>
       </c>
       <c r="D325"/>
       <c r="E325" t="s">
@@ -8114,10 +8220,10 @@
     </row>
     <row r="326" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B326">
-        <v>305307</v>
+        <v>305225</v>
       </c>
       <c r="C326" t="s">
-        <v>141</v>
+        <v>257</v>
       </c>
       <c r="D326"/>
       <c r="E326" t="s">
@@ -8126,10 +8232,10 @@
     </row>
     <row r="327" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B327">
-        <v>305308</v>
+        <v>305226</v>
       </c>
       <c r="C327" t="s">
-        <v>142</v>
+        <v>258</v>
       </c>
       <c r="D327"/>
       <c r="E327" t="s">
@@ -8138,10 +8244,10 @@
     </row>
     <row r="328" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B328">
-        <v>305309</v>
+        <v>305300</v>
       </c>
       <c r="C328" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D328"/>
       <c r="E328" t="s">
@@ -8150,10 +8256,10 @@
     </row>
     <row r="329" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B329">
-        <v>305310</v>
+        <v>305301</v>
       </c>
       <c r="C329" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D329"/>
       <c r="E329" t="s">
@@ -8162,10 +8268,10 @@
     </row>
     <row r="330" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B330">
-        <v>305311</v>
+        <v>305302</v>
       </c>
       <c r="C330" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D330"/>
       <c r="E330" t="s">
@@ -8174,10 +8280,10 @@
     </row>
     <row r="331" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B331">
-        <v>305312</v>
+        <v>305303</v>
       </c>
       <c r="C331" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D331"/>
       <c r="E331" t="s">
@@ -8186,10 +8292,10 @@
     </row>
     <row r="332" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B332">
-        <v>305313</v>
+        <v>305304</v>
       </c>
       <c r="C332" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D332"/>
       <c r="E332" t="s">
@@ -8198,10 +8304,10 @@
     </row>
     <row r="333" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B333">
-        <v>305314</v>
+        <v>305305</v>
       </c>
       <c r="C333" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D333"/>
       <c r="E333" t="s">
@@ -8210,10 +8316,10 @@
     </row>
     <row r="334" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B334">
-        <v>305315</v>
+        <v>305306</v>
       </c>
       <c r="C334" t="s">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="D334"/>
       <c r="E334" t="s">
@@ -8222,10 +8328,10 @@
     </row>
     <row r="335" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B335">
-        <v>305316</v>
+        <v>305307</v>
       </c>
       <c r="C335" t="s">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="D335"/>
       <c r="E335" t="s">
@@ -8234,10 +8340,10 @@
     </row>
     <row r="336" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B336">
-        <v>305317</v>
+        <v>305308</v>
       </c>
       <c r="C336" t="s">
-        <v>210</v>
+        <v>142</v>
       </c>
       <c r="D336"/>
       <c r="E336" t="s">
@@ -8246,10 +8352,10 @@
     </row>
     <row r="337" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B337">
-        <v>305318</v>
+        <v>305309</v>
       </c>
       <c r="C337" t="s">
-        <v>215</v>
+        <v>143</v>
       </c>
       <c r="D337"/>
       <c r="E337" t="s">
@@ -8258,10 +8364,10 @@
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B338">
-        <v>305319</v>
+        <v>305310</v>
       </c>
       <c r="C338" t="s">
-        <v>228</v>
+        <v>144</v>
       </c>
       <c r="D338"/>
       <c r="E338" t="s">
@@ -8270,10 +8376,10 @@
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B339">
-        <v>305320</v>
+        <v>305311</v>
       </c>
       <c r="C339" t="s">
-        <v>230</v>
+        <v>145</v>
       </c>
       <c r="D339"/>
       <c r="E339" t="s">
@@ -8282,10 +8388,10 @@
     </row>
     <row r="340" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B340">
-        <v>305321</v>
-      </c>
-      <c r="C340" s="15" t="s">
-        <v>238</v>
+        <v>305312</v>
+      </c>
+      <c r="C340" t="s">
+        <v>146</v>
       </c>
       <c r="D340"/>
       <c r="E340" t="s">
@@ -8294,10 +8400,10 @@
     </row>
     <row r="341" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B341">
-        <v>305322</v>
-      </c>
-      <c r="C341" s="15" t="s">
-        <v>248</v>
+        <v>305313</v>
+      </c>
+      <c r="C341" t="s">
+        <v>147</v>
       </c>
       <c r="D341"/>
       <c r="E341" t="s">
@@ -8306,10 +8412,10 @@
     </row>
     <row r="342" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B342">
-        <v>305323</v>
+        <v>305314</v>
       </c>
       <c r="C342" t="s">
-        <v>255</v>
+        <v>148</v>
       </c>
       <c r="D342"/>
       <c r="E342" t="s">
@@ -8318,10 +8424,10 @@
     </row>
     <row r="343" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B343">
-        <v>305324</v>
+        <v>305315</v>
       </c>
       <c r="C343" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="D343"/>
       <c r="E343" t="s">
@@ -8330,10 +8436,10 @@
     </row>
     <row r="344" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B344">
-        <v>305325</v>
+        <v>305316</v>
       </c>
       <c r="C344" t="s">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D344"/>
       <c r="E344" t="s">
@@ -8342,10 +8448,10 @@
     </row>
     <row r="345" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B345">
-        <v>305326</v>
-      </c>
-      <c r="C345" s="15" t="s">
-        <v>261</v>
+        <v>305317</v>
+      </c>
+      <c r="C345" t="s">
+        <v>210</v>
       </c>
       <c r="D345"/>
       <c r="E345" t="s">
@@ -8354,10 +8460,10 @@
     </row>
     <row r="346" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B346">
-        <v>30530001</v>
-      </c>
-      <c r="C346" s="15" t="s">
-        <v>308</v>
+        <v>305318</v>
+      </c>
+      <c r="C346" t="s">
+        <v>215</v>
       </c>
       <c r="D346"/>
       <c r="E346" t="s">
@@ -8366,10 +8472,10 @@
     </row>
     <row r="347" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B347">
-        <v>30530002</v>
+        <v>305319</v>
       </c>
       <c r="C347" t="s">
-        <v>317</v>
+        <v>228</v>
       </c>
       <c r="D347"/>
       <c r="E347" t="s">
@@ -8378,10 +8484,10 @@
     </row>
     <row r="348" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B348">
-        <v>30530003</v>
-      </c>
-      <c r="C348" s="15" t="s">
-        <v>327</v>
+        <v>305320</v>
+      </c>
+      <c r="C348" t="s">
+        <v>230</v>
       </c>
       <c r="D348"/>
       <c r="E348" t="s">
@@ -8390,10 +8496,10 @@
     </row>
     <row r="349" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B349">
-        <v>30530004</v>
+        <v>305321</v>
       </c>
       <c r="C349" s="15" t="s">
-        <v>404</v>
+        <v>238</v>
       </c>
       <c r="D349"/>
       <c r="E349" t="s">
@@ -8402,10 +8508,10 @@
     </row>
     <row r="350" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B350">
-        <v>30530005</v>
+        <v>305322</v>
       </c>
       <c r="C350" s="15" t="s">
-        <v>423</v>
+        <v>248</v>
       </c>
       <c r="D350"/>
       <c r="E350" t="s">
@@ -8414,10 +8520,10 @@
     </row>
     <row r="351" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B351">
-        <v>30530006</v>
-      </c>
-      <c r="C351" s="15" t="s">
-        <v>422</v>
+        <v>305323</v>
+      </c>
+      <c r="C351" t="s">
+        <v>255</v>
       </c>
       <c r="D351"/>
       <c r="E351" t="s">
@@ -8426,57 +8532,58 @@
     </row>
     <row r="352" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B352">
-        <v>30530007</v>
-      </c>
-      <c r="C352" s="15" t="s">
-        <v>512</v>
+        <v>305324</v>
+      </c>
+      <c r="C352" t="s">
+        <v>259</v>
       </c>
       <c r="D352"/>
-      <c r="E352" s="15" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="353" spans="2:5" s="51" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B353" s="51">
-        <v>30530008</v>
-      </c>
-      <c r="C353" s="52" t="s">
-        <v>553</v>
-      </c>
-      <c r="E353" s="52" t="s">
-        <v>554</v>
+      <c r="E352" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="353" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B353">
+        <v>305325</v>
+      </c>
+      <c r="C353" t="s">
+        <v>260</v>
+      </c>
+      <c r="D353"/>
+      <c r="E353" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="354" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B354" s="17">
-        <v>30530009</v>
-      </c>
-      <c r="C354" s="18" t="s">
-        <v>698</v>
-      </c>
-      <c r="D354" s="17"/>
-      <c r="E354" s="18" t="s">
-        <v>697</v>
+      <c r="B354">
+        <v>305326</v>
+      </c>
+      <c r="C354" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="D354"/>
+      <c r="E354" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="355" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B355" s="17">
-        <v>30530010</v>
-      </c>
-      <c r="C355" s="18" t="s">
-        <v>699</v>
-      </c>
-      <c r="D355" s="17"/>
-      <c r="E355" s="18" t="s">
-        <v>697</v>
+      <c r="B355">
+        <v>30530001</v>
+      </c>
+      <c r="C355" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="D355"/>
+      <c r="E355" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="356" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B356">
-        <v>309205</v>
+        <v>30530002</v>
       </c>
       <c r="C356" t="s">
-        <v>231</v>
+        <v>317</v>
       </c>
       <c r="D356"/>
       <c r="E356" t="s">
@@ -8485,10 +8592,10 @@
     </row>
     <row r="357" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B357">
-        <v>308001</v>
-      </c>
-      <c r="C357" t="s">
-        <v>149</v>
+        <v>30530003</v>
+      </c>
+      <c r="C357" s="15" t="s">
+        <v>327</v>
       </c>
       <c r="D357"/>
       <c r="E357" t="s">
@@ -8497,10 +8604,10 @@
     </row>
     <row r="358" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B358">
-        <v>308002</v>
-      </c>
-      <c r="C358" t="s">
-        <v>150</v>
+        <v>30530004</v>
+      </c>
+      <c r="C358" s="15" t="s">
+        <v>404</v>
       </c>
       <c r="D358"/>
       <c r="E358" t="s">
@@ -8509,10 +8616,10 @@
     </row>
     <row r="359" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B359">
-        <v>308006</v>
-      </c>
-      <c r="C359" t="s">
-        <v>151</v>
+        <v>30530005</v>
+      </c>
+      <c r="C359" s="15" t="s">
+        <v>423</v>
       </c>
       <c r="D359"/>
       <c r="E359" t="s">
@@ -8521,10 +8628,10 @@
     </row>
     <row r="360" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B360">
-        <v>308007</v>
-      </c>
-      <c r="C360" t="s">
-        <v>152</v>
+        <v>30530006</v>
+      </c>
+      <c r="C360" s="15" t="s">
+        <v>422</v>
       </c>
       <c r="D360"/>
       <c r="E360" t="s">
@@ -8533,58 +8640,58 @@
     </row>
     <row r="361" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B361">
-        <v>308011</v>
-      </c>
-      <c r="C361" t="s">
-        <v>153</v>
+        <v>30530007</v>
+      </c>
+      <c r="C361" s="15" t="s">
+        <v>512</v>
       </c>
       <c r="D361"/>
-      <c r="E361" t="s">
-        <v>74</v>
+      <c r="E361" s="15" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="362" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B362">
-        <v>308012</v>
-      </c>
-      <c r="C362" t="s">
-        <v>154</v>
+        <v>30530008</v>
+      </c>
+      <c r="C362" s="15" t="s">
+        <v>553</v>
       </c>
       <c r="D362"/>
-      <c r="E362" t="s">
-        <v>74</v>
+      <c r="E362" s="15" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="363" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B363">
-        <v>308016</v>
-      </c>
-      <c r="C363" t="s">
-        <v>212</v>
-      </c>
-      <c r="D363"/>
-      <c r="E363" t="s">
-        <v>74</v>
+      <c r="B363" s="17">
+        <v>30530009</v>
+      </c>
+      <c r="C363" s="18" t="s">
+        <v>696</v>
+      </c>
+      <c r="D363" s="17"/>
+      <c r="E363" s="18" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="364" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B364">
-        <v>308017</v>
-      </c>
-      <c r="C364" t="s">
-        <v>213</v>
-      </c>
-      <c r="D364"/>
-      <c r="E364" t="s">
-        <v>74</v>
+      <c r="B364" s="17">
+        <v>30530010</v>
+      </c>
+      <c r="C364" s="18" t="s">
+        <v>697</v>
+      </c>
+      <c r="D364" s="17"/>
+      <c r="E364" s="18" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="365" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B365">
-        <v>308021</v>
-      </c>
-      <c r="C365" s="15" t="s">
-        <v>236</v>
+        <v>309205</v>
+      </c>
+      <c r="C365" t="s">
+        <v>231</v>
       </c>
       <c r="D365"/>
       <c r="E365" t="s">
@@ -8593,10 +8700,10 @@
     </row>
     <row r="366" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B366">
-        <v>308022</v>
-      </c>
-      <c r="C366" s="15" t="s">
-        <v>237</v>
+        <v>308001</v>
+      </c>
+      <c r="C366" t="s">
+        <v>149</v>
       </c>
       <c r="D366"/>
       <c r="E366" t="s">
@@ -8605,10 +8712,10 @@
     </row>
     <row r="367" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B367">
-        <v>308026</v>
-      </c>
-      <c r="C367" s="15" t="s">
-        <v>245</v>
+        <v>308002</v>
+      </c>
+      <c r="C367" t="s">
+        <v>150</v>
       </c>
       <c r="D367"/>
       <c r="E367" t="s">
@@ -8617,10 +8724,10 @@
     </row>
     <row r="368" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B368">
-        <v>308027</v>
-      </c>
-      <c r="C368" s="15" t="s">
-        <v>246</v>
+        <v>308006</v>
+      </c>
+      <c r="C368" t="s">
+        <v>151</v>
       </c>
       <c r="D368"/>
       <c r="E368" t="s">
@@ -8629,10 +8736,10 @@
     </row>
     <row r="369" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B369">
-        <v>308031</v>
-      </c>
-      <c r="C369" s="15" t="s">
-        <v>314</v>
+        <v>308007</v>
+      </c>
+      <c r="C369" t="s">
+        <v>152</v>
       </c>
       <c r="D369"/>
       <c r="E369" t="s">
@@ -8641,10 +8748,10 @@
     </row>
     <row r="370" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B370">
-        <v>308032</v>
-      </c>
-      <c r="C370" s="15" t="s">
-        <v>315</v>
+        <v>308011</v>
+      </c>
+      <c r="C370" t="s">
+        <v>153</v>
       </c>
       <c r="D370"/>
       <c r="E370" t="s">
@@ -8653,10 +8760,10 @@
     </row>
     <row r="371" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B371">
-        <v>308036</v>
-      </c>
-      <c r="C371" s="15" t="s">
-        <v>381</v>
+        <v>308012</v>
+      </c>
+      <c r="C371" t="s">
+        <v>154</v>
       </c>
       <c r="D371"/>
       <c r="E371" t="s">
@@ -8665,10 +8772,10 @@
     </row>
     <row r="372" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B372">
-        <v>308037</v>
-      </c>
-      <c r="C372" s="15" t="s">
-        <v>382</v>
+        <v>308016</v>
+      </c>
+      <c r="C372" t="s">
+        <v>212</v>
       </c>
       <c r="D372"/>
       <c r="E372" t="s">
@@ -8676,30 +8783,162 @@
       </c>
     </row>
     <row r="373" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B373" s="17">
+      <c r="B373">
+        <v>308017</v>
+      </c>
+      <c r="C373" t="s">
+        <v>213</v>
+      </c>
+      <c r="D373"/>
+      <c r="E373" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="374" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B374">
+        <v>308021</v>
+      </c>
+      <c r="C374" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="D374"/>
+      <c r="E374" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="375" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B375">
+        <v>308022</v>
+      </c>
+      <c r="C375" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="D375"/>
+      <c r="E375" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="376" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B376">
+        <v>308026</v>
+      </c>
+      <c r="C376" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="D376"/>
+      <c r="E376" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="377" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B377">
+        <v>308027</v>
+      </c>
+      <c r="C377" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="D377"/>
+      <c r="E377" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="378" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B378">
+        <v>308031</v>
+      </c>
+      <c r="C378" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="D378"/>
+      <c r="E378" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="379" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B379">
+        <v>308032</v>
+      </c>
+      <c r="C379" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="D379"/>
+      <c r="E379" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="380" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B380">
+        <v>308036</v>
+      </c>
+      <c r="C380" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="D380"/>
+      <c r="E380" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="381" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B381">
+        <v>308037</v>
+      </c>
+      <c r="C381" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D381"/>
+      <c r="E381" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="382" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B382">
         <v>308041</v>
       </c>
-      <c r="C373" s="17" t="s">
+      <c r="C382" s="15" t="s">
+        <v>720</v>
+      </c>
+      <c r="D382"/>
+      <c r="E382" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="383" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B383">
+        <v>308042</v>
+      </c>
+      <c r="C383" s="15" t="s">
+        <v>721</v>
+      </c>
+      <c r="D383"/>
+      <c r="E383" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="384" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B384" s="17">
+        <v>308046</v>
+      </c>
+      <c r="C384" s="18" t="s">
+        <v>700</v>
+      </c>
+      <c r="D384" s="44" t="s">
         <v>605</v>
       </c>
-      <c r="D373" s="44" t="s">
-        <v>606</v>
-      </c>
-      <c r="E373" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="374" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B374" s="17">
-        <v>308042</v>
-      </c>
-      <c r="C374" s="17" t="s">
-        <v>607</v>
-      </c>
-      <c r="D374" s="44" t="s">
-        <v>606</v>
-      </c>
-      <c r="E374" s="17" t="s">
+      <c r="E384" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="385" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B385" s="17">
+        <v>308047</v>
+      </c>
+      <c r="C385" s="18" t="s">
+        <v>701</v>
+      </c>
+      <c r="D385" s="44" t="s">
+        <v>605</v>
+      </c>
+      <c r="E385" s="17" t="s">
         <v>74</v>
       </c>
     </row>
@@ -9179,22 +9418,22 @@
         <v>1</v>
       </c>
       <c r="D11" s="48" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E11" s="49" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F11" s="47" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G11" s="50" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -9686,7 +9925,7 @@
         <v>503</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G22" s="15" t="s">
         <v>504</v>
@@ -9733,7 +9972,7 @@
         <v>596</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G23" s="43" t="s">
         <v>597</v>
@@ -9774,22 +10013,22 @@
         <v>1</v>
       </c>
       <c r="D24" s="45" t="s">
+        <v>645</v>
+      </c>
+      <c r="E24" s="45" t="s">
+        <v>646</v>
+      </c>
+      <c r="F24" s="46" t="s">
+        <v>651</v>
+      </c>
+      <c r="G24" s="47" t="s">
         <v>647</v>
       </c>
-      <c r="E24" s="45" t="s">
+      <c r="H24" s="47" t="s">
         <v>648</v>
       </c>
-      <c r="F24" s="46" t="s">
-        <v>653</v>
-      </c>
-      <c r="G24" s="47" t="s">
-        <v>649</v>
-      </c>
-      <c r="H24" s="47" t="s">
-        <v>650</v>
-      </c>
       <c r="I24" s="15" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="K24" t="s">
         <v>44</v>

--- a/source/bin/excel/audio.xlsx
+++ b/source/bin/excel/audio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2527F154-67EF-4DE2-9305-39B6E7250D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55053574-7EDD-4849-BEB5-E5F061EE4CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28770" yWindow="210" windowWidth="15000" windowHeight="14925" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="736">
   <si>
     <t>sheet</t>
   </si>
@@ -2880,6 +2880,62 @@
   </si>
   <si>
     <t>audio/audio_mj/effect_liqi_25hf</t>
+  </si>
+  <si>
+    <t>audio/audio_lobby/gacha_banner_yh</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>银魂卡池切换页签</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2511游戏机_进入关卡/下一关卡</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2511yuehui_enter_game</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2511游戏机_切换弹窗页</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2511yuehui_exchange_page</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2511游戏机_移动飞机</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2511yuehui_move_airplane</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2511游戏机_发射子弹</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2511yuehui_shoot_bullet</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2511游戏机_击中敌人</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2511yuehui_hit_enemy</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2511yuehui_defeat_enemy</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2511游戏机_击破敌人</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3638,7 +3694,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E385"/>
+  <dimension ref="A1:E392"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -4368,28 +4424,29 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B57">
-        <v>201</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="D57">
-        <v>2098</v>
-      </c>
+      <c r="A57" s="15" t="s">
+        <v>723</v>
+      </c>
+      <c r="B57" s="29">
+        <v>156</v>
+      </c>
+      <c r="C57" s="30" t="s">
+        <v>722</v>
+      </c>
+      <c r="D57"/>
       <c r="E57" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B58">
-        <v>202</v>
-      </c>
-      <c r="C58" t="s">
-        <v>45</v>
+        <v>201</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>244</v>
       </c>
       <c r="D58">
-        <v>1000</v>
+        <v>2098</v>
       </c>
       <c r="E58" t="s">
         <v>44</v>
@@ -4397,10 +4454,10 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B59">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D59">
         <v>1000</v>
@@ -4411,10 +4468,10 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B60">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D60">
         <v>1000</v>
@@ -4425,10 +4482,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B61">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D61">
         <v>1000</v>
@@ -4439,13 +4496,13 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B62">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C62" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D62">
-        <v>1583</v>
+        <v>1000</v>
       </c>
       <c r="E62" t="s">
         <v>44</v>
@@ -4453,13 +4510,13 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B63">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C63" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D63">
-        <v>1000</v>
+        <v>1583</v>
       </c>
       <c r="E63" t="s">
         <v>44</v>
@@ -4467,13 +4524,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B64">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C64" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D64">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="E64" t="s">
         <v>44</v>
@@ -4481,13 +4538,13 @@
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B65">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C65" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D65">
-        <v>1000</v>
+        <v>1105</v>
       </c>
       <c r="E65" t="s">
         <v>44</v>
@@ -4495,10 +4552,10 @@
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B66">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C66" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D66">
         <v>1000</v>
@@ -4509,13 +4566,13 @@
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B67">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C67" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D67">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="E67" t="s">
         <v>44</v>
@@ -4523,13 +4580,13 @@
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B68">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C68" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D68">
-        <v>1602</v>
+        <v>1105</v>
       </c>
       <c r="E68" t="s">
         <v>44</v>
@@ -4537,13 +4594,13 @@
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B69">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C69" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D69">
-        <v>2098</v>
+        <v>1602</v>
       </c>
       <c r="E69" t="s">
         <v>44</v>
@@ -4551,10 +4608,10 @@
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B70">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C70" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D70">
         <v>2098</v>
@@ -4565,13 +4622,13 @@
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B71">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C71" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D71">
-        <v>1000</v>
+        <v>2098</v>
       </c>
       <c r="E71" t="s">
         <v>44</v>
@@ -4579,10 +4636,10 @@
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B72">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D72">
         <v>1000</v>
@@ -4593,10 +4650,10 @@
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B73">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C73" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D73">
         <v>1000</v>
@@ -4607,13 +4664,13 @@
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B74">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C74" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D74">
-        <v>1714</v>
+        <v>1000</v>
       </c>
       <c r="E74" t="s">
         <v>44</v>
@@ -4621,13 +4678,13 @@
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B75">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D75">
-        <v>1000</v>
+        <v>1714</v>
       </c>
       <c r="E75" t="s">
         <v>44</v>
@@ -4635,10 +4692,10 @@
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B76">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C76" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D76">
         <v>1000</v>
@@ -4649,13 +4706,13 @@
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B77">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D77">
-        <v>1602</v>
+        <v>1000</v>
       </c>
       <c r="E77" t="s">
         <v>44</v>
@@ -4663,13 +4720,13 @@
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B78">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C78" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D78">
-        <v>1000</v>
+        <v>1602</v>
       </c>
       <c r="E78" t="s">
         <v>44</v>
@@ -4677,13 +4734,13 @@
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B79">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C79" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D79">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="E79" t="s">
         <v>44</v>
@@ -4691,13 +4748,13 @@
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B80">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C80" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D80">
-        <v>2098</v>
+        <v>1105</v>
       </c>
       <c r="E80" t="s">
         <v>44</v>
@@ -4705,13 +4762,13 @@
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B81">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C81" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D81">
-        <v>2206</v>
+        <v>2098</v>
       </c>
       <c r="E81" t="s">
         <v>44</v>
@@ -4719,13 +4776,13 @@
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B82">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C82" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D82">
-        <v>2098</v>
+        <v>2206</v>
       </c>
       <c r="E82" t="s">
         <v>44</v>
@@ -4733,13 +4790,13 @@
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B83">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C83" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D83">
-        <v>1031</v>
+        <v>2098</v>
       </c>
       <c r="E83" t="s">
         <v>44</v>
@@ -4747,13 +4804,13 @@
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B84">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C84" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D84">
-        <v>1000</v>
+        <v>1031</v>
       </c>
       <c r="E84" t="s">
         <v>44</v>
@@ -4761,10 +4818,10 @@
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B85">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C85" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D85">
         <v>1000</v>
@@ -4775,27 +4832,27 @@
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B86">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C86" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D86">
-        <v>1702</v>
+        <v>1000</v>
       </c>
       <c r="E86" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B87">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C87" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D87">
-        <v>2391</v>
+        <v>1702</v>
       </c>
       <c r="E87" t="s">
         <v>74</v>
@@ -4803,13 +4860,13 @@
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B88">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C88" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D88">
-        <v>2628</v>
+        <v>2391</v>
       </c>
       <c r="E88" t="s">
         <v>74</v>
@@ -4817,22 +4874,24 @@
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B89">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C89" t="s">
-        <v>77</v>
-      </c>
-      <c r="D89"/>
+        <v>76</v>
+      </c>
+      <c r="D89">
+        <v>2628</v>
+      </c>
       <c r="E89" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B90">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C90" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D90"/>
       <c r="E90" t="s">
@@ -4841,27 +4900,25 @@
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B91">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C91" t="s">
-        <v>79</v>
-      </c>
-      <c r="D91">
-        <v>4051</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="D91"/>
       <c r="E91" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B92">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C92" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D92">
-        <v>1104</v>
+        <v>4051</v>
       </c>
       <c r="E92" t="s">
         <v>74</v>
@@ -4869,13 +4926,13 @@
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B93">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C93" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D93">
-        <v>2176</v>
+        <v>1104</v>
       </c>
       <c r="E93" t="s">
         <v>74</v>
@@ -4883,13 +4940,13 @@
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B94">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C94" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D94">
-        <v>4057</v>
+        <v>2176</v>
       </c>
       <c r="E94" t="s">
         <v>74</v>
@@ -4897,22 +4954,24 @@
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B95">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C95" t="s">
-        <v>83</v>
-      </c>
-      <c r="D95"/>
+        <v>82</v>
+      </c>
+      <c r="D95">
+        <v>4057</v>
+      </c>
       <c r="E95" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B96">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C96" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D96"/>
       <c r="E96" t="s">
@@ -4921,22 +4980,22 @@
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B97">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C97" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D97"/>
       <c r="E97" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B98">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C98" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D98"/>
       <c r="E98" t="s">
@@ -4945,10 +5004,10 @@
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B99">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C99" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D99"/>
       <c r="E99" t="s">
@@ -4957,10 +5016,10 @@
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B100">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C100" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D100"/>
       <c r="E100" t="s">
@@ -4969,10 +5028,10 @@
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B101">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C101" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D101"/>
       <c r="E101" t="s">
@@ -4981,10 +5040,10 @@
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B102">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C102" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D102"/>
       <c r="E102" t="s">
@@ -4993,27 +5052,25 @@
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B103">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C103" t="s">
-        <v>91</v>
-      </c>
-      <c r="D103">
-        <v>5434</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D103"/>
       <c r="E103" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B104">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C104" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D104">
-        <v>5517</v>
+        <v>5434</v>
       </c>
       <c r="E104" t="s">
         <v>92</v>
@@ -5021,13 +5078,13 @@
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B105">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C105" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D105">
-        <v>5550</v>
+        <v>5517</v>
       </c>
       <c r="E105" t="s">
         <v>92</v>
@@ -5035,13 +5092,13 @@
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B106">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C106" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D106">
-        <v>5717</v>
+        <v>5550</v>
       </c>
       <c r="E106" t="s">
         <v>92</v>
@@ -5049,13 +5106,13 @@
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B107">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C107" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D107">
-        <v>5484</v>
+        <v>5717</v>
       </c>
       <c r="E107" t="s">
         <v>92</v>
@@ -5063,10 +5120,10 @@
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B108">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C108" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D108">
         <v>5484</v>
@@ -5077,13 +5134,13 @@
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B109">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C109" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D109">
-        <v>5350</v>
+        <v>5484</v>
       </c>
       <c r="E109" t="s">
         <v>92</v>
@@ -5091,13 +5148,13 @@
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B110">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C110" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D110">
-        <v>5217</v>
+        <v>5350</v>
       </c>
       <c r="E110" t="s">
         <v>92</v>
@@ -5105,13 +5162,13 @@
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B111">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C111" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D111">
-        <v>5650</v>
+        <v>5217</v>
       </c>
       <c r="E111" t="s">
         <v>92</v>
@@ -5119,10 +5176,10 @@
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B112">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C112" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D112">
         <v>5650</v>
@@ -5133,13 +5190,13 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B113">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C113" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D113">
-        <v>5534</v>
+        <v>5650</v>
       </c>
       <c r="E113" t="s">
         <v>92</v>
@@ -5147,13 +5204,13 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B114">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C114" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D114">
-        <v>5800</v>
+        <v>5534</v>
       </c>
       <c r="E114" t="s">
         <v>92</v>
@@ -5161,13 +5218,13 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B115">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C115" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D115">
-        <v>5617</v>
+        <v>5800</v>
       </c>
       <c r="E115" t="s">
         <v>92</v>
@@ -5175,10 +5232,10 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B116">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D116">
         <v>5617</v>
@@ -5189,13 +5246,13 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B117">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C117" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D117">
-        <v>5550</v>
+        <v>5617</v>
       </c>
       <c r="E117" t="s">
         <v>92</v>
@@ -5203,34 +5260,36 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B118">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C118" t="s">
-        <v>107</v>
-      </c>
-      <c r="D118"/>
+        <v>106</v>
+      </c>
+      <c r="D118">
+        <v>5550</v>
+      </c>
       <c r="E118" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B119">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C119" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D119"/>
       <c r="E119" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B120">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C120" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D120"/>
       <c r="E120" t="s">
@@ -5239,10 +5298,10 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B121">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C121" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D121"/>
       <c r="E121" t="s">
@@ -5251,42 +5310,39 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B122">
+        <v>265</v>
+      </c>
+      <c r="C122" t="s">
+        <v>110</v>
+      </c>
+      <c r="D122"/>
+      <c r="E122" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B123">
         <v>266</v>
       </c>
-      <c r="C122" s="15" t="s">
+      <c r="C123" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="D122">
+      <c r="D123">
         <v>30000</v>
       </c>
-      <c r="E122" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A123" s="15" t="s">
+      <c r="E123" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" s="15" t="s">
         <v>568</v>
       </c>
-      <c r="B123">
+      <c r="B124">
         <v>8001</v>
       </c>
-      <c r="C123" s="15" t="s">
+      <c r="C124" s="15" t="s">
         <v>372</v>
-      </c>
-      <c r="D123"/>
-      <c r="E123" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
-        <v>374</v>
-      </c>
-      <c r="B124">
-        <v>8002</v>
-      </c>
-      <c r="C124" s="15" t="s">
-        <v>375</v>
       </c>
       <c r="D124"/>
       <c r="E124" t="s">
@@ -5295,13 +5351,13 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B125">
-        <v>8003</v>
+        <v>8002</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D125"/>
       <c r="E125" t="s">
@@ -5309,14 +5365,14 @@
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A126" s="15" t="s">
-        <v>649</v>
+      <c r="A126" t="s">
+        <v>376</v>
       </c>
       <c r="B126">
-        <v>10000</v>
+        <v>8003</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>650</v>
+        <v>377</v>
       </c>
       <c r="D126"/>
       <c r="E126" t="s">
@@ -5325,28 +5381,28 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="15" t="s">
-        <v>321</v>
+        <v>649</v>
       </c>
       <c r="B127">
-        <v>10001</v>
+        <v>10000</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>318</v>
+        <v>650</v>
       </c>
       <c r="D127"/>
       <c r="E127" t="s">
-        <v>203</v>
+        <v>373</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="15" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B128">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D128"/>
       <c r="E128" t="s">
@@ -5355,13 +5411,13 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B129">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D129"/>
       <c r="E129" t="s">
@@ -5370,33 +5426,31 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="15" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B130">
-        <v>10101</v>
+        <v>10003</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>328</v>
-      </c>
-      <c r="D130">
-        <v>7500</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="D130"/>
       <c r="E130" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B131">
-        <v>10102</v>
+        <v>10101</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D131">
-        <v>73427</v>
+        <v>7500</v>
       </c>
       <c r="E131" t="s">
         <v>203</v>
@@ -5404,28 +5458,30 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="15" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B132">
-        <v>10103</v>
+        <v>10102</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="D132"/>
+        <v>329</v>
+      </c>
+      <c r="D132">
+        <v>73427</v>
+      </c>
       <c r="E132" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B133">
-        <v>10104</v>
+        <v>10103</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D133"/>
       <c r="E133" t="s">
@@ -5434,13 +5490,13 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B134">
-        <v>10105</v>
+        <v>10104</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D134"/>
       <c r="E134" t="s">
@@ -5449,13 +5505,13 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B135">
-        <v>10106</v>
+        <v>10105</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D135"/>
       <c r="E135" t="s">
@@ -5464,13 +5520,13 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="15" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B136">
-        <v>10107</v>
+        <v>10106</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D136"/>
       <c r="E136" t="s">
@@ -5479,43 +5535,43 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B137">
-        <v>10108</v>
+        <v>10107</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D137"/>
       <c r="E137" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A138" s="37" t="s">
-        <v>355</v>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A138" s="15" t="s">
+        <v>340</v>
       </c>
       <c r="B138">
-        <v>10109</v>
+        <v>10108</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D138"/>
       <c r="E138" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A139" s="15" t="s">
-        <v>341</v>
+    <row r="139" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A139" s="37" t="s">
+        <v>355</v>
       </c>
       <c r="B139">
-        <v>10110</v>
+        <v>10109</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D139"/>
       <c r="E139" t="s">
@@ -5524,13 +5580,13 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" s="15" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B140">
-        <v>10111</v>
+        <v>10110</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D140"/>
       <c r="E140" t="s">
@@ -5539,13 +5595,13 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="15" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B141">
-        <v>10112</v>
+        <v>10111</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D141"/>
       <c r="E141" t="s">
@@ -5554,13 +5610,13 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="15" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B142">
-        <v>10113</v>
+        <v>10112</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D142"/>
       <c r="E142" t="s">
@@ -5569,13 +5625,13 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" s="15" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B143">
-        <v>10114</v>
+        <v>10113</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D143"/>
       <c r="E143" t="s">
@@ -5584,13 +5640,13 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="15" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B144">
-        <v>10115</v>
+        <v>10114</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D144"/>
       <c r="E144" t="s">
@@ -5599,13 +5655,13 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="15" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="B145">
-        <v>10116</v>
+        <v>10115</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D145"/>
       <c r="E145" t="s">
@@ -5614,13 +5670,13 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="15" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B146">
-        <v>10117</v>
+        <v>10116</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D146"/>
       <c r="E146" t="s">
@@ -5629,45 +5685,45 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="15" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="B147">
-        <v>10118</v>
+        <v>10117</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="D147" s="15">
-        <v>120048</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="D147"/>
       <c r="E147" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="15" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="B148">
-        <v>10119</v>
+        <v>10118</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>384</v>
-      </c>
-      <c r="D148" s="15"/>
+        <v>379</v>
+      </c>
+      <c r="D148" s="15">
+        <v>120048</v>
+      </c>
       <c r="E148" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="15" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B149">
-        <v>10120</v>
+        <v>10119</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D149" s="15"/>
       <c r="E149" t="s">
@@ -5676,13 +5732,13 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" s="15" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B150">
-        <v>10121</v>
+        <v>10120</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D150" s="15"/>
       <c r="E150" t="s">
@@ -5691,13 +5747,13 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="15" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B151">
-        <v>10122</v>
+        <v>10121</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D151" s="15"/>
       <c r="E151" t="s">
@@ -5706,13 +5762,13 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B152">
-        <v>10123</v>
+        <v>10122</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D152" s="15"/>
       <c r="E152" t="s">
@@ -5721,13 +5777,13 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B153">
-        <v>10124</v>
+        <v>10123</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D153" s="15"/>
       <c r="E153" t="s">
@@ -5736,13 +5792,13 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B154">
-        <v>10125</v>
+        <v>10124</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D154" s="15"/>
       <c r="E154" t="s">
@@ -5751,13 +5807,13 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="15" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B155">
-        <v>10126</v>
+        <v>10125</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D155" s="15"/>
       <c r="E155" t="s">
@@ -5766,13 +5822,13 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" s="15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B156">
-        <v>10127</v>
+        <v>10126</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D156" s="15"/>
       <c r="E156" t="s">
@@ -5781,13 +5837,13 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="15" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B157">
-        <v>10128</v>
+        <v>10127</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="D157" s="15"/>
       <c r="E157" t="s">
@@ -5796,45 +5852,45 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="15" t="s">
-        <v>406</v>
-      </c>
-      <c r="B158" s="15">
-        <v>10129</v>
+        <v>401</v>
+      </c>
+      <c r="B158">
+        <v>10128</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="D158" s="15">
-        <v>65184</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="D158" s="15"/>
       <c r="E158" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="15" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B159" s="15">
-        <v>10130</v>
+        <v>10129</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>414</v>
-      </c>
-      <c r="D159" s="15"/>
+        <v>413</v>
+      </c>
+      <c r="D159" s="15">
+        <v>65184</v>
+      </c>
       <c r="E159" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="15" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B160" s="15">
-        <v>10131</v>
+        <v>10130</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D160" s="15"/>
       <c r="E160" t="s">
@@ -5843,13 +5899,13 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B161" s="15">
-        <v>10132</v>
+        <v>10131</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D161" s="15"/>
       <c r="E161" t="s">
@@ -5858,13 +5914,13 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="15" t="s">
-        <v>338</v>
+        <v>409</v>
       </c>
       <c r="B162" s="15">
-        <v>10133</v>
+        <v>10132</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D162" s="15"/>
       <c r="E162" t="s">
@@ -5873,13 +5929,13 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" s="15" t="s">
-        <v>410</v>
+        <v>338</v>
       </c>
       <c r="B163" s="15">
-        <v>10134</v>
+        <v>10133</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D163" s="15"/>
       <c r="E163" t="s">
@@ -5888,13 +5944,13 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="15" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B164" s="15">
-        <v>10135</v>
+        <v>10134</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D164" s="15"/>
       <c r="E164" t="s">
@@ -5903,13 +5959,13 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="15" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B165" s="15">
-        <v>10136</v>
+        <v>10135</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D165" s="15"/>
       <c r="E165" t="s">
@@ -5918,33 +5974,31 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="15" t="s">
-        <v>443</v>
-      </c>
-      <c r="B166" s="30">
-        <v>10137</v>
-      </c>
-      <c r="C166" s="30" t="s">
-        <v>437</v>
-      </c>
-      <c r="D166" s="15">
-        <v>7500</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="B166" s="15">
+        <v>10136</v>
+      </c>
+      <c r="C166" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="D166" s="15"/>
       <c r="E166" t="s">
-        <v>373</v>
+        <v>203</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B167" s="30">
-        <v>10138</v>
+        <v>10137</v>
       </c>
       <c r="C167" s="30" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D167" s="15">
-        <v>73427</v>
+        <v>7500</v>
       </c>
       <c r="E167" t="s">
         <v>373</v>
@@ -5952,28 +6006,30 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="15" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B168" s="30">
-        <v>10139</v>
+        <v>10138</v>
       </c>
       <c r="C168" s="30" t="s">
-        <v>433</v>
-      </c>
-      <c r="D168" s="15"/>
+        <v>438</v>
+      </c>
+      <c r="D168" s="15">
+        <v>73427</v>
+      </c>
       <c r="E168" t="s">
-        <v>203</v>
+        <v>373</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="15" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B169" s="30">
-        <v>10140</v>
+        <v>10139</v>
       </c>
       <c r="C169" s="30" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D169" s="15"/>
       <c r="E169" t="s">
@@ -5982,13 +6038,13 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="15" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B170" s="30">
-        <v>10141</v>
+        <v>10140</v>
       </c>
       <c r="C170" s="30" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D170" s="15"/>
       <c r="E170" t="s">
@@ -5997,13 +6053,13 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" s="15" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B171" s="30">
-        <v>10142</v>
+        <v>10141</v>
       </c>
       <c r="C171" s="30" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D171" s="15"/>
       <c r="E171" t="s">
@@ -6012,60 +6068,60 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="15" t="s">
-        <v>446</v>
-      </c>
-      <c r="B172" s="41">
-        <v>10143</v>
-      </c>
-      <c r="C172" s="41" t="s">
-        <v>445</v>
-      </c>
-      <c r="D172" s="15">
-        <v>180000</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="B172" s="30">
+        <v>10142</v>
+      </c>
+      <c r="C172" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="D172" s="15"/>
       <c r="E172" t="s">
-        <v>373</v>
+        <v>203</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="15" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="B173" s="41">
-        <v>10144</v>
+        <v>10143</v>
       </c>
       <c r="C173" s="41" t="s">
-        <v>463</v>
-      </c>
-      <c r="D173" s="15"/>
+        <v>445</v>
+      </c>
+      <c r="D173" s="15">
+        <v>180000</v>
+      </c>
       <c r="E173" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="15" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B174" s="41">
-        <v>10145</v>
+        <v>10144</v>
       </c>
       <c r="C174" s="41" t="s">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="D174" s="15"/>
       <c r="E174" t="s">
-        <v>203</v>
+        <v>373</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="15" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="B175" s="41">
-        <v>10146</v>
+        <v>10145</v>
       </c>
       <c r="C175" s="41" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="D175" s="15"/>
       <c r="E175" t="s">
@@ -6074,13 +6130,13 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="15" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B176" s="41">
-        <v>10147</v>
+        <v>10146</v>
       </c>
       <c r="C176" s="41" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D176" s="15"/>
       <c r="E176" t="s">
@@ -6089,13 +6145,13 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="15" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="B177" s="41">
-        <v>10148</v>
+        <v>10147</v>
       </c>
       <c r="C177" s="41" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D177" s="15"/>
       <c r="E177" t="s">
@@ -6104,43 +6160,43 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B178" s="41">
-        <v>10149</v>
+        <v>10148</v>
       </c>
       <c r="C178" s="41" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D178" s="15"/>
       <c r="E178" t="s">
-        <v>373</v>
+        <v>203</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="15" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="B179" s="41">
-        <v>10150</v>
+        <v>10149</v>
       </c>
       <c r="C179" s="41" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D179" s="15"/>
       <c r="E179" t="s">
-        <v>203</v>
+        <v>373</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="15" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B180" s="41">
-        <v>10151</v>
+        <v>10150</v>
       </c>
       <c r="C180" s="41" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D180" s="15"/>
       <c r="E180" t="s">
@@ -6149,13 +6205,13 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="15" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="B181" s="41">
-        <v>10152</v>
+        <v>10151</v>
       </c>
       <c r="C181" s="41" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D181" s="15"/>
       <c r="E181" t="s">
@@ -6164,13 +6220,13 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="15" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="B182" s="41">
-        <v>10153</v>
+        <v>10152</v>
       </c>
       <c r="C182" s="41" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D182" s="15"/>
       <c r="E182" t="s">
@@ -6179,43 +6235,43 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="15" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B183" s="41">
-        <v>10154</v>
+        <v>10153</v>
       </c>
       <c r="C183" s="41" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D183" s="15"/>
       <c r="E183" t="s">
-        <v>373</v>
+        <v>203</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="15" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="B184" s="41">
-        <v>10155</v>
+        <v>10154</v>
       </c>
       <c r="C184" s="41" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D184" s="15"/>
       <c r="E184" t="s">
-        <v>203</v>
+        <v>373</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B185" s="41">
-        <v>10156</v>
+        <v>10155</v>
       </c>
       <c r="C185" s="41" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D185" s="15"/>
       <c r="E185" t="s">
@@ -6224,13 +6280,13 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="15" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B186" s="41">
-        <v>10157</v>
+        <v>10156</v>
       </c>
       <c r="C186" s="41" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D186" s="15"/>
       <c r="E186" t="s">
@@ -6239,13 +6295,13 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="15" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B187" s="41">
-        <v>10158</v>
+        <v>10157</v>
       </c>
       <c r="C187" s="41" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D187" s="15"/>
       <c r="E187" t="s">
@@ -6254,43 +6310,43 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="15" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="B188" s="41">
-        <v>10159</v>
+        <v>10158</v>
       </c>
       <c r="C188" s="41" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D188" s="15"/>
       <c r="E188" t="s">
-        <v>373</v>
+        <v>203</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="15" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="B189" s="41">
-        <v>10160</v>
+        <v>10159</v>
       </c>
       <c r="C189" s="41" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D189" s="15"/>
       <c r="E189" t="s">
-        <v>203</v>
+        <v>373</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="15" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B190" s="41">
-        <v>10161</v>
+        <v>10160</v>
       </c>
       <c r="C190" s="41" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D190" s="15"/>
       <c r="E190" t="s">
@@ -6299,13 +6355,13 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="15" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B191" s="41">
-        <v>10162</v>
+        <v>10161</v>
       </c>
       <c r="C191" s="41" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D191" s="15"/>
       <c r="E191" t="s">
@@ -6314,13 +6370,13 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="15" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B192" s="41">
-        <v>10163</v>
+        <v>10162</v>
       </c>
       <c r="C192" s="41" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D192" s="15"/>
       <c r="E192" t="s">
@@ -6329,13 +6385,13 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" s="15" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B193" s="41">
-        <v>10164</v>
+        <v>10163</v>
       </c>
       <c r="C193" s="41" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D193" s="15"/>
       <c r="E193" t="s">
@@ -6344,13 +6400,13 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="15" t="s">
-        <v>496</v>
+        <v>461</v>
       </c>
       <c r="B194" s="41">
-        <v>10165</v>
+        <v>10164</v>
       </c>
       <c r="C194" s="41" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D194" s="15"/>
       <c r="E194" t="s">
@@ -6359,13 +6415,13 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="15" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="B195" s="41">
-        <v>10166</v>
+        <v>10165</v>
       </c>
       <c r="C195" s="41" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D195" s="15"/>
       <c r="E195" t="s">
@@ -6374,13 +6430,13 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="15" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B196" s="41">
-        <v>10167</v>
+        <v>10166</v>
       </c>
       <c r="C196" s="41" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D196" s="15"/>
       <c r="E196" t="s">
@@ -6389,13 +6445,13 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="15" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B197" s="41">
-        <v>10168</v>
+        <v>10167</v>
       </c>
       <c r="C197" s="41" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D197" s="15"/>
       <c r="E197" t="s">
@@ -6404,13 +6460,13 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="15" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B198" s="41">
-        <v>10169</v>
+        <v>10168</v>
       </c>
       <c r="C198" s="41" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="D198" s="15"/>
       <c r="E198" t="s">
@@ -6419,13 +6475,13 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="15" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B199" s="41">
-        <v>10170</v>
+        <v>10169</v>
       </c>
       <c r="C199" s="41" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D199" s="15"/>
       <c r="E199" t="s">
@@ -6434,45 +6490,45 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="15" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
       <c r="B200" s="41">
-        <v>10171</v>
+        <v>10170</v>
       </c>
       <c r="C200" s="41" t="s">
-        <v>530</v>
-      </c>
-      <c r="D200" s="15">
-        <v>76000</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="D200" s="15"/>
       <c r="E200" t="s">
-        <v>373</v>
+        <v>203</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" s="15" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="B201" s="41">
-        <v>10172</v>
+        <v>10171</v>
       </c>
       <c r="C201" s="41" t="s">
-        <v>518</v>
-      </c>
-      <c r="D201" s="15"/>
+        <v>530</v>
+      </c>
+      <c r="D201" s="15">
+        <v>76000</v>
+      </c>
       <c r="E201" t="s">
-        <v>203</v>
+        <v>373</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="15" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="B202" s="41">
-        <v>10173</v>
+        <v>10172</v>
       </c>
       <c r="C202" s="41" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D202" s="15"/>
       <c r="E202" t="s">
@@ -6481,13 +6537,13 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B203" s="41">
-        <v>10174</v>
+        <v>10173</v>
       </c>
       <c r="C203" s="41" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D203" s="15"/>
       <c r="E203" t="s">
@@ -6496,13 +6552,13 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" s="15" t="s">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="B204" s="41">
-        <v>10175</v>
+        <v>10174</v>
       </c>
       <c r="C204" s="41" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D204" s="15"/>
       <c r="E204" t="s">
@@ -6511,13 +6567,13 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" s="15" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B205" s="41">
-        <v>10176</v>
+        <v>10175</v>
       </c>
       <c r="C205" s="41" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D205" s="15"/>
       <c r="E205" t="s">
@@ -6526,13 +6582,13 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" s="15" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B206" s="41">
-        <v>10177</v>
+        <v>10176</v>
       </c>
       <c r="C206" s="41" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D206" s="15"/>
       <c r="E206" t="s">
@@ -6541,13 +6597,13 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B207" s="41">
-        <v>10178</v>
+        <v>10177</v>
       </c>
       <c r="C207" s="41" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D207" s="15"/>
       <c r="E207" t="s">
@@ -6556,13 +6612,13 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" s="15" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="B208" s="41">
-        <v>10179</v>
+        <v>10178</v>
       </c>
       <c r="C208" s="41" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D208" s="15"/>
       <c r="E208" t="s">
@@ -6571,13 +6627,13 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" s="15" t="s">
-        <v>551</v>
+        <v>528</v>
       </c>
       <c r="B209" s="41">
-        <v>10180</v>
+        <v>10179</v>
       </c>
       <c r="C209" s="41" t="s">
-        <v>548</v>
+        <v>525</v>
       </c>
       <c r="D209" s="15"/>
       <c r="E209" t="s">
@@ -6586,13 +6642,13 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" s="15" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="B210" s="41">
-        <v>10181</v>
+        <v>10180</v>
       </c>
       <c r="C210" s="41" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="D210" s="15"/>
       <c r="E210" t="s">
@@ -6601,13 +6657,13 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" s="15" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B211" s="41">
-        <v>10182</v>
+        <v>10181</v>
       </c>
       <c r="C211" s="41" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D211" s="15"/>
       <c r="E211" t="s">
@@ -6616,13 +6672,13 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" s="15" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B212" s="41">
-        <v>10183</v>
+        <v>10182</v>
       </c>
       <c r="C212" s="41" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D212" s="15"/>
       <c r="E212" t="s">
@@ -6631,13 +6687,13 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" s="15" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B213" s="41">
-        <v>10184</v>
+        <v>10183</v>
       </c>
       <c r="C213" s="41" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D213" s="15"/>
       <c r="E213" t="s">
@@ -6646,13 +6702,13 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" s="15" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B214" s="41">
-        <v>10185</v>
+        <v>10184</v>
       </c>
       <c r="C214" s="41" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D214" s="15"/>
       <c r="E214" t="s">
@@ -6661,13 +6717,13 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" s="15" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B215" s="41">
-        <v>10186</v>
+        <v>10185</v>
       </c>
       <c r="C215" s="41" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D215" s="15"/>
       <c r="E215" t="s">
@@ -6676,13 +6732,13 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" s="15" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="B216" s="41">
-        <v>10187</v>
+        <v>10186</v>
       </c>
       <c r="C216" s="41" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="D216" s="15"/>
       <c r="E216" t="s">
@@ -6691,13 +6747,13 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" s="15" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B217" s="41">
-        <v>10188</v>
+        <v>10187</v>
       </c>
       <c r="C217" s="41" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="D217" s="15"/>
       <c r="E217" t="s">
@@ -6706,13 +6762,13 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B218" s="41">
-        <v>10189</v>
+        <v>10188</v>
       </c>
       <c r="C218" s="41" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D218" s="15"/>
       <c r="E218" t="s">
@@ -6721,45 +6777,45 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" s="15" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="B219" s="41">
-        <v>10190</v>
+        <v>10189</v>
       </c>
       <c r="C219" s="41" t="s">
-        <v>557</v>
-      </c>
-      <c r="D219" s="15">
-        <v>174000</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="D219" s="15"/>
       <c r="E219" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" s="15" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B220" s="41">
-        <v>10191</v>
+        <v>10190</v>
       </c>
       <c r="C220" s="41" t="s">
-        <v>558</v>
-      </c>
-      <c r="D220" s="15"/>
+        <v>557</v>
+      </c>
+      <c r="D220" s="15">
+        <v>174000</v>
+      </c>
       <c r="E220" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" s="15" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B221" s="41">
-        <v>10192</v>
+        <v>10191</v>
       </c>
       <c r="C221" s="41" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D221" s="15"/>
       <c r="E221" t="s">
@@ -6768,13 +6824,13 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" s="15" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B222" s="41">
-        <v>10193</v>
+        <v>10192</v>
       </c>
       <c r="C222" s="41" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D222" s="15"/>
       <c r="E222" t="s">
@@ -6783,13 +6839,13 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" s="15" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B223" s="41">
-        <v>10194</v>
+        <v>10193</v>
       </c>
       <c r="C223" s="41" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D223" s="15"/>
       <c r="E223" t="s">
@@ -6798,13 +6854,13 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" s="15" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B224" s="41">
-        <v>10195</v>
+        <v>10194</v>
       </c>
       <c r="C224" s="41" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D224" s="15"/>
       <c r="E224" t="s">
@@ -6813,45 +6869,45 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" s="15" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="B225" s="41">
-        <v>10300</v>
+        <v>10195</v>
       </c>
       <c r="C225" s="41" t="s">
-        <v>569</v>
-      </c>
-      <c r="D225" s="15">
-        <v>63000</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="D225" s="15"/>
       <c r="E225" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" s="15" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B226" s="41">
-        <v>10301</v>
+        <v>10300</v>
       </c>
       <c r="C226" s="41" t="s">
-        <v>570</v>
-      </c>
-      <c r="D226" s="15"/>
+        <v>569</v>
+      </c>
+      <c r="D226" s="15">
+        <v>63000</v>
+      </c>
       <c r="E226" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" s="15" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B227" s="41">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="C227" s="41" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="D227" s="15"/>
       <c r="E227" t="s">
@@ -6860,13 +6916,13 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" s="15" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="B228" s="41">
-        <v>10303</v>
+        <v>10302</v>
       </c>
       <c r="C228" s="41" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="D228" s="15"/>
       <c r="E228" t="s">
@@ -6875,13 +6931,13 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" s="15" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="B229" s="41">
-        <v>10304</v>
+        <v>10303</v>
       </c>
       <c r="C229" s="41" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D229" s="15"/>
       <c r="E229" t="s">
@@ -6890,13 +6946,13 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" s="15" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="B230" s="41">
-        <v>10305</v>
+        <v>10304</v>
       </c>
       <c r="C230" s="41" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D230" s="15"/>
       <c r="E230" t="s">
@@ -6905,13 +6961,13 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" s="15" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B231" s="41">
-        <v>10306</v>
+        <v>10305</v>
       </c>
       <c r="C231" s="41" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D231" s="15"/>
       <c r="E231" t="s">
@@ -6920,13 +6976,13 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" s="15" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B232" s="41">
-        <v>10307</v>
+        <v>10306</v>
       </c>
       <c r="C232" s="41" t="s">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="D232" s="15"/>
       <c r="E232" t="s">
@@ -6935,13 +6991,13 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" s="15" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B233" s="41">
-        <v>10308</v>
+        <v>10307</v>
       </c>
       <c r="C233" s="41" t="s">
-        <v>574</v>
+        <v>590</v>
       </c>
       <c r="D233" s="15"/>
       <c r="E233" t="s">
@@ -6950,13 +7006,13 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" s="15" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="B234" s="41">
-        <v>10309</v>
+        <v>10308</v>
       </c>
       <c r="C234" s="41" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="D234" s="15"/>
       <c r="E234" t="s">
@@ -6965,13 +7021,13 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" s="15" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B235" s="41">
-        <v>10310</v>
+        <v>10309</v>
       </c>
       <c r="C235" s="41" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D235" s="15"/>
       <c r="E235" t="s">
@@ -6980,13 +7036,13 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" s="15" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B236" s="41">
-        <v>10311</v>
+        <v>10310</v>
       </c>
       <c r="C236" s="41" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D236" s="15"/>
       <c r="E236" t="s">
@@ -6995,13 +7051,13 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" s="15" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="B237" s="41">
-        <v>10312</v>
+        <v>10311</v>
       </c>
       <c r="C237" s="41" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D237" s="15"/>
       <c r="E237" t="s">
@@ -7010,13 +7066,13 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" s="15" t="s">
-        <v>609</v>
+        <v>587</v>
       </c>
       <c r="B238" s="41">
-        <v>10313</v>
+        <v>10312</v>
       </c>
       <c r="C238" s="41" t="s">
-        <v>610</v>
+        <v>588</v>
       </c>
       <c r="D238" s="15"/>
       <c r="E238" t="s">
@@ -7025,13 +7081,13 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" s="15" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B239" s="41">
-        <v>10314</v>
+        <v>10313</v>
       </c>
       <c r="C239" s="41" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D239" s="15"/>
       <c r="E239" t="s">
@@ -7040,13 +7096,13 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" s="15" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="B240" s="41">
-        <v>10315</v>
+        <v>10314</v>
       </c>
       <c r="C240" s="41" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D240" s="15"/>
       <c r="E240" t="s">
@@ -7055,13 +7111,13 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" s="15" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B241" s="41">
-        <v>10316</v>
+        <v>10315</v>
       </c>
       <c r="C241" s="41" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D241" s="15"/>
       <c r="E241" t="s">
@@ -7070,13 +7126,13 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" s="15" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B242" s="41">
-        <v>10317</v>
+        <v>10316</v>
       </c>
       <c r="C242" s="41" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="D242" s="15"/>
       <c r="E242" t="s">
@@ -7085,13 +7141,13 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" s="15" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B243" s="41">
-        <v>10318</v>
+        <v>10317</v>
       </c>
       <c r="C243" s="41" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D243" s="15"/>
       <c r="E243" t="s">
@@ -7100,13 +7156,13 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" s="15" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B244" s="41">
-        <v>10319</v>
+        <v>10318</v>
       </c>
       <c r="C244" s="41" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D244" s="15"/>
       <c r="E244" t="s">
@@ -7115,13 +7171,13 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" s="15" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="B245" s="41">
-        <v>10320</v>
+        <v>10319</v>
       </c>
       <c r="C245" s="41" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D245" s="15"/>
       <c r="E245" t="s">
@@ -7130,13 +7186,13 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" s="15" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B246" s="41">
-        <v>10321</v>
+        <v>10320</v>
       </c>
       <c r="C246" s="41" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="D246" s="15"/>
       <c r="E246" t="s">
@@ -7145,13 +7201,13 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" s="15" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B247" s="41">
-        <v>10322</v>
+        <v>10321</v>
       </c>
       <c r="C247" s="41" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D247" s="15"/>
       <c r="E247" t="s">
@@ -7160,13 +7216,13 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" s="15" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B248" s="41">
-        <v>10323</v>
+        <v>10322</v>
       </c>
       <c r="C248" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D248" s="15"/>
       <c r="E248" t="s">
@@ -7175,13 +7231,13 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" s="15" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B249" s="41">
-        <v>10324</v>
+        <v>10323</v>
       </c>
       <c r="C249" s="41" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D249" s="15"/>
       <c r="E249" t="s">
@@ -7190,13 +7246,13 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" s="15" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B250" s="41">
-        <v>10325</v>
+        <v>10324</v>
       </c>
       <c r="C250" s="41" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D250" s="15"/>
       <c r="E250" t="s">
@@ -7205,13 +7261,13 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" s="15" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B251" s="41">
-        <v>10326</v>
+        <v>10325</v>
       </c>
       <c r="C251" s="41" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D251" s="15"/>
       <c r="E251" t="s">
@@ -7220,13 +7276,13 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" s="15" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B252" s="41">
-        <v>10327</v>
+        <v>10326</v>
       </c>
       <c r="C252" s="41" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="D252" s="15"/>
       <c r="E252" t="s">
@@ -7235,13 +7291,13 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" s="15" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B253" s="41">
-        <v>10328</v>
+        <v>10327</v>
       </c>
       <c r="C253" s="41" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D253" s="15"/>
       <c r="E253" t="s">
@@ -7250,13 +7306,13 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" s="15" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B254" s="41">
-        <v>10329</v>
+        <v>10328</v>
       </c>
       <c r="C254" s="41" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D254" s="15"/>
       <c r="E254" t="s">
@@ -7265,13 +7321,13 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" s="15" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B255" s="41">
-        <v>10330</v>
+        <v>10329</v>
       </c>
       <c r="C255" s="41" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D255" s="15"/>
       <c r="E255" t="s">
@@ -7280,30 +7336,28 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256" s="15" t="s">
-        <v>670</v>
+        <v>643</v>
       </c>
       <c r="B256" s="41">
-        <v>10331</v>
+        <v>10330</v>
       </c>
       <c r="C256" s="41" t="s">
-        <v>671</v>
-      </c>
-      <c r="D256" s="15">
-        <v>60000</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="D256" s="15"/>
       <c r="E256" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257" s="15" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B257" s="41">
-        <v>10332</v>
+        <v>10331</v>
       </c>
       <c r="C257" s="41" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D257" s="15">
         <v>60000</v>
@@ -7314,28 +7368,30 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" s="15" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B258" s="41">
-        <v>10333</v>
+        <v>10332</v>
       </c>
       <c r="C258" s="41" t="s">
-        <v>675</v>
-      </c>
-      <c r="D258" s="15"/>
+        <v>673</v>
+      </c>
+      <c r="D258" s="15">
+        <v>60000</v>
+      </c>
       <c r="E258" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" s="15" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B259" s="41">
-        <v>10334</v>
+        <v>10333</v>
       </c>
       <c r="C259" s="41" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D259" s="15"/>
       <c r="E259" t="s">
@@ -7344,13 +7400,13 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" s="15" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B260" s="41">
-        <v>10335</v>
+        <v>10334</v>
       </c>
       <c r="C260" s="41" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D260" s="15"/>
       <c r="E260" t="s">
@@ -7359,13 +7415,13 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" s="15" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B261" s="41">
-        <v>10336</v>
+        <v>10335</v>
       </c>
       <c r="C261" s="41" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D261" s="15"/>
       <c r="E261" t="s">
@@ -7374,13 +7430,13 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" s="15" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B262" s="41">
-        <v>10337</v>
+        <v>10336</v>
       </c>
       <c r="C262" s="41" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D262" s="15"/>
       <c r="E262" t="s">
@@ -7389,13 +7445,13 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" s="15" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B263" s="41">
-        <v>10338</v>
+        <v>10337</v>
       </c>
       <c r="C263" s="41" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D263" s="15"/>
       <c r="E263" t="s">
@@ -7404,13 +7460,13 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" s="15" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B264" s="41">
-        <v>10339</v>
+        <v>10338</v>
       </c>
       <c r="C264" s="41" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D264" s="15"/>
       <c r="E264" t="s">
@@ -7419,13 +7475,13 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" s="15" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B265" s="41">
-        <v>10340</v>
+        <v>10339</v>
       </c>
       <c r="C265" s="41" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D265" s="15"/>
       <c r="E265" t="s">
@@ -7434,13 +7490,13 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" s="15" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B266" s="41">
-        <v>10341</v>
+        <v>10340</v>
       </c>
       <c r="C266" s="41" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D266" s="15"/>
       <c r="E266" t="s">
@@ -7449,43 +7505,43 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" s="15" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B267" s="41">
-        <v>10342</v>
+        <v>10341</v>
       </c>
       <c r="C267" s="41" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D267" s="15"/>
-      <c r="E267" s="15" t="s">
+      <c r="E267" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" s="15" t="s">
-        <v>662</v>
+        <v>692</v>
       </c>
       <c r="B268" s="41">
-        <v>10350</v>
+        <v>10342</v>
       </c>
       <c r="C268" s="41" t="s">
-        <v>659</v>
+        <v>693</v>
       </c>
       <c r="D268" s="15"/>
-      <c r="E268" t="s">
+      <c r="E268" s="15" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" s="15" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B269" s="41">
-        <v>10351</v>
+        <v>10350</v>
       </c>
       <c r="C269" s="41" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D269" s="15"/>
       <c r="E269" t="s">
@@ -7494,13 +7550,13 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" s="15" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B270" s="41">
-        <v>10352</v>
+        <v>10351</v>
       </c>
       <c r="C270" s="41" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D270" s="15"/>
       <c r="E270" t="s">
@@ -7509,13 +7565,13 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" s="15" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B271" s="41">
-        <v>10353</v>
+        <v>10352</v>
       </c>
       <c r="C271" s="41" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D271" s="15"/>
       <c r="E271" t="s">
@@ -7524,13 +7580,13 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" s="15" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B272" s="41">
-        <v>10354</v>
+        <v>10353</v>
       </c>
       <c r="C272" s="41" t="s">
-        <v>614</v>
+        <v>667</v>
       </c>
       <c r="D272" s="15"/>
       <c r="E272" t="s">
@@ -7539,13 +7595,13 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" s="15" t="s">
-        <v>703</v>
+        <v>665</v>
       </c>
       <c r="B273" s="41">
-        <v>10355</v>
+        <v>10354</v>
       </c>
       <c r="C273" s="41" t="s">
-        <v>702</v>
+        <v>614</v>
       </c>
       <c r="D273" s="15"/>
       <c r="E273" t="s">
@@ -7554,13 +7610,13 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274" s="15" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="B274" s="41">
-        <v>10356</v>
+        <v>10355</v>
       </c>
       <c r="C274" s="41" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D274" s="15"/>
       <c r="E274" t="s">
@@ -7569,13 +7625,13 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A275" s="15" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B275" s="41">
-        <v>10357</v>
+        <v>10356</v>
       </c>
       <c r="C275" s="41" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D275" s="15"/>
       <c r="E275" t="s">
@@ -7584,13 +7640,13 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276" s="15" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B276" s="41">
-        <v>10358</v>
+        <v>10357</v>
       </c>
       <c r="C276" s="41" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D276" s="15"/>
       <c r="E276" t="s">
@@ -7599,13 +7655,13 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277" s="15" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B277" s="41">
-        <v>10359</v>
+        <v>10358</v>
       </c>
       <c r="C277" s="41" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D277" s="15"/>
       <c r="E277" t="s">
@@ -7614,13 +7670,13 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" s="15" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B278" s="41">
-        <v>10360</v>
+        <v>10359</v>
       </c>
       <c r="C278" s="41" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D278" s="15"/>
       <c r="E278" t="s">
@@ -7629,13 +7685,13 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B279" s="41">
-        <v>10361</v>
+        <v>10360</v>
       </c>
       <c r="C279" s="41" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="D279" s="15"/>
       <c r="E279" t="s">
@@ -7644,13 +7700,13 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280" s="15" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B280" s="41">
-        <v>10362</v>
+        <v>10361</v>
       </c>
       <c r="C280" s="41" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D280" s="15"/>
       <c r="E280" t="s">
@@ -7659,13 +7715,13 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A281" s="15" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B281" s="41">
-        <v>10363</v>
+        <v>10362</v>
       </c>
       <c r="C281" s="41" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D281" s="15"/>
       <c r="E281" t="s">
@@ -7673,112 +7729,119 @@
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B282">
-        <v>305032</v>
-      </c>
-      <c r="C282" t="s">
-        <v>111</v>
-      </c>
-      <c r="D282">
-        <v>1314</v>
-      </c>
+      <c r="A282" s="15" t="s">
+        <v>719</v>
+      </c>
+      <c r="B282" s="41">
+        <v>10363</v>
+      </c>
+      <c r="C282" s="41" t="s">
+        <v>711</v>
+      </c>
+      <c r="D282" s="15"/>
       <c r="E282" t="s">
-        <v>74</v>
+        <v>203</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B283">
-        <v>305033</v>
-      </c>
-      <c r="C283" t="s">
-        <v>112</v>
-      </c>
-      <c r="D283">
-        <v>1445</v>
-      </c>
+      <c r="A283" s="15" t="s">
+        <v>724</v>
+      </c>
+      <c r="B283" s="41">
+        <v>10364</v>
+      </c>
+      <c r="C283" s="41" t="s">
+        <v>725</v>
+      </c>
+      <c r="D283" s="15"/>
       <c r="E283" t="s">
-        <v>74</v>
+        <v>203</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B284">
-        <v>305034</v>
-      </c>
-      <c r="C284" t="s">
-        <v>113</v>
-      </c>
-      <c r="D284">
-        <v>2098</v>
-      </c>
+      <c r="A284" s="15" t="s">
+        <v>726</v>
+      </c>
+      <c r="B284" s="41">
+        <v>10365</v>
+      </c>
+      <c r="C284" s="41" t="s">
+        <v>727</v>
+      </c>
+      <c r="D284" s="15"/>
       <c r="E284" t="s">
-        <v>74</v>
+        <v>203</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B285">
-        <v>305035</v>
-      </c>
-      <c r="C285" t="s">
-        <v>114</v>
-      </c>
-      <c r="D285">
-        <v>1523</v>
-      </c>
+      <c r="A285" s="15" t="s">
+        <v>728</v>
+      </c>
+      <c r="B285" s="41">
+        <v>10366</v>
+      </c>
+      <c r="C285" s="41" t="s">
+        <v>729</v>
+      </c>
+      <c r="D285" s="15"/>
       <c r="E285" t="s">
-        <v>74</v>
+        <v>203</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B286">
-        <v>305036</v>
-      </c>
-      <c r="C286" s="15" t="s">
-        <v>380</v>
-      </c>
-      <c r="D286">
-        <v>1915</v>
-      </c>
+      <c r="A286" s="15" t="s">
+        <v>730</v>
+      </c>
+      <c r="B286" s="41">
+        <v>10367</v>
+      </c>
+      <c r="C286" s="41" t="s">
+        <v>731</v>
+      </c>
+      <c r="D286" s="15"/>
       <c r="E286" t="s">
-        <v>74</v>
+        <v>203</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B287">
-        <v>305037</v>
-      </c>
-      <c r="C287" t="s">
-        <v>115</v>
-      </c>
-      <c r="D287">
-        <v>1200</v>
-      </c>
+      <c r="A287" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="B287" s="41">
+        <v>10368</v>
+      </c>
+      <c r="C287" s="41" t="s">
+        <v>733</v>
+      </c>
+      <c r="D287" s="15"/>
       <c r="E287" t="s">
-        <v>74</v>
+        <v>203</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B288">
-        <v>305038</v>
-      </c>
-      <c r="C288" t="s">
-        <v>116</v>
-      </c>
-      <c r="D288">
-        <v>2500</v>
-      </c>
+      <c r="A288" s="15" t="s">
+        <v>735</v>
+      </c>
+      <c r="B288" s="41">
+        <v>10369</v>
+      </c>
+      <c r="C288" s="41" t="s">
+        <v>734</v>
+      </c>
+      <c r="D288" s="15"/>
       <c r="E288" t="s">
-        <v>74</v>
+        <v>203</v>
       </c>
     </row>
     <row r="289" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B289">
-        <v>305039</v>
+        <v>305032</v>
       </c>
       <c r="C289" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D289">
-        <v>1200</v>
+        <v>1314</v>
       </c>
       <c r="E289" t="s">
         <v>74</v>
@@ -7786,13 +7849,13 @@
     </row>
     <row r="290" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B290">
-        <v>305040</v>
+        <v>305033</v>
       </c>
       <c r="C290" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D290">
-        <v>2500</v>
+        <v>1445</v>
       </c>
       <c r="E290" t="s">
         <v>74</v>
@@ -7800,94 +7863,108 @@
     </row>
     <row r="291" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B291">
-        <v>305200</v>
+        <v>305034</v>
       </c>
       <c r="C291" t="s">
-        <v>119</v>
-      </c>
-      <c r="D291"/>
+        <v>113</v>
+      </c>
+      <c r="D291">
+        <v>2098</v>
+      </c>
       <c r="E291" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="292" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B292">
-        <v>305201</v>
+        <v>305035</v>
       </c>
       <c r="C292" t="s">
-        <v>120</v>
-      </c>
-      <c r="D292"/>
+        <v>114</v>
+      </c>
+      <c r="D292">
+        <v>1523</v>
+      </c>
       <c r="E292" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="293" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B293">
-        <v>305202</v>
-      </c>
-      <c r="C293" t="s">
-        <v>121</v>
-      </c>
-      <c r="D293"/>
+        <v>305036</v>
+      </c>
+      <c r="C293" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="D293">
+        <v>1915</v>
+      </c>
       <c r="E293" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="294" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B294">
-        <v>305203</v>
+        <v>305037</v>
       </c>
       <c r="C294" t="s">
-        <v>122</v>
-      </c>
-      <c r="D294"/>
+        <v>115</v>
+      </c>
+      <c r="D294">
+        <v>1200</v>
+      </c>
       <c r="E294" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="295" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B295">
-        <v>305204</v>
+        <v>305038</v>
       </c>
       <c r="C295" t="s">
-        <v>123</v>
-      </c>
-      <c r="D295"/>
+        <v>116</v>
+      </c>
+      <c r="D295">
+        <v>2500</v>
+      </c>
       <c r="E295" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="296" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B296">
-        <v>305205</v>
+        <v>305039</v>
       </c>
       <c r="C296" t="s">
-        <v>124</v>
-      </c>
-      <c r="D296"/>
+        <v>117</v>
+      </c>
+      <c r="D296">
+        <v>1200</v>
+      </c>
       <c r="E296" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="297" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B297">
-        <v>305206</v>
+        <v>305040</v>
       </c>
       <c r="C297" t="s">
-        <v>125</v>
-      </c>
-      <c r="D297"/>
+        <v>118</v>
+      </c>
+      <c r="D297">
+        <v>2500</v>
+      </c>
       <c r="E297" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="298" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B298">
-        <v>305207</v>
+        <v>305200</v>
       </c>
       <c r="C298" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D298"/>
       <c r="E298" t="s">
@@ -7896,10 +7973,10 @@
     </row>
     <row r="299" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B299">
-        <v>305208</v>
+        <v>305201</v>
       </c>
       <c r="C299" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D299"/>
       <c r="E299" t="s">
@@ -7908,10 +7985,10 @@
     </row>
     <row r="300" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B300">
-        <v>305209</v>
+        <v>305202</v>
       </c>
       <c r="C300" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D300"/>
       <c r="E300" t="s">
@@ -7920,10 +7997,10 @@
     </row>
     <row r="301" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B301">
-        <v>305210</v>
+        <v>305203</v>
       </c>
       <c r="C301" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D301"/>
       <c r="E301" t="s">
@@ -7932,10 +8009,10 @@
     </row>
     <row r="302" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B302">
-        <v>305211</v>
+        <v>305204</v>
       </c>
       <c r="C302" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D302"/>
       <c r="E302" t="s">
@@ -7944,10 +8021,10 @@
     </row>
     <row r="303" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B303">
-        <v>305212</v>
+        <v>305205</v>
       </c>
       <c r="C303" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D303"/>
       <c r="E303" t="s">
@@ -7956,10 +8033,10 @@
     </row>
     <row r="304" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B304">
-        <v>305213</v>
+        <v>305206</v>
       </c>
       <c r="C304" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D304"/>
       <c r="E304" t="s">
@@ -7968,10 +8045,10 @@
     </row>
     <row r="305" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B305">
-        <v>305214</v>
+        <v>305207</v>
       </c>
       <c r="C305" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D305"/>
       <c r="E305" t="s">
@@ -7980,10 +8057,10 @@
     </row>
     <row r="306" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B306">
-        <v>305215</v>
+        <v>305208</v>
       </c>
       <c r="C306" t="s">
-        <v>207</v>
+        <v>127</v>
       </c>
       <c r="D306"/>
       <c r="E306" t="s">
@@ -7992,10 +8069,10 @@
     </row>
     <row r="307" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B307">
-        <v>305216</v>
+        <v>305209</v>
       </c>
       <c r="C307" t="s">
-        <v>208</v>
+        <v>128</v>
       </c>
       <c r="D307"/>
       <c r="E307" t="s">
@@ -8004,10 +8081,10 @@
     </row>
     <row r="308" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B308">
-        <v>305217</v>
+        <v>305210</v>
       </c>
       <c r="C308" t="s">
-        <v>209</v>
+        <v>129</v>
       </c>
       <c r="D308"/>
       <c r="E308" t="s">
@@ -8016,10 +8093,10 @@
     </row>
     <row r="309" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B309">
-        <v>305218</v>
+        <v>305211</v>
       </c>
       <c r="C309" t="s">
-        <v>214</v>
+        <v>130</v>
       </c>
       <c r="D309"/>
       <c r="E309" t="s">
@@ -8028,10 +8105,10 @@
     </row>
     <row r="310" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B310">
-        <v>305219</v>
+        <v>305212</v>
       </c>
       <c r="C310" t="s">
-        <v>227</v>
+        <v>131</v>
       </c>
       <c r="D310"/>
       <c r="E310" t="s">
@@ -8040,10 +8117,10 @@
     </row>
     <row r="311" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B311">
-        <v>305220</v>
+        <v>305213</v>
       </c>
       <c r="C311" t="s">
-        <v>229</v>
+        <v>132</v>
       </c>
       <c r="D311"/>
       <c r="E311" t="s">
@@ -8052,10 +8129,10 @@
     </row>
     <row r="312" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B312">
-        <v>305221</v>
-      </c>
-      <c r="C312" s="15" t="s">
-        <v>239</v>
+        <v>305214</v>
+      </c>
+      <c r="C312" t="s">
+        <v>133</v>
       </c>
       <c r="D312"/>
       <c r="E312" t="s">
@@ -8064,10 +8141,10 @@
     </row>
     <row r="313" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B313">
-        <v>305222</v>
-      </c>
-      <c r="C313" s="15" t="s">
-        <v>247</v>
+        <v>305215</v>
+      </c>
+      <c r="C313" t="s">
+        <v>207</v>
       </c>
       <c r="D313"/>
       <c r="E313" t="s">
@@ -8076,10 +8153,10 @@
     </row>
     <row r="314" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B314">
-        <v>305223</v>
+        <v>305216</v>
       </c>
       <c r="C314" t="s">
-        <v>254</v>
+        <v>208</v>
       </c>
       <c r="D314"/>
       <c r="E314" t="s">
@@ -8088,10 +8165,10 @@
     </row>
     <row r="315" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B315">
-        <v>30520001</v>
-      </c>
-      <c r="C315" s="15" t="s">
-        <v>307</v>
+        <v>305217</v>
+      </c>
+      <c r="C315" t="s">
+        <v>209</v>
       </c>
       <c r="D315"/>
       <c r="E315" t="s">
@@ -8100,10 +8177,10 @@
     </row>
     <row r="316" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B316">
-        <v>30520002</v>
-      </c>
-      <c r="C316" s="15" t="s">
-        <v>316</v>
+        <v>305218</v>
+      </c>
+      <c r="C316" t="s">
+        <v>214</v>
       </c>
       <c r="D316"/>
       <c r="E316" t="s">
@@ -8112,10 +8189,10 @@
     </row>
     <row r="317" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B317">
-        <v>30520003</v>
-      </c>
-      <c r="C317" s="15" t="s">
-        <v>326</v>
+        <v>305219</v>
+      </c>
+      <c r="C317" t="s">
+        <v>227</v>
       </c>
       <c r="D317"/>
       <c r="E317" t="s">
@@ -8124,10 +8201,10 @@
     </row>
     <row r="318" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B318">
-        <v>30520004</v>
-      </c>
-      <c r="C318" s="15" t="s">
-        <v>403</v>
+        <v>305220</v>
+      </c>
+      <c r="C318" t="s">
+        <v>229</v>
       </c>
       <c r="D318"/>
       <c r="E318" t="s">
@@ -8136,10 +8213,10 @@
     </row>
     <row r="319" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B319">
-        <v>30520005</v>
+        <v>305221</v>
       </c>
       <c r="C319" s="15" t="s">
-        <v>424</v>
+        <v>239</v>
       </c>
       <c r="D319"/>
       <c r="E319" t="s">
@@ -8148,10 +8225,10 @@
     </row>
     <row r="320" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B320">
-        <v>30520006</v>
+        <v>305222</v>
       </c>
       <c r="C320" s="15" t="s">
-        <v>425</v>
+        <v>247</v>
       </c>
       <c r="D320"/>
       <c r="E320" t="s">
@@ -8160,10 +8237,10 @@
     </row>
     <row r="321" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B321">
-        <v>30520007</v>
-      </c>
-      <c r="C321" s="15" t="s">
-        <v>511</v>
+        <v>305223</v>
+      </c>
+      <c r="C321" t="s">
+        <v>254</v>
       </c>
       <c r="D321"/>
       <c r="E321" t="s">
@@ -8172,46 +8249,46 @@
     </row>
     <row r="322" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B322">
-        <v>30520008</v>
+        <v>30520001</v>
       </c>
       <c r="C322" s="15" t="s">
-        <v>552</v>
+        <v>307</v>
       </c>
       <c r="D322"/>
-      <c r="E322" s="15" t="s">
-        <v>695</v>
+      <c r="E322" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="323" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B323" s="17">
-        <v>30520009</v>
-      </c>
-      <c r="C323" s="18" t="s">
-        <v>698</v>
-      </c>
-      <c r="D323" s="17"/>
-      <c r="E323" s="18" t="s">
-        <v>695</v>
+      <c r="B323">
+        <v>30520002</v>
+      </c>
+      <c r="C323" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="D323"/>
+      <c r="E323" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="324" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B324" s="17">
-        <v>30520010</v>
-      </c>
-      <c r="C324" s="18" t="s">
-        <v>699</v>
-      </c>
-      <c r="D324" s="17"/>
-      <c r="E324" s="18" t="s">
-        <v>695</v>
+      <c r="B324">
+        <v>30520003</v>
+      </c>
+      <c r="C324" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="D324"/>
+      <c r="E324" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="325" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B325">
-        <v>305224</v>
-      </c>
-      <c r="C325" t="s">
-        <v>256</v>
+        <v>30520004</v>
+      </c>
+      <c r="C325" s="15" t="s">
+        <v>403</v>
       </c>
       <c r="D325"/>
       <c r="E325" t="s">
@@ -8220,10 +8297,10 @@
     </row>
     <row r="326" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B326">
-        <v>305225</v>
-      </c>
-      <c r="C326" t="s">
-        <v>257</v>
+        <v>30520005</v>
+      </c>
+      <c r="C326" s="15" t="s">
+        <v>424</v>
       </c>
       <c r="D326"/>
       <c r="E326" t="s">
@@ -8232,10 +8309,10 @@
     </row>
     <row r="327" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B327">
-        <v>305226</v>
-      </c>
-      <c r="C327" t="s">
-        <v>258</v>
+        <v>30520006</v>
+      </c>
+      <c r="C327" s="15" t="s">
+        <v>425</v>
       </c>
       <c r="D327"/>
       <c r="E327" t="s">
@@ -8244,10 +8321,10 @@
     </row>
     <row r="328" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B328">
-        <v>305300</v>
-      </c>
-      <c r="C328" t="s">
-        <v>134</v>
+        <v>30520007</v>
+      </c>
+      <c r="C328" s="15" t="s">
+        <v>511</v>
       </c>
       <c r="D328"/>
       <c r="E328" t="s">
@@ -8256,46 +8333,46 @@
     </row>
     <row r="329" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B329">
-        <v>305301</v>
-      </c>
-      <c r="C329" t="s">
-        <v>135</v>
+        <v>30520008</v>
+      </c>
+      <c r="C329" s="15" t="s">
+        <v>552</v>
       </c>
       <c r="D329"/>
-      <c r="E329" t="s">
-        <v>74</v>
+      <c r="E329" s="15" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="330" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B330">
-        <v>305302</v>
-      </c>
-      <c r="C330" t="s">
-        <v>136</v>
-      </c>
-      <c r="D330"/>
-      <c r="E330" t="s">
-        <v>74</v>
+      <c r="B330" s="17">
+        <v>30520009</v>
+      </c>
+      <c r="C330" s="18" t="s">
+        <v>698</v>
+      </c>
+      <c r="D330" s="17"/>
+      <c r="E330" s="18" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="331" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B331">
-        <v>305303</v>
-      </c>
-      <c r="C331" t="s">
-        <v>137</v>
-      </c>
-      <c r="D331"/>
-      <c r="E331" t="s">
-        <v>74</v>
+      <c r="B331" s="17">
+        <v>30520010</v>
+      </c>
+      <c r="C331" s="18" t="s">
+        <v>699</v>
+      </c>
+      <c r="D331" s="17"/>
+      <c r="E331" s="18" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="332" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B332">
-        <v>305304</v>
+        <v>305224</v>
       </c>
       <c r="C332" t="s">
-        <v>138</v>
+        <v>256</v>
       </c>
       <c r="D332"/>
       <c r="E332" t="s">
@@ -8304,10 +8381,10 @@
     </row>
     <row r="333" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B333">
-        <v>305305</v>
+        <v>305225</v>
       </c>
       <c r="C333" t="s">
-        <v>139</v>
+        <v>257</v>
       </c>
       <c r="D333"/>
       <c r="E333" t="s">
@@ -8316,10 +8393,10 @@
     </row>
     <row r="334" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B334">
-        <v>305306</v>
+        <v>305226</v>
       </c>
       <c r="C334" t="s">
-        <v>140</v>
+        <v>258</v>
       </c>
       <c r="D334"/>
       <c r="E334" t="s">
@@ -8328,10 +8405,10 @@
     </row>
     <row r="335" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B335">
-        <v>305307</v>
+        <v>305300</v>
       </c>
       <c r="C335" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D335"/>
       <c r="E335" t="s">
@@ -8340,10 +8417,10 @@
     </row>
     <row r="336" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B336">
-        <v>305308</v>
+        <v>305301</v>
       </c>
       <c r="C336" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D336"/>
       <c r="E336" t="s">
@@ -8352,10 +8429,10 @@
     </row>
     <row r="337" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B337">
-        <v>305309</v>
+        <v>305302</v>
       </c>
       <c r="C337" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D337"/>
       <c r="E337" t="s">
@@ -8364,10 +8441,10 @@
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B338">
-        <v>305310</v>
+        <v>305303</v>
       </c>
       <c r="C338" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D338"/>
       <c r="E338" t="s">
@@ -8376,10 +8453,10 @@
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B339">
-        <v>305311</v>
+        <v>305304</v>
       </c>
       <c r="C339" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D339"/>
       <c r="E339" t="s">
@@ -8388,10 +8465,10 @@
     </row>
     <row r="340" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B340">
-        <v>305312</v>
+        <v>305305</v>
       </c>
       <c r="C340" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D340"/>
       <c r="E340" t="s">
@@ -8400,10 +8477,10 @@
     </row>
     <row r="341" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B341">
-        <v>305313</v>
+        <v>305306</v>
       </c>
       <c r="C341" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D341"/>
       <c r="E341" t="s">
@@ -8412,10 +8489,10 @@
     </row>
     <row r="342" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B342">
-        <v>305314</v>
+        <v>305307</v>
       </c>
       <c r="C342" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D342"/>
       <c r="E342" t="s">
@@ -8424,10 +8501,10 @@
     </row>
     <row r="343" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B343">
-        <v>305315</v>
+        <v>305308</v>
       </c>
       <c r="C343" t="s">
-        <v>205</v>
+        <v>142</v>
       </c>
       <c r="D343"/>
       <c r="E343" t="s">
@@ -8436,10 +8513,10 @@
     </row>
     <row r="344" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B344">
-        <v>305316</v>
+        <v>305309</v>
       </c>
       <c r="C344" t="s">
-        <v>206</v>
+        <v>143</v>
       </c>
       <c r="D344"/>
       <c r="E344" t="s">
@@ -8448,10 +8525,10 @@
     </row>
     <row r="345" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B345">
-        <v>305317</v>
+        <v>305310</v>
       </c>
       <c r="C345" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
       <c r="D345"/>
       <c r="E345" t="s">
@@ -8460,10 +8537,10 @@
     </row>
     <row r="346" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B346">
-        <v>305318</v>
+        <v>305311</v>
       </c>
       <c r="C346" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="D346"/>
       <c r="E346" t="s">
@@ -8472,10 +8549,10 @@
     </row>
     <row r="347" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B347">
-        <v>305319</v>
+        <v>305312</v>
       </c>
       <c r="C347" t="s">
-        <v>228</v>
+        <v>146</v>
       </c>
       <c r="D347"/>
       <c r="E347" t="s">
@@ -8484,10 +8561,10 @@
     </row>
     <row r="348" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B348">
-        <v>305320</v>
+        <v>305313</v>
       </c>
       <c r="C348" t="s">
-        <v>230</v>
+        <v>147</v>
       </c>
       <c r="D348"/>
       <c r="E348" t="s">
@@ -8496,10 +8573,10 @@
     </row>
     <row r="349" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B349">
-        <v>305321</v>
-      </c>
-      <c r="C349" s="15" t="s">
-        <v>238</v>
+        <v>305314</v>
+      </c>
+      <c r="C349" t="s">
+        <v>148</v>
       </c>
       <c r="D349"/>
       <c r="E349" t="s">
@@ -8508,10 +8585,10 @@
     </row>
     <row r="350" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B350">
-        <v>305322</v>
-      </c>
-      <c r="C350" s="15" t="s">
-        <v>248</v>
+        <v>305315</v>
+      </c>
+      <c r="C350" t="s">
+        <v>205</v>
       </c>
       <c r="D350"/>
       <c r="E350" t="s">
@@ -8520,10 +8597,10 @@
     </row>
     <row r="351" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B351">
-        <v>305323</v>
+        <v>305316</v>
       </c>
       <c r="C351" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="D351"/>
       <c r="E351" t="s">
@@ -8532,10 +8609,10 @@
     </row>
     <row r="352" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B352">
-        <v>305324</v>
+        <v>305317</v>
       </c>
       <c r="C352" t="s">
-        <v>259</v>
+        <v>210</v>
       </c>
       <c r="D352"/>
       <c r="E352" t="s">
@@ -8544,10 +8621,10 @@
     </row>
     <row r="353" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B353">
-        <v>305325</v>
+        <v>305318</v>
       </c>
       <c r="C353" t="s">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="D353"/>
       <c r="E353" t="s">
@@ -8556,10 +8633,10 @@
     </row>
     <row r="354" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B354">
-        <v>305326</v>
-      </c>
-      <c r="C354" s="15" t="s">
-        <v>261</v>
+        <v>305319</v>
+      </c>
+      <c r="C354" t="s">
+        <v>228</v>
       </c>
       <c r="D354"/>
       <c r="E354" t="s">
@@ -8568,10 +8645,10 @@
     </row>
     <row r="355" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B355">
-        <v>30530001</v>
-      </c>
-      <c r="C355" s="15" t="s">
-        <v>308</v>
+        <v>305320</v>
+      </c>
+      <c r="C355" t="s">
+        <v>230</v>
       </c>
       <c r="D355"/>
       <c r="E355" t="s">
@@ -8580,10 +8657,10 @@
     </row>
     <row r="356" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B356">
-        <v>30530002</v>
-      </c>
-      <c r="C356" t="s">
-        <v>317</v>
+        <v>305321</v>
+      </c>
+      <c r="C356" s="15" t="s">
+        <v>238</v>
       </c>
       <c r="D356"/>
       <c r="E356" t="s">
@@ -8592,10 +8669,10 @@
     </row>
     <row r="357" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B357">
-        <v>30530003</v>
+        <v>305322</v>
       </c>
       <c r="C357" s="15" t="s">
-        <v>327</v>
+        <v>248</v>
       </c>
       <c r="D357"/>
       <c r="E357" t="s">
@@ -8604,10 +8681,10 @@
     </row>
     <row r="358" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B358">
-        <v>30530004</v>
-      </c>
-      <c r="C358" s="15" t="s">
-        <v>404</v>
+        <v>305323</v>
+      </c>
+      <c r="C358" t="s">
+        <v>255</v>
       </c>
       <c r="D358"/>
       <c r="E358" t="s">
@@ -8616,10 +8693,10 @@
     </row>
     <row r="359" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B359">
-        <v>30530005</v>
-      </c>
-      <c r="C359" s="15" t="s">
-        <v>423</v>
+        <v>305324</v>
+      </c>
+      <c r="C359" t="s">
+        <v>259</v>
       </c>
       <c r="D359"/>
       <c r="E359" t="s">
@@ -8628,10 +8705,10 @@
     </row>
     <row r="360" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B360">
-        <v>30530006</v>
-      </c>
-      <c r="C360" s="15" t="s">
-        <v>422</v>
+        <v>305325</v>
+      </c>
+      <c r="C360" t="s">
+        <v>260</v>
       </c>
       <c r="D360"/>
       <c r="E360" t="s">
@@ -8640,58 +8717,58 @@
     </row>
     <row r="361" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B361">
-        <v>30530007</v>
+        <v>305326</v>
       </c>
       <c r="C361" s="15" t="s">
-        <v>512</v>
+        <v>261</v>
       </c>
       <c r="D361"/>
-      <c r="E361" s="15" t="s">
-        <v>554</v>
+      <c r="E361" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="362" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B362">
-        <v>30530008</v>
+        <v>30530001</v>
       </c>
       <c r="C362" s="15" t="s">
-        <v>553</v>
+        <v>308</v>
       </c>
       <c r="D362"/>
-      <c r="E362" s="15" t="s">
-        <v>554</v>
+      <c r="E362" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="363" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B363" s="17">
-        <v>30530009</v>
-      </c>
-      <c r="C363" s="18" t="s">
-        <v>696</v>
-      </c>
-      <c r="D363" s="17"/>
-      <c r="E363" s="18" t="s">
-        <v>695</v>
+      <c r="B363">
+        <v>30530002</v>
+      </c>
+      <c r="C363" t="s">
+        <v>317</v>
+      </c>
+      <c r="D363"/>
+      <c r="E363" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="364" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B364" s="17">
-        <v>30530010</v>
-      </c>
-      <c r="C364" s="18" t="s">
-        <v>697</v>
-      </c>
-      <c r="D364" s="17"/>
-      <c r="E364" s="18" t="s">
-        <v>695</v>
+      <c r="B364">
+        <v>30530003</v>
+      </c>
+      <c r="C364" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="D364"/>
+      <c r="E364" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="365" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B365">
-        <v>309205</v>
-      </c>
-      <c r="C365" t="s">
-        <v>231</v>
+        <v>30530004</v>
+      </c>
+      <c r="C365" s="15" t="s">
+        <v>404</v>
       </c>
       <c r="D365"/>
       <c r="E365" t="s">
@@ -8700,10 +8777,10 @@
     </row>
     <row r="366" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B366">
-        <v>308001</v>
-      </c>
-      <c r="C366" t="s">
-        <v>149</v>
+        <v>30530005</v>
+      </c>
+      <c r="C366" s="15" t="s">
+        <v>423</v>
       </c>
       <c r="D366"/>
       <c r="E366" t="s">
@@ -8712,10 +8789,10 @@
     </row>
     <row r="367" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B367">
-        <v>308002</v>
-      </c>
-      <c r="C367" t="s">
-        <v>150</v>
+        <v>30530006</v>
+      </c>
+      <c r="C367" s="15" t="s">
+        <v>422</v>
       </c>
       <c r="D367"/>
       <c r="E367" t="s">
@@ -8724,58 +8801,58 @@
     </row>
     <row r="368" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B368">
-        <v>308006</v>
-      </c>
-      <c r="C368" t="s">
-        <v>151</v>
+        <v>30530007</v>
+      </c>
+      <c r="C368" s="15" t="s">
+        <v>512</v>
       </c>
       <c r="D368"/>
-      <c r="E368" t="s">
-        <v>74</v>
+      <c r="E368" s="15" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="369" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B369">
-        <v>308007</v>
-      </c>
-      <c r="C369" t="s">
-        <v>152</v>
+        <v>30530008</v>
+      </c>
+      <c r="C369" s="15" t="s">
+        <v>553</v>
       </c>
       <c r="D369"/>
-      <c r="E369" t="s">
-        <v>74</v>
+      <c r="E369" s="15" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="370" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B370">
-        <v>308011</v>
-      </c>
-      <c r="C370" t="s">
-        <v>153</v>
-      </c>
-      <c r="D370"/>
-      <c r="E370" t="s">
-        <v>74</v>
+      <c r="B370" s="17">
+        <v>30530009</v>
+      </c>
+      <c r="C370" s="18" t="s">
+        <v>696</v>
+      </c>
+      <c r="D370" s="17"/>
+      <c r="E370" s="18" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="371" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B371">
-        <v>308012</v>
-      </c>
-      <c r="C371" t="s">
-        <v>154</v>
-      </c>
-      <c r="D371"/>
-      <c r="E371" t="s">
-        <v>74</v>
+      <c r="B371" s="17">
+        <v>30530010</v>
+      </c>
+      <c r="C371" s="18" t="s">
+        <v>697</v>
+      </c>
+      <c r="D371" s="17"/>
+      <c r="E371" s="18" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="372" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B372">
-        <v>308016</v>
+        <v>309205</v>
       </c>
       <c r="C372" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="D372"/>
       <c r="E372" t="s">
@@ -8784,10 +8861,10 @@
     </row>
     <row r="373" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B373">
-        <v>308017</v>
+        <v>308001</v>
       </c>
       <c r="C373" t="s">
-        <v>213</v>
+        <v>149</v>
       </c>
       <c r="D373"/>
       <c r="E373" t="s">
@@ -8796,10 +8873,10 @@
     </row>
     <row r="374" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B374">
-        <v>308021</v>
-      </c>
-      <c r="C374" s="15" t="s">
-        <v>236</v>
+        <v>308002</v>
+      </c>
+      <c r="C374" t="s">
+        <v>150</v>
       </c>
       <c r="D374"/>
       <c r="E374" t="s">
@@ -8808,10 +8885,10 @@
     </row>
     <row r="375" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B375">
-        <v>308022</v>
-      </c>
-      <c r="C375" s="15" t="s">
-        <v>237</v>
+        <v>308006</v>
+      </c>
+      <c r="C375" t="s">
+        <v>151</v>
       </c>
       <c r="D375"/>
       <c r="E375" t="s">
@@ -8820,10 +8897,10 @@
     </row>
     <row r="376" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B376">
-        <v>308026</v>
-      </c>
-      <c r="C376" s="15" t="s">
-        <v>245</v>
+        <v>308007</v>
+      </c>
+      <c r="C376" t="s">
+        <v>152</v>
       </c>
       <c r="D376"/>
       <c r="E376" t="s">
@@ -8832,10 +8909,10 @@
     </row>
     <row r="377" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B377">
-        <v>308027</v>
-      </c>
-      <c r="C377" s="15" t="s">
-        <v>246</v>
+        <v>308011</v>
+      </c>
+      <c r="C377" t="s">
+        <v>153</v>
       </c>
       <c r="D377"/>
       <c r="E377" t="s">
@@ -8844,10 +8921,10 @@
     </row>
     <row r="378" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B378">
-        <v>308031</v>
-      </c>
-      <c r="C378" s="15" t="s">
-        <v>314</v>
+        <v>308012</v>
+      </c>
+      <c r="C378" t="s">
+        <v>154</v>
       </c>
       <c r="D378"/>
       <c r="E378" t="s">
@@ -8856,10 +8933,10 @@
     </row>
     <row r="379" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B379">
-        <v>308032</v>
-      </c>
-      <c r="C379" s="15" t="s">
-        <v>315</v>
+        <v>308016</v>
+      </c>
+      <c r="C379" t="s">
+        <v>212</v>
       </c>
       <c r="D379"/>
       <c r="E379" t="s">
@@ -8868,10 +8945,10 @@
     </row>
     <row r="380" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B380">
-        <v>308036</v>
-      </c>
-      <c r="C380" s="15" t="s">
-        <v>381</v>
+        <v>308017</v>
+      </c>
+      <c r="C380" t="s">
+        <v>213</v>
       </c>
       <c r="D380"/>
       <c r="E380" t="s">
@@ -8880,10 +8957,10 @@
     </row>
     <row r="381" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B381">
-        <v>308037</v>
+        <v>308021</v>
       </c>
       <c r="C381" s="15" t="s">
-        <v>382</v>
+        <v>236</v>
       </c>
       <c r="D381"/>
       <c r="E381" t="s">
@@ -8892,10 +8969,10 @@
     </row>
     <row r="382" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B382">
-        <v>308041</v>
+        <v>308022</v>
       </c>
       <c r="C382" s="15" t="s">
-        <v>720</v>
+        <v>237</v>
       </c>
       <c r="D382"/>
       <c r="E382" t="s">
@@ -8904,10 +8981,10 @@
     </row>
     <row r="383" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B383">
-        <v>308042</v>
+        <v>308026</v>
       </c>
       <c r="C383" s="15" t="s">
-        <v>721</v>
+        <v>245</v>
       </c>
       <c r="D383"/>
       <c r="E383" t="s">
@@ -8915,30 +8992,114 @@
       </c>
     </row>
     <row r="384" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B384" s="17">
+      <c r="B384">
+        <v>308027</v>
+      </c>
+      <c r="C384" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="D384"/>
+      <c r="E384" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="385" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B385">
+        <v>308031</v>
+      </c>
+      <c r="C385" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="D385"/>
+      <c r="E385" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="386" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B386">
+        <v>308032</v>
+      </c>
+      <c r="C386" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="D386"/>
+      <c r="E386" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="387" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B387">
+        <v>308036</v>
+      </c>
+      <c r="C387" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="D387"/>
+      <c r="E387" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="388" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B388">
+        <v>308037</v>
+      </c>
+      <c r="C388" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D388"/>
+      <c r="E388" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="389" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B389">
+        <v>308041</v>
+      </c>
+      <c r="C389" s="15" t="s">
+        <v>720</v>
+      </c>
+      <c r="D389"/>
+      <c r="E389" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="390" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B390">
+        <v>308042</v>
+      </c>
+      <c r="C390" s="15" t="s">
+        <v>721</v>
+      </c>
+      <c r="D390"/>
+      <c r="E390" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="391" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B391" s="17">
         <v>308046</v>
       </c>
-      <c r="C384" s="18" t="s">
+      <c r="C391" s="18" t="s">
         <v>700</v>
       </c>
-      <c r="D384" s="44" t="s">
+      <c r="D391" s="44" t="s">
         <v>605</v>
       </c>
-      <c r="E384" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="385" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B385" s="17">
+      <c r="E391" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="392" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B392" s="17">
         <v>308047</v>
       </c>
-      <c r="C385" s="18" t="s">
+      <c r="C392" s="18" t="s">
         <v>701</v>
       </c>
-      <c r="D385" s="44" t="s">
+      <c r="D392" s="44" t="s">
         <v>605</v>
       </c>
-      <c r="E385" s="17" t="s">
+      <c r="E392" s="17" t="s">
         <v>74</v>
       </c>
     </row>

--- a/source/bin/excel/audio.xlsx
+++ b/source/bin/excel/audio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55053574-7EDD-4849-BEB5-E5F061EE4CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C8855F-7C75-43C1-8D7D-BCEF914AE789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28770" yWindow="210" windowWidth="15000" windowHeight="14925" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="738">
   <si>
     <t>sheet</t>
   </si>
@@ -2935,6 +2935,14 @@
   </si>
   <si>
     <t>2511游戏机_击破敌人</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>tbd</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>music/lobby_25dongri.mp3</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -3252,7 +3260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3361,6 +3369,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9113,7 +9124,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="7" width="20.5" customWidth="1"/>
@@ -9619,107 +9630,107 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B12">
-        <v>306101</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="I12" t="s">
-        <v>194</v>
+      <c r="B12" s="14">
+        <v>30600003</v>
+      </c>
+      <c r="C12" s="16">
+        <v>1</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>736</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>736</v>
+      </c>
+      <c r="F12" s="51" t="s">
+        <v>736</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>736</v>
+      </c>
+      <c r="H12" s="51" t="s">
+        <v>736</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>737</v>
       </c>
       <c r="K12" t="s">
-        <v>44</v>
-      </c>
-      <c r="L12" s="7"/>
-      <c r="P12" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="P12" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q12" s="14">
+        <v>30600003</v>
+      </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13">
-        <v>306102</v>
-      </c>
-      <c r="C13" s="16">
-        <v>1</v>
+        <v>306101</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>196</v>
+        <v>191</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>192</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K13" t="s">
         <v>44</v>
       </c>
-      <c r="L13" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="P13" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q13">
-        <v>306102</v>
-      </c>
+      <c r="L13" s="7"/>
+      <c r="P13" s="13"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14">
-        <v>306103</v>
+        <v>306102</v>
       </c>
       <c r="C14" s="16">
         <v>1</v>
       </c>
-      <c r="D14" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="G14" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="H14" s="28" t="s">
-        <v>252</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>249</v>
+      <c r="D14" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I14" t="s">
+        <v>198</v>
       </c>
       <c r="K14" t="s">
         <v>44</v>
@@ -9739,81 +9750,81 @@
       <c r="P14" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="Q14" s="16">
-        <v>306103</v>
+      <c r="Q14">
+        <v>306102</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15">
-        <v>306104</v>
+        <v>306103</v>
       </c>
       <c r="C15" s="16">
-        <v>0</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>266</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>270</v>
+        <v>1</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>250</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>295</v>
+        <v>253</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="H15" s="27" t="s">
-        <v>285</v>
+        <v>251</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>252</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="K15" t="s">
         <v>44</v>
       </c>
-      <c r="L15" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="N15" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="O15" s="25" t="s">
-        <v>305</v>
-      </c>
-      <c r="P15" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q15" s="29">
-        <v>306104</v>
+      <c r="L15" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="P15" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q15" s="16">
+        <v>306103</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16">
-        <v>306105</v>
+        <v>306104</v>
       </c>
       <c r="C16" s="16">
         <v>0</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H16" s="27" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K16" t="s">
         <v>44</v>
@@ -9834,33 +9845,33 @@
         <v>306</v>
       </c>
       <c r="Q16" s="29">
-        <v>306105</v>
+        <v>306104</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B17">
-        <v>306106</v>
+        <v>306105</v>
       </c>
       <c r="C17" s="16">
         <v>0</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K17" t="s">
         <v>44</v>
@@ -9881,33 +9892,33 @@
         <v>306</v>
       </c>
       <c r="Q17" s="29">
-        <v>306106</v>
+        <v>306105</v>
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B18">
-        <v>306107</v>
+        <v>306106</v>
       </c>
       <c r="C18" s="16">
         <v>0</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G18" s="27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H18" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K18" t="s">
         <v>44</v>
@@ -9928,33 +9939,33 @@
         <v>306</v>
       </c>
       <c r="Q18" s="29">
+        <v>306106</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B19">
         <v>306107</v>
       </c>
-    </row>
-    <row r="19" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="16">
-        <v>30610001</v>
-      </c>
       <c r="C19" s="16">
-        <v>1</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>310</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>310</v>
-      </c>
-      <c r="F19" s="33" t="s">
-        <v>313</v>
+        <v>0</v>
+      </c>
+      <c r="D19" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="E19" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>292</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>311</v>
-      </c>
-      <c r="H19" s="28" t="s">
-        <v>312</v>
+        <v>290</v>
+      </c>
+      <c r="H19" s="27" t="s">
+        <v>291</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>309</v>
+        <v>265</v>
       </c>
       <c r="K19" t="s">
         <v>44</v>
@@ -9974,81 +9985,81 @@
       <c r="P19" s="25" t="s">
         <v>306</v>
       </c>
-      <c r="Q19" s="16">
-        <v>30610001</v>
+      <c r="Q19" s="29">
+        <v>306107</v>
       </c>
     </row>
     <row r="20" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="16">
-        <v>30610002</v>
+        <v>30610001</v>
       </c>
       <c r="C20" s="16">
         <v>1</v>
       </c>
-      <c r="D20" s="34" t="s">
-        <v>324</v>
-      </c>
-      <c r="E20" s="34" t="s">
-        <v>324</v>
-      </c>
-      <c r="F20" s="35" t="s">
-        <v>347</v>
-      </c>
-      <c r="G20" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="H20" s="36" t="s">
-        <v>333</v>
+      <c r="D20" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="H20" s="28" t="s">
+        <v>312</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="K20" t="s">
         <v>44</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="P20" s="13" t="s">
-        <v>225</v>
+        <v>301</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="N20" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="O20" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="P20" s="25" t="s">
+        <v>306</v>
       </c>
       <c r="Q20" s="16">
-        <v>30610002</v>
+        <v>30610001</v>
       </c>
     </row>
     <row r="21" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B21" s="16">
-        <v>30610003</v>
+        <v>30610002</v>
       </c>
       <c r="C21" s="16">
         <v>1</v>
       </c>
-      <c r="D21" s="31" t="s">
-        <v>426</v>
-      </c>
-      <c r="E21" s="31" t="s">
-        <v>426</v>
-      </c>
-      <c r="F21" s="40" t="s">
-        <v>427</v>
-      </c>
-      <c r="G21" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="H21" s="40" t="s">
-        <v>429</v>
+      <c r="D21" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>347</v>
+      </c>
+      <c r="G21" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="H21" s="36" t="s">
+        <v>333</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>421</v>
+        <v>325</v>
       </c>
       <c r="K21" t="s">
         <v>44</v>
@@ -10069,33 +10080,33 @@
         <v>225</v>
       </c>
       <c r="Q21" s="16">
+        <v>30610002</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="16">
         <v>30610003</v>
-      </c>
-    </row>
-    <row r="22" spans="2:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B22" s="16">
-        <v>30610004</v>
       </c>
       <c r="C22" s="16">
         <v>1</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>502</v>
+        <v>426</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>503</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>653</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>504</v>
-      </c>
-      <c r="H22" s="42" t="s">
-        <v>531</v>
+        <v>426</v>
+      </c>
+      <c r="F22" s="40" t="s">
+        <v>427</v>
+      </c>
+      <c r="G22" s="40" t="s">
+        <v>428</v>
+      </c>
+      <c r="H22" s="40" t="s">
+        <v>429</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>501</v>
+        <v>421</v>
       </c>
       <c r="K22" t="s">
         <v>44</v>
@@ -10116,33 +10127,33 @@
         <v>225</v>
       </c>
       <c r="Q22" s="16">
+        <v>30610003</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B23" s="16">
         <v>30610004</v>
-      </c>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B23" s="16">
-        <v>30610005</v>
       </c>
       <c r="C23" s="16">
         <v>1</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>595</v>
+        <v>502</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>596</v>
+        <v>503</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>652</v>
-      </c>
-      <c r="G23" s="43" t="s">
-        <v>597</v>
-      </c>
-      <c r="H23" s="43" t="s">
-        <v>598</v>
+        <v>653</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>504</v>
+      </c>
+      <c r="H23" s="42" t="s">
+        <v>531</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>555</v>
+        <v>501</v>
       </c>
       <c r="K23" t="s">
         <v>44</v>
@@ -10163,53 +10174,100 @@
         <v>225</v>
       </c>
       <c r="Q23" s="16">
-        <v>30610005</v>
+        <v>30610004</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B24" s="16">
-        <v>30610006</v>
+        <v>30610005</v>
       </c>
       <c r="C24" s="16">
         <v>1</v>
       </c>
-      <c r="D24" s="45" t="s">
-        <v>645</v>
-      </c>
-      <c r="E24" s="45" t="s">
-        <v>646</v>
-      </c>
-      <c r="F24" s="46" t="s">
-        <v>651</v>
-      </c>
-      <c r="G24" s="47" t="s">
-        <v>647</v>
-      </c>
-      <c r="H24" s="47" t="s">
-        <v>648</v>
+      <c r="D24" s="31" t="s">
+        <v>595</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>596</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>652</v>
+      </c>
+      <c r="G24" s="43" t="s">
+        <v>597</v>
+      </c>
+      <c r="H24" s="43" t="s">
+        <v>598</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>644</v>
+        <v>555</v>
       </c>
       <c r="K24" t="s">
         <v>44</v>
       </c>
       <c r="L24" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="P24" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q24" s="16">
+        <v>30610005</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B25" s="16">
+        <v>30610006</v>
+      </c>
+      <c r="C25" s="16">
+        <v>1</v>
+      </c>
+      <c r="D25" s="45" t="s">
+        <v>645</v>
+      </c>
+      <c r="E25" s="45" t="s">
+        <v>646</v>
+      </c>
+      <c r="F25" s="46" t="s">
+        <v>651</v>
+      </c>
+      <c r="G25" s="47" t="s">
+        <v>647</v>
+      </c>
+      <c r="H25" s="47" t="s">
+        <v>648</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>644</v>
+      </c>
+      <c r="K25" t="s">
+        <v>44</v>
+      </c>
+      <c r="L25" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="M24" s="9" t="s">
+      <c r="M25" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="N24" s="25" t="s">
+      <c r="N25" s="25" t="s">
         <v>304</v>
       </c>
-      <c r="O24" s="25" t="s">
+      <c r="O25" s="25" t="s">
         <v>305</v>
       </c>
-      <c r="P24" s="25" t="s">
+      <c r="P25" s="25" t="s">
         <v>306</v>
       </c>
-      <c r="Q24" s="16">
+      <c r="Q25" s="16">
         <v>30610006</v>
       </c>
     </row>

--- a/source/bin/excel/audio.xlsx
+++ b/source/bin/excel/audio.xlsx
@@ -5,30 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596E5D16-AA16-44EB-9D70-A539E3C405B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BD6CE5-9D7E-43CD-B6E6-765A065D0F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="1" r:id="rId1"/>
     <sheet name="audio" sheetId="2" r:id="rId2"/>
     <sheet name="bgm" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -59,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="767">
   <si>
     <t>sheet</t>
   </si>
@@ -2314,6 +2303,70 @@
   </si>
   <si>
     <t>deco/effect_hupai/ron_26chunjie/ron_26chunjie</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2602神驰集愿_小游戏bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2602神驰集愿_极速时间bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2602神驰集愿_开始倒计时</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2602神驰集愿_撞普通牌</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2602神驰集愿_撞福牌</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2602神驰集愿_吃碰消除</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2602神驰集愿_吃道具</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2602神驰集愿_游戏结束吹哨</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2602chunjie/main/audio/2602chunjie_bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2602chunjie/main/audio/2602chunjie_start</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2602chunjie/main/audio/2602chunjie_end</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2602chunjie/main/audio/2602chunjie_pai1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2602chunjie/main/audio/2602chunjie_pai2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2602chunjie/main/audio/2602chunjie_item</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2602chunjie/main/audio/2602chunjie_remove</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2602chunjie/main/audio/2602chunjie_fever</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -2455,7 +2508,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2525,6 +2578,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2616,7 +2675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2729,6 +2788,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3056,10 +3116,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E407"/>
+  <dimension ref="A1:E415"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="1" max="1" width="40.875" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="58.125" customWidth="1"/>
     <col min="4" max="4" width="39.875" style="3" customWidth="1"/>
@@ -7265,258 +7325,290 @@
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B300">
+      <c r="A300" s="52" t="s">
+        <v>751</v>
+      </c>
+      <c r="B300" s="52">
+        <v>10381</v>
+      </c>
+      <c r="C300" s="15" t="s">
+        <v>759</v>
+      </c>
+      <c r="D300" s="15"/>
+      <c r="E300" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A301" s="52" t="s">
+        <v>752</v>
+      </c>
+      <c r="B301" s="52">
+        <v>10382</v>
+      </c>
+      <c r="C301" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D301" s="15"/>
+      <c r="E301" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A302" s="52" t="s">
+        <v>753</v>
+      </c>
+      <c r="B302" s="52">
+        <v>10383</v>
+      </c>
+      <c r="C302" s="15" t="s">
+        <v>760</v>
+      </c>
+      <c r="D302" s="15"/>
+      <c r="E302" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A303" s="52" t="s">
+        <v>754</v>
+      </c>
+      <c r="B303" s="52">
+        <v>10384</v>
+      </c>
+      <c r="C303" s="15" t="s">
+        <v>762</v>
+      </c>
+      <c r="D303" s="15"/>
+      <c r="E303" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A304" s="52" t="s">
+        <v>755</v>
+      </c>
+      <c r="B304" s="52">
+        <v>10385</v>
+      </c>
+      <c r="C304" s="15" t="s">
+        <v>763</v>
+      </c>
+      <c r="D304" s="15"/>
+      <c r="E304" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A305" s="52" t="s">
+        <v>756</v>
+      </c>
+      <c r="B305" s="52">
+        <v>10386</v>
+      </c>
+      <c r="C305" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="D305" s="15"/>
+      <c r="E305" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A306" s="52" t="s">
+        <v>757</v>
+      </c>
+      <c r="B306" s="52">
+        <v>10387</v>
+      </c>
+      <c r="C306" s="15" t="s">
+        <v>764</v>
+      </c>
+      <c r="D306" s="15"/>
+      <c r="E306" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A307" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="B307" s="52">
+        <v>10388</v>
+      </c>
+      <c r="C307" s="15" t="s">
+        <v>761</v>
+      </c>
+      <c r="D307" s="15"/>
+      <c r="E307" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B308">
         <v>305032</v>
       </c>
-      <c r="C300" t="s">
+      <c r="C308" t="s">
         <v>494</v>
       </c>
-      <c r="D300">
+      <c r="D308">
         <v>1314</v>
       </c>
-      <c r="E300" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B301">
+      <c r="E308" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B309">
         <v>305033</v>
       </c>
-      <c r="C301" t="s">
+      <c r="C309" t="s">
         <v>495</v>
       </c>
-      <c r="D301">
+      <c r="D309">
         <v>1445</v>
       </c>
-      <c r="E301" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B302">
+      <c r="E309" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B310">
         <v>305034</v>
       </c>
-      <c r="C302" t="s">
+      <c r="C310" t="s">
         <v>496</v>
       </c>
-      <c r="D302">
+      <c r="D310">
         <v>2098</v>
       </c>
-      <c r="E302" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B303">
+      <c r="E310" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B311">
         <v>305035</v>
       </c>
-      <c r="C303" t="s">
+      <c r="C311" t="s">
         <v>497</v>
       </c>
-      <c r="D303">
+      <c r="D311">
         <v>1523</v>
       </c>
-      <c r="E303" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B304">
+      <c r="E311" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B312">
         <v>305036</v>
       </c>
-      <c r="C304" s="15" t="s">
+      <c r="C312" s="15" t="s">
         <v>498</v>
       </c>
-      <c r="D304">
+      <c r="D312">
         <v>1915</v>
       </c>
-      <c r="E304" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="305" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B305">
+      <c r="E312" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B313">
         <v>305037</v>
       </c>
-      <c r="C305" t="s">
+      <c r="C313" t="s">
         <v>499</v>
       </c>
-      <c r="D305">
+      <c r="D313">
         <v>1200</v>
       </c>
-      <c r="E305" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="306" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B306">
+      <c r="E313" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B314">
         <v>305038</v>
       </c>
-      <c r="C306" t="s">
+      <c r="C314" t="s">
         <v>500</v>
       </c>
-      <c r="D306">
+      <c r="D314">
         <v>2500</v>
       </c>
-      <c r="E306" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="307" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B307">
+      <c r="E314" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B315">
         <v>305039</v>
       </c>
-      <c r="C307" t="s">
+      <c r="C315" t="s">
         <v>501</v>
       </c>
-      <c r="D307">
+      <c r="D315">
         <v>1200</v>
       </c>
-      <c r="E307" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="308" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B308">
+      <c r="E315" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B316">
         <v>305040</v>
       </c>
-      <c r="C308" t="s">
+      <c r="C316" t="s">
         <v>502</v>
       </c>
-      <c r="D308">
+      <c r="D316">
         <v>2500</v>
       </c>
-      <c r="E308" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="309" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B309">
+      <c r="E316" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B317">
         <v>305200</v>
       </c>
-      <c r="C309" t="s">
+      <c r="C317" t="s">
         <v>503</v>
       </c>
-      <c r="E309" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="310" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B310">
+      <c r="E317" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B318">
         <v>305201</v>
       </c>
-      <c r="C310" t="s">
+      <c r="C318" t="s">
         <v>504</v>
       </c>
-      <c r="E310" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="311" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B311">
+      <c r="E318" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B319">
         <v>305202</v>
       </c>
-      <c r="C311" t="s">
+      <c r="C319" t="s">
         <v>505</v>
       </c>
-      <c r="E311" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="312" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B312">
+      <c r="E319" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B320">
         <v>305203</v>
       </c>
-      <c r="C312" t="s">
+      <c r="C320" t="s">
         <v>506</v>
-      </c>
-      <c r="E312" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="313" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B313">
-        <v>305204</v>
-      </c>
-      <c r="C313" t="s">
-        <v>507</v>
-      </c>
-      <c r="E313" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="314" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B314">
-        <v>305205</v>
-      </c>
-      <c r="C314" t="s">
-        <v>508</v>
-      </c>
-      <c r="E314" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="315" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B315">
-        <v>305206</v>
-      </c>
-      <c r="C315" t="s">
-        <v>509</v>
-      </c>
-      <c r="E315" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="316" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B316">
-        <v>305207</v>
-      </c>
-      <c r="C316" t="s">
-        <v>510</v>
-      </c>
-      <c r="E316" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="317" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B317">
-        <v>305208</v>
-      </c>
-      <c r="C317" t="s">
-        <v>511</v>
-      </c>
-      <c r="E317" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="318" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B318">
-        <v>305209</v>
-      </c>
-      <c r="C318" t="s">
-        <v>512</v>
-      </c>
-      <c r="E318" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="319" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B319">
-        <v>305210</v>
-      </c>
-      <c r="C319" t="s">
-        <v>513</v>
-      </c>
-      <c r="E319" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="320" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B320">
-        <v>305211</v>
-      </c>
-      <c r="C320" t="s">
-        <v>514</v>
       </c>
       <c r="E320" t="s">
         <v>114</v>
@@ -7524,10 +7616,10 @@
     </row>
     <row r="321" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B321">
-        <v>305212</v>
+        <v>305204</v>
       </c>
       <c r="C321" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="E321" t="s">
         <v>114</v>
@@ -7535,10 +7627,10 @@
     </row>
     <row r="322" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B322">
-        <v>305213</v>
+        <v>305205</v>
       </c>
       <c r="C322" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="E322" t="s">
         <v>114</v>
@@ -7546,7 +7638,10 @@
     </row>
     <row r="323" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B323">
-        <v>305214</v>
+        <v>305206</v>
+      </c>
+      <c r="C323" t="s">
+        <v>509</v>
       </c>
       <c r="E323" t="s">
         <v>114</v>
@@ -7554,10 +7649,10 @@
     </row>
     <row r="324" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B324">
-        <v>305215</v>
+        <v>305207</v>
       </c>
       <c r="C324" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="E324" t="s">
         <v>114</v>
@@ -7565,10 +7660,10 @@
     </row>
     <row r="325" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B325">
-        <v>305216</v>
+        <v>305208</v>
       </c>
       <c r="C325" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="E325" t="s">
         <v>114</v>
@@ -7576,10 +7671,10 @@
     </row>
     <row r="326" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B326">
-        <v>305217</v>
+        <v>305209</v>
       </c>
       <c r="C326" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="E326" t="s">
         <v>114</v>
@@ -7587,10 +7682,10 @@
     </row>
     <row r="327" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B327">
-        <v>305218</v>
+        <v>305210</v>
       </c>
       <c r="C327" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="E327" t="s">
         <v>114</v>
@@ -7598,10 +7693,10 @@
     </row>
     <row r="328" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B328">
-        <v>305219</v>
+        <v>305211</v>
       </c>
       <c r="C328" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="E328" t="s">
         <v>114</v>
@@ -7609,10 +7704,10 @@
     </row>
     <row r="329" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B329">
-        <v>305220</v>
+        <v>305212</v>
       </c>
       <c r="C329" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="E329" t="s">
         <v>114</v>
@@ -7620,10 +7715,10 @@
     </row>
     <row r="330" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B330">
-        <v>305221</v>
-      </c>
-      <c r="C330" s="15" t="s">
-        <v>523</v>
+        <v>305213</v>
+      </c>
+      <c r="C330" t="s">
+        <v>516</v>
       </c>
       <c r="E330" t="s">
         <v>114</v>
@@ -7631,10 +7726,7 @@
     </row>
     <row r="331" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B331">
-        <v>305222</v>
-      </c>
-      <c r="C331" s="15" t="s">
-        <v>524</v>
+        <v>305214</v>
       </c>
       <c r="E331" t="s">
         <v>114</v>
@@ -7642,10 +7734,10 @@
     </row>
     <row r="332" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B332">
-        <v>305223</v>
+        <v>305215</v>
       </c>
       <c r="C332" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="E332" t="s">
         <v>114</v>
@@ -7653,10 +7745,10 @@
     </row>
     <row r="333" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B333">
-        <v>30520001</v>
-      </c>
-      <c r="C333" s="15" t="s">
-        <v>526</v>
+        <v>305216</v>
+      </c>
+      <c r="C333" t="s">
+        <v>518</v>
       </c>
       <c r="E333" t="s">
         <v>114</v>
@@ -7664,10 +7756,10 @@
     </row>
     <row r="334" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B334">
-        <v>30520002</v>
-      </c>
-      <c r="C334" s="15" t="s">
-        <v>527</v>
+        <v>305217</v>
+      </c>
+      <c r="C334" t="s">
+        <v>519</v>
       </c>
       <c r="E334" t="s">
         <v>114</v>
@@ -7675,10 +7767,10 @@
     </row>
     <row r="335" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B335">
-        <v>30520003</v>
-      </c>
-      <c r="C335" s="15" t="s">
-        <v>528</v>
+        <v>305218</v>
+      </c>
+      <c r="C335" t="s">
+        <v>520</v>
       </c>
       <c r="E335" t="s">
         <v>114</v>
@@ -7686,10 +7778,10 @@
     </row>
     <row r="336" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B336">
-        <v>30520004</v>
-      </c>
-      <c r="C336" s="15" t="s">
-        <v>529</v>
+        <v>305219</v>
+      </c>
+      <c r="C336" t="s">
+        <v>521</v>
       </c>
       <c r="E336" t="s">
         <v>114</v>
@@ -7697,10 +7789,10 @@
     </row>
     <row r="337" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B337">
-        <v>30520005</v>
-      </c>
-      <c r="C337" s="15" t="s">
-        <v>530</v>
+        <v>305220</v>
+      </c>
+      <c r="C337" t="s">
+        <v>522</v>
       </c>
       <c r="E337" t="s">
         <v>114</v>
@@ -7708,10 +7800,10 @@
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B338">
-        <v>30520006</v>
+        <v>305221</v>
       </c>
       <c r="C338" s="15" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="E338" t="s">
         <v>114</v>
@@ -7719,10 +7811,10 @@
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B339">
-        <v>30520007</v>
+        <v>305222</v>
       </c>
       <c r="C339" s="15" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="E339" t="s">
         <v>114</v>
@@ -7730,67 +7822,65 @@
     </row>
     <row r="340" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B340">
-        <v>30520008</v>
-      </c>
-      <c r="C340" s="15" t="s">
-        <v>533</v>
-      </c>
-      <c r="E340" s="15" t="s">
+        <v>305223</v>
+      </c>
+      <c r="C340" t="s">
+        <v>525</v>
+      </c>
+      <c r="E340" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="341" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B341">
-        <v>30520009</v>
+        <v>30520001</v>
       </c>
       <c r="C341" s="15" t="s">
-        <v>534</v>
-      </c>
-      <c r="E341" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="E341" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="342" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B342">
-        <v>30520010</v>
+        <v>30520002</v>
       </c>
       <c r="C342" s="15" t="s">
-        <v>535</v>
-      </c>
-      <c r="E342" s="15" t="s">
+        <v>527</v>
+      </c>
+      <c r="E342" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="343" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B343" s="17">
-        <v>30520011</v>
-      </c>
-      <c r="C343" s="18" t="s">
-        <v>536</v>
-      </c>
-      <c r="D343" s="17"/>
-      <c r="E343" s="15" t="s">
+      <c r="B343">
+        <v>30520003</v>
+      </c>
+      <c r="C343" s="15" t="s">
+        <v>528</v>
+      </c>
+      <c r="E343" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="344" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B344">
-        <v>30520012</v>
-      </c>
-      <c r="C344" s="18" t="s">
-        <v>750</v>
-      </c>
-      <c r="D344" s="17"/>
-      <c r="E344" s="15" t="s">
+        <v>30520004</v>
+      </c>
+      <c r="C344" s="15" t="s">
+        <v>529</v>
+      </c>
+      <c r="E344" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="345" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B345">
-        <v>305224</v>
-      </c>
-      <c r="C345" t="s">
-        <v>537</v>
+        <v>30520005</v>
+      </c>
+      <c r="C345" s="15" t="s">
+        <v>530</v>
       </c>
       <c r="E345" t="s">
         <v>114</v>
@@ -7798,10 +7888,10 @@
     </row>
     <row r="346" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B346">
-        <v>305225</v>
-      </c>
-      <c r="C346" t="s">
-        <v>538</v>
+        <v>30520006</v>
+      </c>
+      <c r="C346" s="15" t="s">
+        <v>531</v>
       </c>
       <c r="E346" t="s">
         <v>114</v>
@@ -7809,10 +7899,10 @@
     </row>
     <row r="347" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B347">
-        <v>305226</v>
-      </c>
-      <c r="C347" t="s">
-        <v>539</v>
+        <v>30520007</v>
+      </c>
+      <c r="C347" s="15" t="s">
+        <v>532</v>
       </c>
       <c r="E347" t="s">
         <v>114</v>
@@ -7820,65 +7910,67 @@
     </row>
     <row r="348" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B348">
-        <v>305300</v>
-      </c>
-      <c r="C348" t="s">
-        <v>540</v>
-      </c>
-      <c r="E348" t="s">
+        <v>30520008</v>
+      </c>
+      <c r="C348" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="E348" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="349" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B349">
-        <v>305301</v>
-      </c>
-      <c r="C349" t="s">
-        <v>541</v>
-      </c>
-      <c r="E349" t="s">
+        <v>30520009</v>
+      </c>
+      <c r="C349" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="E349" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="350" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B350">
-        <v>305302</v>
-      </c>
-      <c r="C350" t="s">
-        <v>542</v>
-      </c>
-      <c r="E350" t="s">
+        <v>30520010</v>
+      </c>
+      <c r="C350" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="E350" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="351" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B351">
-        <v>305303</v>
-      </c>
-      <c r="C351" t="s">
-        <v>543</v>
-      </c>
-      <c r="E351" t="s">
+      <c r="B351" s="17">
+        <v>30520011</v>
+      </c>
+      <c r="C351" s="18" t="s">
+        <v>536</v>
+      </c>
+      <c r="D351" s="17"/>
+      <c r="E351" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="352" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B352">
-        <v>305304</v>
-      </c>
-      <c r="C352" t="s">
-        <v>544</v>
-      </c>
-      <c r="E352" t="s">
+        <v>30520012</v>
+      </c>
+      <c r="C352" s="18" t="s">
+        <v>750</v>
+      </c>
+      <c r="D352" s="17"/>
+      <c r="E352" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="353" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B353">
-        <v>305305</v>
+        <v>305224</v>
       </c>
       <c r="C353" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="E353" t="s">
         <v>114</v>
@@ -7886,10 +7978,10 @@
     </row>
     <row r="354" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B354">
-        <v>305306</v>
+        <v>305225</v>
       </c>
       <c r="C354" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="E354" t="s">
         <v>114</v>
@@ -7897,10 +7989,10 @@
     </row>
     <row r="355" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B355">
-        <v>305307</v>
+        <v>305226</v>
       </c>
       <c r="C355" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="E355" t="s">
         <v>114</v>
@@ -7908,10 +8000,10 @@
     </row>
     <row r="356" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B356">
-        <v>305308</v>
+        <v>305300</v>
       </c>
       <c r="C356" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="E356" t="s">
         <v>114</v>
@@ -7919,10 +8011,10 @@
     </row>
     <row r="357" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B357">
-        <v>305309</v>
+        <v>305301</v>
       </c>
       <c r="C357" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="E357" t="s">
         <v>114</v>
@@ -7930,10 +8022,10 @@
     </row>
     <row r="358" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B358">
-        <v>305310</v>
+        <v>305302</v>
       </c>
       <c r="C358" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E358" t="s">
         <v>114</v>
@@ -7941,10 +8033,10 @@
     </row>
     <row r="359" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B359">
-        <v>305311</v>
+        <v>305303</v>
       </c>
       <c r="C359" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="E359" t="s">
         <v>114</v>
@@ -7952,10 +8044,10 @@
     </row>
     <row r="360" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B360">
-        <v>305312</v>
+        <v>305304</v>
       </c>
       <c r="C360" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="E360" t="s">
         <v>114</v>
@@ -7963,10 +8055,10 @@
     </row>
     <row r="361" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B361">
-        <v>305313</v>
+        <v>305305</v>
       </c>
       <c r="C361" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="E361" t="s">
         <v>114</v>
@@ -7974,7 +8066,10 @@
     </row>
     <row r="362" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B362">
-        <v>305314</v>
+        <v>305306</v>
+      </c>
+      <c r="C362" t="s">
+        <v>546</v>
       </c>
       <c r="E362" t="s">
         <v>114</v>
@@ -7982,10 +8077,10 @@
     </row>
     <row r="363" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B363">
-        <v>305315</v>
+        <v>305307</v>
       </c>
       <c r="C363" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="E363" t="s">
         <v>114</v>
@@ -7993,10 +8088,10 @@
     </row>
     <row r="364" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B364">
-        <v>305316</v>
+        <v>305308</v>
       </c>
       <c r="C364" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="E364" t="s">
         <v>114</v>
@@ -8004,10 +8099,10 @@
     </row>
     <row r="365" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B365">
-        <v>305317</v>
+        <v>305309</v>
       </c>
       <c r="C365" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="E365" t="s">
         <v>114</v>
@@ -8015,10 +8110,10 @@
     </row>
     <row r="366" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B366">
-        <v>305318</v>
+        <v>305310</v>
       </c>
       <c r="C366" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="E366" t="s">
         <v>114</v>
@@ -8026,10 +8121,10 @@
     </row>
     <row r="367" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B367">
-        <v>305319</v>
+        <v>305311</v>
       </c>
       <c r="C367" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="E367" t="s">
         <v>114</v>
@@ -8037,10 +8132,10 @@
     </row>
     <row r="368" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B368">
-        <v>305320</v>
+        <v>305312</v>
       </c>
       <c r="C368" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="E368" t="s">
         <v>114</v>
@@ -8048,10 +8143,10 @@
     </row>
     <row r="369" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B369">
-        <v>305321</v>
-      </c>
-      <c r="C369" s="15" t="s">
-        <v>560</v>
+        <v>305313</v>
+      </c>
+      <c r="C369" t="s">
+        <v>553</v>
       </c>
       <c r="E369" t="s">
         <v>114</v>
@@ -8059,10 +8154,7 @@
     </row>
     <row r="370" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B370">
-        <v>305322</v>
-      </c>
-      <c r="C370" s="15" t="s">
-        <v>561</v>
+        <v>305314</v>
       </c>
       <c r="E370" t="s">
         <v>114</v>
@@ -8070,10 +8162,10 @@
     </row>
     <row r="371" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B371">
-        <v>305323</v>
+        <v>305315</v>
       </c>
       <c r="C371" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="E371" t="s">
         <v>114</v>
@@ -8081,10 +8173,10 @@
     </row>
     <row r="372" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B372">
-        <v>305324</v>
+        <v>305316</v>
       </c>
       <c r="C372" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="E372" t="s">
         <v>114</v>
@@ -8092,10 +8184,10 @@
     </row>
     <row r="373" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B373">
-        <v>305325</v>
+        <v>305317</v>
       </c>
       <c r="C373" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="E373" t="s">
         <v>114</v>
@@ -8103,10 +8195,10 @@
     </row>
     <row r="374" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B374">
-        <v>305326</v>
-      </c>
-      <c r="C374" s="15" t="s">
-        <v>565</v>
+        <v>305318</v>
+      </c>
+      <c r="C374" t="s">
+        <v>557</v>
       </c>
       <c r="E374" t="s">
         <v>114</v>
@@ -8114,10 +8206,10 @@
     </row>
     <row r="375" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B375">
-        <v>30530001</v>
-      </c>
-      <c r="C375" s="15" t="s">
-        <v>566</v>
+        <v>305319</v>
+      </c>
+      <c r="C375" t="s">
+        <v>558</v>
       </c>
       <c r="E375" t="s">
         <v>114</v>
@@ -8125,10 +8217,10 @@
     </row>
     <row r="376" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B376">
-        <v>30530002</v>
+        <v>305320</v>
       </c>
       <c r="C376" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="E376" t="s">
         <v>114</v>
@@ -8136,10 +8228,10 @@
     </row>
     <row r="377" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B377">
-        <v>30530003</v>
+        <v>305321</v>
       </c>
       <c r="C377" s="15" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="E377" t="s">
         <v>114</v>
@@ -8147,10 +8239,10 @@
     </row>
     <row r="378" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B378">
-        <v>30530004</v>
+        <v>305322</v>
       </c>
       <c r="C378" s="15" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="E378" t="s">
         <v>114</v>
@@ -8158,10 +8250,10 @@
     </row>
     <row r="379" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B379">
-        <v>30530005</v>
-      </c>
-      <c r="C379" s="15" t="s">
-        <v>570</v>
+        <v>305323</v>
+      </c>
+      <c r="C379" t="s">
+        <v>562</v>
       </c>
       <c r="E379" t="s">
         <v>114</v>
@@ -8169,10 +8261,10 @@
     </row>
     <row r="380" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B380">
-        <v>30530006</v>
-      </c>
-      <c r="C380" s="15" t="s">
-        <v>571</v>
+        <v>305324</v>
+      </c>
+      <c r="C380" t="s">
+        <v>563</v>
       </c>
       <c r="E380" t="s">
         <v>114</v>
@@ -8180,78 +8272,76 @@
     </row>
     <row r="381" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B381">
-        <v>30530007</v>
-      </c>
-      <c r="C381" s="15" t="s">
-        <v>572</v>
-      </c>
-      <c r="E381" s="15" t="s">
+        <v>305325</v>
+      </c>
+      <c r="C381" t="s">
+        <v>564</v>
+      </c>
+      <c r="E381" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="382" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B382">
-        <v>30530008</v>
+        <v>305326</v>
       </c>
       <c r="C382" s="15" t="s">
-        <v>573</v>
-      </c>
-      <c r="E382" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="E382" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="383" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B383">
-        <v>30530009</v>
+        <v>30530001</v>
       </c>
       <c r="C383" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="E383" s="15" t="s">
+        <v>566</v>
+      </c>
+      <c r="E383" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="384" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B384">
-        <v>30530010</v>
-      </c>
-      <c r="C384" s="15" t="s">
-        <v>575</v>
-      </c>
-      <c r="E384" s="15" t="s">
+        <v>30530002</v>
+      </c>
+      <c r="C384" t="s">
+        <v>567</v>
+      </c>
+      <c r="E384" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="385" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B385" s="17">
-        <v>30530011</v>
-      </c>
-      <c r="C385" s="18" t="s">
-        <v>576</v>
-      </c>
-      <c r="D385" s="17"/>
-      <c r="E385" s="18" t="s">
+      <c r="B385">
+        <v>30530003</v>
+      </c>
+      <c r="C385" s="15" t="s">
+        <v>568</v>
+      </c>
+      <c r="E385" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="386" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B386">
-        <v>30530012</v>
-      </c>
-      <c r="C386" s="18" t="s">
-        <v>749</v>
-      </c>
-      <c r="D386" s="17"/>
-      <c r="E386" s="18" t="s">
+        <v>30530004</v>
+      </c>
+      <c r="C386" s="15" t="s">
+        <v>569</v>
+      </c>
+      <c r="E386" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="387" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B387">
-        <v>309205</v>
-      </c>
-      <c r="C387" t="s">
-        <v>577</v>
+        <v>30530005</v>
+      </c>
+      <c r="C387" s="15" t="s">
+        <v>570</v>
       </c>
       <c r="E387" t="s">
         <v>114</v>
@@ -8259,10 +8349,10 @@
     </row>
     <row r="388" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B388">
-        <v>308001</v>
-      </c>
-      <c r="C388" t="s">
-        <v>578</v>
+        <v>30530006</v>
+      </c>
+      <c r="C388" s="15" t="s">
+        <v>571</v>
       </c>
       <c r="E388" t="s">
         <v>114</v>
@@ -8270,76 +8360,78 @@
     </row>
     <row r="389" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B389">
-        <v>308002</v>
-      </c>
-      <c r="C389" t="s">
-        <v>579</v>
-      </c>
-      <c r="E389" t="s">
+        <v>30530007</v>
+      </c>
+      <c r="C389" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="E389" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="390" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B390">
-        <v>308006</v>
-      </c>
-      <c r="C390" t="s">
-        <v>580</v>
-      </c>
-      <c r="E390" t="s">
+        <v>30530008</v>
+      </c>
+      <c r="C390" s="15" t="s">
+        <v>573</v>
+      </c>
+      <c r="E390" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="391" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B391">
-        <v>308007</v>
-      </c>
-      <c r="C391" t="s">
-        <v>581</v>
-      </c>
-      <c r="E391" t="s">
+        <v>30530009</v>
+      </c>
+      <c r="C391" s="15" t="s">
+        <v>574</v>
+      </c>
+      <c r="E391" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="392" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B392">
-        <v>308011</v>
-      </c>
-      <c r="C392" t="s">
-        <v>582</v>
-      </c>
-      <c r="E392" t="s">
+        <v>30530010</v>
+      </c>
+      <c r="C392" s="15" t="s">
+        <v>575</v>
+      </c>
+      <c r="E392" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="393" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B393">
-        <v>308012</v>
-      </c>
-      <c r="C393" t="s">
-        <v>583</v>
-      </c>
-      <c r="E393" t="s">
+      <c r="B393" s="17">
+        <v>30530011</v>
+      </c>
+      <c r="C393" s="18" t="s">
+        <v>576</v>
+      </c>
+      <c r="D393" s="17"/>
+      <c r="E393" s="18" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="394" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B394">
-        <v>308016</v>
-      </c>
-      <c r="C394" t="s">
-        <v>584</v>
-      </c>
-      <c r="E394" t="s">
+        <v>30530012</v>
+      </c>
+      <c r="C394" s="18" t="s">
+        <v>749</v>
+      </c>
+      <c r="D394" s="17"/>
+      <c r="E394" s="18" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="395" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B395">
-        <v>308017</v>
+        <v>309205</v>
       </c>
       <c r="C395" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="E395" t="s">
         <v>114</v>
@@ -8347,10 +8439,10 @@
     </row>
     <row r="396" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B396">
-        <v>308021</v>
-      </c>
-      <c r="C396" s="15" t="s">
-        <v>586</v>
+        <v>308001</v>
+      </c>
+      <c r="C396" t="s">
+        <v>578</v>
       </c>
       <c r="E396" t="s">
         <v>114</v>
@@ -8358,10 +8450,10 @@
     </row>
     <row r="397" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B397">
-        <v>308022</v>
-      </c>
-      <c r="C397" s="15" t="s">
-        <v>587</v>
+        <v>308002</v>
+      </c>
+      <c r="C397" t="s">
+        <v>579</v>
       </c>
       <c r="E397" t="s">
         <v>114</v>
@@ -8369,10 +8461,10 @@
     </row>
     <row r="398" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B398">
-        <v>308026</v>
-      </c>
-      <c r="C398" s="15" t="s">
-        <v>588</v>
+        <v>308006</v>
+      </c>
+      <c r="C398" t="s">
+        <v>580</v>
       </c>
       <c r="E398" t="s">
         <v>114</v>
@@ -8380,10 +8472,10 @@
     </row>
     <row r="399" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B399">
-        <v>308027</v>
-      </c>
-      <c r="C399" s="15" t="s">
-        <v>589</v>
+        <v>308007</v>
+      </c>
+      <c r="C399" t="s">
+        <v>581</v>
       </c>
       <c r="E399" t="s">
         <v>114</v>
@@ -8391,10 +8483,10 @@
     </row>
     <row r="400" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B400">
-        <v>308031</v>
-      </c>
-      <c r="C400" s="15" t="s">
-        <v>590</v>
+        <v>308011</v>
+      </c>
+      <c r="C400" t="s">
+        <v>582</v>
       </c>
       <c r="E400" t="s">
         <v>114</v>
@@ -8402,10 +8494,10 @@
     </row>
     <row r="401" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B401">
-        <v>308032</v>
-      </c>
-      <c r="C401" s="15" t="s">
-        <v>591</v>
+        <v>308012</v>
+      </c>
+      <c r="C401" t="s">
+        <v>583</v>
       </c>
       <c r="E401" t="s">
         <v>114</v>
@@ -8413,10 +8505,10 @@
     </row>
     <row r="402" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B402">
-        <v>308036</v>
-      </c>
-      <c r="C402" s="15" t="s">
-        <v>592</v>
+        <v>308016</v>
+      </c>
+      <c r="C402" t="s">
+        <v>584</v>
       </c>
       <c r="E402" t="s">
         <v>114</v>
@@ -8424,10 +8516,10 @@
     </row>
     <row r="403" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B403">
-        <v>308037</v>
-      </c>
-      <c r="C403" s="15" t="s">
-        <v>593</v>
+        <v>308017</v>
+      </c>
+      <c r="C403" t="s">
+        <v>585</v>
       </c>
       <c r="E403" t="s">
         <v>114</v>
@@ -8435,10 +8527,10 @@
     </row>
     <row r="404" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B404">
-        <v>308041</v>
+        <v>308021</v>
       </c>
       <c r="C404" s="15" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E404" t="s">
         <v>114</v>
@@ -8446,44 +8538,132 @@
     </row>
     <row r="405" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B405">
+        <v>308022</v>
+      </c>
+      <c r="C405" s="15" t="s">
+        <v>587</v>
+      </c>
+      <c r="E405" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="406" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B406">
+        <v>308026</v>
+      </c>
+      <c r="C406" s="15" t="s">
+        <v>588</v>
+      </c>
+      <c r="E406" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="407" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B407">
+        <v>308027</v>
+      </c>
+      <c r="C407" s="15" t="s">
+        <v>589</v>
+      </c>
+      <c r="E407" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="408" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B408">
+        <v>308031</v>
+      </c>
+      <c r="C408" s="15" t="s">
+        <v>590</v>
+      </c>
+      <c r="E408" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="409" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B409">
+        <v>308032</v>
+      </c>
+      <c r="C409" s="15" t="s">
+        <v>591</v>
+      </c>
+      <c r="E409" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="410" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B410">
+        <v>308036</v>
+      </c>
+      <c r="C410" s="15" t="s">
+        <v>592</v>
+      </c>
+      <c r="E410" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="411" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B411">
+        <v>308037</v>
+      </c>
+      <c r="C411" s="15" t="s">
+        <v>593</v>
+      </c>
+      <c r="E411" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="412" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B412">
+        <v>308041</v>
+      </c>
+      <c r="C412" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="E412" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="413" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B413">
         <v>308042</v>
       </c>
-      <c r="C405" s="15" t="s">
+      <c r="C413" s="15" t="s">
         <v>595</v>
       </c>
-      <c r="E405" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="406" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B406" s="17">
+      <c r="E413" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="414" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B414" s="17">
         <v>308046</v>
       </c>
-      <c r="C406" s="18" t="s">
+      <c r="C414" s="18" t="s">
         <v>596</v>
       </c>
-      <c r="D406" s="44"/>
-      <c r="E406" s="17" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="407" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B407" s="17">
+      <c r="D414" s="44"/>
+      <c r="E414" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="415" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B415" s="17">
         <v>308047</v>
       </c>
-      <c r="C407" s="18" t="s">
+      <c r="C415" s="18" t="s">
         <v>597</v>
       </c>
-      <c r="D407" s="44"/>
-      <c r="E407" s="17" t="s">
+      <c r="D415" s="44"/>
+      <c r="E415" s="17" t="s">
         <v>114</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/source/bin/excel/audio.xlsx
+++ b/source/bin/excel/audio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BD6CE5-9D7E-43CD-B6E6-765A065D0F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5BD7F1-87D8-43F3-98F4-95BCA653086F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
             <charset val="134"/>
             <scheme val="minor"/>
           </rPr>
@@ -2037,9 +2038,6 @@
     <t>閒暇炒麵</t>
   </si>
   <si>
-    <t xml:space="preserve">リーヒマ -Piano Version- </t>
-  </si>
-  <si>
     <t>Mayo Yakisoba</t>
   </si>
   <si>
@@ -2367,6 +2365,10 @@
   </si>
   <si>
     <t>ui/activity/extend/2602chunjie/main/audio/2602chunjie_fever</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>リーヒマ -Piano Version-</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -7326,13 +7328,13 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" s="52" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B300" s="52">
         <v>10381</v>
       </c>
       <c r="C300" s="15" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D300" s="15"/>
       <c r="E300" t="s">
@@ -7341,13 +7343,13 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" s="52" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B301" s="52">
         <v>10382</v>
       </c>
       <c r="C301" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D301" s="15"/>
       <c r="E301" t="s">
@@ -7356,13 +7358,13 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" s="52" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B302" s="52">
         <v>10383</v>
       </c>
       <c r="C302" s="15" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D302" s="15"/>
       <c r="E302" t="s">
@@ -7371,13 +7373,13 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" s="52" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B303" s="52">
         <v>10384</v>
       </c>
       <c r="C303" s="15" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D303" s="15"/>
       <c r="E303" t="s">
@@ -7386,13 +7388,13 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304" s="52" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B304" s="52">
         <v>10385</v>
       </c>
       <c r="C304" s="15" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D304" s="15"/>
       <c r="E304" t="s">
@@ -7401,13 +7403,13 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305" s="52" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B305" s="52">
         <v>10386</v>
       </c>
       <c r="C305" s="15" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D305" s="15"/>
       <c r="E305" t="s">
@@ -7416,13 +7418,13 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" s="52" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B306" s="52">
         <v>10387</v>
       </c>
       <c r="C306" s="15" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D306" s="15"/>
       <c r="E306" t="s">
@@ -7431,13 +7433,13 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" s="52" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B307" s="52">
         <v>10388</v>
       </c>
       <c r="C307" s="15" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D307" s="15"/>
       <c r="E307" t="s">
@@ -7958,7 +7960,7 @@
         <v>30520012</v>
       </c>
       <c r="C352" s="18" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D352" s="17"/>
       <c r="E352" s="15" t="s">
@@ -8419,7 +8421,7 @@
         <v>30530012</v>
       </c>
       <c r="C394" s="18" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D394" s="17"/>
       <c r="E394" s="18" t="s">
@@ -9141,16 +9143,16 @@
         <v>661</v>
       </c>
       <c r="F11" s="47" t="s">
+        <v>766</v>
+      </c>
+      <c r="G11" s="50" t="s">
         <v>662</v>
       </c>
-      <c r="G11" s="50" t="s">
+      <c r="H11" s="50" t="s">
         <v>663</v>
       </c>
-      <c r="H11" s="50" t="s">
+      <c r="I11" s="15" t="s">
         <v>664</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>665</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -9182,22 +9184,22 @@
         <v>1</v>
       </c>
       <c r="D12" s="51" t="s">
+        <v>665</v>
+      </c>
+      <c r="E12" s="51" t="s">
         <v>666</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="F12" s="47" t="s">
         <v>667</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="G12" s="47" t="s">
         <v>668</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="H12" s="47" t="s">
         <v>669</v>
       </c>
-      <c r="H12" s="47" t="s">
+      <c r="I12" s="15" t="s">
         <v>670</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>671</v>
       </c>
       <c r="K12" t="s">
         <v>20</v>
@@ -9229,22 +9231,22 @@
         <v>0</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>673</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="6" t="s">
         <v>674</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="H13" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="I13" t="s">
         <v>676</v>
-      </c>
-      <c r="I13" t="s">
-        <v>677</v>
       </c>
       <c r="K13" t="s">
         <v>84</v>
@@ -9260,22 +9262,22 @@
         <v>1</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>679</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>679</v>
-      </c>
-      <c r="G14" s="6" t="s">
+      <c r="H14" s="10" t="s">
         <v>680</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="I14" t="s">
         <v>681</v>
-      </c>
-      <c r="I14" t="s">
-        <v>682</v>
       </c>
       <c r="K14" t="s">
         <v>84</v>
@@ -9307,22 +9309,22 @@
         <v>1</v>
       </c>
       <c r="D15" s="26" t="s">
+        <v>682</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>682</v>
+      </c>
+      <c r="F15" s="26" t="s">
         <v>683</v>
       </c>
-      <c r="E15" s="26" t="s">
-        <v>683</v>
-      </c>
-      <c r="F15" s="26" t="s">
+      <c r="G15" s="27" t="s">
         <v>684</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="H15" s="28" t="s">
         <v>685</v>
       </c>
-      <c r="H15" s="28" t="s">
+      <c r="I15" s="15" t="s">
         <v>686</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>687</v>
       </c>
       <c r="K15" t="s">
         <v>84</v>
@@ -9354,40 +9356,40 @@
         <v>0</v>
       </c>
       <c r="D16" s="31" t="s">
+        <v>687</v>
+      </c>
+      <c r="E16" s="31" t="s">
         <v>688</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="F16" s="26" t="s">
         <v>689</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="G16" s="27" t="s">
         <v>690</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="H16" s="27" t="s">
         <v>691</v>
       </c>
-      <c r="H16" s="27" t="s">
+      <c r="I16" s="15" t="s">
         <v>692</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>693</v>
       </c>
       <c r="K16" t="s">
         <v>84</v>
       </c>
       <c r="L16" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="M16" s="9" t="s">
         <v>694</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="N16" s="25" t="s">
         <v>695</v>
       </c>
-      <c r="N16" s="25" t="s">
+      <c r="O16" s="25" t="s">
         <v>696</v>
       </c>
-      <c r="O16" s="25" t="s">
+      <c r="P16" s="25" t="s">
         <v>697</v>
-      </c>
-      <c r="P16" s="25" t="s">
-        <v>698</v>
       </c>
       <c r="Q16" s="29">
         <v>306104</v>
@@ -9401,40 +9403,40 @@
         <v>0</v>
       </c>
       <c r="D17" s="31" t="s">
+        <v>698</v>
+      </c>
+      <c r="E17" s="31" t="s">
         <v>699</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="F17" s="26" t="s">
         <v>700</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="G17" s="27" t="s">
         <v>701</v>
       </c>
-      <c r="G17" s="27" t="s">
+      <c r="H17" s="27" t="s">
         <v>702</v>
       </c>
-      <c r="H17" s="27" t="s">
+      <c r="I17" s="15" t="s">
         <v>703</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>704</v>
       </c>
       <c r="K17" t="s">
         <v>84</v>
       </c>
       <c r="L17" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="M17" s="9" t="s">
         <v>694</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="N17" s="25" t="s">
         <v>695</v>
       </c>
-      <c r="N17" s="25" t="s">
+      <c r="O17" s="25" t="s">
         <v>696</v>
       </c>
-      <c r="O17" s="25" t="s">
+      <c r="P17" s="25" t="s">
         <v>697</v>
-      </c>
-      <c r="P17" s="25" t="s">
-        <v>698</v>
       </c>
       <c r="Q17" s="29">
         <v>306105</v>
@@ -9448,40 +9450,40 @@
         <v>0</v>
       </c>
       <c r="D18" s="31" t="s">
+        <v>704</v>
+      </c>
+      <c r="E18" s="31" t="s">
         <v>705</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="F18" s="26" t="s">
         <v>706</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="G18" s="27" t="s">
         <v>707</v>
       </c>
-      <c r="G18" s="27" t="s">
+      <c r="H18" s="27" t="s">
         <v>708</v>
       </c>
-      <c r="H18" s="27" t="s">
+      <c r="I18" s="15" t="s">
         <v>709</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>710</v>
       </c>
       <c r="K18" t="s">
         <v>84</v>
       </c>
       <c r="L18" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="M18" s="9" t="s">
         <v>694</v>
       </c>
-      <c r="M18" s="9" t="s">
+      <c r="N18" s="25" t="s">
         <v>695</v>
       </c>
-      <c r="N18" s="25" t="s">
+      <c r="O18" s="25" t="s">
         <v>696</v>
       </c>
-      <c r="O18" s="25" t="s">
+      <c r="P18" s="25" t="s">
         <v>697</v>
-      </c>
-      <c r="P18" s="25" t="s">
-        <v>698</v>
       </c>
       <c r="Q18" s="29">
         <v>306106</v>
@@ -9495,40 +9497,40 @@
         <v>0</v>
       </c>
       <c r="D19" s="31" t="s">
+        <v>710</v>
+      </c>
+      <c r="E19" s="31" t="s">
         <v>711</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="F19" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="G19" s="27" t="s">
         <v>712</v>
       </c>
-      <c r="F19" s="26" t="s">
-        <v>711</v>
-      </c>
-      <c r="G19" s="27" t="s">
+      <c r="H19" s="27" t="s">
         <v>713</v>
       </c>
-      <c r="H19" s="27" t="s">
+      <c r="I19" s="15" t="s">
         <v>714</v>
-      </c>
-      <c r="I19" s="15" t="s">
-        <v>715</v>
       </c>
       <c r="K19" t="s">
         <v>84</v>
       </c>
       <c r="L19" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="M19" s="9" t="s">
         <v>694</v>
       </c>
-      <c r="M19" s="9" t="s">
+      <c r="N19" s="25" t="s">
         <v>695</v>
       </c>
-      <c r="N19" s="25" t="s">
+      <c r="O19" s="25" t="s">
         <v>696</v>
       </c>
-      <c r="O19" s="25" t="s">
+      <c r="P19" s="25" t="s">
         <v>697</v>
-      </c>
-      <c r="P19" s="25" t="s">
-        <v>698</v>
       </c>
       <c r="Q19" s="29">
         <v>306107</v>
@@ -9542,40 +9544,40 @@
         <v>1</v>
       </c>
       <c r="D20" s="32" t="s">
+        <v>715</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>715</v>
+      </c>
+      <c r="F20" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="E20" s="32" t="s">
-        <v>716</v>
-      </c>
-      <c r="F20" s="33" t="s">
+      <c r="G20" s="27" t="s">
         <v>717</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="H20" s="28" t="s">
         <v>718</v>
       </c>
-      <c r="H20" s="28" t="s">
+      <c r="I20" s="15" t="s">
         <v>719</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>720</v>
       </c>
       <c r="K20" t="s">
         <v>84</v>
       </c>
       <c r="L20" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="M20" s="9" t="s">
         <v>694</v>
       </c>
-      <c r="M20" s="9" t="s">
+      <c r="N20" s="25" t="s">
         <v>695</v>
       </c>
-      <c r="N20" s="25" t="s">
+      <c r="O20" s="25" t="s">
         <v>696</v>
       </c>
-      <c r="O20" s="25" t="s">
+      <c r="P20" s="25" t="s">
         <v>697</v>
-      </c>
-      <c r="P20" s="25" t="s">
-        <v>698</v>
       </c>
       <c r="Q20" s="16">
         <v>30610001</v>
@@ -9589,22 +9591,22 @@
         <v>1</v>
       </c>
       <c r="D21" s="34" t="s">
+        <v>720</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>720</v>
+      </c>
+      <c r="F21" s="35" t="s">
         <v>721</v>
       </c>
-      <c r="E21" s="34" t="s">
-        <v>721</v>
-      </c>
-      <c r="F21" s="35" t="s">
+      <c r="G21" s="36" t="s">
         <v>722</v>
       </c>
-      <c r="G21" s="36" t="s">
+      <c r="H21" s="36" t="s">
         <v>723</v>
       </c>
-      <c r="H21" s="36" t="s">
+      <c r="I21" s="15" t="s">
         <v>724</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>725</v>
       </c>
       <c r="K21" t="s">
         <v>84</v>
@@ -9636,22 +9638,22 @@
         <v>1</v>
       </c>
       <c r="D22" s="31" t="s">
+        <v>725</v>
+      </c>
+      <c r="E22" s="31" t="s">
+        <v>725</v>
+      </c>
+      <c r="F22" s="40" t="s">
         <v>726</v>
       </c>
-      <c r="E22" s="31" t="s">
-        <v>726</v>
-      </c>
-      <c r="F22" s="40" t="s">
+      <c r="G22" s="40" t="s">
         <v>727</v>
       </c>
-      <c r="G22" s="40" t="s">
+      <c r="H22" s="40" t="s">
         <v>728</v>
       </c>
-      <c r="H22" s="40" t="s">
+      <c r="I22" s="15" t="s">
         <v>729</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>730</v>
       </c>
       <c r="K22" t="s">
         <v>84</v>
@@ -9683,22 +9685,22 @@
         <v>1</v>
       </c>
       <c r="D23" s="31" t="s">
+        <v>730</v>
+      </c>
+      <c r="E23" s="31" t="s">
         <v>731</v>
       </c>
-      <c r="E23" s="31" t="s">
+      <c r="F23" s="15" t="s">
         <v>732</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="G23" s="15" t="s">
         <v>733</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="H23" s="42" t="s">
         <v>734</v>
       </c>
-      <c r="H23" s="42" t="s">
+      <c r="I23" s="15" t="s">
         <v>735</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>736</v>
       </c>
       <c r="K23" t="s">
         <v>84</v>
@@ -9730,22 +9732,22 @@
         <v>1</v>
       </c>
       <c r="D24" s="31" t="s">
+        <v>736</v>
+      </c>
+      <c r="E24" s="31" t="s">
         <v>737</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="F24" s="15" t="s">
         <v>738</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="G24" s="43" t="s">
         <v>739</v>
       </c>
-      <c r="G24" s="43" t="s">
+      <c r="H24" s="43" t="s">
         <v>740</v>
       </c>
-      <c r="H24" s="43" t="s">
+      <c r="I24" s="15" t="s">
         <v>741</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>742</v>
       </c>
       <c r="K24" t="s">
         <v>84</v>
@@ -9777,40 +9779,40 @@
         <v>1</v>
       </c>
       <c r="D25" s="45" t="s">
+        <v>742</v>
+      </c>
+      <c r="E25" s="45" t="s">
         <v>743</v>
       </c>
-      <c r="E25" s="45" t="s">
+      <c r="F25" s="46" t="s">
         <v>744</v>
       </c>
-      <c r="F25" s="46" t="s">
+      <c r="G25" s="47" t="s">
         <v>745</v>
       </c>
-      <c r="G25" s="47" t="s">
+      <c r="H25" s="47" t="s">
         <v>746</v>
       </c>
-      <c r="H25" s="47" t="s">
+      <c r="I25" s="15" t="s">
         <v>747</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>748</v>
       </c>
       <c r="K25" t="s">
         <v>84</v>
       </c>
       <c r="L25" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="M25" s="9" t="s">
         <v>694</v>
       </c>
-      <c r="M25" s="9" t="s">
+      <c r="N25" s="25" t="s">
         <v>695</v>
       </c>
-      <c r="N25" s="25" t="s">
+      <c r="O25" s="25" t="s">
         <v>696</v>
       </c>
-      <c r="O25" s="25" t="s">
+      <c r="P25" s="25" t="s">
         <v>697</v>
-      </c>
-      <c r="P25" s="25" t="s">
-        <v>698</v>
       </c>
       <c r="Q25" s="16">
         <v>30610006</v>

--- a/source/bin/excel/audio.xlsx
+++ b/source/bin/excel/audio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5BD7F1-87D8-43F3-98F4-95BCA653086F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AFACC2-A8EE-4F60-ABC8-F01964A2B76A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="769">
   <si>
     <t>sheet</t>
   </si>
@@ -2369,6 +2369,14 @@
   </si>
   <si>
     <t>リーヒマ -Piano Version-</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>deco/effect_hupai/ron_25yh/ron_26daojian</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>deco/effect_lizhi/effect_liqi_25yh/effect_liqi_26daojian</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -2677,7 +2685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2791,6 +2799,11 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3118,7 +3131,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E415"/>
+  <dimension ref="A1:E417"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.875" customWidth="1"/>
@@ -8637,27 +8650,51 @@
         <v>114</v>
       </c>
     </row>
-    <row r="414" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B414" s="17">
+    <row r="414" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B414" s="53">
         <v>308046</v>
       </c>
-      <c r="C414" s="18" t="s">
+      <c r="C414" s="54" t="s">
         <v>596</v>
       </c>
-      <c r="D414" s="44"/>
-      <c r="E414" s="17" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="415" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B415" s="17">
+      <c r="D414" s="55"/>
+      <c r="E414" s="53" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="415" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B415" s="53">
         <v>308047</v>
       </c>
-      <c r="C415" s="18" t="s">
+      <c r="C415" s="54" t="s">
         <v>597</v>
       </c>
-      <c r="D415" s="44"/>
-      <c r="E415" s="17" t="s">
+      <c r="D415" s="55"/>
+      <c r="E415" s="53" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="416" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B416" s="53">
+        <v>308048</v>
+      </c>
+      <c r="C416" s="18" t="s">
+        <v>767</v>
+      </c>
+      <c r="D416" s="44"/>
+      <c r="E416" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="417" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B417" s="53">
+        <v>308049</v>
+      </c>
+      <c r="C417" s="18" t="s">
+        <v>768</v>
+      </c>
+      <c r="D417" s="44"/>
+      <c r="E417" s="17" t="s">
         <v>114</v>
       </c>
     </row>

--- a/source/bin/excel/audio.xlsx
+++ b/source/bin/excel/audio.xlsx
@@ -1,23 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AFACC2-A8EE-4F60-ABC8-F01964A2B76A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F9B814-59F5-45C6-8383-7BF11D7AFD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="1" r:id="rId1"/>
     <sheet name="audio" sheetId="2" r:id="rId2"/>
     <sheet name="bgm" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -49,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="779">
   <si>
     <t>sheet</t>
   </si>
@@ -1480,9 +1491,6 @@
     <t>2512打雪仗_bgm</t>
   </si>
   <si>
-    <t>ui/activity/extend/snowball/main/audio/2512dongri_bgm</t>
-  </si>
-  <si>
     <t>2512打雪仗_进入主界面时标题音效</t>
   </si>
   <si>
@@ -2075,9 +2083,6 @@
   </si>
   <si>
     <t>Bamboo</t>
-  </si>
-  <si>
-    <t>타케토리모노가타리</t>
   </si>
   <si>
     <t>music/game.mp3</t>
@@ -2372,11 +2377,56 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>deco/effect_hupai/ron_25yh/ron_26daojian</t>
+    <t>刀剑卡池切换页签</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>deco/effect_lizhi/effect_liqi_25yh/effect_liqi_26daojian</t>
+    <t>ui/lobby/main/audio/gacha_banner_dj</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>deco/effect_hupai/ron_26dj/ron_26dj</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>deco/effect_lizhi/effect_liqi_26dj/effect_liqi_26dj</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>죽림의 속삭임</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2604签到_打开签到</t>
+  </si>
+  <si>
+    <t>ui/activity/extend/2604dj_signin/main/audio/2604dj_signin_enter</t>
+  </si>
+  <si>
+    <t>2604签到_点领取</t>
+  </si>
+  <si>
+    <t>ui/activity/extend/snowball/main/audio/2512dongri_bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2604dj_signin/main/audio/2604dj_signin_claim</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2604dj/main/audio/2604dj_dungeon_bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2604剑域誓约_小镇bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2604剑域誓约_副本bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2604dj/main/audio/2604dj_village_bgm</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -2384,7 +2434,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2516,6 +2566,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="14">
@@ -2685,7 +2742,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2799,11 +2856,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3131,7 +3184,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E417"/>
+  <dimension ref="A1:E422"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.875" customWidth="1"/>
@@ -3822,28 +3875,28 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B58">
-        <v>201</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D58">
-        <v>2098</v>
+      <c r="A58" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="B58" s="29">
+        <v>157</v>
+      </c>
+      <c r="C58" s="30" t="s">
+        <v>766</v>
       </c>
       <c r="E58" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B59">
-        <v>202</v>
-      </c>
-      <c r="C59" t="s">
-        <v>85</v>
+        <v>201</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="D59">
-        <v>1000</v>
+        <v>2098</v>
       </c>
       <c r="E59" t="s">
         <v>84</v>
@@ -3851,10 +3904,10 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B60">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D60">
         <v>1000</v>
@@ -3865,10 +3918,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B61">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C61" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D61">
         <v>1000</v>
@@ -3879,10 +3932,10 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B62">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C62" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D62">
         <v>1000</v>
@@ -3893,13 +3946,13 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B63">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C63" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D63">
-        <v>1583</v>
+        <v>1000</v>
       </c>
       <c r="E63" t="s">
         <v>84</v>
@@ -3907,13 +3960,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B64">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C64" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D64">
-        <v>1000</v>
+        <v>1583</v>
       </c>
       <c r="E64" t="s">
         <v>84</v>
@@ -3921,13 +3974,13 @@
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B65">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C65" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D65">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="E65" t="s">
         <v>84</v>
@@ -3935,13 +3988,13 @@
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B66">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C66" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D66">
-        <v>1000</v>
+        <v>1105</v>
       </c>
       <c r="E66" t="s">
         <v>84</v>
@@ -3949,10 +4002,10 @@
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B67">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C67" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D67">
         <v>1000</v>
@@ -3963,13 +4016,13 @@
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B68">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C68" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D68">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="E68" t="s">
         <v>84</v>
@@ -3977,13 +4030,13 @@
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B69">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C69" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D69">
-        <v>1602</v>
+        <v>1105</v>
       </c>
       <c r="E69" t="s">
         <v>84</v>
@@ -3991,13 +4044,13 @@
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B70">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C70" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D70">
-        <v>2098</v>
+        <v>1602</v>
       </c>
       <c r="E70" t="s">
         <v>84</v>
@@ -4005,10 +4058,10 @@
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B71">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C71" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D71">
         <v>2098</v>
@@ -4019,13 +4072,13 @@
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B72">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C72" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D72">
-        <v>1000</v>
+        <v>2098</v>
       </c>
       <c r="E72" t="s">
         <v>84</v>
@@ -4033,10 +4086,10 @@
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B73">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C73" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D73">
         <v>1000</v>
@@ -4047,10 +4100,10 @@
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B74">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C74" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D74">
         <v>1000</v>
@@ -4061,13 +4114,13 @@
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B75">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C75" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D75">
-        <v>1714</v>
+        <v>1000</v>
       </c>
       <c r="E75" t="s">
         <v>84</v>
@@ -4075,13 +4128,13 @@
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B76">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C76" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D76">
-        <v>1000</v>
+        <v>1714</v>
       </c>
       <c r="E76" t="s">
         <v>84</v>
@@ -4089,10 +4142,10 @@
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B77">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C77" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D77">
         <v>1000</v>
@@ -4103,13 +4156,13 @@
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B78">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C78" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D78">
-        <v>1602</v>
+        <v>1000</v>
       </c>
       <c r="E78" t="s">
         <v>84</v>
@@ -4117,13 +4170,13 @@
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B79">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C79" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D79">
-        <v>1000</v>
+        <v>1602</v>
       </c>
       <c r="E79" t="s">
         <v>84</v>
@@ -4131,13 +4184,13 @@
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B80">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C80" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D80">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="E80" t="s">
         <v>84</v>
@@ -4145,13 +4198,13 @@
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B81">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C81" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D81">
-        <v>2098</v>
+        <v>1105</v>
       </c>
       <c r="E81" t="s">
         <v>84</v>
@@ -4159,13 +4212,13 @@
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B82">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C82" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D82">
-        <v>2206</v>
+        <v>2098</v>
       </c>
       <c r="E82" t="s">
         <v>84</v>
@@ -4173,13 +4226,13 @@
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B83">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C83" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D83">
-        <v>2098</v>
+        <v>2206</v>
       </c>
       <c r="E83" t="s">
         <v>84</v>
@@ -4187,13 +4240,13 @@
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B84">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C84" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D84">
-        <v>1031</v>
+        <v>2098</v>
       </c>
       <c r="E84" t="s">
         <v>84</v>
@@ -4201,13 +4254,13 @@
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B85">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C85" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D85">
-        <v>1000</v>
+        <v>1031</v>
       </c>
       <c r="E85" t="s">
         <v>84</v>
@@ -4215,10 +4268,10 @@
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B86">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C86" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D86">
         <v>1000</v>
@@ -4229,27 +4282,27 @@
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B87">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C87" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D87">
-        <v>1702</v>
+        <v>1000</v>
       </c>
       <c r="E87" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B88">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C88" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D88">
-        <v>2391</v>
+        <v>1702</v>
       </c>
       <c r="E88" t="s">
         <v>114</v>
@@ -4257,13 +4310,13 @@
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B89">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C89" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D89">
-        <v>2628</v>
+        <v>2391</v>
       </c>
       <c r="E89" t="s">
         <v>114</v>
@@ -4271,7 +4324,13 @@
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B90">
-        <v>233</v>
+        <v>232</v>
+      </c>
+      <c r="C90" t="s">
+        <v>116</v>
+      </c>
+      <c r="D90">
+        <v>2628</v>
       </c>
       <c r="E90" t="s">
         <v>114</v>
@@ -4279,7 +4338,7 @@
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B91">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E91" t="s">
         <v>114</v>
@@ -4287,13 +4346,7 @@
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B92">
-        <v>235</v>
-      </c>
-      <c r="C92" t="s">
-        <v>117</v>
-      </c>
-      <c r="D92">
-        <v>4051</v>
+        <v>234</v>
       </c>
       <c r="E92" t="s">
         <v>114</v>
@@ -4301,13 +4354,13 @@
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B93">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C93" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D93">
-        <v>1104</v>
+        <v>4051</v>
       </c>
       <c r="E93" t="s">
         <v>114</v>
@@ -4315,13 +4368,13 @@
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B94">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C94" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D94">
-        <v>2176</v>
+        <v>1104</v>
       </c>
       <c r="E94" t="s">
         <v>114</v>
@@ -4329,13 +4382,13 @@
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B95">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C95" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D95">
-        <v>4057</v>
+        <v>2176</v>
       </c>
       <c r="E95" t="s">
         <v>114</v>
@@ -4343,21 +4396,24 @@
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B96">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C96" t="s">
-        <v>121</v>
+        <v>120</v>
+      </c>
+      <c r="D96">
+        <v>4057</v>
       </c>
       <c r="E96" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B97">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C97" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E97" t="s">
         <v>84</v>
@@ -4365,21 +4421,21 @@
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B98">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C98" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E98" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B99">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C99" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E99" t="s">
         <v>114</v>
@@ -4387,10 +4443,10 @@
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B100">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C100" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E100" t="s">
         <v>114</v>
@@ -4398,10 +4454,10 @@
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B101">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C101" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E101" t="s">
         <v>114</v>
@@ -4409,10 +4465,10 @@
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B102">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C102" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E102" t="s">
         <v>114</v>
@@ -4420,10 +4476,10 @@
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B103">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C103" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E103" t="s">
         <v>114</v>
@@ -4431,27 +4487,24 @@
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B104">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C104" t="s">
-        <v>129</v>
-      </c>
-      <c r="D104">
-        <v>5434</v>
+        <v>128</v>
       </c>
       <c r="E104" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B105">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C105" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D105">
-        <v>5517</v>
+        <v>5434</v>
       </c>
       <c r="E105" t="s">
         <v>130</v>
@@ -4459,13 +4512,13 @@
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B106">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C106" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D106">
-        <v>5550</v>
+        <v>5517</v>
       </c>
       <c r="E106" t="s">
         <v>130</v>
@@ -4473,13 +4526,13 @@
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B107">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C107" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D107">
-        <v>5717</v>
+        <v>5550</v>
       </c>
       <c r="E107" t="s">
         <v>130</v>
@@ -4487,13 +4540,13 @@
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B108">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C108" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D108">
-        <v>5484</v>
+        <v>5717</v>
       </c>
       <c r="E108" t="s">
         <v>130</v>
@@ -4501,10 +4554,10 @@
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B109">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C109" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D109">
         <v>5484</v>
@@ -4515,13 +4568,13 @@
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B110">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C110" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D110">
-        <v>5350</v>
+        <v>5484</v>
       </c>
       <c r="E110" t="s">
         <v>130</v>
@@ -4529,13 +4582,13 @@
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B111">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C111" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D111">
-        <v>5217</v>
+        <v>5350</v>
       </c>
       <c r="E111" t="s">
         <v>130</v>
@@ -4543,13 +4596,13 @@
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B112">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C112" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D112">
-        <v>5650</v>
+        <v>5217</v>
       </c>
       <c r="E112" t="s">
         <v>130</v>
@@ -4557,10 +4610,10 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B113">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C113" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D113">
         <v>5650</v>
@@ -4571,13 +4624,13 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B114">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C114" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D114">
-        <v>5534</v>
+        <v>5650</v>
       </c>
       <c r="E114" t="s">
         <v>130</v>
@@ -4585,13 +4638,13 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B115">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C115" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D115">
-        <v>5800</v>
+        <v>5534</v>
       </c>
       <c r="E115" t="s">
         <v>130</v>
@@ -4599,13 +4652,13 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B116">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C116" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D116">
-        <v>5617</v>
+        <v>5800</v>
       </c>
       <c r="E116" t="s">
         <v>130</v>
@@ -4613,10 +4666,10 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B117">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C117" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D117">
         <v>5617</v>
@@ -4627,13 +4680,13 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B118">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D118">
-        <v>5550</v>
+        <v>5617</v>
       </c>
       <c r="E118" t="s">
         <v>130</v>
@@ -4641,10 +4694,13 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B119">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>145</v>
+        <v>144</v>
+      </c>
+      <c r="D119">
+        <v>5550</v>
       </c>
       <c r="E119" t="s">
         <v>130</v>
@@ -4652,21 +4708,21 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B120">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E120" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B121">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C121" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E121" t="s">
         <v>84</v>
@@ -4674,10 +4730,10 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B122">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C122" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E122" t="s">
         <v>84</v>
@@ -4685,41 +4741,38 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B123">
+        <v>265</v>
+      </c>
+      <c r="C123" t="s">
+        <v>148</v>
+      </c>
+      <c r="E123" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B124">
         <v>266</v>
       </c>
-      <c r="C123" s="15" t="s">
+      <c r="C124" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="D123">
+      <c r="D124">
         <v>30000</v>
       </c>
-      <c r="E123" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A124" s="15" t="s">
+      <c r="E124" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="B124">
+      <c r="B125">
         <v>8001</v>
       </c>
-      <c r="C124" s="15" t="s">
+      <c r="C125" s="15" t="s">
         <v>152</v>
-      </c>
-      <c r="E124" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
-        <v>153</v>
-      </c>
-      <c r="B125">
-        <v>8002</v>
-      </c>
-      <c r="C125" s="15" t="s">
-        <v>154</v>
       </c>
       <c r="E125" t="s">
         <v>150</v>
@@ -4727,27 +4780,27 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
+        <v>153</v>
+      </c>
+      <c r="B126">
+        <v>8002</v>
+      </c>
+      <c r="C126" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E126" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
         <v>155</v>
       </c>
-      <c r="B126">
+      <c r="B127">
         <v>8003</v>
       </c>
-      <c r="C126" s="15" t="s">
+      <c r="C127" s="15" t="s">
         <v>156</v>
-      </c>
-      <c r="E126" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A127" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="B127">
-        <v>10000</v>
-      </c>
-      <c r="C127" s="15" t="s">
-        <v>158</v>
       </c>
       <c r="E127" t="s">
         <v>150</v>
@@ -4755,13 +4808,13 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B128">
-        <v>10001</v>
+        <v>10000</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E128" t="s">
         <v>150</v>
@@ -4769,13 +4822,13 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="15" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B129">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E129" t="s">
         <v>150</v>
@@ -4783,13 +4836,13 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="15" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B130">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E130" t="s">
         <v>150</v>
@@ -4797,16 +4850,13 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B131">
-        <v>10101</v>
+        <v>10003</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="D131">
-        <v>7500</v>
+        <v>164</v>
       </c>
       <c r="E131" t="s">
         <v>150</v>
@@ -4814,16 +4864,16 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="15" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B132">
-        <v>10102</v>
+        <v>10101</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D132">
-        <v>73427</v>
+        <v>7500</v>
       </c>
       <c r="E132" t="s">
         <v>150</v>
@@ -4831,13 +4881,16 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B133">
-        <v>10103</v>
+        <v>10102</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>170</v>
+        <v>168</v>
+      </c>
+      <c r="D133">
+        <v>73427</v>
       </c>
       <c r="E133" t="s">
         <v>150</v>
@@ -4845,13 +4898,13 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B134">
-        <v>10104</v>
+        <v>10103</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E134" t="s">
         <v>150</v>
@@ -4859,13 +4912,13 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B135">
-        <v>10105</v>
+        <v>10104</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E135" t="s">
         <v>150</v>
@@ -4873,13 +4926,13 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B136">
-        <v>10106</v>
+        <v>10105</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E136" t="s">
         <v>150</v>
@@ -4887,13 +4940,13 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="15" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B137">
-        <v>10107</v>
+        <v>10106</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E137" t="s">
         <v>150</v>
@@ -4901,41 +4954,41 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="B138">
+        <v>10107</v>
+      </c>
+      <c r="C138" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="E138" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A139" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="B138">
+      <c r="B139">
         <v>10108</v>
       </c>
-      <c r="C138" s="15" t="s">
+      <c r="C139" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="E138" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="37" t="s">
+      <c r="E139" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="B139">
+      <c r="B140">
         <v>10109</v>
       </c>
-      <c r="C139" s="15" t="s">
+      <c r="C140" s="15" t="s">
         <v>182</v>
-      </c>
-      <c r="E139" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A140" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="B140">
-        <v>10110</v>
-      </c>
-      <c r="C140" s="15" t="s">
-        <v>184</v>
       </c>
       <c r="E140" t="s">
         <v>150</v>
@@ -4943,13 +4996,13 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="15" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B141">
-        <v>10111</v>
+        <v>10110</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E141" t="s">
         <v>150</v>
@@ -4957,13 +5010,13 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B142">
-        <v>10112</v>
+        <v>10111</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E142" t="s">
         <v>150</v>
@@ -4971,13 +5024,13 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B143">
-        <v>10113</v>
+        <v>10112</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E143" t="s">
         <v>150</v>
@@ -4985,13 +5038,13 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B144">
-        <v>10114</v>
+        <v>10113</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E144" t="s">
         <v>150</v>
@@ -4999,13 +5052,13 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B145">
-        <v>10115</v>
+        <v>10114</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E145" t="s">
         <v>150</v>
@@ -5013,13 +5066,13 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B146">
-        <v>10116</v>
+        <v>10115</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E146" t="s">
         <v>150</v>
@@ -5027,13 +5080,13 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="15" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B147">
-        <v>10117</v>
+        <v>10116</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E147" t="s">
         <v>150</v>
@@ -5041,16 +5094,13 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B148">
-        <v>10118</v>
+        <v>10117</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="D148" s="15">
-        <v>120048</v>
+        <v>198</v>
       </c>
       <c r="E148" t="s">
         <v>150</v>
@@ -5058,28 +5108,30 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B149">
-        <v>10119</v>
+        <v>10118</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="D149" s="15"/>
+        <v>200</v>
+      </c>
+      <c r="D149" s="15">
+        <v>120048</v>
+      </c>
       <c r="E149" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B150">
-        <v>10120</v>
+        <v>10119</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D150" s="15"/>
       <c r="E150" t="s">
@@ -5088,13 +5140,13 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B151">
-        <v>10121</v>
+        <v>10120</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D151" s="15"/>
       <c r="E151" t="s">
@@ -5103,13 +5155,13 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B152">
-        <v>10122</v>
+        <v>10121</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D152" s="15"/>
       <c r="E152" t="s">
@@ -5118,13 +5170,13 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="15" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="B153">
-        <v>10123</v>
+        <v>10122</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D153" s="15"/>
       <c r="E153" t="s">
@@ -5133,13 +5185,13 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="15" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="B154">
-        <v>10124</v>
+        <v>10123</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D154" s="15"/>
       <c r="E154" t="s">
@@ -5148,13 +5200,13 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="15" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B155">
-        <v>10125</v>
+        <v>10124</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D155" s="15"/>
       <c r="E155" t="s">
@@ -5163,13 +5215,13 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" s="15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B156">
-        <v>10126</v>
+        <v>10125</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D156" s="15"/>
       <c r="E156" t="s">
@@ -5178,13 +5230,13 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B157">
-        <v>10127</v>
+        <v>10126</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D157" s="15"/>
       <c r="E157" t="s">
@@ -5193,13 +5245,13 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="15" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B158">
-        <v>10128</v>
+        <v>10127</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D158" s="15"/>
       <c r="E158" t="s">
@@ -5208,45 +5260,45 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="B159" s="15">
-        <v>10129</v>
+        <v>218</v>
+      </c>
+      <c r="B159">
+        <v>10128</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="D159" s="15">
-        <v>65184</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="D159" s="15"/>
       <c r="E159" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B160" s="15">
-        <v>10130</v>
+        <v>10129</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="D160" s="15"/>
+        <v>221</v>
+      </c>
+      <c r="D160" s="15">
+        <v>65184</v>
+      </c>
       <c r="E160" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B161" s="15">
-        <v>10131</v>
+        <v>10130</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D161" s="15"/>
       <c r="E161" t="s">
@@ -5255,13 +5307,13 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B162" s="15">
-        <v>10132</v>
+        <v>10131</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D162" s="15"/>
       <c r="E162" t="s">
@@ -5270,13 +5322,13 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" s="15" t="s">
-        <v>175</v>
+        <v>226</v>
       </c>
       <c r="B163" s="15">
-        <v>10133</v>
+        <v>10132</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D163" s="15"/>
       <c r="E163" t="s">
@@ -5285,13 +5337,13 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="15" t="s">
-        <v>229</v>
+        <v>175</v>
       </c>
       <c r="B164" s="15">
-        <v>10134</v>
+        <v>10133</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D164" s="15"/>
       <c r="E164" t="s">
@@ -5300,13 +5352,13 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B165" s="15">
-        <v>10135</v>
+        <v>10134</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D165" s="15"/>
       <c r="E165" t="s">
@@ -5315,13 +5367,13 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="15" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B166" s="15">
-        <v>10136</v>
+        <v>10135</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D166" s="15"/>
       <c r="E166" t="s">
@@ -5330,33 +5382,31 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="B167" s="30">
-        <v>10137</v>
-      </c>
-      <c r="C167" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="D167" s="15">
-        <v>7500</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="B167" s="15">
+        <v>10136</v>
+      </c>
+      <c r="C167" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="D167" s="15"/>
       <c r="E167" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B168" s="30">
-        <v>10138</v>
+        <v>10137</v>
       </c>
       <c r="C168" s="30" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D168" s="15">
-        <v>73427</v>
+        <v>7500</v>
       </c>
       <c r="E168" t="s">
         <v>150</v>
@@ -5364,28 +5414,30 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B169" s="30">
-        <v>10139</v>
+        <v>10138</v>
       </c>
       <c r="C169" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="D169" s="15"/>
+        <v>168</v>
+      </c>
+      <c r="D169" s="15">
+        <v>73427</v>
+      </c>
       <c r="E169" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="15" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B170" s="30">
-        <v>10140</v>
+        <v>10139</v>
       </c>
       <c r="C170" s="30" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D170" s="15"/>
       <c r="E170" t="s">
@@ -5394,13 +5446,13 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" s="15" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B171" s="30">
-        <v>10141</v>
+        <v>10140</v>
       </c>
       <c r="C171" s="30" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D171" s="15"/>
       <c r="E171" t="s">
@@ -5409,13 +5461,13 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="15" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B172" s="30">
-        <v>10142</v>
+        <v>10141</v>
       </c>
       <c r="C172" s="30" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D172" s="15"/>
       <c r="E172" t="s">
@@ -5424,45 +5476,45 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="B173" s="41">
-        <v>10143</v>
-      </c>
-      <c r="C173" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D173" s="15">
-        <v>180000</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="B173" s="30">
+        <v>10142</v>
+      </c>
+      <c r="C173" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="D173" s="15"/>
       <c r="E173" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="15" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B174" s="41">
-        <v>10144</v>
+        <v>10143</v>
       </c>
       <c r="C174" s="41" t="s">
-        <v>248</v>
-      </c>
-      <c r="D174" s="15"/>
+        <v>246</v>
+      </c>
+      <c r="D174" s="15">
+        <v>180000</v>
+      </c>
       <c r="E174" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="15" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B175" s="41">
-        <v>10145</v>
+        <v>10144</v>
       </c>
       <c r="C175" s="41" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D175" s="15"/>
       <c r="E175" t="s">
@@ -5471,13 +5523,13 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="15" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B176" s="41">
-        <v>10146</v>
+        <v>10145</v>
       </c>
       <c r="C176" s="41" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D176" s="15"/>
       <c r="E176" t="s">
@@ -5486,13 +5538,13 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="15" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B177" s="41">
-        <v>10147</v>
+        <v>10146</v>
       </c>
       <c r="C177" s="41" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D177" s="15"/>
       <c r="E177" t="s">
@@ -5501,13 +5553,13 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="15" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B178" s="41">
-        <v>10148</v>
+        <v>10147</v>
       </c>
       <c r="C178" s="41" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D178" s="15"/>
       <c r="E178" t="s">
@@ -5516,13 +5568,13 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B179" s="41">
-        <v>10149</v>
+        <v>10148</v>
       </c>
       <c r="C179" s="41" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D179" s="15"/>
       <c r="E179" t="s">
@@ -5531,13 +5583,13 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="15" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B180" s="41">
-        <v>10150</v>
+        <v>10149</v>
       </c>
       <c r="C180" s="41" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D180" s="15"/>
       <c r="E180" t="s">
@@ -5546,13 +5598,13 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B181" s="41">
-        <v>10151</v>
+        <v>10150</v>
       </c>
       <c r="C181" s="41" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D181" s="15"/>
       <c r="E181" t="s">
@@ -5561,13 +5613,13 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="15" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B182" s="41">
-        <v>10152</v>
+        <v>10151</v>
       </c>
       <c r="C182" s="41" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D182" s="15"/>
       <c r="E182" t="s">
@@ -5576,13 +5628,13 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="15" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B183" s="41">
-        <v>10153</v>
+        <v>10152</v>
       </c>
       <c r="C183" s="41" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D183" s="15"/>
       <c r="E183" t="s">
@@ -5591,13 +5643,13 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B184" s="41">
-        <v>10154</v>
+        <v>10153</v>
       </c>
       <c r="C184" s="41" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D184" s="15"/>
       <c r="E184" t="s">
@@ -5606,13 +5658,13 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="15" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B185" s="41">
-        <v>10155</v>
+        <v>10154</v>
       </c>
       <c r="C185" s="41" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D185" s="15"/>
       <c r="E185" t="s">
@@ -5621,13 +5673,13 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="15" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B186" s="41">
-        <v>10156</v>
+        <v>10155</v>
       </c>
       <c r="C186" s="41" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D186" s="15"/>
       <c r="E186" t="s">
@@ -5636,13 +5688,13 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="15" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B187" s="41">
-        <v>10157</v>
+        <v>10156</v>
       </c>
       <c r="C187" s="41" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D187" s="15"/>
       <c r="E187" t="s">
@@ -5651,13 +5703,13 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B188" s="41">
-        <v>10158</v>
+        <v>10157</v>
       </c>
       <c r="C188" s="41" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D188" s="15"/>
       <c r="E188" t="s">
@@ -5666,13 +5718,13 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B189" s="41">
-        <v>10159</v>
+        <v>10158</v>
       </c>
       <c r="C189" s="41" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D189" s="15"/>
       <c r="E189" t="s">
@@ -5681,13 +5733,13 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B190" s="41">
-        <v>10160</v>
+        <v>10159</v>
       </c>
       <c r="C190" s="41" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D190" s="15"/>
       <c r="E190" t="s">
@@ -5696,13 +5748,13 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="15" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B191" s="41">
-        <v>10161</v>
+        <v>10160</v>
       </c>
       <c r="C191" s="41" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D191" s="15"/>
       <c r="E191" t="s">
@@ -5711,13 +5763,13 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="15" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B192" s="41">
-        <v>10162</v>
+        <v>10161</v>
       </c>
       <c r="C192" s="41" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D192" s="15"/>
       <c r="E192" t="s">
@@ -5726,13 +5778,13 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" s="15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B193" s="41">
-        <v>10163</v>
+        <v>10162</v>
       </c>
       <c r="C193" s="41" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D193" s="15"/>
       <c r="E193" t="s">
@@ -5741,13 +5793,13 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="15" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B194" s="41">
-        <v>10164</v>
+        <v>10163</v>
       </c>
       <c r="C194" s="41" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D194" s="15"/>
       <c r="E194" t="s">
@@ -5756,13 +5808,13 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="15" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B195" s="41">
-        <v>10165</v>
+        <v>10164</v>
       </c>
       <c r="C195" s="41" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D195" s="15"/>
       <c r="E195" t="s">
@@ -5771,13 +5823,13 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="15" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B196" s="41">
-        <v>10166</v>
+        <v>10165</v>
       </c>
       <c r="C196" s="41" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D196" s="15"/>
       <c r="E196" t="s">
@@ -5786,13 +5838,13 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="15" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B197" s="41">
-        <v>10167</v>
+        <v>10166</v>
       </c>
       <c r="C197" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D197" s="15"/>
       <c r="E197" t="s">
@@ -5801,13 +5853,13 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="15" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B198" s="41">
-        <v>10168</v>
+        <v>10167</v>
       </c>
       <c r="C198" s="41" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D198" s="15"/>
       <c r="E198" t="s">
@@ -5816,13 +5868,13 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="15" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B199" s="41">
-        <v>10169</v>
+        <v>10168</v>
       </c>
       <c r="C199" s="41" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D199" s="15"/>
       <c r="E199" t="s">
@@ -5831,13 +5883,13 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="15" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B200" s="41">
-        <v>10170</v>
+        <v>10169</v>
       </c>
       <c r="C200" s="41" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D200" s="15"/>
       <c r="E200" t="s">
@@ -5846,45 +5898,45 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" s="15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B201" s="41">
-        <v>10171</v>
+        <v>10170</v>
       </c>
       <c r="C201" s="41" t="s">
-        <v>302</v>
-      </c>
-      <c r="D201" s="15">
-        <v>76000</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="D201" s="15"/>
       <c r="E201" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="15" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B202" s="41">
-        <v>10172</v>
+        <v>10171</v>
       </c>
       <c r="C202" s="41" t="s">
-        <v>304</v>
-      </c>
-      <c r="D202" s="15"/>
+        <v>302</v>
+      </c>
+      <c r="D202" s="15">
+        <v>76000</v>
+      </c>
       <c r="E202" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="15" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B203" s="41">
-        <v>10173</v>
+        <v>10172</v>
       </c>
       <c r="C203" s="41" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D203" s="15"/>
       <c r="E203" t="s">
@@ -5893,13 +5945,13 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B204" s="41">
-        <v>10174</v>
+        <v>10173</v>
       </c>
       <c r="C204" s="41" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D204" s="15"/>
       <c r="E204" t="s">
@@ -5908,13 +5960,13 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" s="15" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B205" s="41">
-        <v>10175</v>
+        <v>10174</v>
       </c>
       <c r="C205" s="41" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D205" s="15"/>
       <c r="E205" t="s">
@@ -5923,13 +5975,13 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" s="15" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B206" s="41">
-        <v>10176</v>
+        <v>10175</v>
       </c>
       <c r="C206" s="41" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D206" s="15"/>
       <c r="E206" t="s">
@@ -5938,13 +5990,13 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" s="15" t="s">
-        <v>175</v>
+        <v>311</v>
       </c>
       <c r="B207" s="41">
-        <v>10177</v>
+        <v>10176</v>
       </c>
       <c r="C207" s="41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D207" s="15"/>
       <c r="E207" t="s">
@@ -5953,13 +6005,13 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" s="15" t="s">
-        <v>314</v>
+        <v>175</v>
       </c>
       <c r="B208" s="41">
-        <v>10178</v>
+        <v>10177</v>
       </c>
       <c r="C208" s="41" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D208" s="15"/>
       <c r="E208" t="s">
@@ -5968,13 +6020,13 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" s="15" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B209" s="41">
-        <v>10179</v>
+        <v>10178</v>
       </c>
       <c r="C209" s="41" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D209" s="15"/>
       <c r="E209" t="s">
@@ -5983,13 +6035,13 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" s="15" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B210" s="41">
-        <v>10180</v>
+        <v>10179</v>
       </c>
       <c r="C210" s="41" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D210" s="15"/>
       <c r="E210" t="s">
@@ -5998,13 +6050,13 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" s="15" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B211" s="41">
-        <v>10181</v>
+        <v>10180</v>
       </c>
       <c r="C211" s="41" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D211" s="15"/>
       <c r="E211" t="s">
@@ -6013,13 +6065,13 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" s="15" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B212" s="41">
-        <v>10182</v>
+        <v>10181</v>
       </c>
       <c r="C212" s="41" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D212" s="15"/>
       <c r="E212" t="s">
@@ -6028,13 +6080,13 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" s="15" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B213" s="41">
-        <v>10183</v>
+        <v>10182</v>
       </c>
       <c r="C213" s="41" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D213" s="15"/>
       <c r="E213" t="s">
@@ -6043,13 +6095,13 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" s="15" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B214" s="41">
-        <v>10184</v>
+        <v>10183</v>
       </c>
       <c r="C214" s="41" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D214" s="15"/>
       <c r="E214" t="s">
@@ -6058,13 +6110,13 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B215" s="41">
-        <v>10185</v>
+        <v>10184</v>
       </c>
       <c r="C215" s="41" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D215" s="15"/>
       <c r="E215" t="s">
@@ -6073,13 +6125,13 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" s="15" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B216" s="41">
-        <v>10186</v>
+        <v>10185</v>
       </c>
       <c r="C216" s="41" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D216" s="15"/>
       <c r="E216" t="s">
@@ -6088,13 +6140,13 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" s="15" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B217" s="41">
-        <v>10187</v>
+        <v>10186</v>
       </c>
       <c r="C217" s="41" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D217" s="15"/>
       <c r="E217" t="s">
@@ -6103,13 +6155,13 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" s="15" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B218" s="41">
-        <v>10188</v>
+        <v>10187</v>
       </c>
       <c r="C218" s="41" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D218" s="15"/>
       <c r="E218" t="s">
@@ -6118,13 +6170,13 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" s="15" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B219" s="41">
-        <v>10189</v>
+        <v>10188</v>
       </c>
       <c r="C219" s="41" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D219" s="15"/>
       <c r="E219" t="s">
@@ -6133,45 +6185,45 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" s="15" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B220" s="41">
-        <v>10190</v>
+        <v>10189</v>
       </c>
       <c r="C220" s="41" t="s">
-        <v>339</v>
-      </c>
-      <c r="D220" s="15">
-        <v>174000</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="D220" s="15"/>
       <c r="E220" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" s="15" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B221" s="41">
-        <v>10191</v>
+        <v>10190</v>
       </c>
       <c r="C221" s="41" t="s">
-        <v>341</v>
-      </c>
-      <c r="D221" s="15"/>
+        <v>339</v>
+      </c>
+      <c r="D221" s="15">
+        <v>174000</v>
+      </c>
       <c r="E221" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" s="15" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B222" s="41">
-        <v>10192</v>
+        <v>10191</v>
       </c>
       <c r="C222" s="41" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D222" s="15"/>
       <c r="E222" t="s">
@@ -6180,13 +6232,13 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" s="15" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B223" s="41">
-        <v>10193</v>
+        <v>10192</v>
       </c>
       <c r="C223" s="41" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D223" s="15"/>
       <c r="E223" t="s">
@@ -6195,13 +6247,13 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" s="15" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B224" s="41">
-        <v>10194</v>
+        <v>10193</v>
       </c>
       <c r="C224" s="41" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D224" s="15"/>
       <c r="E224" t="s">
@@ -6210,13 +6262,13 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" s="15" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B225" s="41">
-        <v>10195</v>
+        <v>10194</v>
       </c>
       <c r="C225" s="41" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D225" s="15"/>
       <c r="E225" t="s">
@@ -6225,45 +6277,45 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" s="15" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B226" s="41">
-        <v>10300</v>
+        <v>10195</v>
       </c>
       <c r="C226" s="41" t="s">
-        <v>351</v>
-      </c>
-      <c r="D226" s="15">
-        <v>63000</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="D226" s="15"/>
       <c r="E226" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" s="15" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B227" s="41">
-        <v>10301</v>
+        <v>10300</v>
       </c>
       <c r="C227" s="41" t="s">
-        <v>353</v>
-      </c>
-      <c r="D227" s="15"/>
+        <v>351</v>
+      </c>
+      <c r="D227" s="15">
+        <v>63000</v>
+      </c>
       <c r="E227" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" s="15" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B228" s="41">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="C228" s="41" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D228" s="15"/>
       <c r="E228" t="s">
@@ -6272,13 +6324,13 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" s="15" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B229" s="41">
-        <v>10303</v>
+        <v>10302</v>
       </c>
       <c r="C229" s="41" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D229" s="15"/>
       <c r="E229" t="s">
@@ -6287,13 +6339,13 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" s="15" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B230" s="41">
-        <v>10304</v>
+        <v>10303</v>
       </c>
       <c r="C230" s="41" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D230" s="15"/>
       <c r="E230" t="s">
@@ -6302,13 +6354,13 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" s="15" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B231" s="41">
-        <v>10305</v>
+        <v>10304</v>
       </c>
       <c r="C231" s="41" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D231" s="15"/>
       <c r="E231" t="s">
@@ -6317,13 +6369,13 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" s="15" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B232" s="41">
-        <v>10306</v>
+        <v>10305</v>
       </c>
       <c r="C232" s="41" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D232" s="15"/>
       <c r="E232" t="s">
@@ -6332,13 +6384,13 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" s="15" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B233" s="41">
-        <v>10307</v>
+        <v>10306</v>
       </c>
       <c r="C233" s="41" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D233" s="15"/>
       <c r="E233" t="s">
@@ -6347,13 +6399,13 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" s="15" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B234" s="41">
-        <v>10308</v>
+        <v>10307</v>
       </c>
       <c r="C234" s="41" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D234" s="15"/>
       <c r="E234" t="s">
@@ -6362,13 +6414,13 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B235" s="41">
-        <v>10309</v>
+        <v>10308</v>
       </c>
       <c r="C235" s="41" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D235" s="15"/>
       <c r="E235" t="s">
@@ -6377,13 +6429,13 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B236" s="41">
-        <v>10310</v>
+        <v>10309</v>
       </c>
       <c r="C236" s="41" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D236" s="15"/>
       <c r="E236" t="s">
@@ -6392,13 +6444,13 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" s="15" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B237" s="41">
-        <v>10311</v>
+        <v>10310</v>
       </c>
       <c r="C237" s="41" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D237" s="15"/>
       <c r="E237" t="s">
@@ -6407,13 +6459,13 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" s="15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B238" s="41">
-        <v>10312</v>
+        <v>10311</v>
       </c>
       <c r="C238" s="41" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D238" s="15"/>
       <c r="E238" t="s">
@@ -6422,13 +6474,13 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" s="15" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B239" s="41">
-        <v>10313</v>
+        <v>10312</v>
       </c>
       <c r="C239" s="41" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D239" s="15"/>
       <c r="E239" t="s">
@@ -6437,13 +6489,13 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" s="15" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B240" s="41">
-        <v>10314</v>
+        <v>10313</v>
       </c>
       <c r="C240" s="41" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D240" s="15"/>
       <c r="E240" t="s">
@@ -6452,13 +6504,13 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B241" s="41">
-        <v>10315</v>
+        <v>10314</v>
       </c>
       <c r="C241" s="41" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D241" s="15"/>
       <c r="E241" t="s">
@@ -6467,13 +6519,13 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" s="15" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B242" s="41">
-        <v>10316</v>
+        <v>10315</v>
       </c>
       <c r="C242" s="41" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D242" s="15"/>
       <c r="E242" t="s">
@@ -6482,13 +6534,13 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" s="15" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B243" s="41">
-        <v>10317</v>
+        <v>10316</v>
       </c>
       <c r="C243" s="41" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D243" s="15"/>
       <c r="E243" t="s">
@@ -6497,13 +6549,13 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" s="15" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B244" s="41">
-        <v>10318</v>
+        <v>10317</v>
       </c>
       <c r="C244" s="41" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D244" s="15"/>
       <c r="E244" t="s">
@@ -6512,13 +6564,13 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" s="15" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B245" s="41">
-        <v>10319</v>
+        <v>10318</v>
       </c>
       <c r="C245" s="41" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D245" s="15"/>
       <c r="E245" t="s">
@@ -6527,13 +6579,13 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" s="15" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B246" s="41">
-        <v>10320</v>
+        <v>10319</v>
       </c>
       <c r="C246" s="41" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D246" s="15"/>
       <c r="E246" t="s">
@@ -6542,13 +6594,13 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" s="15" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B247" s="41">
-        <v>10321</v>
+        <v>10320</v>
       </c>
       <c r="C247" s="41" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D247" s="15"/>
       <c r="E247" t="s">
@@ -6557,13 +6609,13 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" s="15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B248" s="41">
-        <v>10322</v>
+        <v>10321</v>
       </c>
       <c r="C248" s="41" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D248" s="15"/>
       <c r="E248" t="s">
@@ -6572,13 +6624,13 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" s="15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B249" s="41">
-        <v>10323</v>
+        <v>10322</v>
       </c>
       <c r="C249" s="41" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D249" s="15"/>
       <c r="E249" t="s">
@@ -6587,13 +6639,13 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" s="15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B250" s="41">
-        <v>10324</v>
+        <v>10323</v>
       </c>
       <c r="C250" s="41" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D250" s="15"/>
       <c r="E250" t="s">
@@ -6602,13 +6654,13 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" s="15" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B251" s="41">
-        <v>10325</v>
+        <v>10324</v>
       </c>
       <c r="C251" s="41" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D251" s="15"/>
       <c r="E251" t="s">
@@ -6617,13 +6669,13 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" s="15" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B252" s="41">
-        <v>10326</v>
+        <v>10325</v>
       </c>
       <c r="C252" s="41" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D252" s="15"/>
       <c r="E252" t="s">
@@ -6632,13 +6684,13 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" s="15" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B253" s="41">
-        <v>10327</v>
+        <v>10326</v>
       </c>
       <c r="C253" s="41" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D253" s="15"/>
       <c r="E253" t="s">
@@ -6647,13 +6699,13 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" s="15" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B254" s="41">
-        <v>10328</v>
+        <v>10327</v>
       </c>
       <c r="C254" s="41" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D254" s="15"/>
       <c r="E254" t="s">
@@ -6662,13 +6714,13 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" s="15" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B255" s="41">
-        <v>10329</v>
+        <v>10328</v>
       </c>
       <c r="C255" s="41" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D255" s="15"/>
       <c r="E255" t="s">
@@ -6677,13 +6729,13 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256" s="15" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B256" s="41">
-        <v>10330</v>
+        <v>10329</v>
       </c>
       <c r="C256" s="41" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D256" s="15"/>
       <c r="E256" t="s">
@@ -6692,30 +6744,28 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257" s="15" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B257" s="41">
-        <v>10331</v>
+        <v>10330</v>
       </c>
       <c r="C257" s="41" t="s">
-        <v>413</v>
-      </c>
-      <c r="D257" s="15">
-        <v>60000</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="D257" s="15"/>
       <c r="E257" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" s="15" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B258" s="41">
-        <v>10332</v>
+        <v>10331</v>
       </c>
       <c r="C258" s="41" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D258" s="15">
         <v>60000</v>
@@ -6726,28 +6776,30 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" s="15" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B259" s="41">
-        <v>10333</v>
+        <v>10332</v>
       </c>
       <c r="C259" s="41" t="s">
-        <v>417</v>
-      </c>
-      <c r="D259" s="15"/>
+        <v>415</v>
+      </c>
+      <c r="D259" s="15">
+        <v>60000</v>
+      </c>
       <c r="E259" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" s="15" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B260" s="41">
-        <v>10334</v>
+        <v>10333</v>
       </c>
       <c r="C260" s="41" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D260" s="15"/>
       <c r="E260" t="s">
@@ -6756,13 +6808,13 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" s="15" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B261" s="41">
-        <v>10335</v>
+        <v>10334</v>
       </c>
       <c r="C261" s="41" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D261" s="15"/>
       <c r="E261" t="s">
@@ -6771,13 +6823,13 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" s="15" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B262" s="41">
-        <v>10336</v>
+        <v>10335</v>
       </c>
       <c r="C262" s="41" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D262" s="15"/>
       <c r="E262" t="s">
@@ -6786,13 +6838,13 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" s="15" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B263" s="41">
-        <v>10337</v>
+        <v>10336</v>
       </c>
       <c r="C263" s="41" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D263" s="15"/>
       <c r="E263" t="s">
@@ -6801,13 +6853,13 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" s="15" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B264" s="41">
-        <v>10338</v>
+        <v>10337</v>
       </c>
       <c r="C264" s="41" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D264" s="15"/>
       <c r="E264" t="s">
@@ -6816,13 +6868,13 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" s="15" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B265" s="41">
-        <v>10339</v>
+        <v>10338</v>
       </c>
       <c r="C265" s="41" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D265" s="15"/>
       <c r="E265" t="s">
@@ -6831,13 +6883,13 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" s="15" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B266" s="41">
-        <v>10340</v>
+        <v>10339</v>
       </c>
       <c r="C266" s="41" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D266" s="15"/>
       <c r="E266" t="s">
@@ -6846,13 +6898,13 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" s="15" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B267" s="41">
-        <v>10341</v>
+        <v>10340</v>
       </c>
       <c r="C267" s="41" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D267" s="15"/>
       <c r="E267" t="s">
@@ -6861,43 +6913,43 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" s="15" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B268" s="41">
-        <v>10342</v>
+        <v>10341</v>
       </c>
       <c r="C268" s="41" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D268" s="15"/>
-      <c r="E268" s="15" t="s">
+      <c r="E268" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" s="15" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B269" s="41">
-        <v>10350</v>
+        <v>10342</v>
       </c>
       <c r="C269" s="41" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D269" s="15"/>
-      <c r="E269" t="s">
+      <c r="E269" s="15" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" s="15" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B270" s="41">
-        <v>10351</v>
+        <v>10350</v>
       </c>
       <c r="C270" s="41" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D270" s="15"/>
       <c r="E270" t="s">
@@ -6906,13 +6958,13 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" s="15" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B271" s="41">
-        <v>10352</v>
+        <v>10351</v>
       </c>
       <c r="C271" s="41" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D271" s="15"/>
       <c r="E271" t="s">
@@ -6921,13 +6973,13 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" s="15" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B272" s="41">
-        <v>10353</v>
+        <v>10352</v>
       </c>
       <c r="C272" s="41" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D272" s="15"/>
       <c r="E272" t="s">
@@ -6936,13 +6988,13 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" s="15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B273" s="41">
-        <v>10354</v>
+        <v>10353</v>
       </c>
       <c r="C273" s="41" t="s">
-        <v>383</v>
+        <v>443</v>
       </c>
       <c r="D273" s="15"/>
       <c r="E273" t="s">
@@ -6951,13 +7003,13 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274" s="15" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B274" s="41">
-        <v>10355</v>
+        <v>10354</v>
       </c>
       <c r="C274" s="41" t="s">
-        <v>446</v>
+        <v>383</v>
       </c>
       <c r="D274" s="15"/>
       <c r="E274" t="s">
@@ -6966,13 +7018,13 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A275" s="15" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B275" s="41">
-        <v>10356</v>
+        <v>10355</v>
       </c>
       <c r="C275" s="41" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D275" s="15"/>
       <c r="E275" t="s">
@@ -6981,13 +7033,13 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276" s="15" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B276" s="41">
-        <v>10357</v>
+        <v>10356</v>
       </c>
       <c r="C276" s="41" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D276" s="15"/>
       <c r="E276" t="s">
@@ -6996,13 +7048,13 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277" s="15" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B277" s="41">
-        <v>10358</v>
+        <v>10357</v>
       </c>
       <c r="C277" s="41" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D277" s="15"/>
       <c r="E277" t="s">
@@ -7011,13 +7063,13 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" s="15" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B278" s="41">
-        <v>10359</v>
+        <v>10358</v>
       </c>
       <c r="C278" s="41" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D278" s="15"/>
       <c r="E278" t="s">
@@ -7026,13 +7078,13 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" s="15" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B279" s="41">
-        <v>10360</v>
+        <v>10359</v>
       </c>
       <c r="C279" s="41" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D279" s="15"/>
       <c r="E279" t="s">
@@ -7041,13 +7093,13 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280" s="15" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B280" s="41">
-        <v>10361</v>
+        <v>10360</v>
       </c>
       <c r="C280" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D280" s="15"/>
       <c r="E280" t="s">
@@ -7056,13 +7108,13 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A281" s="15" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B281" s="41">
-        <v>10362</v>
+        <v>10361</v>
       </c>
       <c r="C281" s="41" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D281" s="15"/>
       <c r="E281" t="s">
@@ -7071,13 +7123,13 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A282" s="15" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B282" s="41">
-        <v>10363</v>
+        <v>10362</v>
       </c>
       <c r="C282" s="41" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D282" s="15"/>
       <c r="E282" t="s">
@@ -7086,13 +7138,13 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A283" s="15" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B283" s="41">
-        <v>10364</v>
+        <v>10363</v>
       </c>
       <c r="C283" s="41" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D283" s="15"/>
       <c r="E283" t="s">
@@ -7101,13 +7153,13 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A284" s="15" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B284" s="41">
-        <v>10365</v>
+        <v>10364</v>
       </c>
       <c r="C284" s="41" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D284" s="15"/>
       <c r="E284" t="s">
@@ -7116,13 +7168,13 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A285" s="15" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B285" s="41">
-        <v>10366</v>
+        <v>10365</v>
       </c>
       <c r="C285" s="41" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D285" s="15"/>
       <c r="E285" t="s">
@@ -7131,13 +7183,13 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A286" s="15" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B286" s="41">
-        <v>10367</v>
+        <v>10366</v>
       </c>
       <c r="C286" s="41" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D286" s="15"/>
       <c r="E286" t="s">
@@ -7146,13 +7198,13 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A287" s="15" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B287" s="41">
-        <v>10368</v>
+        <v>10367</v>
       </c>
       <c r="C287" s="41" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D287" s="15"/>
       <c r="E287" t="s">
@@ -7161,13 +7213,13 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A288" s="15" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B288" s="41">
-        <v>10369</v>
+        <v>10368</v>
       </c>
       <c r="C288" s="41" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D288" s="15"/>
       <c r="E288" t="s">
@@ -7176,13 +7228,13 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" s="15" t="s">
-        <v>475</v>
-      </c>
-      <c r="B289" s="15">
-        <v>10370</v>
-      </c>
-      <c r="C289" s="15" t="s">
-        <v>476</v>
+        <v>473</v>
+      </c>
+      <c r="B289" s="41">
+        <v>10369</v>
+      </c>
+      <c r="C289" s="41" t="s">
+        <v>474</v>
       </c>
       <c r="D289" s="15"/>
       <c r="E289" t="s">
@@ -7191,13 +7243,13 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" s="15" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B290" s="15">
-        <v>10371</v>
+        <v>10370</v>
       </c>
       <c r="C290" s="15" t="s">
-        <v>478</v>
+        <v>773</v>
       </c>
       <c r="D290" s="15"/>
       <c r="E290" t="s">
@@ -7206,13 +7258,13 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" s="15" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B291" s="15">
-        <v>10372</v>
+        <v>10371</v>
       </c>
       <c r="C291" s="15" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D291" s="15"/>
       <c r="E291" t="s">
@@ -7221,13 +7273,13 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292" s="15" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B292" s="15">
-        <v>10373</v>
+        <v>10372</v>
       </c>
       <c r="C292" s="15" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D292" s="15"/>
       <c r="E292" t="s">
@@ -7236,13 +7288,13 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293" s="15" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B293" s="15">
-        <v>10374</v>
+        <v>10373</v>
       </c>
       <c r="C293" s="15" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D293" s="15"/>
       <c r="E293" t="s">
@@ -7251,13 +7303,13 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294" s="15" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B294" s="15">
-        <v>10375</v>
+        <v>10374</v>
       </c>
       <c r="C294" s="15" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D294" s="15"/>
       <c r="E294" t="s">
@@ -7266,13 +7318,13 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A295" s="15" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B295" s="15">
-        <v>10376</v>
+        <v>10375</v>
       </c>
       <c r="C295" s="15" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D295" s="15"/>
       <c r="E295" t="s">
@@ -7281,13 +7333,13 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A296" s="15" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B296" s="15">
-        <v>10377</v>
+        <v>10376</v>
       </c>
       <c r="C296" s="15" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D296" s="15"/>
       <c r="E296" t="s">
@@ -7296,13 +7348,13 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A297" s="15" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B297" s="15">
-        <v>10378</v>
+        <v>10377</v>
       </c>
       <c r="C297" s="15" t="s">
-        <v>204</v>
+        <v>489</v>
       </c>
       <c r="D297" s="15"/>
       <c r="E297" t="s">
@@ -7311,13 +7363,13 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A298" s="15" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B298" s="15">
-        <v>10379</v>
+        <v>10378</v>
       </c>
       <c r="C298" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D298" s="15"/>
       <c r="E298" t="s">
@@ -7326,13 +7378,13 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299" s="15" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B299" s="15">
-        <v>10380</v>
+        <v>10379</v>
       </c>
       <c r="C299" s="15" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D299" s="15"/>
       <c r="E299" t="s">
@@ -7340,14 +7392,14 @@
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A300" s="52" t="s">
-        <v>750</v>
-      </c>
-      <c r="B300" s="52">
-        <v>10381</v>
+      <c r="A300" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="B300" s="15">
+        <v>10380</v>
       </c>
       <c r="C300" s="15" t="s">
-        <v>758</v>
+        <v>225</v>
       </c>
       <c r="D300" s="15"/>
       <c r="E300" t="s">
@@ -7356,13 +7408,13 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" s="52" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B301" s="52">
-        <v>10382</v>
+        <v>10381</v>
       </c>
       <c r="C301" s="15" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="D301" s="15"/>
       <c r="E301" t="s">
@@ -7371,13 +7423,13 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" s="52" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B302" s="52">
-        <v>10383</v>
+        <v>10382</v>
       </c>
       <c r="C302" s="15" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="D302" s="15"/>
       <c r="E302" t="s">
@@ -7386,13 +7438,13 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" s="52" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="B303" s="52">
-        <v>10384</v>
+        <v>10383</v>
       </c>
       <c r="C303" s="15" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="D303" s="15"/>
       <c r="E303" t="s">
@@ -7401,13 +7453,13 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304" s="52" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B304" s="52">
-        <v>10385</v>
+        <v>10384</v>
       </c>
       <c r="C304" s="15" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D304" s="15"/>
       <c r="E304" t="s">
@@ -7416,13 +7468,13 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305" s="52" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B305" s="52">
-        <v>10386</v>
+        <v>10385</v>
       </c>
       <c r="C305" s="15" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="D305" s="15"/>
       <c r="E305" t="s">
@@ -7431,13 +7483,13 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" s="52" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B306" s="52">
-        <v>10387</v>
+        <v>10386</v>
       </c>
       <c r="C306" s="15" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D306" s="15"/>
       <c r="E306" t="s">
@@ -7446,13 +7498,13 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" s="52" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B307" s="52">
-        <v>10388</v>
+        <v>10387</v>
       </c>
       <c r="C307" s="15" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D307" s="15"/>
       <c r="E307" t="s">
@@ -7460,84 +7512,89 @@
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B308">
-        <v>305032</v>
-      </c>
-      <c r="C308" t="s">
-        <v>494</v>
-      </c>
-      <c r="D308">
-        <v>1314</v>
-      </c>
+      <c r="A308" s="52" t="s">
+        <v>755</v>
+      </c>
+      <c r="B308" s="52">
+        <v>10388</v>
+      </c>
+      <c r="C308" s="15" t="s">
+        <v>758</v>
+      </c>
+      <c r="D308" s="15"/>
       <c r="E308" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B309">
-        <v>305033</v>
-      </c>
-      <c r="C309" t="s">
-        <v>495</v>
-      </c>
-      <c r="D309">
-        <v>1445</v>
-      </c>
+      <c r="A309" s="52" t="s">
+        <v>770</v>
+      </c>
+      <c r="B309" s="52">
+        <v>10389</v>
+      </c>
+      <c r="C309" s="15" t="s">
+        <v>771</v>
+      </c>
+      <c r="D309" s="15"/>
       <c r="E309" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B310">
-        <v>305034</v>
-      </c>
-      <c r="C310" t="s">
-        <v>496</v>
-      </c>
-      <c r="D310">
-        <v>2098</v>
-      </c>
+      <c r="A310" s="52" t="s">
+        <v>772</v>
+      </c>
+      <c r="B310" s="52">
+        <v>10390</v>
+      </c>
+      <c r="C310" s="15" t="s">
+        <v>774</v>
+      </c>
+      <c r="D310" s="15"/>
       <c r="E310" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B311">
-        <v>305035</v>
-      </c>
-      <c r="C311" t="s">
-        <v>497</v>
-      </c>
-      <c r="D311">
-        <v>1523</v>
-      </c>
+      <c r="A311" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="B311" s="52">
+        <v>10391</v>
+      </c>
+      <c r="C311" s="15" t="s">
+        <v>778</v>
+      </c>
+      <c r="D311" s="15"/>
       <c r="E311" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B312">
-        <v>305036</v>
+      <c r="A312" s="52" t="s">
+        <v>777</v>
+      </c>
+      <c r="B312" s="52">
+        <v>10392</v>
       </c>
       <c r="C312" s="15" t="s">
-        <v>498</v>
-      </c>
-      <c r="D312">
-        <v>1915</v>
-      </c>
+        <v>775</v>
+      </c>
+      <c r="D312" s="15"/>
       <c r="E312" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B313">
-        <v>305037</v>
+        <v>305032</v>
       </c>
       <c r="C313" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="D313">
-        <v>1200</v>
+        <v>1314</v>
       </c>
       <c r="E313" t="s">
         <v>114</v>
@@ -7545,13 +7602,13 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B314">
-        <v>305038</v>
+        <v>305033</v>
       </c>
       <c r="C314" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="D314">
-        <v>2500</v>
+        <v>1445</v>
       </c>
       <c r="E314" t="s">
         <v>114</v>
@@ -7559,13 +7616,13 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B315">
-        <v>305039</v>
+        <v>305034</v>
       </c>
       <c r="C315" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="D315">
-        <v>1200</v>
+        <v>2098</v>
       </c>
       <c r="E315" t="s">
         <v>114</v>
@@ -7573,13 +7630,13 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B316">
-        <v>305040</v>
+        <v>305035</v>
       </c>
       <c r="C316" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="D316">
-        <v>2500</v>
+        <v>1523</v>
       </c>
       <c r="E316" t="s">
         <v>114</v>
@@ -7587,10 +7644,13 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B317">
-        <v>305200</v>
-      </c>
-      <c r="C317" t="s">
-        <v>503</v>
+        <v>305036</v>
+      </c>
+      <c r="C317" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="D317">
+        <v>1915</v>
       </c>
       <c r="E317" t="s">
         <v>114</v>
@@ -7598,10 +7658,13 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B318">
-        <v>305201</v>
+        <v>305037</v>
       </c>
       <c r="C318" t="s">
-        <v>504</v>
+        <v>498</v>
+      </c>
+      <c r="D318">
+        <v>1200</v>
       </c>
       <c r="E318" t="s">
         <v>114</v>
@@ -7609,10 +7672,13 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B319">
-        <v>305202</v>
+        <v>305038</v>
       </c>
       <c r="C319" t="s">
-        <v>505</v>
+        <v>499</v>
+      </c>
+      <c r="D319">
+        <v>2500</v>
       </c>
       <c r="E319" t="s">
         <v>114</v>
@@ -7620,10 +7686,13 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B320">
-        <v>305203</v>
+        <v>305039</v>
       </c>
       <c r="C320" t="s">
-        <v>506</v>
+        <v>500</v>
+      </c>
+      <c r="D320">
+        <v>1200</v>
       </c>
       <c r="E320" t="s">
         <v>114</v>
@@ -7631,10 +7700,13 @@
     </row>
     <row r="321" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B321">
-        <v>305204</v>
+        <v>305040</v>
       </c>
       <c r="C321" t="s">
-        <v>507</v>
+        <v>501</v>
+      </c>
+      <c r="D321">
+        <v>2500</v>
       </c>
       <c r="E321" t="s">
         <v>114</v>
@@ -7642,10 +7714,10 @@
     </row>
     <row r="322" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B322">
-        <v>305205</v>
+        <v>305200</v>
       </c>
       <c r="C322" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="E322" t="s">
         <v>114</v>
@@ -7653,10 +7725,10 @@
     </row>
     <row r="323" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B323">
-        <v>305206</v>
+        <v>305201</v>
       </c>
       <c r="C323" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="E323" t="s">
         <v>114</v>
@@ -7664,10 +7736,10 @@
     </row>
     <row r="324" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B324">
-        <v>305207</v>
+        <v>305202</v>
       </c>
       <c r="C324" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="E324" t="s">
         <v>114</v>
@@ -7675,10 +7747,10 @@
     </row>
     <row r="325" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B325">
-        <v>305208</v>
+        <v>305203</v>
       </c>
       <c r="C325" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="E325" t="s">
         <v>114</v>
@@ -7686,10 +7758,10 @@
     </row>
     <row r="326" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B326">
-        <v>305209</v>
+        <v>305204</v>
       </c>
       <c r="C326" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="E326" t="s">
         <v>114</v>
@@ -7697,10 +7769,10 @@
     </row>
     <row r="327" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B327">
-        <v>305210</v>
+        <v>305205</v>
       </c>
       <c r="C327" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="E327" t="s">
         <v>114</v>
@@ -7708,10 +7780,10 @@
     </row>
     <row r="328" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B328">
-        <v>305211</v>
+        <v>305206</v>
       </c>
       <c r="C328" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E328" t="s">
         <v>114</v>
@@ -7719,10 +7791,10 @@
     </row>
     <row r="329" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B329">
-        <v>305212</v>
+        <v>305207</v>
       </c>
       <c r="C329" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="E329" t="s">
         <v>114</v>
@@ -7730,10 +7802,10 @@
     </row>
     <row r="330" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B330">
-        <v>305213</v>
+        <v>305208</v>
       </c>
       <c r="C330" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="E330" t="s">
         <v>114</v>
@@ -7741,7 +7813,10 @@
     </row>
     <row r="331" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B331">
-        <v>305214</v>
+        <v>305209</v>
+      </c>
+      <c r="C331" t="s">
+        <v>511</v>
       </c>
       <c r="E331" t="s">
         <v>114</v>
@@ -7749,10 +7824,10 @@
     </row>
     <row r="332" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B332">
-        <v>305215</v>
+        <v>305210</v>
       </c>
       <c r="C332" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="E332" t="s">
         <v>114</v>
@@ -7760,10 +7835,10 @@
     </row>
     <row r="333" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B333">
-        <v>305216</v>
+        <v>305211</v>
       </c>
       <c r="C333" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E333" t="s">
         <v>114</v>
@@ -7771,10 +7846,10 @@
     </row>
     <row r="334" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B334">
-        <v>305217</v>
+        <v>305212</v>
       </c>
       <c r="C334" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="E334" t="s">
         <v>114</v>
@@ -7782,10 +7857,10 @@
     </row>
     <row r="335" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B335">
-        <v>305218</v>
+        <v>305213</v>
       </c>
       <c r="C335" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E335" t="s">
         <v>114</v>
@@ -7793,10 +7868,7 @@
     </row>
     <row r="336" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B336">
-        <v>305219</v>
-      </c>
-      <c r="C336" t="s">
-        <v>521</v>
+        <v>305214</v>
       </c>
       <c r="E336" t="s">
         <v>114</v>
@@ -7804,10 +7876,10 @@
     </row>
     <row r="337" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B337">
-        <v>305220</v>
+        <v>305215</v>
       </c>
       <c r="C337" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="E337" t="s">
         <v>114</v>
@@ -7815,10 +7887,10 @@
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B338">
-        <v>305221</v>
-      </c>
-      <c r="C338" s="15" t="s">
-        <v>523</v>
+        <v>305216</v>
+      </c>
+      <c r="C338" t="s">
+        <v>517</v>
       </c>
       <c r="E338" t="s">
         <v>114</v>
@@ -7826,10 +7898,10 @@
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B339">
-        <v>305222</v>
-      </c>
-      <c r="C339" s="15" t="s">
-        <v>524</v>
+        <v>305217</v>
+      </c>
+      <c r="C339" t="s">
+        <v>518</v>
       </c>
       <c r="E339" t="s">
         <v>114</v>
@@ -7837,10 +7909,10 @@
     </row>
     <row r="340" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B340">
-        <v>305223</v>
+        <v>305218</v>
       </c>
       <c r="C340" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="E340" t="s">
         <v>114</v>
@@ -7848,10 +7920,10 @@
     </row>
     <row r="341" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B341">
-        <v>30520001</v>
-      </c>
-      <c r="C341" s="15" t="s">
-        <v>526</v>
+        <v>305219</v>
+      </c>
+      <c r="C341" t="s">
+        <v>520</v>
       </c>
       <c r="E341" t="s">
         <v>114</v>
@@ -7859,10 +7931,10 @@
     </row>
     <row r="342" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B342">
-        <v>30520002</v>
-      </c>
-      <c r="C342" s="15" t="s">
-        <v>527</v>
+        <v>305220</v>
+      </c>
+      <c r="C342" t="s">
+        <v>521</v>
       </c>
       <c r="E342" t="s">
         <v>114</v>
@@ -7870,10 +7942,10 @@
     </row>
     <row r="343" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B343">
-        <v>30520003</v>
+        <v>305221</v>
       </c>
       <c r="C343" s="15" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="E343" t="s">
         <v>114</v>
@@ -7881,10 +7953,10 @@
     </row>
     <row r="344" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B344">
-        <v>30520004</v>
+        <v>305222</v>
       </c>
       <c r="C344" s="15" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="E344" t="s">
         <v>114</v>
@@ -7892,10 +7964,10 @@
     </row>
     <row r="345" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B345">
-        <v>30520005</v>
-      </c>
-      <c r="C345" s="15" t="s">
-        <v>530</v>
+        <v>305223</v>
+      </c>
+      <c r="C345" t="s">
+        <v>524</v>
       </c>
       <c r="E345" t="s">
         <v>114</v>
@@ -7903,10 +7975,10 @@
     </row>
     <row r="346" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B346">
-        <v>30520006</v>
+        <v>30520001</v>
       </c>
       <c r="C346" s="15" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="E346" t="s">
         <v>114</v>
@@ -7914,10 +7986,10 @@
     </row>
     <row r="347" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B347">
-        <v>30520007</v>
+        <v>30520002</v>
       </c>
       <c r="C347" s="15" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="E347" t="s">
         <v>114</v>
@@ -7925,122 +7997,122 @@
     </row>
     <row r="348" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B348">
-        <v>30520008</v>
+        <v>30520003</v>
       </c>
       <c r="C348" s="15" t="s">
-        <v>533</v>
-      </c>
-      <c r="E348" s="15" t="s">
+        <v>527</v>
+      </c>
+      <c r="E348" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="349" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B349">
-        <v>30520009</v>
+        <v>30520004</v>
       </c>
       <c r="C349" s="15" t="s">
-        <v>534</v>
-      </c>
-      <c r="E349" s="15" t="s">
+        <v>528</v>
+      </c>
+      <c r="E349" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="350" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B350">
-        <v>30520010</v>
+        <v>30520005</v>
       </c>
       <c r="C350" s="15" t="s">
-        <v>535</v>
-      </c>
-      <c r="E350" s="15" t="s">
+        <v>529</v>
+      </c>
+      <c r="E350" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="351" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B351" s="17">
-        <v>30520011</v>
-      </c>
-      <c r="C351" s="18" t="s">
-        <v>536</v>
-      </c>
-      <c r="D351" s="17"/>
-      <c r="E351" s="15" t="s">
+      <c r="B351">
+        <v>30520006</v>
+      </c>
+      <c r="C351" s="15" t="s">
+        <v>530</v>
+      </c>
+      <c r="E351" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="352" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B352">
-        <v>30520012</v>
-      </c>
-      <c r="C352" s="18" t="s">
-        <v>749</v>
-      </c>
-      <c r="D352" s="17"/>
-      <c r="E352" s="15" t="s">
+        <v>30520007</v>
+      </c>
+      <c r="C352" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="E352" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="353" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B353">
-        <v>305224</v>
-      </c>
-      <c r="C353" t="s">
-        <v>537</v>
-      </c>
-      <c r="E353" t="s">
+        <v>30520008</v>
+      </c>
+      <c r="C353" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="E353" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="354" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B354">
-        <v>305225</v>
-      </c>
-      <c r="C354" t="s">
-        <v>538</v>
-      </c>
-      <c r="E354" t="s">
+        <v>30520009</v>
+      </c>
+      <c r="C354" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="E354" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="355" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B355">
-        <v>305226</v>
-      </c>
-      <c r="C355" t="s">
-        <v>539</v>
-      </c>
-      <c r="E355" t="s">
+        <v>30520010</v>
+      </c>
+      <c r="C355" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="E355" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="356" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B356">
-        <v>305300</v>
-      </c>
-      <c r="C356" t="s">
-        <v>540</v>
-      </c>
-      <c r="E356" t="s">
+      <c r="B356" s="17">
+        <v>30520011</v>
+      </c>
+      <c r="C356" s="18" t="s">
+        <v>535</v>
+      </c>
+      <c r="D356" s="17"/>
+      <c r="E356" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="357" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B357">
-        <v>305301</v>
-      </c>
-      <c r="C357" t="s">
-        <v>541</v>
-      </c>
-      <c r="E357" t="s">
+        <v>30520012</v>
+      </c>
+      <c r="C357" s="18" t="s">
+        <v>747</v>
+      </c>
+      <c r="D357" s="17"/>
+      <c r="E357" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="358" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B358">
-        <v>305302</v>
+        <v>305224</v>
       </c>
       <c r="C358" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="E358" t="s">
         <v>114</v>
@@ -8048,10 +8120,10 @@
     </row>
     <row r="359" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B359">
-        <v>305303</v>
+        <v>305225</v>
       </c>
       <c r="C359" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="E359" t="s">
         <v>114</v>
@@ -8059,10 +8131,10 @@
     </row>
     <row r="360" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B360">
-        <v>305304</v>
+        <v>305226</v>
       </c>
       <c r="C360" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="E360" t="s">
         <v>114</v>
@@ -8070,10 +8142,10 @@
     </row>
     <row r="361" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B361">
-        <v>305305</v>
+        <v>305300</v>
       </c>
       <c r="C361" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="E361" t="s">
         <v>114</v>
@@ -8081,10 +8153,10 @@
     </row>
     <row r="362" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B362">
-        <v>305306</v>
+        <v>305301</v>
       </c>
       <c r="C362" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="E362" t="s">
         <v>114</v>
@@ -8092,10 +8164,10 @@
     </row>
     <row r="363" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B363">
-        <v>305307</v>
+        <v>305302</v>
       </c>
       <c r="C363" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="E363" t="s">
         <v>114</v>
@@ -8103,10 +8175,10 @@
     </row>
     <row r="364" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B364">
-        <v>305308</v>
+        <v>305303</v>
       </c>
       <c r="C364" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E364" t="s">
         <v>114</v>
@@ -8114,10 +8186,10 @@
     </row>
     <row r="365" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B365">
-        <v>305309</v>
+        <v>305304</v>
       </c>
       <c r="C365" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="E365" t="s">
         <v>114</v>
@@ -8125,10 +8197,10 @@
     </row>
     <row r="366" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B366">
-        <v>305310</v>
+        <v>305305</v>
       </c>
       <c r="C366" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E366" t="s">
         <v>114</v>
@@ -8136,10 +8208,10 @@
     </row>
     <row r="367" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B367">
-        <v>305311</v>
+        <v>305306</v>
       </c>
       <c r="C367" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="E367" t="s">
         <v>114</v>
@@ -8147,10 +8219,10 @@
     </row>
     <row r="368" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B368">
-        <v>305312</v>
+        <v>305307</v>
       </c>
       <c r="C368" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="E368" t="s">
         <v>114</v>
@@ -8158,10 +8230,10 @@
     </row>
     <row r="369" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B369">
-        <v>305313</v>
+        <v>305308</v>
       </c>
       <c r="C369" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="E369" t="s">
         <v>114</v>
@@ -8169,7 +8241,10 @@
     </row>
     <row r="370" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B370">
-        <v>305314</v>
+        <v>305309</v>
+      </c>
+      <c r="C370" t="s">
+        <v>548</v>
       </c>
       <c r="E370" t="s">
         <v>114</v>
@@ -8177,10 +8252,10 @@
     </row>
     <row r="371" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B371">
-        <v>305315</v>
+        <v>305310</v>
       </c>
       <c r="C371" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="E371" t="s">
         <v>114</v>
@@ -8188,10 +8263,10 @@
     </row>
     <row r="372" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B372">
-        <v>305316</v>
+        <v>305311</v>
       </c>
       <c r="C372" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="E372" t="s">
         <v>114</v>
@@ -8199,10 +8274,10 @@
     </row>
     <row r="373" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B373">
-        <v>305317</v>
+        <v>305312</v>
       </c>
       <c r="C373" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="E373" t="s">
         <v>114</v>
@@ -8210,10 +8285,10 @@
     </row>
     <row r="374" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B374">
-        <v>305318</v>
+        <v>305313</v>
       </c>
       <c r="C374" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E374" t="s">
         <v>114</v>
@@ -8221,10 +8296,7 @@
     </row>
     <row r="375" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B375">
-        <v>305319</v>
-      </c>
-      <c r="C375" t="s">
-        <v>558</v>
+        <v>305314</v>
       </c>
       <c r="E375" t="s">
         <v>114</v>
@@ -8232,10 +8304,10 @@
     </row>
     <row r="376" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B376">
-        <v>305320</v>
+        <v>305315</v>
       </c>
       <c r="C376" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="E376" t="s">
         <v>114</v>
@@ -8243,10 +8315,10 @@
     </row>
     <row r="377" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B377">
-        <v>305321</v>
-      </c>
-      <c r="C377" s="15" t="s">
-        <v>560</v>
+        <v>305316</v>
+      </c>
+      <c r="C377" t="s">
+        <v>554</v>
       </c>
       <c r="E377" t="s">
         <v>114</v>
@@ -8254,10 +8326,10 @@
     </row>
     <row r="378" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B378">
-        <v>305322</v>
-      </c>
-      <c r="C378" s="15" t="s">
-        <v>561</v>
+        <v>305317</v>
+      </c>
+      <c r="C378" t="s">
+        <v>555</v>
       </c>
       <c r="E378" t="s">
         <v>114</v>
@@ -8265,10 +8337,10 @@
     </row>
     <row r="379" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B379">
-        <v>305323</v>
+        <v>305318</v>
       </c>
       <c r="C379" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="E379" t="s">
         <v>114</v>
@@ -8276,10 +8348,10 @@
     </row>
     <row r="380" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B380">
-        <v>305324</v>
+        <v>305319</v>
       </c>
       <c r="C380" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="E380" t="s">
         <v>114</v>
@@ -8287,10 +8359,10 @@
     </row>
     <row r="381" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B381">
-        <v>305325</v>
+        <v>305320</v>
       </c>
       <c r="C381" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="E381" t="s">
         <v>114</v>
@@ -8298,10 +8370,10 @@
     </row>
     <row r="382" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B382">
-        <v>305326</v>
+        <v>305321</v>
       </c>
       <c r="C382" s="15" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="E382" t="s">
         <v>114</v>
@@ -8309,10 +8381,10 @@
     </row>
     <row r="383" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B383">
-        <v>30530001</v>
+        <v>305322</v>
       </c>
       <c r="C383" s="15" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="E383" t="s">
         <v>114</v>
@@ -8320,10 +8392,10 @@
     </row>
     <row r="384" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B384">
-        <v>30530002</v>
+        <v>305323</v>
       </c>
       <c r="C384" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="E384" t="s">
         <v>114</v>
@@ -8331,10 +8403,10 @@
     </row>
     <row r="385" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B385">
-        <v>30530003</v>
-      </c>
-      <c r="C385" s="15" t="s">
-        <v>568</v>
+        <v>305324</v>
+      </c>
+      <c r="C385" t="s">
+        <v>562</v>
       </c>
       <c r="E385" t="s">
         <v>114</v>
@@ -8342,10 +8414,10 @@
     </row>
     <row r="386" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B386">
-        <v>30530004</v>
-      </c>
-      <c r="C386" s="15" t="s">
-        <v>569</v>
+        <v>305325</v>
+      </c>
+      <c r="C386" t="s">
+        <v>563</v>
       </c>
       <c r="E386" t="s">
         <v>114</v>
@@ -8353,10 +8425,10 @@
     </row>
     <row r="387" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B387">
-        <v>30530005</v>
+        <v>305326</v>
       </c>
       <c r="C387" s="15" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E387" t="s">
         <v>114</v>
@@ -8364,10 +8436,10 @@
     </row>
     <row r="388" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B388">
-        <v>30530006</v>
+        <v>30530001</v>
       </c>
       <c r="C388" s="15" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="E388" t="s">
         <v>114</v>
@@ -8375,133 +8447,133 @@
     </row>
     <row r="389" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B389">
-        <v>30530007</v>
-      </c>
-      <c r="C389" s="15" t="s">
-        <v>572</v>
-      </c>
-      <c r="E389" s="15" t="s">
+        <v>30530002</v>
+      </c>
+      <c r="C389" t="s">
+        <v>566</v>
+      </c>
+      <c r="E389" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="390" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B390">
-        <v>30530008</v>
+        <v>30530003</v>
       </c>
       <c r="C390" s="15" t="s">
-        <v>573</v>
-      </c>
-      <c r="E390" s="15" t="s">
+        <v>567</v>
+      </c>
+      <c r="E390" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="391" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B391">
-        <v>30530009</v>
+        <v>30530004</v>
       </c>
       <c r="C391" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="E391" s="15" t="s">
+        <v>568</v>
+      </c>
+      <c r="E391" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="392" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B392">
-        <v>30530010</v>
+        <v>30530005</v>
       </c>
       <c r="C392" s="15" t="s">
-        <v>575</v>
-      </c>
-      <c r="E392" s="15" t="s">
+        <v>569</v>
+      </c>
+      <c r="E392" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="393" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B393" s="17">
-        <v>30530011</v>
-      </c>
-      <c r="C393" s="18" t="s">
-        <v>576</v>
-      </c>
-      <c r="D393" s="17"/>
-      <c r="E393" s="18" t="s">
+      <c r="B393">
+        <v>30530006</v>
+      </c>
+      <c r="C393" s="15" t="s">
+        <v>570</v>
+      </c>
+      <c r="E393" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="394" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B394">
-        <v>30530012</v>
-      </c>
-      <c r="C394" s="18" t="s">
-        <v>748</v>
-      </c>
-      <c r="D394" s="17"/>
-      <c r="E394" s="18" t="s">
+        <v>30530007</v>
+      </c>
+      <c r="C394" s="15" t="s">
+        <v>571</v>
+      </c>
+      <c r="E394" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="395" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B395">
-        <v>309205</v>
-      </c>
-      <c r="C395" t="s">
-        <v>577</v>
-      </c>
-      <c r="E395" t="s">
+        <v>30530008</v>
+      </c>
+      <c r="C395" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="E395" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="396" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B396">
-        <v>308001</v>
-      </c>
-      <c r="C396" t="s">
-        <v>578</v>
-      </c>
-      <c r="E396" t="s">
+        <v>30530009</v>
+      </c>
+      <c r="C396" s="15" t="s">
+        <v>573</v>
+      </c>
+      <c r="E396" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="397" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B397">
-        <v>308002</v>
-      </c>
-      <c r="C397" t="s">
-        <v>579</v>
-      </c>
-      <c r="E397" t="s">
+        <v>30530010</v>
+      </c>
+      <c r="C397" s="15" t="s">
+        <v>574</v>
+      </c>
+      <c r="E397" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="398" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B398">
-        <v>308006</v>
-      </c>
-      <c r="C398" t="s">
-        <v>580</v>
-      </c>
-      <c r="E398" t="s">
+      <c r="B398" s="17">
+        <v>30530011</v>
+      </c>
+      <c r="C398" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="D398" s="17"/>
+      <c r="E398" s="18" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="399" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B399">
-        <v>308007</v>
-      </c>
-      <c r="C399" t="s">
-        <v>581</v>
-      </c>
-      <c r="E399" t="s">
+        <v>30530012</v>
+      </c>
+      <c r="C399" s="18" t="s">
+        <v>746</v>
+      </c>
+      <c r="D399" s="17"/>
+      <c r="E399" s="18" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="400" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B400">
-        <v>308011</v>
+        <v>309205</v>
       </c>
       <c r="C400" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="E400" t="s">
         <v>114</v>
@@ -8509,10 +8581,10 @@
     </row>
     <row r="401" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B401">
-        <v>308012</v>
+        <v>308001</v>
       </c>
       <c r="C401" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="E401" t="s">
         <v>114</v>
@@ -8520,10 +8592,10 @@
     </row>
     <row r="402" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B402">
-        <v>308016</v>
+        <v>308002</v>
       </c>
       <c r="C402" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="E402" t="s">
         <v>114</v>
@@ -8531,10 +8603,10 @@
     </row>
     <row r="403" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B403">
-        <v>308017</v>
+        <v>308006</v>
       </c>
       <c r="C403" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E403" t="s">
         <v>114</v>
@@ -8542,10 +8614,10 @@
     </row>
     <row r="404" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B404">
-        <v>308021</v>
-      </c>
-      <c r="C404" s="15" t="s">
-        <v>586</v>
+        <v>308007</v>
+      </c>
+      <c r="C404" t="s">
+        <v>580</v>
       </c>
       <c r="E404" t="s">
         <v>114</v>
@@ -8553,10 +8625,10 @@
     </row>
     <row r="405" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B405">
-        <v>308022</v>
-      </c>
-      <c r="C405" s="15" t="s">
-        <v>587</v>
+        <v>308011</v>
+      </c>
+      <c r="C405" t="s">
+        <v>581</v>
       </c>
       <c r="E405" t="s">
         <v>114</v>
@@ -8564,10 +8636,10 @@
     </row>
     <row r="406" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B406">
-        <v>308026</v>
-      </c>
-      <c r="C406" s="15" t="s">
-        <v>588</v>
+        <v>308012</v>
+      </c>
+      <c r="C406" t="s">
+        <v>582</v>
       </c>
       <c r="E406" t="s">
         <v>114</v>
@@ -8575,10 +8647,10 @@
     </row>
     <row r="407" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B407">
-        <v>308027</v>
-      </c>
-      <c r="C407" s="15" t="s">
-        <v>589</v>
+        <v>308016</v>
+      </c>
+      <c r="C407" t="s">
+        <v>583</v>
       </c>
       <c r="E407" t="s">
         <v>114</v>
@@ -8586,10 +8658,10 @@
     </row>
     <row r="408" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B408">
-        <v>308031</v>
-      </c>
-      <c r="C408" s="15" t="s">
-        <v>590</v>
+        <v>308017</v>
+      </c>
+      <c r="C408" t="s">
+        <v>584</v>
       </c>
       <c r="E408" t="s">
         <v>114</v>
@@ -8597,10 +8669,10 @@
     </row>
     <row r="409" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B409">
-        <v>308032</v>
+        <v>308021</v>
       </c>
       <c r="C409" s="15" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="E409" t="s">
         <v>114</v>
@@ -8608,10 +8680,10 @@
     </row>
     <row r="410" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B410">
-        <v>308036</v>
+        <v>308022</v>
       </c>
       <c r="C410" s="15" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="E410" t="s">
         <v>114</v>
@@ -8619,10 +8691,10 @@
     </row>
     <row r="411" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B411">
-        <v>308037</v>
+        <v>308026</v>
       </c>
       <c r="C411" s="15" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="E411" t="s">
         <v>114</v>
@@ -8630,10 +8702,10 @@
     </row>
     <row r="412" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B412">
-        <v>308041</v>
+        <v>308027</v>
       </c>
       <c r="C412" s="15" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="E412" t="s">
         <v>114</v>
@@ -8641,60 +8713,113 @@
     </row>
     <row r="413" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B413">
+        <v>308031</v>
+      </c>
+      <c r="C413" s="15" t="s">
+        <v>589</v>
+      </c>
+      <c r="E413" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="414" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B414">
+        <v>308032</v>
+      </c>
+      <c r="C414" s="15" t="s">
+        <v>590</v>
+      </c>
+      <c r="E414" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="415" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B415">
+        <v>308036</v>
+      </c>
+      <c r="C415" s="15" t="s">
+        <v>591</v>
+      </c>
+      <c r="E415" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="416" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B416">
+        <v>308037</v>
+      </c>
+      <c r="C416" s="15" t="s">
+        <v>592</v>
+      </c>
+      <c r="E416" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="417" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B417">
+        <v>308041</v>
+      </c>
+      <c r="C417" s="15" t="s">
+        <v>593</v>
+      </c>
+      <c r="E417" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="418" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B418">
         <v>308042</v>
       </c>
-      <c r="C413" s="15" t="s">
+      <c r="C418" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="E418" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="419" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B419">
+        <v>308046</v>
+      </c>
+      <c r="C419" s="15" t="s">
         <v>595</v>
       </c>
-      <c r="E413" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="414" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B414" s="53">
-        <v>308046</v>
-      </c>
-      <c r="C414" s="54" t="s">
+      <c r="E419" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="420" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B420">
+        <v>308047</v>
+      </c>
+      <c r="C420" s="15" t="s">
         <v>596</v>
       </c>
-      <c r="D414" s="55"/>
-      <c r="E414" s="53" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="415" spans="2:5" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B415" s="53">
-        <v>308047</v>
-      </c>
-      <c r="C415" s="54" t="s">
-        <v>597</v>
-      </c>
-      <c r="D415" s="55"/>
-      <c r="E415" s="53" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="416" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B416" s="53">
+      <c r="E420" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="421" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B421">
         <v>308048</v>
       </c>
-      <c r="C416" s="18" t="s">
+      <c r="C421" s="18" t="s">
         <v>767</v>
       </c>
-      <c r="D416" s="44"/>
-      <c r="E416" s="17" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="417" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B417" s="53">
+      <c r="D421" s="44"/>
+      <c r="E421" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="422" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B422">
         <v>308049</v>
       </c>
-      <c r="C417" s="18" t="s">
+      <c r="C422" s="18" t="s">
         <v>768</v>
       </c>
-      <c r="D417" s="44"/>
-      <c r="E417" s="17" t="s">
+      <c r="D422" s="44"/>
+      <c r="E422" s="17" t="s">
         <v>114</v>
       </c>
     </row>
@@ -8730,22 +8855,22 @@
         <v>5</v>
       </c>
       <c r="C1" s="15" t="s">
+        <v>597</v>
+      </c>
+      <c r="D1" t="s">
         <v>598</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>599</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>600</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>601</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>602</v>
-      </c>
-      <c r="H1" t="s">
-        <v>603</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
@@ -8757,22 +8882,22 @@
         <v>2</v>
       </c>
       <c r="L1" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="M1" s="8" t="s">
         <v>604</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>605</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>606</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="11" t="s">
         <v>607</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="Q1" s="8" t="s">
         <v>608</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -8782,7 +8907,7 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -8791,10 +8916,10 @@
         <v>13</v>
       </c>
       <c r="K2" t="s">
+        <v>610</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>611</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>612</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
@@ -8863,22 +8988,22 @@
         <v>0</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="I4" t="s">
         <v>617</v>
-      </c>
-      <c r="I4" t="s">
-        <v>618</v>
       </c>
       <c r="K4" t="s">
         <v>20</v>
@@ -8892,40 +9017,40 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
+        <v>618</v>
+      </c>
+      <c r="E5" t="s">
         <v>619</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>621</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="10" t="s">
         <v>622</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="I5" t="s">
         <v>623</v>
-      </c>
-      <c r="I5" t="s">
-        <v>624</v>
       </c>
       <c r="K5" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="M5" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="N5" s="9" t="s">
         <v>626</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="O5" s="7" t="s">
         <v>627</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="P5" s="12" t="s">
         <v>628</v>
-      </c>
-      <c r="P5" s="12" t="s">
-        <v>629</v>
       </c>
       <c r="Q5">
         <v>306002</v>
@@ -8939,40 +9064,40 @@
         <v>0</v>
       </c>
       <c r="D6" s="21" t="s">
+        <v>629</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>629</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="E6" s="21" t="s">
-        <v>630</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="22" t="s">
         <v>632</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="I6" t="s">
         <v>633</v>
-      </c>
-      <c r="I6" t="s">
-        <v>634</v>
       </c>
       <c r="K6" t="s">
         <v>20</v>
       </c>
       <c r="L6" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="M6" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="N6" s="7" t="s">
         <v>626</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="O6" s="7" t="s">
         <v>627</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="P6" s="12" t="s">
         <v>628</v>
-      </c>
-      <c r="P6" s="12" t="s">
-        <v>629</v>
       </c>
       <c r="Q6">
         <v>306003</v>
@@ -8986,40 +9111,40 @@
         <v>0</v>
       </c>
       <c r="D7" s="21" t="s">
+        <v>634</v>
+      </c>
+      <c r="E7" s="21" t="s">
         <v>635</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="F7" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="6" t="s">
         <v>637</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="22" t="s">
         <v>638</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="I7" t="s">
         <v>639</v>
-      </c>
-      <c r="I7" t="s">
-        <v>640</v>
       </c>
       <c r="K7" t="s">
         <v>20</v>
       </c>
       <c r="L7" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="M7" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="N7" s="7" t="s">
         <v>626</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="O7" s="7" t="s">
         <v>627</v>
       </c>
-      <c r="O7" s="7" t="s">
+      <c r="P7" s="12" t="s">
         <v>628</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>629</v>
       </c>
       <c r="Q7">
         <v>306004</v>
@@ -9033,40 +9158,40 @@
         <v>1</v>
       </c>
       <c r="D8" s="21" t="s">
+        <v>640</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>640</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>640</v>
+      </c>
+      <c r="G8" s="25" t="s">
         <v>641</v>
       </c>
-      <c r="E8" s="21" t="s">
-        <v>641</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>641</v>
-      </c>
-      <c r="G8" s="25" t="s">
+      <c r="H8" s="26" t="s">
         <v>642</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="I8" s="15" t="s">
         <v>643</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>644</v>
       </c>
       <c r="K8" t="s">
         <v>20</v>
       </c>
       <c r="L8" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="M8" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="N8" s="7" t="s">
         <v>646</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="O8" s="7" t="s">
         <v>647</v>
       </c>
-      <c r="O8" s="7" t="s">
+      <c r="P8" s="13" t="s">
         <v>648</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>649</v>
       </c>
       <c r="Q8" s="14">
         <v>306005</v>
@@ -9080,40 +9205,40 @@
         <v>1</v>
       </c>
       <c r="D9" s="19" t="s">
+        <v>649</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>649</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>649</v>
+      </c>
+      <c r="G9" s="20" t="s">
         <v>650</v>
       </c>
-      <c r="E9" s="19" t="s">
-        <v>650</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>650</v>
-      </c>
-      <c r="G9" s="20" t="s">
+      <c r="H9" s="20" t="s">
         <v>651</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="I9" s="15" t="s">
         <v>652</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>653</v>
       </c>
       <c r="K9" t="s">
         <v>20</v>
       </c>
       <c r="L9" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="N9" s="7" t="s">
         <v>646</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="O9" s="7" t="s">
         <v>647</v>
       </c>
-      <c r="O9" s="7" t="s">
+      <c r="P9" s="13" t="s">
         <v>648</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>649</v>
       </c>
       <c r="Q9" s="14">
         <v>306006</v>
@@ -9127,40 +9252,40 @@
         <v>1</v>
       </c>
       <c r="D10" s="38" t="s">
+        <v>653</v>
+      </c>
+      <c r="E10" s="38" t="s">
         <v>654</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="F10" s="39" t="s">
         <v>655</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="G10" s="40" t="s">
         <v>656</v>
       </c>
-      <c r="G10" s="40" t="s">
+      <c r="H10" s="40" t="s">
         <v>657</v>
       </c>
-      <c r="H10" s="40" t="s">
+      <c r="I10" s="15" t="s">
         <v>658</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>659</v>
       </c>
       <c r="K10" t="s">
         <v>20</v>
       </c>
       <c r="L10" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="M10" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="N10" s="7" t="s">
         <v>646</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="O10" s="7" t="s">
         <v>647</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="P10" s="13" t="s">
         <v>648</v>
-      </c>
-      <c r="P10" s="13" t="s">
-        <v>649</v>
       </c>
       <c r="Q10" s="14">
         <v>30600001</v>
@@ -9170,44 +9295,44 @@
       <c r="B11" s="14">
         <v>30600002</v>
       </c>
-      <c r="C11" s="16">
-        <v>1</v>
+      <c r="C11">
+        <v>0</v>
       </c>
       <c r="D11" s="48" t="s">
+        <v>659</v>
+      </c>
+      <c r="E11" s="49" t="s">
         <v>660</v>
       </c>
-      <c r="E11" s="49" t="s">
+      <c r="F11" s="47" t="s">
+        <v>764</v>
+      </c>
+      <c r="G11" s="50" t="s">
         <v>661</v>
       </c>
-      <c r="F11" s="47" t="s">
-        <v>766</v>
-      </c>
-      <c r="G11" s="50" t="s">
+      <c r="H11" s="50" t="s">
         <v>662</v>
       </c>
-      <c r="H11" s="50" t="s">
+      <c r="I11" s="15" t="s">
         <v>663</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>664</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
       </c>
       <c r="L11" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="M11" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="M11" s="8" t="s">
+      <c r="N11" s="7" t="s">
         <v>626</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="O11" s="7" t="s">
         <v>627</v>
       </c>
-      <c r="O11" s="7" t="s">
+      <c r="P11" s="12" t="s">
         <v>628</v>
-      </c>
-      <c r="P11" s="12" t="s">
-        <v>629</v>
       </c>
       <c r="Q11" s="16">
         <v>30600002</v>
@@ -9221,46 +9346,46 @@
         <v>1</v>
       </c>
       <c r="D12" s="51" t="s">
+        <v>664</v>
+      </c>
+      <c r="E12" s="51" t="s">
         <v>665</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="F12" s="47" t="s">
         <v>666</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="G12" s="47" t="s">
         <v>667</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="H12" s="47" t="s">
         <v>668</v>
       </c>
-      <c r="H12" s="47" t="s">
+      <c r="I12" s="15" t="s">
         <v>669</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>670</v>
       </c>
       <c r="K12" t="s">
         <v>20</v>
       </c>
       <c r="L12" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="M12" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="N12" s="7" t="s">
         <v>646</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="O12" s="7" t="s">
         <v>647</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="P12" s="13" t="s">
         <v>648</v>
-      </c>
-      <c r="P12" s="13" t="s">
-        <v>649</v>
       </c>
       <c r="Q12" s="14">
         <v>30600003</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>306101</v>
       </c>
@@ -9268,22 +9393,22 @@
         <v>0</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>672</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="6" t="s">
         <v>673</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="H13" s="53" t="s">
+        <v>769</v>
+      </c>
+      <c r="I13" t="s">
         <v>674</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>675</v>
-      </c>
-      <c r="I13" t="s">
-        <v>676</v>
       </c>
       <c r="K13" t="s">
         <v>84</v>
@@ -9299,40 +9424,40 @@
         <v>1</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>677</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="H14" s="10" t="s">
         <v>678</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>678</v>
-      </c>
-      <c r="G14" s="6" t="s">
+      <c r="I14" t="s">
         <v>679</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>680</v>
-      </c>
-      <c r="I14" t="s">
-        <v>681</v>
       </c>
       <c r="K14" t="s">
         <v>84</v>
       </c>
       <c r="L14" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="M14" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="M14" s="7" t="s">
+      <c r="N14" s="7" t="s">
         <v>646</v>
       </c>
-      <c r="N14" s="7" t="s">
+      <c r="O14" s="7" t="s">
         <v>647</v>
       </c>
-      <c r="O14" s="7" t="s">
+      <c r="P14" s="13" t="s">
         <v>648</v>
-      </c>
-      <c r="P14" s="13" t="s">
-        <v>649</v>
       </c>
       <c r="Q14">
         <v>306102</v>
@@ -9346,40 +9471,40 @@
         <v>1</v>
       </c>
       <c r="D15" s="26" t="s">
+        <v>680</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>680</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>681</v>
+      </c>
+      <c r="G15" s="27" t="s">
         <v>682</v>
       </c>
-      <c r="E15" s="26" t="s">
-        <v>682</v>
-      </c>
-      <c r="F15" s="26" t="s">
+      <c r="H15" s="28" t="s">
         <v>683</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="I15" s="15" t="s">
         <v>684</v>
-      </c>
-      <c r="H15" s="28" t="s">
-        <v>685</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>686</v>
       </c>
       <c r="K15" t="s">
         <v>84</v>
       </c>
       <c r="L15" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="M15" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="M15" s="7" t="s">
+      <c r="N15" s="7" t="s">
         <v>646</v>
       </c>
-      <c r="N15" s="7" t="s">
+      <c r="O15" s="7" t="s">
         <v>647</v>
       </c>
-      <c r="O15" s="7" t="s">
+      <c r="P15" s="13" t="s">
         <v>648</v>
-      </c>
-      <c r="P15" s="13" t="s">
-        <v>649</v>
       </c>
       <c r="Q15" s="16">
         <v>306103</v>
@@ -9393,40 +9518,40 @@
         <v>0</v>
       </c>
       <c r="D16" s="31" t="s">
+        <v>685</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>686</v>
+      </c>
+      <c r="F16" s="26" t="s">
         <v>687</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="G16" s="27" t="s">
         <v>688</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="H16" s="27" t="s">
         <v>689</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="I16" s="15" t="s">
         <v>690</v>
-      </c>
-      <c r="H16" s="27" t="s">
-        <v>691</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>692</v>
       </c>
       <c r="K16" t="s">
         <v>84</v>
       </c>
       <c r="L16" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="N16" s="25" t="s">
         <v>693</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="O16" s="25" t="s">
         <v>694</v>
       </c>
-      <c r="N16" s="25" t="s">
+      <c r="P16" s="25" t="s">
         <v>695</v>
-      </c>
-      <c r="O16" s="25" t="s">
-        <v>696</v>
-      </c>
-      <c r="P16" s="25" t="s">
-        <v>697</v>
       </c>
       <c r="Q16" s="29">
         <v>306104</v>
@@ -9440,40 +9565,40 @@
         <v>0</v>
       </c>
       <c r="D17" s="31" t="s">
+        <v>696</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>697</v>
+      </c>
+      <c r="F17" s="26" t="s">
         <v>698</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="G17" s="27" t="s">
         <v>699</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="H17" s="27" t="s">
         <v>700</v>
       </c>
-      <c r="G17" s="27" t="s">
+      <c r="I17" s="15" t="s">
         <v>701</v>
-      </c>
-      <c r="H17" s="27" t="s">
-        <v>702</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>703</v>
       </c>
       <c r="K17" t="s">
         <v>84</v>
       </c>
       <c r="L17" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="N17" s="25" t="s">
         <v>693</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="O17" s="25" t="s">
         <v>694</v>
       </c>
-      <c r="N17" s="25" t="s">
+      <c r="P17" s="25" t="s">
         <v>695</v>
-      </c>
-      <c r="O17" s="25" t="s">
-        <v>696</v>
-      </c>
-      <c r="P17" s="25" t="s">
-        <v>697</v>
       </c>
       <c r="Q17" s="29">
         <v>306105</v>
@@ -9487,40 +9612,40 @@
         <v>0</v>
       </c>
       <c r="D18" s="31" t="s">
+        <v>702</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>703</v>
+      </c>
+      <c r="F18" s="26" t="s">
         <v>704</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="G18" s="27" t="s">
         <v>705</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="H18" s="27" t="s">
         <v>706</v>
       </c>
-      <c r="G18" s="27" t="s">
+      <c r="I18" s="15" t="s">
         <v>707</v>
-      </c>
-      <c r="H18" s="27" t="s">
-        <v>708</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>709</v>
       </c>
       <c r="K18" t="s">
         <v>84</v>
       </c>
       <c r="L18" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="N18" s="25" t="s">
         <v>693</v>
       </c>
-      <c r="M18" s="9" t="s">
+      <c r="O18" s="25" t="s">
         <v>694</v>
       </c>
-      <c r="N18" s="25" t="s">
+      <c r="P18" s="25" t="s">
         <v>695</v>
-      </c>
-      <c r="O18" s="25" t="s">
-        <v>696</v>
-      </c>
-      <c r="P18" s="25" t="s">
-        <v>697</v>
       </c>
       <c r="Q18" s="29">
         <v>306106</v>
@@ -9534,40 +9659,40 @@
         <v>0</v>
       </c>
       <c r="D19" s="31" t="s">
+        <v>708</v>
+      </c>
+      <c r="E19" s="31" t="s">
+        <v>709</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>708</v>
+      </c>
+      <c r="G19" s="27" t="s">
         <v>710</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="H19" s="27" t="s">
         <v>711</v>
       </c>
-      <c r="F19" s="26" t="s">
-        <v>710</v>
-      </c>
-      <c r="G19" s="27" t="s">
+      <c r="I19" s="15" t="s">
         <v>712</v>
-      </c>
-      <c r="H19" s="27" t="s">
-        <v>713</v>
-      </c>
-      <c r="I19" s="15" t="s">
-        <v>714</v>
       </c>
       <c r="K19" t="s">
         <v>84</v>
       </c>
       <c r="L19" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="N19" s="25" t="s">
         <v>693</v>
       </c>
-      <c r="M19" s="9" t="s">
+      <c r="O19" s="25" t="s">
         <v>694</v>
       </c>
-      <c r="N19" s="25" t="s">
+      <c r="P19" s="25" t="s">
         <v>695</v>
-      </c>
-      <c r="O19" s="25" t="s">
-        <v>696</v>
-      </c>
-      <c r="P19" s="25" t="s">
-        <v>697</v>
       </c>
       <c r="Q19" s="29">
         <v>306107</v>
@@ -9581,40 +9706,40 @@
         <v>1</v>
       </c>
       <c r="D20" s="32" t="s">
+        <v>713</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>713</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>714</v>
+      </c>
+      <c r="G20" s="27" t="s">
         <v>715</v>
       </c>
-      <c r="E20" s="32" t="s">
-        <v>715</v>
-      </c>
-      <c r="F20" s="33" t="s">
+      <c r="H20" s="28" t="s">
         <v>716</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="I20" s="15" t="s">
         <v>717</v>
-      </c>
-      <c r="H20" s="28" t="s">
-        <v>718</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>719</v>
       </c>
       <c r="K20" t="s">
         <v>84</v>
       </c>
       <c r="L20" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="N20" s="25" t="s">
         <v>693</v>
       </c>
-      <c r="M20" s="9" t="s">
+      <c r="O20" s="25" t="s">
         <v>694</v>
       </c>
-      <c r="N20" s="25" t="s">
+      <c r="P20" s="25" t="s">
         <v>695</v>
-      </c>
-      <c r="O20" s="25" t="s">
-        <v>696</v>
-      </c>
-      <c r="P20" s="25" t="s">
-        <v>697</v>
       </c>
       <c r="Q20" s="16">
         <v>30610001</v>
@@ -9628,40 +9753,40 @@
         <v>1</v>
       </c>
       <c r="D21" s="34" t="s">
+        <v>718</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>718</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>719</v>
+      </c>
+      <c r="G21" s="36" t="s">
         <v>720</v>
       </c>
-      <c r="E21" s="34" t="s">
-        <v>720</v>
-      </c>
-      <c r="F21" s="35" t="s">
+      <c r="H21" s="36" t="s">
         <v>721</v>
       </c>
-      <c r="G21" s="36" t="s">
+      <c r="I21" s="15" t="s">
         <v>722</v>
-      </c>
-      <c r="H21" s="36" t="s">
-        <v>723</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>724</v>
       </c>
       <c r="K21" t="s">
         <v>84</v>
       </c>
       <c r="L21" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M21" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="M21" s="7" t="s">
+      <c r="N21" s="7" t="s">
         <v>646</v>
       </c>
-      <c r="N21" s="7" t="s">
+      <c r="O21" s="7" t="s">
         <v>647</v>
       </c>
-      <c r="O21" s="7" t="s">
+      <c r="P21" s="13" t="s">
         <v>648</v>
-      </c>
-      <c r="P21" s="13" t="s">
-        <v>649</v>
       </c>
       <c r="Q21" s="16">
         <v>30610002</v>
@@ -9675,40 +9800,40 @@
         <v>1</v>
       </c>
       <c r="D22" s="31" t="s">
+        <v>723</v>
+      </c>
+      <c r="E22" s="31" t="s">
+        <v>723</v>
+      </c>
+      <c r="F22" s="40" t="s">
+        <v>724</v>
+      </c>
+      <c r="G22" s="40" t="s">
         <v>725</v>
       </c>
-      <c r="E22" s="31" t="s">
-        <v>725</v>
-      </c>
-      <c r="F22" s="40" t="s">
+      <c r="H22" s="40" t="s">
         <v>726</v>
       </c>
-      <c r="G22" s="40" t="s">
+      <c r="I22" s="15" t="s">
         <v>727</v>
-      </c>
-      <c r="H22" s="40" t="s">
-        <v>728</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>729</v>
       </c>
       <c r="K22" t="s">
         <v>84</v>
       </c>
       <c r="L22" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M22" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="M22" s="7" t="s">
+      <c r="N22" s="7" t="s">
         <v>646</v>
       </c>
-      <c r="N22" s="7" t="s">
+      <c r="O22" s="7" t="s">
         <v>647</v>
       </c>
-      <c r="O22" s="7" t="s">
+      <c r="P22" s="13" t="s">
         <v>648</v>
-      </c>
-      <c r="P22" s="13" t="s">
-        <v>649</v>
       </c>
       <c r="Q22" s="16">
         <v>30610003</v>
@@ -9722,40 +9847,40 @@
         <v>1</v>
       </c>
       <c r="D23" s="31" t="s">
+        <v>728</v>
+      </c>
+      <c r="E23" s="31" t="s">
+        <v>729</v>
+      </c>
+      <c r="F23" s="15" t="s">
         <v>730</v>
       </c>
-      <c r="E23" s="31" t="s">
+      <c r="G23" s="15" t="s">
         <v>731</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="H23" s="42" t="s">
         <v>732</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="I23" s="15" t="s">
         <v>733</v>
-      </c>
-      <c r="H23" s="42" t="s">
-        <v>734</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>735</v>
       </c>
       <c r="K23" t="s">
         <v>84</v>
       </c>
       <c r="L23" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M23" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="M23" s="7" t="s">
+      <c r="N23" s="7" t="s">
         <v>646</v>
       </c>
-      <c r="N23" s="7" t="s">
+      <c r="O23" s="7" t="s">
         <v>647</v>
       </c>
-      <c r="O23" s="7" t="s">
+      <c r="P23" s="13" t="s">
         <v>648</v>
-      </c>
-      <c r="P23" s="13" t="s">
-        <v>649</v>
       </c>
       <c r="Q23" s="16">
         <v>30610004</v>
@@ -9769,40 +9894,40 @@
         <v>1</v>
       </c>
       <c r="D24" s="31" t="s">
+        <v>734</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>735</v>
+      </c>
+      <c r="F24" s="15" t="s">
         <v>736</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="G24" s="43" t="s">
         <v>737</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="H24" s="43" t="s">
         <v>738</v>
       </c>
-      <c r="G24" s="43" t="s">
+      <c r="I24" s="15" t="s">
         <v>739</v>
-      </c>
-      <c r="H24" s="43" t="s">
-        <v>740</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>741</v>
       </c>
       <c r="K24" t="s">
         <v>84</v>
       </c>
       <c r="L24" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M24" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="M24" s="7" t="s">
+      <c r="N24" s="7" t="s">
         <v>646</v>
       </c>
-      <c r="N24" s="7" t="s">
+      <c r="O24" s="7" t="s">
         <v>647</v>
       </c>
-      <c r="O24" s="7" t="s">
+      <c r="P24" s="13" t="s">
         <v>648</v>
-      </c>
-      <c r="P24" s="13" t="s">
-        <v>649</v>
       </c>
       <c r="Q24" s="16">
         <v>30610005</v>
@@ -9816,40 +9941,40 @@
         <v>1</v>
       </c>
       <c r="D25" s="45" t="s">
+        <v>740</v>
+      </c>
+      <c r="E25" s="45" t="s">
+        <v>741</v>
+      </c>
+      <c r="F25" s="46" t="s">
         <v>742</v>
       </c>
-      <c r="E25" s="45" t="s">
+      <c r="G25" s="47" t="s">
         <v>743</v>
       </c>
-      <c r="F25" s="46" t="s">
+      <c r="H25" s="47" t="s">
         <v>744</v>
       </c>
-      <c r="G25" s="47" t="s">
+      <c r="I25" s="15" t="s">
         <v>745</v>
-      </c>
-      <c r="H25" s="47" t="s">
-        <v>746</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>747</v>
       </c>
       <c r="K25" t="s">
         <v>84</v>
       </c>
       <c r="L25" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="N25" s="25" t="s">
         <v>693</v>
       </c>
-      <c r="M25" s="9" t="s">
+      <c r="O25" s="25" t="s">
         <v>694</v>
       </c>
-      <c r="N25" s="25" t="s">
+      <c r="P25" s="25" t="s">
         <v>695</v>
-      </c>
-      <c r="O25" s="25" t="s">
-        <v>696</v>
-      </c>
-      <c r="P25" s="25" t="s">
-        <v>697</v>
       </c>
       <c r="Q25" s="16">
         <v>30610006</v>

--- a/source/bin/excel/audio.xlsx
+++ b/source/bin/excel/audio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F9B814-59F5-45C6-8383-7BF11D7AFD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A0896C-40AB-4D3A-96F1-FF042C0A29ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="790">
   <si>
     <t>sheet</t>
   </si>
@@ -1122,9 +1122,6 @@
     <t>庙会_进入界面</t>
   </si>
   <si>
-    <t>audio/audio_event/2501chunjie_activity_enter</t>
-  </si>
-  <si>
     <t>庙会_窗口打开、祈愿打开&amp;切换</t>
   </si>
   <si>
@@ -1162,9 +1159,6 @@
   </si>
   <si>
     <t>庙会_技能升级</t>
-  </si>
-  <si>
-    <t>audio/audio_event/2501chunjie_skill_level_up</t>
   </si>
   <si>
     <t>庙会_等级提升_大（level14~17）</t>
@@ -2427,6 +2421,58 @@
   </si>
   <si>
     <t>ui/activity/extend/2604dj/main/audio/2604dj_village_bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2604剑域誓约_进入主界面时播放</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2501chunjie_activity_enter</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio/audio_event/2501chunjie_skill_level_up</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2604dj/main/audio/2604dj_activity_enter</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/festival/main/audio/2404ba_success</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2604剑域誓约_通关成功</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2604剑域誓约_通关失败</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2604剑域誓约_进入任务/奖励/剧情/对局界面</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2604dj/main/audio/2604dj_ui_open</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2604剑域誓约_角色出现刷光</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2604dj/main/audio/2604dj_character_show</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2604剑域誓约_合成</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2604dj/main/audio/2604dj_crafting</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -3184,7 +3230,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E422"/>
+  <dimension ref="A1:E428"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.875" customWidth="1"/>
@@ -3876,13 +3922,13 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="15" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B58" s="29">
         <v>157</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="E58" t="s">
         <v>20</v>
@@ -6315,7 +6361,7 @@
         <v>10301</v>
       </c>
       <c r="C228" s="41" t="s">
-        <v>353</v>
+        <v>778</v>
       </c>
       <c r="D228" s="15"/>
       <c r="E228" t="s">
@@ -6324,13 +6370,13 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" s="15" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B229" s="41">
         <v>10302</v>
       </c>
       <c r="C229" s="41" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D229" s="15"/>
       <c r="E229" t="s">
@@ -6339,13 +6385,13 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" s="15" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B230" s="41">
         <v>10303</v>
       </c>
       <c r="C230" s="41" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D230" s="15"/>
       <c r="E230" t="s">
@@ -6354,13 +6400,13 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" s="15" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B231" s="41">
         <v>10304</v>
       </c>
       <c r="C231" s="41" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D231" s="15"/>
       <c r="E231" t="s">
@@ -6369,13 +6415,13 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" s="15" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B232" s="41">
         <v>10305</v>
       </c>
       <c r="C232" s="41" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D232" s="15"/>
       <c r="E232" t="s">
@@ -6384,13 +6430,13 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" s="15" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B233" s="41">
         <v>10306</v>
       </c>
       <c r="C233" s="41" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D233" s="15"/>
       <c r="E233" t="s">
@@ -6399,13 +6445,13 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" s="15" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B234" s="41">
         <v>10307</v>
       </c>
       <c r="C234" s="41" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D234" s="15"/>
       <c r="E234" t="s">
@@ -6414,13 +6460,13 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" s="15" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B235" s="41">
         <v>10308</v>
       </c>
       <c r="C235" s="41" t="s">
-        <v>367</v>
+        <v>779</v>
       </c>
       <c r="D235" s="15"/>
       <c r="E235" t="s">
@@ -6429,13 +6475,13 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B236" s="41">
         <v>10309</v>
       </c>
       <c r="C236" s="41" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D236" s="15"/>
       <c r="E236" t="s">
@@ -6444,13 +6490,13 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B237" s="41">
         <v>10310</v>
       </c>
       <c r="C237" s="41" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D237" s="15"/>
       <c r="E237" t="s">
@@ -6459,13 +6505,13 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" s="15" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B238" s="41">
         <v>10311</v>
       </c>
       <c r="C238" s="41" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D238" s="15"/>
       <c r="E238" t="s">
@@ -6474,13 +6520,13 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" s="15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B239" s="41">
         <v>10312</v>
       </c>
       <c r="C239" s="41" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D239" s="15"/>
       <c r="E239" t="s">
@@ -6489,13 +6535,13 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" s="15" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B240" s="41">
         <v>10313</v>
       </c>
       <c r="C240" s="41" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D240" s="15"/>
       <c r="E240" t="s">
@@ -6504,13 +6550,13 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" s="15" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B241" s="41">
         <v>10314</v>
       </c>
       <c r="C241" s="41" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D241" s="15"/>
       <c r="E241" t="s">
@@ -6519,13 +6565,13 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B242" s="41">
         <v>10315</v>
       </c>
       <c r="C242" s="41" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D242" s="15"/>
       <c r="E242" t="s">
@@ -6534,13 +6580,13 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" s="15" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B243" s="41">
         <v>10316</v>
       </c>
       <c r="C243" s="41" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D243" s="15"/>
       <c r="E243" t="s">
@@ -6549,13 +6595,13 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" s="15" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B244" s="41">
         <v>10317</v>
       </c>
       <c r="C244" s="41" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D244" s="15"/>
       <c r="E244" t="s">
@@ -6564,13 +6610,13 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" s="15" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B245" s="41">
         <v>10318</v>
       </c>
       <c r="C245" s="41" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D245" s="15"/>
       <c r="E245" t="s">
@@ -6579,13 +6625,13 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" s="15" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B246" s="41">
         <v>10319</v>
       </c>
       <c r="C246" s="41" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D246" s="15"/>
       <c r="E246" t="s">
@@ -6594,13 +6640,13 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" s="15" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B247" s="41">
         <v>10320</v>
       </c>
       <c r="C247" s="41" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D247" s="15"/>
       <c r="E247" t="s">
@@ -6609,13 +6655,13 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" s="15" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B248" s="41">
         <v>10321</v>
       </c>
       <c r="C248" s="41" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D248" s="15"/>
       <c r="E248" t="s">
@@ -6624,13 +6670,13 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" s="15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B249" s="41">
         <v>10322</v>
       </c>
       <c r="C249" s="41" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D249" s="15"/>
       <c r="E249" t="s">
@@ -6639,13 +6685,13 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" s="15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B250" s="41">
         <v>10323</v>
       </c>
       <c r="C250" s="41" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D250" s="15"/>
       <c r="E250" t="s">
@@ -6654,13 +6700,13 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" s="15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B251" s="41">
         <v>10324</v>
       </c>
       <c r="C251" s="41" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D251" s="15"/>
       <c r="E251" t="s">
@@ -6669,13 +6715,13 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" s="15" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B252" s="41">
         <v>10325</v>
       </c>
       <c r="C252" s="41" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D252" s="15"/>
       <c r="E252" t="s">
@@ -6684,13 +6730,13 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" s="15" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B253" s="41">
         <v>10326</v>
       </c>
       <c r="C253" s="41" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D253" s="15"/>
       <c r="E253" t="s">
@@ -6699,13 +6745,13 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" s="15" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B254" s="41">
         <v>10327</v>
       </c>
       <c r="C254" s="41" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D254" s="15"/>
       <c r="E254" t="s">
@@ -6714,13 +6760,13 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" s="15" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B255" s="41">
         <v>10328</v>
       </c>
       <c r="C255" s="41" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D255" s="15"/>
       <c r="E255" t="s">
@@ -6729,13 +6775,13 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256" s="15" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B256" s="41">
         <v>10329</v>
       </c>
       <c r="C256" s="41" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D256" s="15"/>
       <c r="E256" t="s">
@@ -6744,13 +6790,13 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257" s="15" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B257" s="41">
         <v>10330</v>
       </c>
       <c r="C257" s="41" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D257" s="15"/>
       <c r="E257" t="s">
@@ -6759,13 +6805,13 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" s="15" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B258" s="41">
         <v>10331</v>
       </c>
       <c r="C258" s="41" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D258" s="15">
         <v>60000</v>
@@ -6776,13 +6822,13 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" s="15" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B259" s="41">
         <v>10332</v>
       </c>
       <c r="C259" s="41" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D259" s="15">
         <v>60000</v>
@@ -6793,13 +6839,13 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" s="15" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B260" s="41">
         <v>10333</v>
       </c>
       <c r="C260" s="41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D260" s="15"/>
       <c r="E260" t="s">
@@ -6808,13 +6854,13 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" s="15" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B261" s="41">
         <v>10334</v>
       </c>
       <c r="C261" s="41" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D261" s="15"/>
       <c r="E261" t="s">
@@ -6823,13 +6869,13 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" s="15" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B262" s="41">
         <v>10335</v>
       </c>
       <c r="C262" s="41" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D262" s="15"/>
       <c r="E262" t="s">
@@ -6838,13 +6884,13 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" s="15" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B263" s="41">
         <v>10336</v>
       </c>
       <c r="C263" s="41" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D263" s="15"/>
       <c r="E263" t="s">
@@ -6853,13 +6899,13 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" s="15" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B264" s="41">
         <v>10337</v>
       </c>
       <c r="C264" s="41" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D264" s="15"/>
       <c r="E264" t="s">
@@ -6868,13 +6914,13 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" s="15" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B265" s="41">
         <v>10338</v>
       </c>
       <c r="C265" s="41" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D265" s="15"/>
       <c r="E265" t="s">
@@ -6883,13 +6929,13 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" s="15" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B266" s="41">
         <v>10339</v>
       </c>
       <c r="C266" s="41" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D266" s="15"/>
       <c r="E266" t="s">
@@ -6898,13 +6944,13 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" s="15" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B267" s="41">
         <v>10340</v>
       </c>
       <c r="C267" s="41" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D267" s="15"/>
       <c r="E267" t="s">
@@ -6913,13 +6959,13 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" s="15" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B268" s="41">
         <v>10341</v>
       </c>
       <c r="C268" s="41" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D268" s="15"/>
       <c r="E268" t="s">
@@ -6928,13 +6974,13 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" s="15" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B269" s="41">
         <v>10342</v>
       </c>
       <c r="C269" s="41" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D269" s="15"/>
       <c r="E269" s="15" t="s">
@@ -6943,13 +6989,13 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" s="15" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B270" s="41">
         <v>10350</v>
       </c>
       <c r="C270" s="41" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D270" s="15"/>
       <c r="E270" t="s">
@@ -6958,13 +7004,13 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" s="15" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B271" s="41">
         <v>10351</v>
       </c>
       <c r="C271" s="41" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D271" s="15"/>
       <c r="E271" t="s">
@@ -6973,13 +7019,13 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" s="15" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B272" s="41">
         <v>10352</v>
       </c>
       <c r="C272" s="41" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D272" s="15"/>
       <c r="E272" t="s">
@@ -6988,13 +7034,13 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" s="15" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B273" s="41">
         <v>10353</v>
       </c>
       <c r="C273" s="41" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D273" s="15"/>
       <c r="E273" t="s">
@@ -7003,13 +7049,13 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274" s="15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B274" s="41">
         <v>10354</v>
       </c>
       <c r="C274" s="41" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D274" s="15"/>
       <c r="E274" t="s">
@@ -7018,13 +7064,13 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A275" s="15" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B275" s="41">
         <v>10355</v>
       </c>
       <c r="C275" s="41" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D275" s="15"/>
       <c r="E275" t="s">
@@ -7033,13 +7079,13 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276" s="15" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B276" s="41">
         <v>10356</v>
       </c>
       <c r="C276" s="41" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D276" s="15"/>
       <c r="E276" t="s">
@@ -7048,13 +7094,13 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277" s="15" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B277" s="41">
         <v>10357</v>
       </c>
       <c r="C277" s="41" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D277" s="15"/>
       <c r="E277" t="s">
@@ -7063,13 +7109,13 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" s="15" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B278" s="41">
         <v>10358</v>
       </c>
       <c r="C278" s="41" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D278" s="15"/>
       <c r="E278" t="s">
@@ -7078,13 +7124,13 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" s="15" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B279" s="41">
         <v>10359</v>
       </c>
       <c r="C279" s="41" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D279" s="15"/>
       <c r="E279" t="s">
@@ -7093,13 +7139,13 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280" s="15" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B280" s="41">
         <v>10360</v>
       </c>
       <c r="C280" s="41" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D280" s="15"/>
       <c r="E280" t="s">
@@ -7108,13 +7154,13 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A281" s="15" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B281" s="41">
         <v>10361</v>
       </c>
       <c r="C281" s="41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D281" s="15"/>
       <c r="E281" t="s">
@@ -7123,13 +7169,13 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A282" s="15" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B282" s="41">
         <v>10362</v>
       </c>
       <c r="C282" s="41" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D282" s="15"/>
       <c r="E282" t="s">
@@ -7138,13 +7184,13 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A283" s="15" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B283" s="41">
         <v>10363</v>
       </c>
       <c r="C283" s="41" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D283" s="15"/>
       <c r="E283" t="s">
@@ -7153,13 +7199,13 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A284" s="15" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B284" s="41">
         <v>10364</v>
       </c>
       <c r="C284" s="41" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D284" s="15"/>
       <c r="E284" t="s">
@@ -7168,13 +7214,13 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A285" s="15" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B285" s="41">
         <v>10365</v>
       </c>
       <c r="C285" s="41" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D285" s="15"/>
       <c r="E285" t="s">
@@ -7183,13 +7229,13 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A286" s="15" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B286" s="41">
         <v>10366</v>
       </c>
       <c r="C286" s="41" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D286" s="15"/>
       <c r="E286" t="s">
@@ -7198,13 +7244,13 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A287" s="15" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B287" s="41">
         <v>10367</v>
       </c>
       <c r="C287" s="41" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D287" s="15"/>
       <c r="E287" t="s">
@@ -7213,13 +7259,13 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A288" s="15" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B288" s="41">
         <v>10368</v>
       </c>
       <c r="C288" s="41" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D288" s="15"/>
       <c r="E288" t="s">
@@ -7228,13 +7274,13 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" s="15" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B289" s="41">
         <v>10369</v>
       </c>
       <c r="C289" s="41" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D289" s="15"/>
       <c r="E289" t="s">
@@ -7243,13 +7289,13 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" s="15" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B290" s="15">
         <v>10370</v>
       </c>
       <c r="C290" s="15" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D290" s="15"/>
       <c r="E290" t="s">
@@ -7258,13 +7304,13 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" s="15" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B291" s="15">
         <v>10371</v>
       </c>
       <c r="C291" s="15" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D291" s="15"/>
       <c r="E291" t="s">
@@ -7273,13 +7319,13 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292" s="15" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B292" s="15">
         <v>10372</v>
       </c>
       <c r="C292" s="15" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D292" s="15"/>
       <c r="E292" t="s">
@@ -7288,13 +7334,13 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293" s="15" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B293" s="15">
         <v>10373</v>
       </c>
       <c r="C293" s="15" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D293" s="15"/>
       <c r="E293" t="s">
@@ -7303,13 +7349,13 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294" s="15" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B294" s="15">
         <v>10374</v>
       </c>
       <c r="C294" s="15" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D294" s="15"/>
       <c r="E294" t="s">
@@ -7318,13 +7364,13 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A295" s="15" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B295" s="15">
         <v>10375</v>
       </c>
       <c r="C295" s="15" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D295" s="15"/>
       <c r="E295" t="s">
@@ -7333,13 +7379,13 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A296" s="15" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B296" s="15">
         <v>10376</v>
       </c>
       <c r="C296" s="15" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D296" s="15"/>
       <c r="E296" t="s">
@@ -7348,13 +7394,13 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A297" s="15" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B297" s="15">
         <v>10377</v>
       </c>
       <c r="C297" s="15" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D297" s="15"/>
       <c r="E297" t="s">
@@ -7363,13 +7409,13 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A298" s="15" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B298" s="15">
         <v>10378</v>
       </c>
       <c r="C298" s="15" t="s">
-        <v>204</v>
+        <v>781</v>
       </c>
       <c r="D298" s="15"/>
       <c r="E298" t="s">
@@ -7378,7 +7424,7 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299" s="15" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B299" s="15">
         <v>10379</v>
@@ -7393,7 +7439,7 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" s="15" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B300" s="15">
         <v>10380</v>
@@ -7408,13 +7454,13 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" s="52" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B301" s="52">
         <v>10381</v>
       </c>
       <c r="C301" s="15" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D301" s="15"/>
       <c r="E301" t="s">
@@ -7423,13 +7469,13 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" s="52" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B302" s="52">
         <v>10382</v>
       </c>
       <c r="C302" s="15" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D302" s="15"/>
       <c r="E302" t="s">
@@ -7438,13 +7484,13 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" s="52" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B303" s="52">
         <v>10383</v>
       </c>
       <c r="C303" s="15" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D303" s="15"/>
       <c r="E303" t="s">
@@ -7453,13 +7499,13 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304" s="52" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B304" s="52">
         <v>10384</v>
       </c>
       <c r="C304" s="15" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D304" s="15"/>
       <c r="E304" t="s">
@@ -7468,13 +7514,13 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305" s="52" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B305" s="52">
         <v>10385</v>
       </c>
       <c r="C305" s="15" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D305" s="15"/>
       <c r="E305" t="s">
@@ -7483,13 +7529,13 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" s="52" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B306" s="52">
         <v>10386</v>
       </c>
       <c r="C306" s="15" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D306" s="15"/>
       <c r="E306" t="s">
@@ -7498,13 +7544,13 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" s="52" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B307" s="52">
         <v>10387</v>
       </c>
       <c r="C307" s="15" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D307" s="15"/>
       <c r="E307" t="s">
@@ -7513,13 +7559,13 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308" s="52" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B308" s="52">
         <v>10388</v>
       </c>
       <c r="C308" s="15" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D308" s="15"/>
       <c r="E308" t="s">
@@ -7528,13 +7574,13 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309" s="52" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B309" s="52">
         <v>10389</v>
       </c>
       <c r="C309" s="15" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D309" s="15"/>
       <c r="E309" t="s">
@@ -7543,13 +7589,13 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A310" s="52" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B310" s="52">
         <v>10390</v>
       </c>
       <c r="C310" s="15" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D310" s="15"/>
       <c r="E310" t="s">
@@ -7558,13 +7604,13 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A311" s="52" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B311" s="52">
         <v>10391</v>
       </c>
       <c r="C311" s="15" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D311" s="15"/>
       <c r="E311" t="s">
@@ -7573,13 +7619,13 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A312" s="52" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B312" s="52">
         <v>10392</v>
       </c>
       <c r="C312" s="15" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D312" s="15"/>
       <c r="E312" t="s">
@@ -7587,98 +7633,104 @@
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B313">
-        <v>305032</v>
-      </c>
-      <c r="C313" t="s">
-        <v>493</v>
-      </c>
-      <c r="D313">
-        <v>1314</v>
-      </c>
+      <c r="A313" s="52" t="s">
+        <v>777</v>
+      </c>
+      <c r="B313" s="52">
+        <v>10393</v>
+      </c>
+      <c r="C313" s="15" t="s">
+        <v>780</v>
+      </c>
+      <c r="D313" s="15"/>
       <c r="E313" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B314">
-        <v>305033</v>
-      </c>
-      <c r="C314" t="s">
-        <v>494</v>
-      </c>
-      <c r="D314">
-        <v>1445</v>
-      </c>
+      <c r="A314" s="52" t="s">
+        <v>782</v>
+      </c>
+      <c r="B314" s="52">
+        <v>10394</v>
+      </c>
+      <c r="C314" s="15" t="s">
+        <v>781</v>
+      </c>
+      <c r="D314" s="15"/>
       <c r="E314" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B315">
-        <v>305034</v>
-      </c>
-      <c r="C315" t="s">
-        <v>495</v>
-      </c>
-      <c r="D315">
-        <v>2098</v>
-      </c>
+      <c r="A315" s="52" t="s">
+        <v>783</v>
+      </c>
+      <c r="B315" s="52">
+        <v>10395</v>
+      </c>
+      <c r="C315" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="D315" s="15"/>
       <c r="E315" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B316">
-        <v>305035</v>
-      </c>
-      <c r="C316" t="s">
-        <v>496</v>
-      </c>
-      <c r="D316">
-        <v>1523</v>
-      </c>
+      <c r="A316" s="52" t="s">
+        <v>784</v>
+      </c>
+      <c r="B316" s="52">
+        <v>10396</v>
+      </c>
+      <c r="C316" s="15" t="s">
+        <v>785</v>
+      </c>
+      <c r="D316" s="15"/>
       <c r="E316" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B317">
-        <v>305036</v>
+      <c r="A317" s="52" t="s">
+        <v>786</v>
+      </c>
+      <c r="B317" s="52">
+        <v>10397</v>
       </c>
       <c r="C317" s="15" t="s">
-        <v>497</v>
-      </c>
-      <c r="D317">
-        <v>1915</v>
-      </c>
+        <v>787</v>
+      </c>
+      <c r="D317" s="15"/>
       <c r="E317" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B318">
-        <v>305037</v>
-      </c>
-      <c r="C318" t="s">
-        <v>498</v>
-      </c>
-      <c r="D318">
-        <v>1200</v>
-      </c>
+      <c r="A318" s="52" t="s">
+        <v>788</v>
+      </c>
+      <c r="B318" s="52">
+        <v>10398</v>
+      </c>
+      <c r="C318" s="15" t="s">
+        <v>789</v>
+      </c>
+      <c r="D318" s="15"/>
       <c r="E318" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B319">
-        <v>305038</v>
+        <v>305032</v>
       </c>
       <c r="C319" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="D319">
-        <v>2500</v>
+        <v>1314</v>
       </c>
       <c r="E319" t="s">
         <v>114</v>
@@ -7686,13 +7738,13 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B320">
-        <v>305039</v>
+        <v>305033</v>
       </c>
       <c r="C320" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="D320">
-        <v>1200</v>
+        <v>1445</v>
       </c>
       <c r="E320" t="s">
         <v>114</v>
@@ -7700,13 +7752,13 @@
     </row>
     <row r="321" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B321">
-        <v>305040</v>
+        <v>305034</v>
       </c>
       <c r="C321" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="D321">
-        <v>2500</v>
+        <v>2098</v>
       </c>
       <c r="E321" t="s">
         <v>114</v>
@@ -7714,10 +7766,13 @@
     </row>
     <row r="322" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B322">
-        <v>305200</v>
+        <v>305035</v>
       </c>
       <c r="C322" t="s">
-        <v>502</v>
+        <v>494</v>
+      </c>
+      <c r="D322">
+        <v>1523</v>
       </c>
       <c r="E322" t="s">
         <v>114</v>
@@ -7725,10 +7780,13 @@
     </row>
     <row r="323" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B323">
-        <v>305201</v>
-      </c>
-      <c r="C323" t="s">
-        <v>503</v>
+        <v>305036</v>
+      </c>
+      <c r="C323" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="D323">
+        <v>1915</v>
       </c>
       <c r="E323" t="s">
         <v>114</v>
@@ -7736,10 +7794,13 @@
     </row>
     <row r="324" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B324">
-        <v>305202</v>
+        <v>305037</v>
       </c>
       <c r="C324" t="s">
-        <v>504</v>
+        <v>496</v>
+      </c>
+      <c r="D324">
+        <v>1200</v>
       </c>
       <c r="E324" t="s">
         <v>114</v>
@@ -7747,10 +7808,13 @@
     </row>
     <row r="325" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B325">
-        <v>305203</v>
+        <v>305038</v>
       </c>
       <c r="C325" t="s">
-        <v>505</v>
+        <v>497</v>
+      </c>
+      <c r="D325">
+        <v>2500</v>
       </c>
       <c r="E325" t="s">
         <v>114</v>
@@ -7758,10 +7822,13 @@
     </row>
     <row r="326" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B326">
-        <v>305204</v>
+        <v>305039</v>
       </c>
       <c r="C326" t="s">
-        <v>506</v>
+        <v>498</v>
+      </c>
+      <c r="D326">
+        <v>1200</v>
       </c>
       <c r="E326" t="s">
         <v>114</v>
@@ -7769,10 +7836,13 @@
     </row>
     <row r="327" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B327">
-        <v>305205</v>
+        <v>305040</v>
       </c>
       <c r="C327" t="s">
-        <v>507</v>
+        <v>499</v>
+      </c>
+      <c r="D327">
+        <v>2500</v>
       </c>
       <c r="E327" t="s">
         <v>114</v>
@@ -7780,10 +7850,10 @@
     </row>
     <row r="328" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B328">
-        <v>305206</v>
+        <v>305200</v>
       </c>
       <c r="C328" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="E328" t="s">
         <v>114</v>
@@ -7791,10 +7861,10 @@
     </row>
     <row r="329" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B329">
-        <v>305207</v>
+        <v>305201</v>
       </c>
       <c r="C329" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="E329" t="s">
         <v>114</v>
@@ -7802,10 +7872,10 @@
     </row>
     <row r="330" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B330">
-        <v>305208</v>
+        <v>305202</v>
       </c>
       <c r="C330" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="E330" t="s">
         <v>114</v>
@@ -7813,10 +7883,10 @@
     </row>
     <row r="331" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B331">
-        <v>305209</v>
+        <v>305203</v>
       </c>
       <c r="C331" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="E331" t="s">
         <v>114</v>
@@ -7824,10 +7894,10 @@
     </row>
     <row r="332" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B332">
-        <v>305210</v>
+        <v>305204</v>
       </c>
       <c r="C332" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="E332" t="s">
         <v>114</v>
@@ -7835,10 +7905,10 @@
     </row>
     <row r="333" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B333">
-        <v>305211</v>
+        <v>305205</v>
       </c>
       <c r="C333" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="E333" t="s">
         <v>114</v>
@@ -7846,10 +7916,10 @@
     </row>
     <row r="334" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B334">
-        <v>305212</v>
+        <v>305206</v>
       </c>
       <c r="C334" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="E334" t="s">
         <v>114</v>
@@ -7857,10 +7927,10 @@
     </row>
     <row r="335" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B335">
-        <v>305213</v>
+        <v>305207</v>
       </c>
       <c r="C335" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="E335" t="s">
         <v>114</v>
@@ -7868,7 +7938,10 @@
     </row>
     <row r="336" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B336">
-        <v>305214</v>
+        <v>305208</v>
+      </c>
+      <c r="C336" t="s">
+        <v>508</v>
       </c>
       <c r="E336" t="s">
         <v>114</v>
@@ -7876,10 +7949,10 @@
     </row>
     <row r="337" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B337">
-        <v>305215</v>
+        <v>305209</v>
       </c>
       <c r="C337" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="E337" t="s">
         <v>114</v>
@@ -7887,10 +7960,10 @@
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B338">
-        <v>305216</v>
+        <v>305210</v>
       </c>
       <c r="C338" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="E338" t="s">
         <v>114</v>
@@ -7898,10 +7971,10 @@
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B339">
-        <v>305217</v>
+        <v>305211</v>
       </c>
       <c r="C339" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="E339" t="s">
         <v>114</v>
@@ -7909,10 +7982,10 @@
     </row>
     <row r="340" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B340">
-        <v>305218</v>
+        <v>305212</v>
       </c>
       <c r="C340" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="E340" t="s">
         <v>114</v>
@@ -7920,10 +7993,10 @@
     </row>
     <row r="341" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B341">
-        <v>305219</v>
+        <v>305213</v>
       </c>
       <c r="C341" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="E341" t="s">
         <v>114</v>
@@ -7931,10 +8004,7 @@
     </row>
     <row r="342" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B342">
-        <v>305220</v>
-      </c>
-      <c r="C342" t="s">
-        <v>521</v>
+        <v>305214</v>
       </c>
       <c r="E342" t="s">
         <v>114</v>
@@ -7942,10 +8012,10 @@
     </row>
     <row r="343" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B343">
-        <v>305221</v>
-      </c>
-      <c r="C343" s="15" t="s">
-        <v>522</v>
+        <v>305215</v>
+      </c>
+      <c r="C343" t="s">
+        <v>514</v>
       </c>
       <c r="E343" t="s">
         <v>114</v>
@@ -7953,10 +8023,10 @@
     </row>
     <row r="344" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B344">
-        <v>305222</v>
-      </c>
-      <c r="C344" s="15" t="s">
-        <v>523</v>
+        <v>305216</v>
+      </c>
+      <c r="C344" t="s">
+        <v>515</v>
       </c>
       <c r="E344" t="s">
         <v>114</v>
@@ -7964,10 +8034,10 @@
     </row>
     <row r="345" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B345">
-        <v>305223</v>
+        <v>305217</v>
       </c>
       <c r="C345" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="E345" t="s">
         <v>114</v>
@@ -7975,10 +8045,10 @@
     </row>
     <row r="346" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B346">
-        <v>30520001</v>
-      </c>
-      <c r="C346" s="15" t="s">
-        <v>525</v>
+        <v>305218</v>
+      </c>
+      <c r="C346" t="s">
+        <v>517</v>
       </c>
       <c r="E346" t="s">
         <v>114</v>
@@ -7986,10 +8056,10 @@
     </row>
     <row r="347" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B347">
-        <v>30520002</v>
-      </c>
-      <c r="C347" s="15" t="s">
-        <v>526</v>
+        <v>305219</v>
+      </c>
+      <c r="C347" t="s">
+        <v>518</v>
       </c>
       <c r="E347" t="s">
         <v>114</v>
@@ -7997,10 +8067,10 @@
     </row>
     <row r="348" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B348">
-        <v>30520003</v>
-      </c>
-      <c r="C348" s="15" t="s">
-        <v>527</v>
+        <v>305220</v>
+      </c>
+      <c r="C348" t="s">
+        <v>519</v>
       </c>
       <c r="E348" t="s">
         <v>114</v>
@@ -8008,10 +8078,10 @@
     </row>
     <row r="349" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B349">
-        <v>30520004</v>
+        <v>305221</v>
       </c>
       <c r="C349" s="15" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="E349" t="s">
         <v>114</v>
@@ -8019,10 +8089,10 @@
     </row>
     <row r="350" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B350">
-        <v>30520005</v>
+        <v>305222</v>
       </c>
       <c r="C350" s="15" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="E350" t="s">
         <v>114</v>
@@ -8030,10 +8100,10 @@
     </row>
     <row r="351" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B351">
-        <v>30520006</v>
-      </c>
-      <c r="C351" s="15" t="s">
-        <v>530</v>
+        <v>305223</v>
+      </c>
+      <c r="C351" t="s">
+        <v>522</v>
       </c>
       <c r="E351" t="s">
         <v>114</v>
@@ -8041,10 +8111,10 @@
     </row>
     <row r="352" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B352">
-        <v>30520007</v>
+        <v>30520001</v>
       </c>
       <c r="C352" s="15" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="E352" t="s">
         <v>114</v>
@@ -8052,67 +8122,65 @@
     </row>
     <row r="353" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B353">
-        <v>30520008</v>
+        <v>30520002</v>
       </c>
       <c r="C353" s="15" t="s">
-        <v>532</v>
-      </c>
-      <c r="E353" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="E353" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="354" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B354">
-        <v>30520009</v>
+        <v>30520003</v>
       </c>
       <c r="C354" s="15" t="s">
-        <v>533</v>
-      </c>
-      <c r="E354" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="E354" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="355" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B355">
-        <v>30520010</v>
+        <v>30520004</v>
       </c>
       <c r="C355" s="15" t="s">
-        <v>534</v>
-      </c>
-      <c r="E355" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="E355" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="356" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B356" s="17">
-        <v>30520011</v>
-      </c>
-      <c r="C356" s="18" t="s">
-        <v>535</v>
-      </c>
-      <c r="D356" s="17"/>
-      <c r="E356" s="15" t="s">
+      <c r="B356">
+        <v>30520005</v>
+      </c>
+      <c r="C356" s="15" t="s">
+        <v>527</v>
+      </c>
+      <c r="E356" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="357" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B357">
-        <v>30520012</v>
-      </c>
-      <c r="C357" s="18" t="s">
-        <v>747</v>
-      </c>
-      <c r="D357" s="17"/>
-      <c r="E357" s="15" t="s">
+        <v>30520006</v>
+      </c>
+      <c r="C357" s="15" t="s">
+        <v>528</v>
+      </c>
+      <c r="E357" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="358" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B358">
-        <v>305224</v>
-      </c>
-      <c r="C358" t="s">
-        <v>536</v>
+        <v>30520007</v>
+      </c>
+      <c r="C358" s="15" t="s">
+        <v>529</v>
       </c>
       <c r="E358" t="s">
         <v>114</v>
@@ -8120,65 +8188,67 @@
     </row>
     <row r="359" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B359">
-        <v>305225</v>
-      </c>
-      <c r="C359" t="s">
-        <v>537</v>
-      </c>
-      <c r="E359" t="s">
+        <v>30520008</v>
+      </c>
+      <c r="C359" s="15" t="s">
+        <v>530</v>
+      </c>
+      <c r="E359" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="360" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B360">
-        <v>305226</v>
-      </c>
-      <c r="C360" t="s">
-        <v>538</v>
-      </c>
-      <c r="E360" t="s">
+        <v>30520009</v>
+      </c>
+      <c r="C360" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="E360" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="361" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B361">
-        <v>305300</v>
-      </c>
-      <c r="C361" t="s">
-        <v>539</v>
-      </c>
-      <c r="E361" t="s">
+        <v>30520010</v>
+      </c>
+      <c r="C361" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="E361" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="362" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B362">
-        <v>305301</v>
-      </c>
-      <c r="C362" t="s">
-        <v>540</v>
-      </c>
-      <c r="E362" t="s">
+      <c r="B362" s="17">
+        <v>30520011</v>
+      </c>
+      <c r="C362" s="18" t="s">
+        <v>533</v>
+      </c>
+      <c r="D362" s="17"/>
+      <c r="E362" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="363" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B363">
-        <v>305302</v>
-      </c>
-      <c r="C363" t="s">
-        <v>541</v>
-      </c>
-      <c r="E363" t="s">
+        <v>30520012</v>
+      </c>
+      <c r="C363" s="18" t="s">
+        <v>745</v>
+      </c>
+      <c r="D363" s="17"/>
+      <c r="E363" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="364" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B364">
-        <v>305303</v>
+        <v>305224</v>
       </c>
       <c r="C364" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="E364" t="s">
         <v>114</v>
@@ -8186,10 +8256,10 @@
     </row>
     <row r="365" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B365">
-        <v>305304</v>
+        <v>305225</v>
       </c>
       <c r="C365" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="E365" t="s">
         <v>114</v>
@@ -8197,10 +8267,10 @@
     </row>
     <row r="366" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B366">
-        <v>305305</v>
+        <v>305226</v>
       </c>
       <c r="C366" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="E366" t="s">
         <v>114</v>
@@ -8208,10 +8278,10 @@
     </row>
     <row r="367" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B367">
-        <v>305306</v>
+        <v>305300</v>
       </c>
       <c r="C367" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="E367" t="s">
         <v>114</v>
@@ -8219,10 +8289,10 @@
     </row>
     <row r="368" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B368">
-        <v>305307</v>
+        <v>305301</v>
       </c>
       <c r="C368" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="E368" t="s">
         <v>114</v>
@@ -8230,10 +8300,10 @@
     </row>
     <row r="369" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B369">
-        <v>305308</v>
+        <v>305302</v>
       </c>
       <c r="C369" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="E369" t="s">
         <v>114</v>
@@ -8241,10 +8311,10 @@
     </row>
     <row r="370" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B370">
-        <v>305309</v>
+        <v>305303</v>
       </c>
       <c r="C370" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="E370" t="s">
         <v>114</v>
@@ -8252,10 +8322,10 @@
     </row>
     <row r="371" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B371">
-        <v>305310</v>
+        <v>305304</v>
       </c>
       <c r="C371" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="E371" t="s">
         <v>114</v>
@@ -8263,10 +8333,10 @@
     </row>
     <row r="372" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B372">
-        <v>305311</v>
+        <v>305305</v>
       </c>
       <c r="C372" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E372" t="s">
         <v>114</v>
@@ -8274,10 +8344,10 @@
     </row>
     <row r="373" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B373">
-        <v>305312</v>
+        <v>305306</v>
       </c>
       <c r="C373" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="E373" t="s">
         <v>114</v>
@@ -8285,10 +8355,10 @@
     </row>
     <row r="374" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B374">
-        <v>305313</v>
+        <v>305307</v>
       </c>
       <c r="C374" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="E374" t="s">
         <v>114</v>
@@ -8296,7 +8366,10 @@
     </row>
     <row r="375" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B375">
-        <v>305314</v>
+        <v>305308</v>
+      </c>
+      <c r="C375" t="s">
+        <v>545</v>
       </c>
       <c r="E375" t="s">
         <v>114</v>
@@ -8304,10 +8377,10 @@
     </row>
     <row r="376" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B376">
-        <v>305315</v>
+        <v>305309</v>
       </c>
       <c r="C376" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="E376" t="s">
         <v>114</v>
@@ -8315,10 +8388,10 @@
     </row>
     <row r="377" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B377">
-        <v>305316</v>
+        <v>305310</v>
       </c>
       <c r="C377" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="E377" t="s">
         <v>114</v>
@@ -8326,10 +8399,10 @@
     </row>
     <row r="378" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B378">
-        <v>305317</v>
+        <v>305311</v>
       </c>
       <c r="C378" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="E378" t="s">
         <v>114</v>
@@ -8337,10 +8410,10 @@
     </row>
     <row r="379" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B379">
-        <v>305318</v>
+        <v>305312</v>
       </c>
       <c r="C379" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="E379" t="s">
         <v>114</v>
@@ -8348,10 +8421,10 @@
     </row>
     <row r="380" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B380">
-        <v>305319</v>
+        <v>305313</v>
       </c>
       <c r="C380" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="E380" t="s">
         <v>114</v>
@@ -8359,10 +8432,7 @@
     </row>
     <row r="381" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B381">
-        <v>305320</v>
-      </c>
-      <c r="C381" t="s">
-        <v>558</v>
+        <v>305314</v>
       </c>
       <c r="E381" t="s">
         <v>114</v>
@@ -8370,10 +8440,10 @@
     </row>
     <row r="382" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B382">
-        <v>305321</v>
-      </c>
-      <c r="C382" s="15" t="s">
-        <v>559</v>
+        <v>305315</v>
+      </c>
+      <c r="C382" t="s">
+        <v>551</v>
       </c>
       <c r="E382" t="s">
         <v>114</v>
@@ -8381,10 +8451,10 @@
     </row>
     <row r="383" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B383">
-        <v>305322</v>
-      </c>
-      <c r="C383" s="15" t="s">
-        <v>560</v>
+        <v>305316</v>
+      </c>
+      <c r="C383" t="s">
+        <v>552</v>
       </c>
       <c r="E383" t="s">
         <v>114</v>
@@ -8392,10 +8462,10 @@
     </row>
     <row r="384" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B384">
-        <v>305323</v>
+        <v>305317</v>
       </c>
       <c r="C384" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="E384" t="s">
         <v>114</v>
@@ -8403,10 +8473,10 @@
     </row>
     <row r="385" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B385">
-        <v>305324</v>
+        <v>305318</v>
       </c>
       <c r="C385" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="E385" t="s">
         <v>114</v>
@@ -8414,10 +8484,10 @@
     </row>
     <row r="386" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B386">
-        <v>305325</v>
+        <v>305319</v>
       </c>
       <c r="C386" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="E386" t="s">
         <v>114</v>
@@ -8425,10 +8495,10 @@
     </row>
     <row r="387" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B387">
-        <v>305326</v>
-      </c>
-      <c r="C387" s="15" t="s">
-        <v>564</v>
+        <v>305320</v>
+      </c>
+      <c r="C387" t="s">
+        <v>556</v>
       </c>
       <c r="E387" t="s">
         <v>114</v>
@@ -8436,10 +8506,10 @@
     </row>
     <row r="388" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B388">
-        <v>30530001</v>
+        <v>305321</v>
       </c>
       <c r="C388" s="15" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="E388" t="s">
         <v>114</v>
@@ -8447,10 +8517,10 @@
     </row>
     <row r="389" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B389">
-        <v>30530002</v>
-      </c>
-      <c r="C389" t="s">
-        <v>566</v>
+        <v>305322</v>
+      </c>
+      <c r="C389" s="15" t="s">
+        <v>558</v>
       </c>
       <c r="E389" t="s">
         <v>114</v>
@@ -8458,10 +8528,10 @@
     </row>
     <row r="390" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B390">
-        <v>30530003</v>
-      </c>
-      <c r="C390" s="15" t="s">
-        <v>567</v>
+        <v>305323</v>
+      </c>
+      <c r="C390" t="s">
+        <v>559</v>
       </c>
       <c r="E390" t="s">
         <v>114</v>
@@ -8469,10 +8539,10 @@
     </row>
     <row r="391" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B391">
-        <v>30530004</v>
-      </c>
-      <c r="C391" s="15" t="s">
-        <v>568</v>
+        <v>305324</v>
+      </c>
+      <c r="C391" t="s">
+        <v>560</v>
       </c>
       <c r="E391" t="s">
         <v>114</v>
@@ -8480,10 +8550,10 @@
     </row>
     <row r="392" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B392">
-        <v>30530005</v>
-      </c>
-      <c r="C392" s="15" t="s">
-        <v>569</v>
+        <v>305325</v>
+      </c>
+      <c r="C392" t="s">
+        <v>561</v>
       </c>
       <c r="E392" t="s">
         <v>114</v>
@@ -8491,10 +8561,10 @@
     </row>
     <row r="393" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B393">
-        <v>30530006</v>
+        <v>305326</v>
       </c>
       <c r="C393" s="15" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="E393" t="s">
         <v>114</v>
@@ -8502,144 +8572,144 @@
     </row>
     <row r="394" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B394">
-        <v>30530007</v>
+        <v>30530001</v>
       </c>
       <c r="C394" s="15" t="s">
-        <v>571</v>
-      </c>
-      <c r="E394" s="15" t="s">
+        <v>563</v>
+      </c>
+      <c r="E394" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="395" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B395">
-        <v>30530008</v>
-      </c>
-      <c r="C395" s="15" t="s">
-        <v>572</v>
-      </c>
-      <c r="E395" s="15" t="s">
+        <v>30530002</v>
+      </c>
+      <c r="C395" t="s">
+        <v>564</v>
+      </c>
+      <c r="E395" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="396" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B396">
-        <v>30530009</v>
+        <v>30530003</v>
       </c>
       <c r="C396" s="15" t="s">
-        <v>573</v>
-      </c>
-      <c r="E396" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="E396" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="397" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B397">
-        <v>30530010</v>
+        <v>30530004</v>
       </c>
       <c r="C397" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="E397" s="15" t="s">
+        <v>566</v>
+      </c>
+      <c r="E397" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="398" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B398" s="17">
-        <v>30530011</v>
-      </c>
-      <c r="C398" s="18" t="s">
-        <v>575</v>
-      </c>
-      <c r="D398" s="17"/>
-      <c r="E398" s="18" t="s">
+      <c r="B398">
+        <v>30530005</v>
+      </c>
+      <c r="C398" s="15" t="s">
+        <v>567</v>
+      </c>
+      <c r="E398" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="399" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B399">
-        <v>30530012</v>
-      </c>
-      <c r="C399" s="18" t="s">
-        <v>746</v>
-      </c>
-      <c r="D399" s="17"/>
-      <c r="E399" s="18" t="s">
+        <v>30530006</v>
+      </c>
+      <c r="C399" s="15" t="s">
+        <v>568</v>
+      </c>
+      <c r="E399" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="400" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B400">
-        <v>309205</v>
-      </c>
-      <c r="C400" t="s">
-        <v>576</v>
-      </c>
-      <c r="E400" t="s">
+        <v>30530007</v>
+      </c>
+      <c r="C400" s="15" t="s">
+        <v>569</v>
+      </c>
+      <c r="E400" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="401" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B401">
-        <v>308001</v>
-      </c>
-      <c r="C401" t="s">
-        <v>577</v>
-      </c>
-      <c r="E401" t="s">
+        <v>30530008</v>
+      </c>
+      <c r="C401" s="15" t="s">
+        <v>570</v>
+      </c>
+      <c r="E401" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="402" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B402">
-        <v>308002</v>
-      </c>
-      <c r="C402" t="s">
-        <v>578</v>
-      </c>
-      <c r="E402" t="s">
+        <v>30530009</v>
+      </c>
+      <c r="C402" s="15" t="s">
+        <v>571</v>
+      </c>
+      <c r="E402" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="403" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B403">
-        <v>308006</v>
-      </c>
-      <c r="C403" t="s">
-        <v>579</v>
-      </c>
-      <c r="E403" t="s">
+        <v>30530010</v>
+      </c>
+      <c r="C403" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="E403" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="404" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B404">
-        <v>308007</v>
-      </c>
-      <c r="C404" t="s">
-        <v>580</v>
-      </c>
-      <c r="E404" t="s">
+      <c r="B404" s="17">
+        <v>30530011</v>
+      </c>
+      <c r="C404" s="18" t="s">
+        <v>573</v>
+      </c>
+      <c r="D404" s="17"/>
+      <c r="E404" s="18" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="405" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B405">
-        <v>308011</v>
-      </c>
-      <c r="C405" t="s">
-        <v>581</v>
-      </c>
-      <c r="E405" t="s">
+        <v>30530012</v>
+      </c>
+      <c r="C405" s="18" t="s">
+        <v>744</v>
+      </c>
+      <c r="D405" s="17"/>
+      <c r="E405" s="18" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="406" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B406">
-        <v>308012</v>
+        <v>309205</v>
       </c>
       <c r="C406" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="E406" t="s">
         <v>114</v>
@@ -8647,10 +8717,10 @@
     </row>
     <row r="407" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B407">
-        <v>308016</v>
+        <v>308001</v>
       </c>
       <c r="C407" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="E407" t="s">
         <v>114</v>
@@ -8658,10 +8728,10 @@
     </row>
     <row r="408" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B408">
-        <v>308017</v>
+        <v>308002</v>
       </c>
       <c r="C408" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="E408" t="s">
         <v>114</v>
@@ -8669,10 +8739,10 @@
     </row>
     <row r="409" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B409">
-        <v>308021</v>
-      </c>
-      <c r="C409" s="15" t="s">
-        <v>585</v>
+        <v>308006</v>
+      </c>
+      <c r="C409" t="s">
+        <v>577</v>
       </c>
       <c r="E409" t="s">
         <v>114</v>
@@ -8680,10 +8750,10 @@
     </row>
     <row r="410" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B410">
-        <v>308022</v>
-      </c>
-      <c r="C410" s="15" t="s">
-        <v>586</v>
+        <v>308007</v>
+      </c>
+      <c r="C410" t="s">
+        <v>578</v>
       </c>
       <c r="E410" t="s">
         <v>114</v>
@@ -8691,10 +8761,10 @@
     </row>
     <row r="411" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B411">
-        <v>308026</v>
-      </c>
-      <c r="C411" s="15" t="s">
-        <v>587</v>
+        <v>308011</v>
+      </c>
+      <c r="C411" t="s">
+        <v>579</v>
       </c>
       <c r="E411" t="s">
         <v>114</v>
@@ -8702,10 +8772,10 @@
     </row>
     <row r="412" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B412">
-        <v>308027</v>
-      </c>
-      <c r="C412" s="15" t="s">
-        <v>588</v>
+        <v>308012</v>
+      </c>
+      <c r="C412" t="s">
+        <v>580</v>
       </c>
       <c r="E412" t="s">
         <v>114</v>
@@ -8713,10 +8783,10 @@
     </row>
     <row r="413" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B413">
-        <v>308031</v>
-      </c>
-      <c r="C413" s="15" t="s">
-        <v>589</v>
+        <v>308016</v>
+      </c>
+      <c r="C413" t="s">
+        <v>581</v>
       </c>
       <c r="E413" t="s">
         <v>114</v>
@@ -8724,10 +8794,10 @@
     </row>
     <row r="414" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B414">
-        <v>308032</v>
-      </c>
-      <c r="C414" s="15" t="s">
-        <v>590</v>
+        <v>308017</v>
+      </c>
+      <c r="C414" t="s">
+        <v>582</v>
       </c>
       <c r="E414" t="s">
         <v>114</v>
@@ -8735,10 +8805,10 @@
     </row>
     <row r="415" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B415">
-        <v>308036</v>
+        <v>308021</v>
       </c>
       <c r="C415" s="15" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="E415" t="s">
         <v>114</v>
@@ -8746,10 +8816,10 @@
     </row>
     <row r="416" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B416">
-        <v>308037</v>
+        <v>308022</v>
       </c>
       <c r="C416" s="15" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="E416" t="s">
         <v>114</v>
@@ -8757,10 +8827,10 @@
     </row>
     <row r="417" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B417">
-        <v>308041</v>
+        <v>308026</v>
       </c>
       <c r="C417" s="15" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="E417" t="s">
         <v>114</v>
@@ -8768,10 +8838,10 @@
     </row>
     <row r="418" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B418">
-        <v>308042</v>
+        <v>308027</v>
       </c>
       <c r="C418" s="15" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E418" t="s">
         <v>114</v>
@@ -8779,10 +8849,10 @@
     </row>
     <row r="419" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B419">
-        <v>308046</v>
+        <v>308031</v>
       </c>
       <c r="C419" s="15" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="E419" t="s">
         <v>114</v>
@@ -8790,10 +8860,10 @@
     </row>
     <row r="420" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B420">
-        <v>308047</v>
+        <v>308032</v>
       </c>
       <c r="C420" s="15" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="E420" t="s">
         <v>114</v>
@@ -8801,25 +8871,91 @@
     </row>
     <row r="421" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B421">
-        <v>308048</v>
-      </c>
-      <c r="C421" s="18" t="s">
-        <v>767</v>
-      </c>
-      <c r="D421" s="44"/>
-      <c r="E421" s="17" t="s">
+        <v>308036</v>
+      </c>
+      <c r="C421" s="15" t="s">
+        <v>589</v>
+      </c>
+      <c r="E421" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="422" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B422">
+        <v>308037</v>
+      </c>
+      <c r="C422" s="15" t="s">
+        <v>590</v>
+      </c>
+      <c r="E422" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="423" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B423">
+        <v>308041</v>
+      </c>
+      <c r="C423" s="15" t="s">
+        <v>591</v>
+      </c>
+      <c r="E423" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="424" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B424">
+        <v>308042</v>
+      </c>
+      <c r="C424" s="15" t="s">
+        <v>592</v>
+      </c>
+      <c r="E424" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="425" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B425">
+        <v>308046</v>
+      </c>
+      <c r="C425" s="15" t="s">
+        <v>593</v>
+      </c>
+      <c r="E425" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="426" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B426">
+        <v>308047</v>
+      </c>
+      <c r="C426" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="E426" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="427" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B427">
+        <v>308048</v>
+      </c>
+      <c r="C427" s="18" t="s">
+        <v>765</v>
+      </c>
+      <c r="D427" s="44"/>
+      <c r="E427" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="428" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B428">
         <v>308049</v>
       </c>
-      <c r="C422" s="18" t="s">
-        <v>768</v>
-      </c>
-      <c r="D422" s="44"/>
-      <c r="E422" s="17" t="s">
+      <c r="C428" s="18" t="s">
+        <v>766</v>
+      </c>
+      <c r="D428" s="44"/>
+      <c r="E428" s="17" t="s">
         <v>114</v>
       </c>
     </row>
@@ -8855,22 +8991,22 @@
         <v>5</v>
       </c>
       <c r="C1" s="15" t="s">
+        <v>595</v>
+      </c>
+      <c r="D1" t="s">
+        <v>596</v>
+      </c>
+      <c r="E1" t="s">
         <v>597</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>598</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>599</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>600</v>
-      </c>
-      <c r="G1" t="s">
-        <v>601</v>
-      </c>
-      <c r="H1" t="s">
-        <v>602</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
@@ -8882,22 +9018,22 @@
         <v>2</v>
       </c>
       <c r="L1" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="N1" s="8" t="s">
         <v>603</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>604</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="11" t="s">
         <v>605</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>606</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -8907,7 +9043,7 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -8916,10 +9052,10 @@
         <v>13</v>
       </c>
       <c r="K2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
@@ -8988,22 +9124,22 @@
         <v>0</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="H4" s="10" t="s">
         <v>614</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="I4" t="s">
         <v>615</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>616</v>
-      </c>
-      <c r="I4" t="s">
-        <v>617</v>
       </c>
       <c r="K4" t="s">
         <v>20</v>
@@ -9017,40 +9153,40 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
+        <v>616</v>
+      </c>
+      <c r="E5" t="s">
+        <v>617</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>618</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" s="6" t="s">
         <v>619</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="H5" s="10" t="s">
         <v>620</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="I5" t="s">
         <v>621</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="I5" t="s">
-        <v>623</v>
       </c>
       <c r="K5" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="N5" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="O5" s="7" t="s">
         <v>625</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="P5" s="12" t="s">
         <v>626</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="P5" s="12" t="s">
-        <v>628</v>
       </c>
       <c r="Q5">
         <v>306002</v>
@@ -9064,40 +9200,40 @@
         <v>0</v>
       </c>
       <c r="D6" s="21" t="s">
+        <v>627</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>627</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>629</v>
       </c>
-      <c r="E6" s="21" t="s">
-        <v>629</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="H6" s="22" t="s">
         <v>630</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="I6" t="s">
         <v>631</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>632</v>
-      </c>
-      <c r="I6" t="s">
-        <v>633</v>
       </c>
       <c r="K6" t="s">
         <v>20</v>
       </c>
       <c r="L6" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="N6" s="7" t="s">
         <v>624</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="O6" s="7" t="s">
         <v>625</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="P6" s="12" t="s">
         <v>626</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="P6" s="12" t="s">
-        <v>628</v>
       </c>
       <c r="Q6">
         <v>306003</v>
@@ -9111,40 +9247,40 @@
         <v>0</v>
       </c>
       <c r="D7" s="21" t="s">
+        <v>632</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>633</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="G7" s="6" t="s">
         <v>635</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="H7" s="22" t="s">
         <v>636</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="I7" t="s">
         <v>637</v>
-      </c>
-      <c r="H7" s="22" t="s">
-        <v>638</v>
-      </c>
-      <c r="I7" t="s">
-        <v>639</v>
       </c>
       <c r="K7" t="s">
         <v>20</v>
       </c>
       <c r="L7" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="N7" s="7" t="s">
         <v>624</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="O7" s="7" t="s">
         <v>625</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="P7" s="12" t="s">
         <v>626</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>628</v>
       </c>
       <c r="Q7">
         <v>306004</v>
@@ -9158,40 +9294,40 @@
         <v>1</v>
       </c>
       <c r="D8" s="21" t="s">
+        <v>638</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>638</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>638</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>639</v>
+      </c>
+      <c r="H8" s="26" t="s">
         <v>640</v>
       </c>
-      <c r="E8" s="21" t="s">
-        <v>640</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>640</v>
-      </c>
-      <c r="G8" s="25" t="s">
+      <c r="I8" s="15" t="s">
         <v>641</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>642</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>643</v>
       </c>
       <c r="K8" t="s">
         <v>20</v>
       </c>
       <c r="L8" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N8" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="O8" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="P8" s="13" t="s">
         <v>646</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>648</v>
       </c>
       <c r="Q8" s="14">
         <v>306005</v>
@@ -9205,40 +9341,40 @@
         <v>1</v>
       </c>
       <c r="D9" s="19" t="s">
+        <v>647</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>647</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>647</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>648</v>
+      </c>
+      <c r="H9" s="20" t="s">
         <v>649</v>
       </c>
-      <c r="E9" s="19" t="s">
-        <v>649</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>649</v>
-      </c>
-      <c r="G9" s="20" t="s">
+      <c r="I9" s="15" t="s">
         <v>650</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>651</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>652</v>
       </c>
       <c r="K9" t="s">
         <v>20</v>
       </c>
       <c r="L9" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N9" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="O9" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="P9" s="13" t="s">
         <v>646</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>648</v>
       </c>
       <c r="Q9" s="14">
         <v>306006</v>
@@ -9252,40 +9388,40 @@
         <v>1</v>
       </c>
       <c r="D10" s="38" t="s">
+        <v>651</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>652</v>
+      </c>
+      <c r="F10" s="39" t="s">
         <v>653</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="G10" s="40" t="s">
         <v>654</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="H10" s="40" t="s">
         <v>655</v>
       </c>
-      <c r="G10" s="40" t="s">
+      <c r="I10" s="15" t="s">
         <v>656</v>
-      </c>
-      <c r="H10" s="40" t="s">
-        <v>657</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>658</v>
       </c>
       <c r="K10" t="s">
         <v>20</v>
       </c>
       <c r="L10" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N10" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="O10" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="P10" s="13" t="s">
         <v>646</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="P10" s="13" t="s">
-        <v>648</v>
       </c>
       <c r="Q10" s="14">
         <v>30600001</v>
@@ -9299,40 +9435,40 @@
         <v>0</v>
       </c>
       <c r="D11" s="48" t="s">
+        <v>657</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>658</v>
+      </c>
+      <c r="F11" s="47" t="s">
+        <v>762</v>
+      </c>
+      <c r="G11" s="50" t="s">
         <v>659</v>
       </c>
-      <c r="E11" s="49" t="s">
+      <c r="H11" s="50" t="s">
         <v>660</v>
       </c>
-      <c r="F11" s="47" t="s">
-        <v>764</v>
-      </c>
-      <c r="G11" s="50" t="s">
+      <c r="I11" s="15" t="s">
         <v>661</v>
-      </c>
-      <c r="H11" s="50" t="s">
-        <v>662</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>663</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
       </c>
       <c r="L11" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="N11" s="7" t="s">
         <v>624</v>
       </c>
-      <c r="M11" s="8" t="s">
+      <c r="O11" s="7" t="s">
         <v>625</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="P11" s="12" t="s">
         <v>626</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="P11" s="12" t="s">
-        <v>628</v>
       </c>
       <c r="Q11" s="16">
         <v>30600002</v>
@@ -9346,40 +9482,40 @@
         <v>1</v>
       </c>
       <c r="D12" s="51" t="s">
+        <v>662</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>663</v>
+      </c>
+      <c r="F12" s="47" t="s">
         <v>664</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="G12" s="47" t="s">
         <v>665</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="H12" s="47" t="s">
         <v>666</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="I12" s="15" t="s">
         <v>667</v>
-      </c>
-      <c r="H12" s="47" t="s">
-        <v>668</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>669</v>
       </c>
       <c r="K12" t="s">
         <v>20</v>
       </c>
       <c r="L12" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N12" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="O12" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="P12" s="13" t="s">
         <v>646</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="P12" s="13" t="s">
-        <v>648</v>
       </c>
       <c r="Q12" s="14">
         <v>30600003</v>
@@ -9393,22 +9529,22 @@
         <v>0</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>670</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>671</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="H13" s="53" t="s">
+        <v>767</v>
+      </c>
+      <c r="I13" t="s">
         <v>672</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>673</v>
-      </c>
-      <c r="H13" s="53" t="s">
-        <v>769</v>
-      </c>
-      <c r="I13" t="s">
-        <v>674</v>
       </c>
       <c r="K13" t="s">
         <v>84</v>
@@ -9424,40 +9560,40 @@
         <v>1</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>675</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="H14" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>676</v>
-      </c>
-      <c r="G14" s="6" t="s">
+      <c r="I14" t="s">
         <v>677</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>678</v>
-      </c>
-      <c r="I14" t="s">
-        <v>679</v>
       </c>
       <c r="K14" t="s">
         <v>84</v>
       </c>
       <c r="L14" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N14" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="M14" s="7" t="s">
+      <c r="O14" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="N14" s="7" t="s">
+      <c r="P14" s="13" t="s">
         <v>646</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="P14" s="13" t="s">
-        <v>648</v>
       </c>
       <c r="Q14">
         <v>306102</v>
@@ -9471,40 +9607,40 @@
         <v>1</v>
       </c>
       <c r="D15" s="26" t="s">
+        <v>678</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>678</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>679</v>
+      </c>
+      <c r="G15" s="27" t="s">
         <v>680</v>
       </c>
-      <c r="E15" s="26" t="s">
-        <v>680</v>
-      </c>
-      <c r="F15" s="26" t="s">
+      <c r="H15" s="28" t="s">
         <v>681</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="I15" s="15" t="s">
         <v>682</v>
-      </c>
-      <c r="H15" s="28" t="s">
-        <v>683</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>684</v>
       </c>
       <c r="K15" t="s">
         <v>84</v>
       </c>
       <c r="L15" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N15" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="M15" s="7" t="s">
+      <c r="O15" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="N15" s="7" t="s">
+      <c r="P15" s="13" t="s">
         <v>646</v>
-      </c>
-      <c r="O15" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="P15" s="13" t="s">
-        <v>648</v>
       </c>
       <c r="Q15" s="16">
         <v>306103</v>
@@ -9518,40 +9654,40 @@
         <v>0</v>
       </c>
       <c r="D16" s="31" t="s">
+        <v>683</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>684</v>
+      </c>
+      <c r="F16" s="26" t="s">
         <v>685</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="G16" s="27" t="s">
         <v>686</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="H16" s="27" t="s">
         <v>687</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="I16" s="15" t="s">
         <v>688</v>
-      </c>
-      <c r="H16" s="27" t="s">
-        <v>689</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>690</v>
       </c>
       <c r="K16" t="s">
         <v>84</v>
       </c>
       <c r="L16" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="N16" s="25" t="s">
         <v>691</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="O16" s="25" t="s">
         <v>692</v>
       </c>
-      <c r="N16" s="25" t="s">
+      <c r="P16" s="25" t="s">
         <v>693</v>
-      </c>
-      <c r="O16" s="25" t="s">
-        <v>694</v>
-      </c>
-      <c r="P16" s="25" t="s">
-        <v>695</v>
       </c>
       <c r="Q16" s="29">
         <v>306104</v>
@@ -9565,40 +9701,40 @@
         <v>0</v>
       </c>
       <c r="D17" s="31" t="s">
+        <v>694</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>695</v>
+      </c>
+      <c r="F17" s="26" t="s">
         <v>696</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="G17" s="27" t="s">
         <v>697</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="H17" s="27" t="s">
         <v>698</v>
       </c>
-      <c r="G17" s="27" t="s">
+      <c r="I17" s="15" t="s">
         <v>699</v>
-      </c>
-      <c r="H17" s="27" t="s">
-        <v>700</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>701</v>
       </c>
       <c r="K17" t="s">
         <v>84</v>
       </c>
       <c r="L17" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="N17" s="25" t="s">
         <v>691</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="O17" s="25" t="s">
         <v>692</v>
       </c>
-      <c r="N17" s="25" t="s">
+      <c r="P17" s="25" t="s">
         <v>693</v>
-      </c>
-      <c r="O17" s="25" t="s">
-        <v>694</v>
-      </c>
-      <c r="P17" s="25" t="s">
-        <v>695</v>
       </c>
       <c r="Q17" s="29">
         <v>306105</v>
@@ -9612,40 +9748,40 @@
         <v>0</v>
       </c>
       <c r="D18" s="31" t="s">
+        <v>700</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>701</v>
+      </c>
+      <c r="F18" s="26" t="s">
         <v>702</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="G18" s="27" t="s">
         <v>703</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="H18" s="27" t="s">
         <v>704</v>
       </c>
-      <c r="G18" s="27" t="s">
+      <c r="I18" s="15" t="s">
         <v>705</v>
-      </c>
-      <c r="H18" s="27" t="s">
-        <v>706</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>707</v>
       </c>
       <c r="K18" t="s">
         <v>84</v>
       </c>
       <c r="L18" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="N18" s="25" t="s">
         <v>691</v>
       </c>
-      <c r="M18" s="9" t="s">
+      <c r="O18" s="25" t="s">
         <v>692</v>
       </c>
-      <c r="N18" s="25" t="s">
+      <c r="P18" s="25" t="s">
         <v>693</v>
-      </c>
-      <c r="O18" s="25" t="s">
-        <v>694</v>
-      </c>
-      <c r="P18" s="25" t="s">
-        <v>695</v>
       </c>
       <c r="Q18" s="29">
         <v>306106</v>
@@ -9659,40 +9795,40 @@
         <v>0</v>
       </c>
       <c r="D19" s="31" t="s">
+        <v>706</v>
+      </c>
+      <c r="E19" s="31" t="s">
+        <v>707</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>706</v>
+      </c>
+      <c r="G19" s="27" t="s">
         <v>708</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="H19" s="27" t="s">
         <v>709</v>
       </c>
-      <c r="F19" s="26" t="s">
-        <v>708</v>
-      </c>
-      <c r="G19" s="27" t="s">
+      <c r="I19" s="15" t="s">
         <v>710</v>
-      </c>
-      <c r="H19" s="27" t="s">
-        <v>711</v>
-      </c>
-      <c r="I19" s="15" t="s">
-        <v>712</v>
       </c>
       <c r="K19" t="s">
         <v>84</v>
       </c>
       <c r="L19" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="N19" s="25" t="s">
         <v>691</v>
       </c>
-      <c r="M19" s="9" t="s">
+      <c r="O19" s="25" t="s">
         <v>692</v>
       </c>
-      <c r="N19" s="25" t="s">
+      <c r="P19" s="25" t="s">
         <v>693</v>
-      </c>
-      <c r="O19" s="25" t="s">
-        <v>694</v>
-      </c>
-      <c r="P19" s="25" t="s">
-        <v>695</v>
       </c>
       <c r="Q19" s="29">
         <v>306107</v>
@@ -9706,40 +9842,40 @@
         <v>1</v>
       </c>
       <c r="D20" s="32" t="s">
+        <v>711</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>711</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>712</v>
+      </c>
+      <c r="G20" s="27" t="s">
         <v>713</v>
       </c>
-      <c r="E20" s="32" t="s">
-        <v>713</v>
-      </c>
-      <c r="F20" s="33" t="s">
+      <c r="H20" s="28" t="s">
         <v>714</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="I20" s="15" t="s">
         <v>715</v>
-      </c>
-      <c r="H20" s="28" t="s">
-        <v>716</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>717</v>
       </c>
       <c r="K20" t="s">
         <v>84</v>
       </c>
       <c r="L20" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="N20" s="25" t="s">
         <v>691</v>
       </c>
-      <c r="M20" s="9" t="s">
+      <c r="O20" s="25" t="s">
         <v>692</v>
       </c>
-      <c r="N20" s="25" t="s">
+      <c r="P20" s="25" t="s">
         <v>693</v>
-      </c>
-      <c r="O20" s="25" t="s">
-        <v>694</v>
-      </c>
-      <c r="P20" s="25" t="s">
-        <v>695</v>
       </c>
       <c r="Q20" s="16">
         <v>30610001</v>
@@ -9753,40 +9889,40 @@
         <v>1</v>
       </c>
       <c r="D21" s="34" t="s">
+        <v>716</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>716</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>717</v>
+      </c>
+      <c r="G21" s="36" t="s">
         <v>718</v>
       </c>
-      <c r="E21" s="34" t="s">
-        <v>718</v>
-      </c>
-      <c r="F21" s="35" t="s">
+      <c r="H21" s="36" t="s">
         <v>719</v>
       </c>
-      <c r="G21" s="36" t="s">
+      <c r="I21" s="15" t="s">
         <v>720</v>
-      </c>
-      <c r="H21" s="36" t="s">
-        <v>721</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>722</v>
       </c>
       <c r="K21" t="s">
         <v>84</v>
       </c>
       <c r="L21" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N21" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="M21" s="7" t="s">
+      <c r="O21" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="N21" s="7" t="s">
+      <c r="P21" s="13" t="s">
         <v>646</v>
-      </c>
-      <c r="O21" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="P21" s="13" t="s">
-        <v>648</v>
       </c>
       <c r="Q21" s="16">
         <v>30610002</v>
@@ -9800,40 +9936,40 @@
         <v>1</v>
       </c>
       <c r="D22" s="31" t="s">
+        <v>721</v>
+      </c>
+      <c r="E22" s="31" t="s">
+        <v>721</v>
+      </c>
+      <c r="F22" s="40" t="s">
+        <v>722</v>
+      </c>
+      <c r="G22" s="40" t="s">
         <v>723</v>
       </c>
-      <c r="E22" s="31" t="s">
-        <v>723</v>
-      </c>
-      <c r="F22" s="40" t="s">
+      <c r="H22" s="40" t="s">
         <v>724</v>
       </c>
-      <c r="G22" s="40" t="s">
+      <c r="I22" s="15" t="s">
         <v>725</v>
-      </c>
-      <c r="H22" s="40" t="s">
-        <v>726</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>727</v>
       </c>
       <c r="K22" t="s">
         <v>84</v>
       </c>
       <c r="L22" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N22" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="M22" s="7" t="s">
+      <c r="O22" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="N22" s="7" t="s">
+      <c r="P22" s="13" t="s">
         <v>646</v>
-      </c>
-      <c r="O22" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="P22" s="13" t="s">
-        <v>648</v>
       </c>
       <c r="Q22" s="16">
         <v>30610003</v>
@@ -9847,40 +9983,40 @@
         <v>1</v>
       </c>
       <c r="D23" s="31" t="s">
+        <v>726</v>
+      </c>
+      <c r="E23" s="31" t="s">
+        <v>727</v>
+      </c>
+      <c r="F23" s="15" t="s">
         <v>728</v>
       </c>
-      <c r="E23" s="31" t="s">
+      <c r="G23" s="15" t="s">
         <v>729</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="H23" s="42" t="s">
         <v>730</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="I23" s="15" t="s">
         <v>731</v>
-      </c>
-      <c r="H23" s="42" t="s">
-        <v>732</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>733</v>
       </c>
       <c r="K23" t="s">
         <v>84</v>
       </c>
       <c r="L23" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N23" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="M23" s="7" t="s">
+      <c r="O23" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="N23" s="7" t="s">
+      <c r="P23" s="13" t="s">
         <v>646</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="P23" s="13" t="s">
-        <v>648</v>
       </c>
       <c r="Q23" s="16">
         <v>30610004</v>
@@ -9894,40 +10030,40 @@
         <v>1</v>
       </c>
       <c r="D24" s="31" t="s">
+        <v>732</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>733</v>
+      </c>
+      <c r="F24" s="15" t="s">
         <v>734</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="G24" s="43" t="s">
         <v>735</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="H24" s="43" t="s">
         <v>736</v>
       </c>
-      <c r="G24" s="43" t="s">
+      <c r="I24" s="15" t="s">
         <v>737</v>
-      </c>
-      <c r="H24" s="43" t="s">
-        <v>738</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>739</v>
       </c>
       <c r="K24" t="s">
         <v>84</v>
       </c>
       <c r="L24" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N24" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="M24" s="7" t="s">
+      <c r="O24" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="N24" s="7" t="s">
+      <c r="P24" s="13" t="s">
         <v>646</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="P24" s="13" t="s">
-        <v>648</v>
       </c>
       <c r="Q24" s="16">
         <v>30610005</v>
@@ -9941,40 +10077,40 @@
         <v>1</v>
       </c>
       <c r="D25" s="45" t="s">
+        <v>738</v>
+      </c>
+      <c r="E25" s="45" t="s">
+        <v>739</v>
+      </c>
+      <c r="F25" s="46" t="s">
         <v>740</v>
       </c>
-      <c r="E25" s="45" t="s">
+      <c r="G25" s="47" t="s">
         <v>741</v>
       </c>
-      <c r="F25" s="46" t="s">
+      <c r="H25" s="47" t="s">
         <v>742</v>
       </c>
-      <c r="G25" s="47" t="s">
+      <c r="I25" s="15" t="s">
         <v>743</v>
-      </c>
-      <c r="H25" s="47" t="s">
-        <v>744</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>745</v>
       </c>
       <c r="K25" t="s">
         <v>84</v>
       </c>
       <c r="L25" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="N25" s="25" t="s">
         <v>691</v>
       </c>
-      <c r="M25" s="9" t="s">
+      <c r="O25" s="25" t="s">
         <v>692</v>
       </c>
-      <c r="N25" s="25" t="s">
+      <c r="P25" s="25" t="s">
         <v>693</v>
-      </c>
-      <c r="O25" s="25" t="s">
-        <v>694</v>
-      </c>
-      <c r="P25" s="25" t="s">
-        <v>695</v>
       </c>
       <c r="Q25" s="16">
         <v>30610006</v>

--- a/source/bin/excel/audio.xlsx
+++ b/source/bin/excel/audio.xlsx
@@ -1,34 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A0896C-40AB-4D3A-96F1-FF042C0A29ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165C1F02-B5B5-4979-B394-B414A42557CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="1" r:id="rId1"/>
     <sheet name="audio" sheetId="2" r:id="rId2"/>
     <sheet name="bgm" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -60,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="824">
   <si>
     <t>sheet</t>
   </si>
@@ -1122,6 +1111,9 @@
     <t>庙会_进入界面</t>
   </si>
   <si>
+    <t>audio/audio_event/2501chunjie_activity_enter</t>
+  </si>
+  <si>
     <t>庙会_窗口打开、祈愿打开&amp;切换</t>
   </si>
   <si>
@@ -1159,6 +1151,9 @@
   </si>
   <si>
     <t>庙会_技能升级</t>
+  </si>
+  <si>
+    <t>audio/audio_event/2501chunjie_skill_level_up</t>
   </si>
   <si>
     <t>庙会_等级提升_大（level14~17）</t>
@@ -2424,30 +2419,34 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>斗牌卡池切换页签</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/lobby/main/audio/gacha_banner_dp</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2606斗牌音效</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>2604剑域誓约_进入主界面时播放</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>audio/audio_event/2501chunjie_activity_enter</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio/audio_event/2501chunjie_skill_level_up</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>ui/activity/extend/2604dj/main/audio/2604dj_activity_enter</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>2604剑域誓约_通关成功</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>ui/activity/extend/festival/main/audio/2404ba_success</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>2604剑域誓约_通关成功</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>2604剑域誓约_通关失败</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -2473,6 +2472,122 @@
   </si>
   <si>
     <t>ui/activity/extend/2604dj/main/audio/2604dj_crafting</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2605青云之志_锻造事件</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2605qy/main/audio/2605qy_forge</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2605青云之志_转盘事件</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2605qy/main/audio/2605qy_gamble</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2605青云之志_转盘事件_失败</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2605qy/main/audio/2605qy_gamble_fail</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2605青云之志_传送事件</t>
+  </si>
+  <si>
+    <t>ui/activity/extend/2605qy/main/audio/2605qy_transport</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2605青云之志_角色受伤_物理</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2605qy/main/audio/2605qy_damage_normal</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2605青云之志_角色受伤_魔法</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2605qy/main/audio/2605qy_damage_magical</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2605青云之志_敌人受伤_物理</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2605qy/main/audio/2605qy_attack_normal</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2605青云之志_敌人受伤_魔法</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2605qy/main/audio/2605qy_attack_magical</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2605青云之志_角色恢复</t>
+  </si>
+  <si>
+    <t>ui/activity/extend/2605qy/main/audio/2605qy_heal</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2605青云之志_确认选择</t>
+  </si>
+  <si>
+    <t>ui/activity/extend/2605qy/main/audio/2605qy_confirm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2605青云之志_角色跳跃</t>
+  </si>
+  <si>
+    <t>ui/activity/extend/2605qy/main/audio/2605qy_jump</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2605青云之志_星币获得</t>
+  </si>
+  <si>
+    <t>ui/activity/extend/2605qy/main/audio/2605qy_common_getmoney</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2605青云之志_获得奖励</t>
+  </si>
+  <si>
+    <t>ui/activity/extend/2605qy/main/audio/2605qy_common_getitem</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2605青云之志_获得役种</t>
+  </si>
+  <si>
+    <t>ui/activity/extend/2605qy/main/audio/2605qy_common_getrunestone</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2605青云之志_失去道具</t>
+  </si>
+  <si>
+    <t>ui/activity/extend/2605qy/main/audio/2605qy_common_lostitem</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2606dp/main/audio/2606dp_event</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -2621,7 +2736,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2697,6 +2812,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2788,7 +2909,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2903,6 +3024,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3230,7 +3352,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E428"/>
+  <dimension ref="A1:E445"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.875" customWidth="1"/>
@@ -3922,41 +4044,41 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="15" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B58" s="29">
         <v>157</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E58" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B59">
-        <v>201</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D59">
-        <v>2098</v>
+      <c r="A59" s="15" t="s">
+        <v>779</v>
+      </c>
+      <c r="B59" s="29">
+        <v>158</v>
+      </c>
+      <c r="C59" s="30" t="s">
+        <v>780</v>
       </c>
       <c r="E59" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B60">
-        <v>202</v>
-      </c>
-      <c r="C60" t="s">
-        <v>85</v>
+        <v>201</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="D60">
-        <v>1000</v>
+        <v>2098</v>
       </c>
       <c r="E60" t="s">
         <v>84</v>
@@ -3964,10 +4086,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B61">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D61">
         <v>1000</v>
@@ -3978,10 +4100,10 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B62">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C62" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D62">
         <v>1000</v>
@@ -3992,10 +4114,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B63">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C63" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D63">
         <v>1000</v>
@@ -4006,13 +4128,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B64">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C64" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D64">
-        <v>1583</v>
+        <v>1000</v>
       </c>
       <c r="E64" t="s">
         <v>84</v>
@@ -4020,13 +4142,13 @@
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B65">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C65" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D65">
-        <v>1000</v>
+        <v>1583</v>
       </c>
       <c r="E65" t="s">
         <v>84</v>
@@ -4034,13 +4156,13 @@
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B66">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C66" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D66">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="E66" t="s">
         <v>84</v>
@@ -4048,13 +4170,13 @@
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B67">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C67" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D67">
-        <v>1000</v>
+        <v>1105</v>
       </c>
       <c r="E67" t="s">
         <v>84</v>
@@ -4062,10 +4184,10 @@
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B68">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C68" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D68">
         <v>1000</v>
@@ -4076,13 +4198,13 @@
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B69">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C69" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D69">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="E69" t="s">
         <v>84</v>
@@ -4090,13 +4212,13 @@
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B70">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C70" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D70">
-        <v>1602</v>
+        <v>1105</v>
       </c>
       <c r="E70" t="s">
         <v>84</v>
@@ -4104,13 +4226,13 @@
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B71">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C71" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D71">
-        <v>2098</v>
+        <v>1602</v>
       </c>
       <c r="E71" t="s">
         <v>84</v>
@@ -4118,10 +4240,10 @@
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B72">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C72" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D72">
         <v>2098</v>
@@ -4132,13 +4254,13 @@
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B73">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C73" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D73">
-        <v>1000</v>
+        <v>2098</v>
       </c>
       <c r="E73" t="s">
         <v>84</v>
@@ -4146,10 +4268,10 @@
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B74">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C74" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D74">
         <v>1000</v>
@@ -4160,10 +4282,10 @@
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B75">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C75" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D75">
         <v>1000</v>
@@ -4174,13 +4296,13 @@
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B76">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C76" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D76">
-        <v>1714</v>
+        <v>1000</v>
       </c>
       <c r="E76" t="s">
         <v>84</v>
@@ -4188,13 +4310,13 @@
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B77">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C77" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D77">
-        <v>1000</v>
+        <v>1714</v>
       </c>
       <c r="E77" t="s">
         <v>84</v>
@@ -4202,10 +4324,10 @@
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B78">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C78" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D78">
         <v>1000</v>
@@ -4216,13 +4338,13 @@
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B79">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C79" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D79">
-        <v>1602</v>
+        <v>1000</v>
       </c>
       <c r="E79" t="s">
         <v>84</v>
@@ -4230,13 +4352,13 @@
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B80">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C80" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D80">
-        <v>1000</v>
+        <v>1602</v>
       </c>
       <c r="E80" t="s">
         <v>84</v>
@@ -4244,13 +4366,13 @@
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B81">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C81" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D81">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="E81" t="s">
         <v>84</v>
@@ -4258,13 +4380,13 @@
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B82">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C82" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D82">
-        <v>2098</v>
+        <v>1105</v>
       </c>
       <c r="E82" t="s">
         <v>84</v>
@@ -4272,13 +4394,13 @@
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B83">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C83" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D83">
-        <v>2206</v>
+        <v>2098</v>
       </c>
       <c r="E83" t="s">
         <v>84</v>
@@ -4286,13 +4408,13 @@
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B84">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C84" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D84">
-        <v>2098</v>
+        <v>2206</v>
       </c>
       <c r="E84" t="s">
         <v>84</v>
@@ -4300,13 +4422,13 @@
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B85">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D85">
-        <v>1031</v>
+        <v>2098</v>
       </c>
       <c r="E85" t="s">
         <v>84</v>
@@ -4314,13 +4436,13 @@
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B86">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C86" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D86">
-        <v>1000</v>
+        <v>1031</v>
       </c>
       <c r="E86" t="s">
         <v>84</v>
@@ -4328,10 +4450,10 @@
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B87">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C87" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D87">
         <v>1000</v>
@@ -4342,27 +4464,27 @@
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B88">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C88" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D88">
-        <v>1702</v>
+        <v>1000</v>
       </c>
       <c r="E88" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B89">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C89" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D89">
-        <v>2391</v>
+        <v>1702</v>
       </c>
       <c r="E89" t="s">
         <v>114</v>
@@ -4370,13 +4492,13 @@
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B90">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C90" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D90">
-        <v>2628</v>
+        <v>2391</v>
       </c>
       <c r="E90" t="s">
         <v>114</v>
@@ -4384,7 +4506,13 @@
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B91">
-        <v>233</v>
+        <v>232</v>
+      </c>
+      <c r="C91" t="s">
+        <v>116</v>
+      </c>
+      <c r="D91">
+        <v>2628</v>
       </c>
       <c r="E91" t="s">
         <v>114</v>
@@ -4392,7 +4520,7 @@
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B92">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E92" t="s">
         <v>114</v>
@@ -4400,13 +4528,7 @@
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B93">
-        <v>235</v>
-      </c>
-      <c r="C93" t="s">
-        <v>117</v>
-      </c>
-      <c r="D93">
-        <v>4051</v>
+        <v>234</v>
       </c>
       <c r="E93" t="s">
         <v>114</v>
@@ -4414,13 +4536,13 @@
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B94">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C94" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D94">
-        <v>1104</v>
+        <v>4051</v>
       </c>
       <c r="E94" t="s">
         <v>114</v>
@@ -4428,13 +4550,13 @@
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B95">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C95" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D95">
-        <v>2176</v>
+        <v>1104</v>
       </c>
       <c r="E95" t="s">
         <v>114</v>
@@ -4442,13 +4564,13 @@
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B96">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C96" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D96">
-        <v>4057</v>
+        <v>2176</v>
       </c>
       <c r="E96" t="s">
         <v>114</v>
@@ -4456,21 +4578,24 @@
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B97">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C97" t="s">
-        <v>121</v>
+        <v>120</v>
+      </c>
+      <c r="D97">
+        <v>4057</v>
       </c>
       <c r="E97" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B98">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C98" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E98" t="s">
         <v>84</v>
@@ -4478,21 +4603,21 @@
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B99">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C99" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E99" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B100">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E100" t="s">
         <v>114</v>
@@ -4500,10 +4625,10 @@
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B101">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C101" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E101" t="s">
         <v>114</v>
@@ -4511,10 +4636,10 @@
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B102">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C102" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E102" t="s">
         <v>114</v>
@@ -4522,10 +4647,10 @@
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B103">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C103" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E103" t="s">
         <v>114</v>
@@ -4533,10 +4658,10 @@
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B104">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C104" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E104" t="s">
         <v>114</v>
@@ -4544,27 +4669,24 @@
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B105">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C105" t="s">
-        <v>129</v>
-      </c>
-      <c r="D105">
-        <v>5434</v>
+        <v>128</v>
       </c>
       <c r="E105" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B106">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C106" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D106">
-        <v>5517</v>
+        <v>5434</v>
       </c>
       <c r="E106" t="s">
         <v>130</v>
@@ -4572,13 +4694,13 @@
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B107">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C107" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D107">
-        <v>5550</v>
+        <v>5517</v>
       </c>
       <c r="E107" t="s">
         <v>130</v>
@@ -4586,13 +4708,13 @@
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B108">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C108" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D108">
-        <v>5717</v>
+        <v>5550</v>
       </c>
       <c r="E108" t="s">
         <v>130</v>
@@ -4600,13 +4722,13 @@
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B109">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C109" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D109">
-        <v>5484</v>
+        <v>5717</v>
       </c>
       <c r="E109" t="s">
         <v>130</v>
@@ -4614,10 +4736,10 @@
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B110">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C110" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D110">
         <v>5484</v>
@@ -4628,13 +4750,13 @@
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B111">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C111" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D111">
-        <v>5350</v>
+        <v>5484</v>
       </c>
       <c r="E111" t="s">
         <v>130</v>
@@ -4642,13 +4764,13 @@
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B112">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C112" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D112">
-        <v>5217</v>
+        <v>5350</v>
       </c>
       <c r="E112" t="s">
         <v>130</v>
@@ -4656,13 +4778,13 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B113">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D113">
-        <v>5650</v>
+        <v>5217</v>
       </c>
       <c r="E113" t="s">
         <v>130</v>
@@ -4670,10 +4792,10 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B114">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C114" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D114">
         <v>5650</v>
@@ -4684,13 +4806,13 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B115">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C115" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D115">
-        <v>5534</v>
+        <v>5650</v>
       </c>
       <c r="E115" t="s">
         <v>130</v>
@@ -4698,13 +4820,13 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B116">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C116" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D116">
-        <v>5800</v>
+        <v>5534</v>
       </c>
       <c r="E116" t="s">
         <v>130</v>
@@ -4712,13 +4834,13 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B117">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C117" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D117">
-        <v>5617</v>
+        <v>5800</v>
       </c>
       <c r="E117" t="s">
         <v>130</v>
@@ -4726,10 +4848,10 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B118">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D118">
         <v>5617</v>
@@ -4740,13 +4862,13 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B119">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C119" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D119">
-        <v>5550</v>
+        <v>5617</v>
       </c>
       <c r="E119" t="s">
         <v>130</v>
@@ -4754,10 +4876,13 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B120">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C120" t="s">
-        <v>145</v>
+        <v>144</v>
+      </c>
+      <c r="D120">
+        <v>5550</v>
       </c>
       <c r="E120" t="s">
         <v>130</v>
@@ -4765,21 +4890,21 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B121">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E121" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B122">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C122" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E122" t="s">
         <v>84</v>
@@ -4787,10 +4912,10 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B123">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C123" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E123" t="s">
         <v>84</v>
@@ -4798,41 +4923,38 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B124">
+        <v>265</v>
+      </c>
+      <c r="C124" t="s">
+        <v>148</v>
+      </c>
+      <c r="E124" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B125">
         <v>266</v>
       </c>
-      <c r="C124" s="15" t="s">
+      <c r="C125" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="D124">
+      <c r="D125">
         <v>30000</v>
       </c>
-      <c r="E124" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A125" s="15" t="s">
+      <c r="E125" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="B125">
+      <c r="B126">
         <v>8001</v>
       </c>
-      <c r="C125" s="15" t="s">
+      <c r="C126" s="15" t="s">
         <v>152</v>
-      </c>
-      <c r="E125" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
-        <v>153</v>
-      </c>
-      <c r="B126">
-        <v>8002</v>
-      </c>
-      <c r="C126" s="15" t="s">
-        <v>154</v>
       </c>
       <c r="E126" t="s">
         <v>150</v>
@@ -4840,27 +4962,27 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
+        <v>153</v>
+      </c>
+      <c r="B127">
+        <v>8002</v>
+      </c>
+      <c r="C127" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E127" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
         <v>155</v>
       </c>
-      <c r="B127">
+      <c r="B128">
         <v>8003</v>
       </c>
-      <c r="C127" s="15" t="s">
+      <c r="C128" s="15" t="s">
         <v>156</v>
-      </c>
-      <c r="E127" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A128" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="B128">
-        <v>10000</v>
-      </c>
-      <c r="C128" s="15" t="s">
-        <v>158</v>
       </c>
       <c r="E128" t="s">
         <v>150</v>
@@ -4868,13 +4990,13 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B129">
-        <v>10001</v>
+        <v>10000</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E129" t="s">
         <v>150</v>
@@ -4882,13 +5004,13 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="15" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B130">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E130" t="s">
         <v>150</v>
@@ -4896,13 +5018,13 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="15" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B131">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E131" t="s">
         <v>150</v>
@@ -4910,16 +5032,13 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B132">
-        <v>10101</v>
+        <v>10003</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="D132">
-        <v>7500</v>
+        <v>164</v>
       </c>
       <c r="E132" t="s">
         <v>150</v>
@@ -4927,16 +5046,16 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="15" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B133">
-        <v>10102</v>
+        <v>10101</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D133">
-        <v>73427</v>
+        <v>7500</v>
       </c>
       <c r="E133" t="s">
         <v>150</v>
@@ -4944,13 +5063,16 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B134">
-        <v>10103</v>
+        <v>10102</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>170</v>
+        <v>168</v>
+      </c>
+      <c r="D134">
+        <v>73427</v>
       </c>
       <c r="E134" t="s">
         <v>150</v>
@@ -4958,13 +5080,13 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B135">
-        <v>10104</v>
+        <v>10103</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E135" t="s">
         <v>150</v>
@@ -4972,13 +5094,13 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B136">
-        <v>10105</v>
+        <v>10104</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E136" t="s">
         <v>150</v>
@@ -4986,13 +5108,13 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B137">
-        <v>10106</v>
+        <v>10105</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E137" t="s">
         <v>150</v>
@@ -5000,13 +5122,13 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="15" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B138">
-        <v>10107</v>
+        <v>10106</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E138" t="s">
         <v>150</v>
@@ -5014,41 +5136,41 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="B139">
+        <v>10107</v>
+      </c>
+      <c r="C139" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="E139" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A140" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="B139">
+      <c r="B140">
         <v>10108</v>
       </c>
-      <c r="C139" s="15" t="s">
+      <c r="C140" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="E139" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="37" t="s">
+      <c r="E140" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="B140">
+      <c r="B141">
         <v>10109</v>
       </c>
-      <c r="C140" s="15" t="s">
+      <c r="C141" s="15" t="s">
         <v>182</v>
-      </c>
-      <c r="E140" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A141" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="B141">
-        <v>10110</v>
-      </c>
-      <c r="C141" s="15" t="s">
-        <v>184</v>
       </c>
       <c r="E141" t="s">
         <v>150</v>
@@ -5056,13 +5178,13 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="15" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B142">
-        <v>10111</v>
+        <v>10110</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E142" t="s">
         <v>150</v>
@@ -5070,13 +5192,13 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B143">
-        <v>10112</v>
+        <v>10111</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E143" t="s">
         <v>150</v>
@@ -5084,13 +5206,13 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B144">
-        <v>10113</v>
+        <v>10112</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E144" t="s">
         <v>150</v>
@@ -5098,13 +5220,13 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B145">
-        <v>10114</v>
+        <v>10113</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E145" t="s">
         <v>150</v>
@@ -5112,13 +5234,13 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B146">
-        <v>10115</v>
+        <v>10114</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E146" t="s">
         <v>150</v>
@@ -5126,13 +5248,13 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B147">
-        <v>10116</v>
+        <v>10115</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E147" t="s">
         <v>150</v>
@@ -5140,13 +5262,13 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="15" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B148">
-        <v>10117</v>
+        <v>10116</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E148" t="s">
         <v>150</v>
@@ -5154,16 +5276,13 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B149">
-        <v>10118</v>
+        <v>10117</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="D149" s="15">
-        <v>120048</v>
+        <v>198</v>
       </c>
       <c r="E149" t="s">
         <v>150</v>
@@ -5171,28 +5290,30 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B150">
-        <v>10119</v>
+        <v>10118</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="D150" s="15"/>
+        <v>200</v>
+      </c>
+      <c r="D150" s="15">
+        <v>120048</v>
+      </c>
       <c r="E150" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B151">
-        <v>10120</v>
+        <v>10119</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D151" s="15"/>
       <c r="E151" t="s">
@@ -5201,13 +5322,13 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B152">
-        <v>10121</v>
+        <v>10120</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D152" s="15"/>
       <c r="E152" t="s">
@@ -5216,13 +5337,13 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B153">
-        <v>10122</v>
+        <v>10121</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D153" s="15"/>
       <c r="E153" t="s">
@@ -5231,13 +5352,13 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="15" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="B154">
-        <v>10123</v>
+        <v>10122</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D154" s="15"/>
       <c r="E154" t="s">
@@ -5246,13 +5367,13 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="15" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="B155">
-        <v>10124</v>
+        <v>10123</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D155" s="15"/>
       <c r="E155" t="s">
@@ -5261,13 +5382,13 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" s="15" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B156">
-        <v>10125</v>
+        <v>10124</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D156" s="15"/>
       <c r="E156" t="s">
@@ -5276,13 +5397,13 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B157">
-        <v>10126</v>
+        <v>10125</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D157" s="15"/>
       <c r="E157" t="s">
@@ -5291,13 +5412,13 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B158">
-        <v>10127</v>
+        <v>10126</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D158" s="15"/>
       <c r="E158" t="s">
@@ -5306,13 +5427,13 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="15" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B159">
-        <v>10128</v>
+        <v>10127</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D159" s="15"/>
       <c r="E159" t="s">
@@ -5321,45 +5442,45 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="B160" s="15">
-        <v>10129</v>
+        <v>218</v>
+      </c>
+      <c r="B160">
+        <v>10128</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="D160" s="15">
-        <v>65184</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="D160" s="15"/>
       <c r="E160" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B161" s="15">
-        <v>10130</v>
+        <v>10129</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="D161" s="15"/>
+        <v>221</v>
+      </c>
+      <c r="D161" s="15">
+        <v>65184</v>
+      </c>
       <c r="E161" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B162" s="15">
-        <v>10131</v>
+        <v>10130</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D162" s="15"/>
       <c r="E162" t="s">
@@ -5368,13 +5489,13 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" s="15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B163" s="15">
-        <v>10132</v>
+        <v>10131</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D163" s="15"/>
       <c r="E163" t="s">
@@ -5383,13 +5504,13 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="15" t="s">
-        <v>175</v>
+        <v>226</v>
       </c>
       <c r="B164" s="15">
-        <v>10133</v>
+        <v>10132</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D164" s="15"/>
       <c r="E164" t="s">
@@ -5398,13 +5519,13 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="15" t="s">
-        <v>229</v>
+        <v>175</v>
       </c>
       <c r="B165" s="15">
-        <v>10134</v>
+        <v>10133</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D165" s="15"/>
       <c r="E165" t="s">
@@ -5413,13 +5534,13 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B166" s="15">
-        <v>10135</v>
+        <v>10134</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D166" s="15"/>
       <c r="E166" t="s">
@@ -5428,13 +5549,13 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="15" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B167" s="15">
-        <v>10136</v>
+        <v>10135</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D167" s="15"/>
       <c r="E167" t="s">
@@ -5443,33 +5564,31 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="B168" s="30">
-        <v>10137</v>
-      </c>
-      <c r="C168" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="D168" s="15">
-        <v>7500</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="B168" s="15">
+        <v>10136</v>
+      </c>
+      <c r="C168" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="D168" s="15"/>
       <c r="E168" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B169" s="30">
-        <v>10138</v>
+        <v>10137</v>
       </c>
       <c r="C169" s="30" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D169" s="15">
-        <v>73427</v>
+        <v>7500</v>
       </c>
       <c r="E169" t="s">
         <v>150</v>
@@ -5477,28 +5596,30 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B170" s="30">
-        <v>10139</v>
+        <v>10138</v>
       </c>
       <c r="C170" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="D170" s="15"/>
+        <v>168</v>
+      </c>
+      <c r="D170" s="15">
+        <v>73427</v>
+      </c>
       <c r="E170" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" s="15" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B171" s="30">
-        <v>10140</v>
+        <v>10139</v>
       </c>
       <c r="C171" s="30" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D171" s="15"/>
       <c r="E171" t="s">
@@ -5507,13 +5628,13 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="15" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B172" s="30">
-        <v>10141</v>
+        <v>10140</v>
       </c>
       <c r="C172" s="30" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D172" s="15"/>
       <c r="E172" t="s">
@@ -5522,13 +5643,13 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="15" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B173" s="30">
-        <v>10142</v>
+        <v>10141</v>
       </c>
       <c r="C173" s="30" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D173" s="15"/>
       <c r="E173" t="s">
@@ -5537,45 +5658,45 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="B174" s="41">
-        <v>10143</v>
-      </c>
-      <c r="C174" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D174" s="15">
-        <v>180000</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="B174" s="30">
+        <v>10142</v>
+      </c>
+      <c r="C174" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="D174" s="15"/>
       <c r="E174" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="15" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B175" s="41">
-        <v>10144</v>
+        <v>10143</v>
       </c>
       <c r="C175" s="41" t="s">
-        <v>248</v>
-      </c>
-      <c r="D175" s="15"/>
+        <v>246</v>
+      </c>
+      <c r="D175" s="15">
+        <v>180000</v>
+      </c>
       <c r="E175" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="15" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B176" s="41">
-        <v>10145</v>
+        <v>10144</v>
       </c>
       <c r="C176" s="41" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D176" s="15"/>
       <c r="E176" t="s">
@@ -5584,13 +5705,13 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="15" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B177" s="41">
-        <v>10146</v>
+        <v>10145</v>
       </c>
       <c r="C177" s="41" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D177" s="15"/>
       <c r="E177" t="s">
@@ -5599,13 +5720,13 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="15" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B178" s="41">
-        <v>10147</v>
+        <v>10146</v>
       </c>
       <c r="C178" s="41" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D178" s="15"/>
       <c r="E178" t="s">
@@ -5614,13 +5735,13 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="15" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B179" s="41">
-        <v>10148</v>
+        <v>10147</v>
       </c>
       <c r="C179" s="41" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D179" s="15"/>
       <c r="E179" t="s">
@@ -5629,13 +5750,13 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B180" s="41">
-        <v>10149</v>
+        <v>10148</v>
       </c>
       <c r="C180" s="41" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D180" s="15"/>
       <c r="E180" t="s">
@@ -5644,13 +5765,13 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="15" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B181" s="41">
-        <v>10150</v>
+        <v>10149</v>
       </c>
       <c r="C181" s="41" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D181" s="15"/>
       <c r="E181" t="s">
@@ -5659,13 +5780,13 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B182" s="41">
-        <v>10151</v>
+        <v>10150</v>
       </c>
       <c r="C182" s="41" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D182" s="15"/>
       <c r="E182" t="s">
@@ -5674,13 +5795,13 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="15" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B183" s="41">
-        <v>10152</v>
+        <v>10151</v>
       </c>
       <c r="C183" s="41" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D183" s="15"/>
       <c r="E183" t="s">
@@ -5689,13 +5810,13 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="15" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B184" s="41">
-        <v>10153</v>
+        <v>10152</v>
       </c>
       <c r="C184" s="41" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D184" s="15"/>
       <c r="E184" t="s">
@@ -5704,13 +5825,13 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B185" s="41">
-        <v>10154</v>
+        <v>10153</v>
       </c>
       <c r="C185" s="41" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D185" s="15"/>
       <c r="E185" t="s">
@@ -5719,13 +5840,13 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="15" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B186" s="41">
-        <v>10155</v>
+        <v>10154</v>
       </c>
       <c r="C186" s="41" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D186" s="15"/>
       <c r="E186" t="s">
@@ -5734,13 +5855,13 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="15" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B187" s="41">
-        <v>10156</v>
+        <v>10155</v>
       </c>
       <c r="C187" s="41" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D187" s="15"/>
       <c r="E187" t="s">
@@ -5749,13 +5870,13 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="15" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B188" s="41">
-        <v>10157</v>
+        <v>10156</v>
       </c>
       <c r="C188" s="41" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D188" s="15"/>
       <c r="E188" t="s">
@@ -5764,13 +5885,13 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B189" s="41">
-        <v>10158</v>
+        <v>10157</v>
       </c>
       <c r="C189" s="41" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D189" s="15"/>
       <c r="E189" t="s">
@@ -5779,13 +5900,13 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B190" s="41">
-        <v>10159</v>
+        <v>10158</v>
       </c>
       <c r="C190" s="41" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D190" s="15"/>
       <c r="E190" t="s">
@@ -5794,13 +5915,13 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B191" s="41">
-        <v>10160</v>
+        <v>10159</v>
       </c>
       <c r="C191" s="41" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D191" s="15"/>
       <c r="E191" t="s">
@@ -5809,13 +5930,13 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="15" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B192" s="41">
-        <v>10161</v>
+        <v>10160</v>
       </c>
       <c r="C192" s="41" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D192" s="15"/>
       <c r="E192" t="s">
@@ -5824,13 +5945,13 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" s="15" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B193" s="41">
-        <v>10162</v>
+        <v>10161</v>
       </c>
       <c r="C193" s="41" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D193" s="15"/>
       <c r="E193" t="s">
@@ -5839,13 +5960,13 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B194" s="41">
-        <v>10163</v>
+        <v>10162</v>
       </c>
       <c r="C194" s="41" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D194" s="15"/>
       <c r="E194" t="s">
@@ -5854,13 +5975,13 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="15" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B195" s="41">
-        <v>10164</v>
+        <v>10163</v>
       </c>
       <c r="C195" s="41" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D195" s="15"/>
       <c r="E195" t="s">
@@ -5869,13 +5990,13 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="15" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B196" s="41">
-        <v>10165</v>
+        <v>10164</v>
       </c>
       <c r="C196" s="41" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D196" s="15"/>
       <c r="E196" t="s">
@@ -5884,13 +6005,13 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="15" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B197" s="41">
-        <v>10166</v>
+        <v>10165</v>
       </c>
       <c r="C197" s="41" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D197" s="15"/>
       <c r="E197" t="s">
@@ -5899,13 +6020,13 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="15" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B198" s="41">
-        <v>10167</v>
+        <v>10166</v>
       </c>
       <c r="C198" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D198" s="15"/>
       <c r="E198" t="s">
@@ -5914,13 +6035,13 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="15" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B199" s="41">
-        <v>10168</v>
+        <v>10167</v>
       </c>
       <c r="C199" s="41" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D199" s="15"/>
       <c r="E199" t="s">
@@ -5929,13 +6050,13 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="15" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B200" s="41">
-        <v>10169</v>
+        <v>10168</v>
       </c>
       <c r="C200" s="41" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D200" s="15"/>
       <c r="E200" t="s">
@@ -5944,13 +6065,13 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" s="15" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B201" s="41">
-        <v>10170</v>
+        <v>10169</v>
       </c>
       <c r="C201" s="41" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D201" s="15"/>
       <c r="E201" t="s">
@@ -5959,45 +6080,45 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B202" s="41">
-        <v>10171</v>
+        <v>10170</v>
       </c>
       <c r="C202" s="41" t="s">
-        <v>302</v>
-      </c>
-      <c r="D202" s="15">
-        <v>76000</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="D202" s="15"/>
       <c r="E202" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="15" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B203" s="41">
-        <v>10172</v>
+        <v>10171</v>
       </c>
       <c r="C203" s="41" t="s">
-        <v>304</v>
-      </c>
-      <c r="D203" s="15"/>
+        <v>302</v>
+      </c>
+      <c r="D203" s="15">
+        <v>76000</v>
+      </c>
       <c r="E203" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" s="15" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B204" s="41">
-        <v>10173</v>
+        <v>10172</v>
       </c>
       <c r="C204" s="41" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D204" s="15"/>
       <c r="E204" t="s">
@@ -6006,13 +6127,13 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B205" s="41">
-        <v>10174</v>
+        <v>10173</v>
       </c>
       <c r="C205" s="41" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D205" s="15"/>
       <c r="E205" t="s">
@@ -6021,13 +6142,13 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" s="15" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B206" s="41">
-        <v>10175</v>
+        <v>10174</v>
       </c>
       <c r="C206" s="41" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D206" s="15"/>
       <c r="E206" t="s">
@@ -6036,13 +6157,13 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" s="15" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B207" s="41">
-        <v>10176</v>
+        <v>10175</v>
       </c>
       <c r="C207" s="41" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D207" s="15"/>
       <c r="E207" t="s">
@@ -6051,13 +6172,13 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" s="15" t="s">
-        <v>175</v>
+        <v>311</v>
       </c>
       <c r="B208" s="41">
-        <v>10177</v>
+        <v>10176</v>
       </c>
       <c r="C208" s="41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D208" s="15"/>
       <c r="E208" t="s">
@@ -6066,13 +6187,13 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" s="15" t="s">
-        <v>314</v>
+        <v>175</v>
       </c>
       <c r="B209" s="41">
-        <v>10178</v>
+        <v>10177</v>
       </c>
       <c r="C209" s="41" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D209" s="15"/>
       <c r="E209" t="s">
@@ -6081,13 +6202,13 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" s="15" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B210" s="41">
-        <v>10179</v>
+        <v>10178</v>
       </c>
       <c r="C210" s="41" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D210" s="15"/>
       <c r="E210" t="s">
@@ -6096,13 +6217,13 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" s="15" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B211" s="41">
-        <v>10180</v>
+        <v>10179</v>
       </c>
       <c r="C211" s="41" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D211" s="15"/>
       <c r="E211" t="s">
@@ -6111,13 +6232,13 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" s="15" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B212" s="41">
-        <v>10181</v>
+        <v>10180</v>
       </c>
       <c r="C212" s="41" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D212" s="15"/>
       <c r="E212" t="s">
@@ -6126,13 +6247,13 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" s="15" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B213" s="41">
-        <v>10182</v>
+        <v>10181</v>
       </c>
       <c r="C213" s="41" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D213" s="15"/>
       <c r="E213" t="s">
@@ -6141,13 +6262,13 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" s="15" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B214" s="41">
-        <v>10183</v>
+        <v>10182</v>
       </c>
       <c r="C214" s="41" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D214" s="15"/>
       <c r="E214" t="s">
@@ -6156,13 +6277,13 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" s="15" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B215" s="41">
-        <v>10184</v>
+        <v>10183</v>
       </c>
       <c r="C215" s="41" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D215" s="15"/>
       <c r="E215" t="s">
@@ -6171,13 +6292,13 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B216" s="41">
-        <v>10185</v>
+        <v>10184</v>
       </c>
       <c r="C216" s="41" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D216" s="15"/>
       <c r="E216" t="s">
@@ -6186,13 +6307,13 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" s="15" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B217" s="41">
-        <v>10186</v>
+        <v>10185</v>
       </c>
       <c r="C217" s="41" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D217" s="15"/>
       <c r="E217" t="s">
@@ -6201,13 +6322,13 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" s="15" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B218" s="41">
-        <v>10187</v>
+        <v>10186</v>
       </c>
       <c r="C218" s="41" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D218" s="15"/>
       <c r="E218" t="s">
@@ -6216,13 +6337,13 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" s="15" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B219" s="41">
-        <v>10188</v>
+        <v>10187</v>
       </c>
       <c r="C219" s="41" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D219" s="15"/>
       <c r="E219" t="s">
@@ -6231,13 +6352,13 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" s="15" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B220" s="41">
-        <v>10189</v>
+        <v>10188</v>
       </c>
       <c r="C220" s="41" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D220" s="15"/>
       <c r="E220" t="s">
@@ -6246,45 +6367,45 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" s="15" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B221" s="41">
-        <v>10190</v>
+        <v>10189</v>
       </c>
       <c r="C221" s="41" t="s">
-        <v>339</v>
-      </c>
-      <c r="D221" s="15">
-        <v>174000</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="D221" s="15"/>
       <c r="E221" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" s="15" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B222" s="41">
-        <v>10191</v>
+        <v>10190</v>
       </c>
       <c r="C222" s="41" t="s">
-        <v>341</v>
-      </c>
-      <c r="D222" s="15"/>
+        <v>339</v>
+      </c>
+      <c r="D222" s="15">
+        <v>174000</v>
+      </c>
       <c r="E222" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" s="15" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B223" s="41">
-        <v>10192</v>
+        <v>10191</v>
       </c>
       <c r="C223" s="41" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D223" s="15"/>
       <c r="E223" t="s">
@@ -6293,13 +6414,13 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" s="15" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B224" s="41">
-        <v>10193</v>
+        <v>10192</v>
       </c>
       <c r="C224" s="41" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D224" s="15"/>
       <c r="E224" t="s">
@@ -6308,13 +6429,13 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" s="15" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B225" s="41">
-        <v>10194</v>
+        <v>10193</v>
       </c>
       <c r="C225" s="41" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D225" s="15"/>
       <c r="E225" t="s">
@@ -6323,13 +6444,13 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" s="15" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B226" s="41">
-        <v>10195</v>
+        <v>10194</v>
       </c>
       <c r="C226" s="41" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D226" s="15"/>
       <c r="E226" t="s">
@@ -6338,45 +6459,45 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" s="15" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B227" s="41">
-        <v>10300</v>
+        <v>10195</v>
       </c>
       <c r="C227" s="41" t="s">
-        <v>351</v>
-      </c>
-      <c r="D227" s="15">
-        <v>63000</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="D227" s="15"/>
       <c r="E227" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" s="15" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B228" s="41">
-        <v>10301</v>
+        <v>10300</v>
       </c>
       <c r="C228" s="41" t="s">
-        <v>778</v>
-      </c>
-      <c r="D228" s="15"/>
+        <v>351</v>
+      </c>
+      <c r="D228" s="15">
+        <v>63000</v>
+      </c>
       <c r="E228" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="B229" s="41">
+        <v>10301</v>
+      </c>
+      <c r="C229" s="41" t="s">
         <v>353</v>
-      </c>
-      <c r="B229" s="41">
-        <v>10302</v>
-      </c>
-      <c r="C229" s="41" t="s">
-        <v>354</v>
       </c>
       <c r="D229" s="15"/>
       <c r="E229" t="s">
@@ -6385,13 +6506,13 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="B230" s="41">
+        <v>10302</v>
+      </c>
+      <c r="C230" s="41" t="s">
         <v>355</v>
-      </c>
-      <c r="B230" s="41">
-        <v>10303</v>
-      </c>
-      <c r="C230" s="41" t="s">
-        <v>356</v>
       </c>
       <c r="D230" s="15"/>
       <c r="E230" t="s">
@@ -6400,13 +6521,13 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="B231" s="41">
+        <v>10303</v>
+      </c>
+      <c r="C231" s="41" t="s">
         <v>357</v>
-      </c>
-      <c r="B231" s="41">
-        <v>10304</v>
-      </c>
-      <c r="C231" s="41" t="s">
-        <v>358</v>
       </c>
       <c r="D231" s="15"/>
       <c r="E231" t="s">
@@ -6415,13 +6536,13 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="B232" s="41">
+        <v>10304</v>
+      </c>
+      <c r="C232" s="41" t="s">
         <v>359</v>
-      </c>
-      <c r="B232" s="41">
-        <v>10305</v>
-      </c>
-      <c r="C232" s="41" t="s">
-        <v>360</v>
       </c>
       <c r="D232" s="15"/>
       <c r="E232" t="s">
@@ -6430,13 +6551,13 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="B233" s="41">
+        <v>10305</v>
+      </c>
+      <c r="C233" s="41" t="s">
         <v>361</v>
-      </c>
-      <c r="B233" s="41">
-        <v>10306</v>
-      </c>
-      <c r="C233" s="41" t="s">
-        <v>362</v>
       </c>
       <c r="D233" s="15"/>
       <c r="E233" t="s">
@@ -6445,13 +6566,13 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="B234" s="41">
+        <v>10306</v>
+      </c>
+      <c r="C234" s="41" t="s">
         <v>363</v>
-      </c>
-      <c r="B234" s="41">
-        <v>10307</v>
-      </c>
-      <c r="C234" s="41" t="s">
-        <v>364</v>
       </c>
       <c r="D234" s="15"/>
       <c r="E234" t="s">
@@ -6460,13 +6581,13 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="B235" s="41">
+        <v>10307</v>
+      </c>
+      <c r="C235" s="41" t="s">
         <v>365</v>
-      </c>
-      <c r="B235" s="41">
-        <v>10308</v>
-      </c>
-      <c r="C235" s="41" t="s">
-        <v>779</v>
       </c>
       <c r="D235" s="15"/>
       <c r="E235" t="s">
@@ -6478,7 +6599,7 @@
         <v>366</v>
       </c>
       <c r="B236" s="41">
-        <v>10309</v>
+        <v>10308</v>
       </c>
       <c r="C236" s="41" t="s">
         <v>367</v>
@@ -6493,7 +6614,7 @@
         <v>368</v>
       </c>
       <c r="B237" s="41">
-        <v>10310</v>
+        <v>10309</v>
       </c>
       <c r="C237" s="41" t="s">
         <v>369</v>
@@ -6508,7 +6629,7 @@
         <v>370</v>
       </c>
       <c r="B238" s="41">
-        <v>10311</v>
+        <v>10310</v>
       </c>
       <c r="C238" s="41" t="s">
         <v>371</v>
@@ -6523,7 +6644,7 @@
         <v>372</v>
       </c>
       <c r="B239" s="41">
-        <v>10312</v>
+        <v>10311</v>
       </c>
       <c r="C239" s="41" t="s">
         <v>373</v>
@@ -6538,7 +6659,7 @@
         <v>374</v>
       </c>
       <c r="B240" s="41">
-        <v>10313</v>
+        <v>10312</v>
       </c>
       <c r="C240" s="41" t="s">
         <v>375</v>
@@ -6553,7 +6674,7 @@
         <v>376</v>
       </c>
       <c r="B241" s="41">
-        <v>10314</v>
+        <v>10313</v>
       </c>
       <c r="C241" s="41" t="s">
         <v>377</v>
@@ -6568,7 +6689,7 @@
         <v>378</v>
       </c>
       <c r="B242" s="41">
-        <v>10315</v>
+        <v>10314</v>
       </c>
       <c r="C242" s="41" t="s">
         <v>379</v>
@@ -6583,7 +6704,7 @@
         <v>380</v>
       </c>
       <c r="B243" s="41">
-        <v>10316</v>
+        <v>10315</v>
       </c>
       <c r="C243" s="41" t="s">
         <v>381</v>
@@ -6598,7 +6719,7 @@
         <v>382</v>
       </c>
       <c r="B244" s="41">
-        <v>10317</v>
+        <v>10316</v>
       </c>
       <c r="C244" s="41" t="s">
         <v>383</v>
@@ -6613,7 +6734,7 @@
         <v>384</v>
       </c>
       <c r="B245" s="41">
-        <v>10318</v>
+        <v>10317</v>
       </c>
       <c r="C245" s="41" t="s">
         <v>385</v>
@@ -6628,7 +6749,7 @@
         <v>386</v>
       </c>
       <c r="B246" s="41">
-        <v>10319</v>
+        <v>10318</v>
       </c>
       <c r="C246" s="41" t="s">
         <v>387</v>
@@ -6643,7 +6764,7 @@
         <v>388</v>
       </c>
       <c r="B247" s="41">
-        <v>10320</v>
+        <v>10319</v>
       </c>
       <c r="C247" s="41" t="s">
         <v>389</v>
@@ -6658,7 +6779,7 @@
         <v>390</v>
       </c>
       <c r="B248" s="41">
-        <v>10321</v>
+        <v>10320</v>
       </c>
       <c r="C248" s="41" t="s">
         <v>391</v>
@@ -6673,7 +6794,7 @@
         <v>392</v>
       </c>
       <c r="B249" s="41">
-        <v>10322</v>
+        <v>10321</v>
       </c>
       <c r="C249" s="41" t="s">
         <v>393</v>
@@ -6688,7 +6809,7 @@
         <v>394</v>
       </c>
       <c r="B250" s="41">
-        <v>10323</v>
+        <v>10322</v>
       </c>
       <c r="C250" s="41" t="s">
         <v>395</v>
@@ -6703,7 +6824,7 @@
         <v>396</v>
       </c>
       <c r="B251" s="41">
-        <v>10324</v>
+        <v>10323</v>
       </c>
       <c r="C251" s="41" t="s">
         <v>397</v>
@@ -6718,7 +6839,7 @@
         <v>398</v>
       </c>
       <c r="B252" s="41">
-        <v>10325</v>
+        <v>10324</v>
       </c>
       <c r="C252" s="41" t="s">
         <v>399</v>
@@ -6733,7 +6854,7 @@
         <v>400</v>
       </c>
       <c r="B253" s="41">
-        <v>10326</v>
+        <v>10325</v>
       </c>
       <c r="C253" s="41" t="s">
         <v>401</v>
@@ -6748,7 +6869,7 @@
         <v>402</v>
       </c>
       <c r="B254" s="41">
-        <v>10327</v>
+        <v>10326</v>
       </c>
       <c r="C254" s="41" t="s">
         <v>403</v>
@@ -6763,7 +6884,7 @@
         <v>404</v>
       </c>
       <c r="B255" s="41">
-        <v>10328</v>
+        <v>10327</v>
       </c>
       <c r="C255" s="41" t="s">
         <v>405</v>
@@ -6778,7 +6899,7 @@
         <v>406</v>
       </c>
       <c r="B256" s="41">
-        <v>10329</v>
+        <v>10328</v>
       </c>
       <c r="C256" s="41" t="s">
         <v>407</v>
@@ -6793,7 +6914,7 @@
         <v>408</v>
       </c>
       <c r="B257" s="41">
-        <v>10330</v>
+        <v>10329</v>
       </c>
       <c r="C257" s="41" t="s">
         <v>409</v>
@@ -6808,14 +6929,12 @@
         <v>410</v>
       </c>
       <c r="B258" s="41">
-        <v>10331</v>
+        <v>10330</v>
       </c>
       <c r="C258" s="41" t="s">
         <v>411</v>
       </c>
-      <c r="D258" s="15">
-        <v>60000</v>
-      </c>
+      <c r="D258" s="15"/>
       <c r="E258" t="s">
         <v>150</v>
       </c>
@@ -6825,7 +6944,7 @@
         <v>412</v>
       </c>
       <c r="B259" s="41">
-        <v>10332</v>
+        <v>10331</v>
       </c>
       <c r="C259" s="41" t="s">
         <v>413</v>
@@ -6842,12 +6961,14 @@
         <v>414</v>
       </c>
       <c r="B260" s="41">
-        <v>10333</v>
+        <v>10332</v>
       </c>
       <c r="C260" s="41" t="s">
         <v>415</v>
       </c>
-      <c r="D260" s="15"/>
+      <c r="D260" s="15">
+        <v>60000</v>
+      </c>
       <c r="E260" t="s">
         <v>150</v>
       </c>
@@ -6857,7 +6978,7 @@
         <v>416</v>
       </c>
       <c r="B261" s="41">
-        <v>10334</v>
+        <v>10333</v>
       </c>
       <c r="C261" s="41" t="s">
         <v>417</v>
@@ -6872,7 +6993,7 @@
         <v>418</v>
       </c>
       <c r="B262" s="41">
-        <v>10335</v>
+        <v>10334</v>
       </c>
       <c r="C262" s="41" t="s">
         <v>419</v>
@@ -6887,7 +7008,7 @@
         <v>420</v>
       </c>
       <c r="B263" s="41">
-        <v>10336</v>
+        <v>10335</v>
       </c>
       <c r="C263" s="41" t="s">
         <v>421</v>
@@ -6902,7 +7023,7 @@
         <v>422</v>
       </c>
       <c r="B264" s="41">
-        <v>10337</v>
+        <v>10336</v>
       </c>
       <c r="C264" s="41" t="s">
         <v>423</v>
@@ -6917,7 +7038,7 @@
         <v>424</v>
       </c>
       <c r="B265" s="41">
-        <v>10338</v>
+        <v>10337</v>
       </c>
       <c r="C265" s="41" t="s">
         <v>425</v>
@@ -6932,7 +7053,7 @@
         <v>426</v>
       </c>
       <c r="B266" s="41">
-        <v>10339</v>
+        <v>10338</v>
       </c>
       <c r="C266" s="41" t="s">
         <v>427</v>
@@ -6947,7 +7068,7 @@
         <v>428</v>
       </c>
       <c r="B267" s="41">
-        <v>10340</v>
+        <v>10339</v>
       </c>
       <c r="C267" s="41" t="s">
         <v>429</v>
@@ -6962,7 +7083,7 @@
         <v>430</v>
       </c>
       <c r="B268" s="41">
-        <v>10341</v>
+        <v>10340</v>
       </c>
       <c r="C268" s="41" t="s">
         <v>431</v>
@@ -6977,13 +7098,13 @@
         <v>432</v>
       </c>
       <c r="B269" s="41">
-        <v>10342</v>
+        <v>10341</v>
       </c>
       <c r="C269" s="41" t="s">
         <v>433</v>
       </c>
       <c r="D269" s="15"/>
-      <c r="E269" s="15" t="s">
+      <c r="E269" t="s">
         <v>150</v>
       </c>
     </row>
@@ -6992,13 +7113,13 @@
         <v>434</v>
       </c>
       <c r="B270" s="41">
-        <v>10350</v>
+        <v>10342</v>
       </c>
       <c r="C270" s="41" t="s">
         <v>435</v>
       </c>
       <c r="D270" s="15"/>
-      <c r="E270" t="s">
+      <c r="E270" s="15" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7007,7 +7128,7 @@
         <v>436</v>
       </c>
       <c r="B271" s="41">
-        <v>10351</v>
+        <v>10350</v>
       </c>
       <c r="C271" s="41" t="s">
         <v>437</v>
@@ -7022,7 +7143,7 @@
         <v>438</v>
       </c>
       <c r="B272" s="41">
-        <v>10352</v>
+        <v>10351</v>
       </c>
       <c r="C272" s="41" t="s">
         <v>439</v>
@@ -7037,7 +7158,7 @@
         <v>440</v>
       </c>
       <c r="B273" s="41">
-        <v>10353</v>
+        <v>10352</v>
       </c>
       <c r="C273" s="41" t="s">
         <v>441</v>
@@ -7052,10 +7173,10 @@
         <v>442</v>
       </c>
       <c r="B274" s="41">
-        <v>10354</v>
+        <v>10353</v>
       </c>
       <c r="C274" s="41" t="s">
-        <v>381</v>
+        <v>443</v>
       </c>
       <c r="D274" s="15"/>
       <c r="E274" t="s">
@@ -7064,13 +7185,13 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A275" s="15" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B275" s="41">
-        <v>10355</v>
+        <v>10354</v>
       </c>
       <c r="C275" s="41" t="s">
-        <v>444</v>
+        <v>383</v>
       </c>
       <c r="D275" s="15"/>
       <c r="E275" t="s">
@@ -7082,7 +7203,7 @@
         <v>445</v>
       </c>
       <c r="B276" s="41">
-        <v>10356</v>
+        <v>10355</v>
       </c>
       <c r="C276" s="41" t="s">
         <v>446</v>
@@ -7097,7 +7218,7 @@
         <v>447</v>
       </c>
       <c r="B277" s="41">
-        <v>10357</v>
+        <v>10356</v>
       </c>
       <c r="C277" s="41" t="s">
         <v>448</v>
@@ -7112,7 +7233,7 @@
         <v>449</v>
       </c>
       <c r="B278" s="41">
-        <v>10358</v>
+        <v>10357</v>
       </c>
       <c r="C278" s="41" t="s">
         <v>450</v>
@@ -7127,7 +7248,7 @@
         <v>451</v>
       </c>
       <c r="B279" s="41">
-        <v>10359</v>
+        <v>10358</v>
       </c>
       <c r="C279" s="41" t="s">
         <v>452</v>
@@ -7142,7 +7263,7 @@
         <v>453</v>
       </c>
       <c r="B280" s="41">
-        <v>10360</v>
+        <v>10359</v>
       </c>
       <c r="C280" s="41" t="s">
         <v>454</v>
@@ -7157,7 +7278,7 @@
         <v>455</v>
       </c>
       <c r="B281" s="41">
-        <v>10361</v>
+        <v>10360</v>
       </c>
       <c r="C281" s="41" t="s">
         <v>456</v>
@@ -7172,7 +7293,7 @@
         <v>457</v>
       </c>
       <c r="B282" s="41">
-        <v>10362</v>
+        <v>10361</v>
       </c>
       <c r="C282" s="41" t="s">
         <v>458</v>
@@ -7187,7 +7308,7 @@
         <v>459</v>
       </c>
       <c r="B283" s="41">
-        <v>10363</v>
+        <v>10362</v>
       </c>
       <c r="C283" s="41" t="s">
         <v>460</v>
@@ -7202,7 +7323,7 @@
         <v>461</v>
       </c>
       <c r="B284" s="41">
-        <v>10364</v>
+        <v>10363</v>
       </c>
       <c r="C284" s="41" t="s">
         <v>462</v>
@@ -7217,7 +7338,7 @@
         <v>463</v>
       </c>
       <c r="B285" s="41">
-        <v>10365</v>
+        <v>10364</v>
       </c>
       <c r="C285" s="41" t="s">
         <v>464</v>
@@ -7232,7 +7353,7 @@
         <v>465</v>
       </c>
       <c r="B286" s="41">
-        <v>10366</v>
+        <v>10365</v>
       </c>
       <c r="C286" s="41" t="s">
         <v>466</v>
@@ -7247,7 +7368,7 @@
         <v>467</v>
       </c>
       <c r="B287" s="41">
-        <v>10367</v>
+        <v>10366</v>
       </c>
       <c r="C287" s="41" t="s">
         <v>468</v>
@@ -7262,7 +7383,7 @@
         <v>469</v>
       </c>
       <c r="B288" s="41">
-        <v>10368</v>
+        <v>10367</v>
       </c>
       <c r="C288" s="41" t="s">
         <v>470</v>
@@ -7277,7 +7398,7 @@
         <v>471</v>
       </c>
       <c r="B289" s="41">
-        <v>10369</v>
+        <v>10368</v>
       </c>
       <c r="C289" s="41" t="s">
         <v>472</v>
@@ -7291,11 +7412,11 @@
       <c r="A290" s="15" t="s">
         <v>473</v>
       </c>
-      <c r="B290" s="15">
-        <v>10370</v>
-      </c>
-      <c r="C290" s="15" t="s">
-        <v>771</v>
+      <c r="B290" s="41">
+        <v>10369</v>
+      </c>
+      <c r="C290" s="41" t="s">
+        <v>474</v>
       </c>
       <c r="D290" s="15"/>
       <c r="E290" t="s">
@@ -7304,13 +7425,13 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" s="15" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B291" s="15">
-        <v>10371</v>
+        <v>10370</v>
       </c>
       <c r="C291" s="15" t="s">
-        <v>475</v>
+        <v>773</v>
       </c>
       <c r="D291" s="15"/>
       <c r="E291" t="s">
@@ -7322,7 +7443,7 @@
         <v>476</v>
       </c>
       <c r="B292" s="15">
-        <v>10372</v>
+        <v>10371</v>
       </c>
       <c r="C292" s="15" t="s">
         <v>477</v>
@@ -7337,7 +7458,7 @@
         <v>478</v>
       </c>
       <c r="B293" s="15">
-        <v>10373</v>
+        <v>10372</v>
       </c>
       <c r="C293" s="15" t="s">
         <v>479</v>
@@ -7352,7 +7473,7 @@
         <v>480</v>
       </c>
       <c r="B294" s="15">
-        <v>10374</v>
+        <v>10373</v>
       </c>
       <c r="C294" s="15" t="s">
         <v>481</v>
@@ -7367,7 +7488,7 @@
         <v>482</v>
       </c>
       <c r="B295" s="15">
-        <v>10375</v>
+        <v>10374</v>
       </c>
       <c r="C295" s="15" t="s">
         <v>483</v>
@@ -7382,7 +7503,7 @@
         <v>484</v>
       </c>
       <c r="B296" s="15">
-        <v>10376</v>
+        <v>10375</v>
       </c>
       <c r="C296" s="15" t="s">
         <v>485</v>
@@ -7397,7 +7518,7 @@
         <v>486</v>
       </c>
       <c r="B297" s="15">
-        <v>10377</v>
+        <v>10376</v>
       </c>
       <c r="C297" s="15" t="s">
         <v>487</v>
@@ -7412,10 +7533,10 @@
         <v>488</v>
       </c>
       <c r="B298" s="15">
-        <v>10378</v>
+        <v>10377</v>
       </c>
       <c r="C298" s="15" t="s">
-        <v>781</v>
+        <v>489</v>
       </c>
       <c r="D298" s="15"/>
       <c r="E298" t="s">
@@ -7424,13 +7545,13 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299" s="15" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B299" s="15">
-        <v>10379</v>
+        <v>10378</v>
       </c>
       <c r="C299" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D299" s="15"/>
       <c r="E299" t="s">
@@ -7439,13 +7560,13 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" s="15" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B300" s="15">
-        <v>10380</v>
+        <v>10379</v>
       </c>
       <c r="C300" s="15" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D300" s="15"/>
       <c r="E300" t="s">
@@ -7453,14 +7574,14 @@
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A301" s="52" t="s">
-        <v>746</v>
-      </c>
-      <c r="B301" s="52">
-        <v>10381</v>
+      <c r="A301" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="B301" s="15">
+        <v>10380</v>
       </c>
       <c r="C301" s="15" t="s">
-        <v>754</v>
+        <v>225</v>
       </c>
       <c r="D301" s="15"/>
       <c r="E301" t="s">
@@ -7469,13 +7590,13 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" s="52" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B302" s="52">
-        <v>10382</v>
+        <v>10381</v>
       </c>
       <c r="C302" s="15" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D302" s="15"/>
       <c r="E302" t="s">
@@ -7484,13 +7605,13 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" s="52" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B303" s="52">
-        <v>10383</v>
+        <v>10382</v>
       </c>
       <c r="C303" s="15" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="D303" s="15"/>
       <c r="E303" t="s">
@@ -7499,10 +7620,10 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304" s="52" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B304" s="52">
-        <v>10384</v>
+        <v>10383</v>
       </c>
       <c r="C304" s="15" t="s">
         <v>757</v>
@@ -7514,13 +7635,13 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305" s="52" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B305" s="52">
-        <v>10385</v>
+        <v>10384</v>
       </c>
       <c r="C305" s="15" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D305" s="15"/>
       <c r="E305" t="s">
@@ -7529,10 +7650,10 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" s="52" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B306" s="52">
-        <v>10386</v>
+        <v>10385</v>
       </c>
       <c r="C306" s="15" t="s">
         <v>760</v>
@@ -7544,13 +7665,13 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" s="52" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B307" s="52">
-        <v>10387</v>
+        <v>10386</v>
       </c>
       <c r="C307" s="15" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="D307" s="15"/>
       <c r="E307" t="s">
@@ -7559,13 +7680,13 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308" s="52" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B308" s="52">
-        <v>10388</v>
+        <v>10387</v>
       </c>
       <c r="C308" s="15" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="D308" s="15"/>
       <c r="E308" t="s">
@@ -7574,13 +7695,13 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309" s="52" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="B309" s="52">
-        <v>10389</v>
+        <v>10388</v>
       </c>
       <c r="C309" s="15" t="s">
-        <v>769</v>
+        <v>758</v>
       </c>
       <c r="D309" s="15"/>
       <c r="E309" t="s">
@@ -7592,10 +7713,10 @@
         <v>770</v>
       </c>
       <c r="B310" s="52">
-        <v>10390</v>
+        <v>10389</v>
       </c>
       <c r="C310" s="15" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D310" s="15"/>
       <c r="E310" t="s">
@@ -7604,13 +7725,13 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A311" s="52" t="s">
+        <v>772</v>
+      </c>
+      <c r="B311" s="52">
+        <v>10390</v>
+      </c>
+      <c r="C311" s="15" t="s">
         <v>774</v>
-      </c>
-      <c r="B311" s="52">
-        <v>10391</v>
-      </c>
-      <c r="C311" s="15" t="s">
-        <v>776</v>
       </c>
       <c r="D311" s="15"/>
       <c r="E311" t="s">
@@ -7619,13 +7740,13 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A312" s="52" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B312" s="52">
-        <v>10392</v>
+        <v>10391</v>
       </c>
       <c r="C312" s="15" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="D312" s="15"/>
       <c r="E312" t="s">
@@ -7637,10 +7758,10 @@
         <v>777</v>
       </c>
       <c r="B313" s="52">
-        <v>10393</v>
+        <v>10392</v>
       </c>
       <c r="C313" s="15" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="D313" s="15"/>
       <c r="E313" t="s">
@@ -7652,10 +7773,10 @@
         <v>782</v>
       </c>
       <c r="B314" s="52">
-        <v>10394</v>
+        <v>10393</v>
       </c>
       <c r="C314" s="15" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D314" s="15"/>
       <c r="E314" t="s">
@@ -7664,13 +7785,13 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A315" s="52" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B315" s="52">
-        <v>10395</v>
+        <v>10394</v>
       </c>
       <c r="C315" s="15" t="s">
-        <v>206</v>
+        <v>785</v>
       </c>
       <c r="D315" s="15"/>
       <c r="E315" t="s">
@@ -7679,13 +7800,13 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A316" s="52" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B316" s="52">
-        <v>10396</v>
+        <v>10395</v>
       </c>
       <c r="C316" s="15" t="s">
-        <v>785</v>
+        <v>206</v>
       </c>
       <c r="D316" s="15"/>
       <c r="E316" t="s">
@@ -7694,13 +7815,13 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A317" s="52" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B317" s="52">
-        <v>10397</v>
+        <v>10396</v>
       </c>
       <c r="C317" s="15" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D317" s="15"/>
       <c r="E317" t="s">
@@ -7709,13 +7830,13 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A318" s="52" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B318" s="52">
-        <v>10398</v>
+        <v>10397</v>
       </c>
       <c r="C318" s="15" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D318" s="15"/>
       <c r="E318" t="s">
@@ -7723,225 +7844,269 @@
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B319">
+      <c r="A319" s="52" t="s">
+        <v>791</v>
+      </c>
+      <c r="B319" s="52">
+        <v>10398</v>
+      </c>
+      <c r="C319" s="15" t="s">
+        <v>792</v>
+      </c>
+      <c r="D319" s="15"/>
+      <c r="E319" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A320" s="52" t="s">
+        <v>793</v>
+      </c>
+      <c r="B320" s="52">
+        <v>10399</v>
+      </c>
+      <c r="C320" s="15" t="s">
+        <v>794</v>
+      </c>
+      <c r="D320" s="15"/>
+      <c r="E320" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A321" s="52" t="s">
+        <v>795</v>
+      </c>
+      <c r="B321" s="52">
+        <v>10400</v>
+      </c>
+      <c r="C321" s="15" t="s">
+        <v>796</v>
+      </c>
+      <c r="D321" s="15"/>
+      <c r="E321" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A322" s="52" t="s">
+        <v>797</v>
+      </c>
+      <c r="B322" s="52">
+        <v>10401</v>
+      </c>
+      <c r="C322" s="15" t="s">
+        <v>798</v>
+      </c>
+      <c r="D322" s="15"/>
+      <c r="E322" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A323" s="52" t="s">
+        <v>799</v>
+      </c>
+      <c r="B323" s="52">
+        <v>10402</v>
+      </c>
+      <c r="C323" s="15" t="s">
+        <v>800</v>
+      </c>
+      <c r="D323" s="15"/>
+      <c r="E323" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A324" s="52" t="s">
+        <v>801</v>
+      </c>
+      <c r="B324" s="52">
+        <v>10403</v>
+      </c>
+      <c r="C324" s="15" t="s">
+        <v>802</v>
+      </c>
+      <c r="D324" s="15"/>
+      <c r="E324" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A325" s="52" t="s">
+        <v>803</v>
+      </c>
+      <c r="B325" s="52">
+        <v>10404</v>
+      </c>
+      <c r="C325" s="15" t="s">
+        <v>804</v>
+      </c>
+      <c r="D325" s="15"/>
+      <c r="E325" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A326" s="52" t="s">
+        <v>805</v>
+      </c>
+      <c r="B326" s="52">
+        <v>10405</v>
+      </c>
+      <c r="C326" s="15" t="s">
+        <v>806</v>
+      </c>
+      <c r="D326" s="15"/>
+      <c r="E326" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A327" s="52" t="s">
+        <v>807</v>
+      </c>
+      <c r="B327" s="52">
+        <v>10406</v>
+      </c>
+      <c r="C327" s="15" t="s">
+        <v>808</v>
+      </c>
+      <c r="D327" s="15"/>
+      <c r="E327" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A328" s="52" t="s">
+        <v>809</v>
+      </c>
+      <c r="B328" s="52">
+        <v>10407</v>
+      </c>
+      <c r="C328" s="15" t="s">
+        <v>810</v>
+      </c>
+      <c r="D328" s="15"/>
+      <c r="E328" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A329" s="52" t="s">
+        <v>811</v>
+      </c>
+      <c r="B329" s="52">
+        <v>10408</v>
+      </c>
+      <c r="C329" s="15" t="s">
+        <v>812</v>
+      </c>
+      <c r="D329" s="15"/>
+      <c r="E329" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A330" s="52" t="s">
+        <v>813</v>
+      </c>
+      <c r="B330" s="52">
+        <v>10409</v>
+      </c>
+      <c r="C330" s="15" t="s">
+        <v>814</v>
+      </c>
+      <c r="D330" s="15"/>
+      <c r="E330" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A331" s="52" t="s">
+        <v>815</v>
+      </c>
+      <c r="B331" s="52">
+        <v>10410</v>
+      </c>
+      <c r="C331" s="15" t="s">
+        <v>816</v>
+      </c>
+      <c r="D331" s="15"/>
+      <c r="E331" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A332" s="52" t="s">
+        <v>817</v>
+      </c>
+      <c r="B332" s="52">
+        <v>10411</v>
+      </c>
+      <c r="C332" s="15" t="s">
+        <v>818</v>
+      </c>
+      <c r="D332" s="15"/>
+      <c r="E332" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A333" s="52" t="s">
+        <v>819</v>
+      </c>
+      <c r="B333" s="52">
+        <v>10412</v>
+      </c>
+      <c r="C333" s="15" t="s">
+        <v>820</v>
+      </c>
+      <c r="D333" s="15"/>
+      <c r="E333" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A334" s="52" t="s">
+        <v>821</v>
+      </c>
+      <c r="B334" s="52">
+        <v>10413</v>
+      </c>
+      <c r="C334" s="15" t="s">
+        <v>822</v>
+      </c>
+      <c r="D334" s="15"/>
+      <c r="E334" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A335" s="52" t="s">
+        <v>781</v>
+      </c>
+      <c r="B335" s="54">
+        <v>10414</v>
+      </c>
+      <c r="C335" s="15" t="s">
+        <v>823</v>
+      </c>
+      <c r="D335" s="15"/>
+      <c r="E335" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B336">
         <v>305032</v>
       </c>
-      <c r="C319" t="s">
-        <v>491</v>
-      </c>
-      <c r="D319">
+      <c r="C336" t="s">
+        <v>493</v>
+      </c>
+      <c r="D336">
         <v>1314</v>
-      </c>
-      <c r="E319" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B320">
-        <v>305033</v>
-      </c>
-      <c r="C320" t="s">
-        <v>492</v>
-      </c>
-      <c r="D320">
-        <v>1445</v>
-      </c>
-      <c r="E320" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="321" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B321">
-        <v>305034</v>
-      </c>
-      <c r="C321" t="s">
-        <v>493</v>
-      </c>
-      <c r="D321">
-        <v>2098</v>
-      </c>
-      <c r="E321" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="322" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B322">
-        <v>305035</v>
-      </c>
-      <c r="C322" t="s">
-        <v>494</v>
-      </c>
-      <c r="D322">
-        <v>1523</v>
-      </c>
-      <c r="E322" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="323" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B323">
-        <v>305036</v>
-      </c>
-      <c r="C323" s="15" t="s">
-        <v>495</v>
-      </c>
-      <c r="D323">
-        <v>1915</v>
-      </c>
-      <c r="E323" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="324" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B324">
-        <v>305037</v>
-      </c>
-      <c r="C324" t="s">
-        <v>496</v>
-      </c>
-      <c r="D324">
-        <v>1200</v>
-      </c>
-      <c r="E324" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="325" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B325">
-        <v>305038</v>
-      </c>
-      <c r="C325" t="s">
-        <v>497</v>
-      </c>
-      <c r="D325">
-        <v>2500</v>
-      </c>
-      <c r="E325" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="326" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B326">
-        <v>305039</v>
-      </c>
-      <c r="C326" t="s">
-        <v>498</v>
-      </c>
-      <c r="D326">
-        <v>1200</v>
-      </c>
-      <c r="E326" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="327" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B327">
-        <v>305040</v>
-      </c>
-      <c r="C327" t="s">
-        <v>499</v>
-      </c>
-      <c r="D327">
-        <v>2500</v>
-      </c>
-      <c r="E327" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="328" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B328">
-        <v>305200</v>
-      </c>
-      <c r="C328" t="s">
-        <v>500</v>
-      </c>
-      <c r="E328" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="329" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B329">
-        <v>305201</v>
-      </c>
-      <c r="C329" t="s">
-        <v>501</v>
-      </c>
-      <c r="E329" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="330" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B330">
-        <v>305202</v>
-      </c>
-      <c r="C330" t="s">
-        <v>502</v>
-      </c>
-      <c r="E330" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="331" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B331">
-        <v>305203</v>
-      </c>
-      <c r="C331" t="s">
-        <v>503</v>
-      </c>
-      <c r="E331" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="332" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B332">
-        <v>305204</v>
-      </c>
-      <c r="C332" t="s">
-        <v>504</v>
-      </c>
-      <c r="E332" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="333" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B333">
-        <v>305205</v>
-      </c>
-      <c r="C333" t="s">
-        <v>505</v>
-      </c>
-      <c r="E333" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="334" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B334">
-        <v>305206</v>
-      </c>
-      <c r="C334" t="s">
-        <v>506</v>
-      </c>
-      <c r="E334" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="335" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B335">
-        <v>305207</v>
-      </c>
-      <c r="C335" t="s">
-        <v>507</v>
-      </c>
-      <c r="E335" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="336" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B336">
-        <v>305208</v>
-      </c>
-      <c r="C336" t="s">
-        <v>508</v>
       </c>
       <c r="E336" t="s">
         <v>114</v>
@@ -7949,10 +8114,13 @@
     </row>
     <row r="337" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B337">
-        <v>305209</v>
+        <v>305033</v>
       </c>
       <c r="C337" t="s">
-        <v>509</v>
+        <v>494</v>
+      </c>
+      <c r="D337">
+        <v>1445</v>
       </c>
       <c r="E337" t="s">
         <v>114</v>
@@ -7960,10 +8128,13 @@
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B338">
-        <v>305210</v>
+        <v>305034</v>
       </c>
       <c r="C338" t="s">
-        <v>510</v>
+        <v>495</v>
+      </c>
+      <c r="D338">
+        <v>2098</v>
       </c>
       <c r="E338" t="s">
         <v>114</v>
@@ -7971,10 +8142,13 @@
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B339">
-        <v>305211</v>
+        <v>305035</v>
       </c>
       <c r="C339" t="s">
-        <v>511</v>
+        <v>496</v>
+      </c>
+      <c r="D339">
+        <v>1523</v>
       </c>
       <c r="E339" t="s">
         <v>114</v>
@@ -7982,10 +8156,13 @@
     </row>
     <row r="340" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B340">
-        <v>305212</v>
-      </c>
-      <c r="C340" t="s">
-        <v>512</v>
+        <v>305036</v>
+      </c>
+      <c r="C340" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="D340">
+        <v>1915</v>
       </c>
       <c r="E340" t="s">
         <v>114</v>
@@ -7993,10 +8170,13 @@
     </row>
     <row r="341" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B341">
-        <v>305213</v>
+        <v>305037</v>
       </c>
       <c r="C341" t="s">
-        <v>513</v>
+        <v>498</v>
+      </c>
+      <c r="D341">
+        <v>1200</v>
       </c>
       <c r="E341" t="s">
         <v>114</v>
@@ -8004,7 +8184,13 @@
     </row>
     <row r="342" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B342">
-        <v>305214</v>
+        <v>305038</v>
+      </c>
+      <c r="C342" t="s">
+        <v>499</v>
+      </c>
+      <c r="D342">
+        <v>2500</v>
       </c>
       <c r="E342" t="s">
         <v>114</v>
@@ -8012,10 +8198,13 @@
     </row>
     <row r="343" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B343">
-        <v>305215</v>
+        <v>305039</v>
       </c>
       <c r="C343" t="s">
-        <v>514</v>
+        <v>500</v>
+      </c>
+      <c r="D343">
+        <v>1200</v>
       </c>
       <c r="E343" t="s">
         <v>114</v>
@@ -8023,10 +8212,13 @@
     </row>
     <row r="344" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B344">
-        <v>305216</v>
+        <v>305040</v>
       </c>
       <c r="C344" t="s">
-        <v>515</v>
+        <v>501</v>
+      </c>
+      <c r="D344">
+        <v>2500</v>
       </c>
       <c r="E344" t="s">
         <v>114</v>
@@ -8034,10 +8226,10 @@
     </row>
     <row r="345" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B345">
-        <v>305217</v>
+        <v>305200</v>
       </c>
       <c r="C345" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="E345" t="s">
         <v>114</v>
@@ -8045,10 +8237,10 @@
     </row>
     <row r="346" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B346">
-        <v>305218</v>
+        <v>305201</v>
       </c>
       <c r="C346" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="E346" t="s">
         <v>114</v>
@@ -8056,10 +8248,10 @@
     </row>
     <row r="347" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B347">
-        <v>305219</v>
+        <v>305202</v>
       </c>
       <c r="C347" t="s">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="E347" t="s">
         <v>114</v>
@@ -8067,10 +8259,10 @@
     </row>
     <row r="348" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B348">
-        <v>305220</v>
+        <v>305203</v>
       </c>
       <c r="C348" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="E348" t="s">
         <v>114</v>
@@ -8078,10 +8270,10 @@
     </row>
     <row r="349" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B349">
-        <v>305221</v>
-      </c>
-      <c r="C349" s="15" t="s">
-        <v>520</v>
+        <v>305204</v>
+      </c>
+      <c r="C349" t="s">
+        <v>506</v>
       </c>
       <c r="E349" t="s">
         <v>114</v>
@@ -8089,10 +8281,10 @@
     </row>
     <row r="350" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B350">
-        <v>305222</v>
-      </c>
-      <c r="C350" s="15" t="s">
-        <v>521</v>
+        <v>305205</v>
+      </c>
+      <c r="C350" t="s">
+        <v>507</v>
       </c>
       <c r="E350" t="s">
         <v>114</v>
@@ -8100,10 +8292,10 @@
     </row>
     <row r="351" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B351">
-        <v>305223</v>
+        <v>305206</v>
       </c>
       <c r="C351" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="E351" t="s">
         <v>114</v>
@@ -8111,10 +8303,10 @@
     </row>
     <row r="352" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B352">
-        <v>30520001</v>
-      </c>
-      <c r="C352" s="15" t="s">
-        <v>523</v>
+        <v>305207</v>
+      </c>
+      <c r="C352" t="s">
+        <v>509</v>
       </c>
       <c r="E352" t="s">
         <v>114</v>
@@ -8122,10 +8314,10 @@
     </row>
     <row r="353" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B353">
-        <v>30520002</v>
-      </c>
-      <c r="C353" s="15" t="s">
-        <v>524</v>
+        <v>305208</v>
+      </c>
+      <c r="C353" t="s">
+        <v>510</v>
       </c>
       <c r="E353" t="s">
         <v>114</v>
@@ -8133,10 +8325,10 @@
     </row>
     <row r="354" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B354">
-        <v>30520003</v>
-      </c>
-      <c r="C354" s="15" t="s">
-        <v>525</v>
+        <v>305209</v>
+      </c>
+      <c r="C354" t="s">
+        <v>511</v>
       </c>
       <c r="E354" t="s">
         <v>114</v>
@@ -8144,10 +8336,10 @@
     </row>
     <row r="355" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B355">
-        <v>30520004</v>
-      </c>
-      <c r="C355" s="15" t="s">
-        <v>526</v>
+        <v>305210</v>
+      </c>
+      <c r="C355" t="s">
+        <v>512</v>
       </c>
       <c r="E355" t="s">
         <v>114</v>
@@ -8155,10 +8347,10 @@
     </row>
     <row r="356" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B356">
-        <v>30520005</v>
-      </c>
-      <c r="C356" s="15" t="s">
-        <v>527</v>
+        <v>305211</v>
+      </c>
+      <c r="C356" t="s">
+        <v>513</v>
       </c>
       <c r="E356" t="s">
         <v>114</v>
@@ -8166,10 +8358,10 @@
     </row>
     <row r="357" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B357">
-        <v>30520006</v>
-      </c>
-      <c r="C357" s="15" t="s">
-        <v>528</v>
+        <v>305212</v>
+      </c>
+      <c r="C357" t="s">
+        <v>514</v>
       </c>
       <c r="E357" t="s">
         <v>114</v>
@@ -8177,10 +8369,10 @@
     </row>
     <row r="358" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B358">
-        <v>30520007</v>
-      </c>
-      <c r="C358" s="15" t="s">
-        <v>529</v>
+        <v>305213</v>
+      </c>
+      <c r="C358" t="s">
+        <v>515</v>
       </c>
       <c r="E358" t="s">
         <v>114</v>
@@ -8188,67 +8380,62 @@
     </row>
     <row r="359" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B359">
-        <v>30520008</v>
-      </c>
-      <c r="C359" s="15" t="s">
-        <v>530</v>
-      </c>
-      <c r="E359" s="15" t="s">
+        <v>305214</v>
+      </c>
+      <c r="E359" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="360" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B360">
-        <v>30520009</v>
-      </c>
-      <c r="C360" s="15" t="s">
-        <v>531</v>
-      </c>
-      <c r="E360" s="15" t="s">
+        <v>305215</v>
+      </c>
+      <c r="C360" t="s">
+        <v>516</v>
+      </c>
+      <c r="E360" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="361" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B361">
-        <v>30520010</v>
-      </c>
-      <c r="C361" s="15" t="s">
-        <v>532</v>
-      </c>
-      <c r="E361" s="15" t="s">
+        <v>305216</v>
+      </c>
+      <c r="C361" t="s">
+        <v>517</v>
+      </c>
+      <c r="E361" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="362" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B362" s="17">
-        <v>30520011</v>
-      </c>
-      <c r="C362" s="18" t="s">
-        <v>533</v>
-      </c>
-      <c r="D362" s="17"/>
-      <c r="E362" s="15" t="s">
+      <c r="B362">
+        <v>305217</v>
+      </c>
+      <c r="C362" t="s">
+        <v>518</v>
+      </c>
+      <c r="E362" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="363" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B363">
-        <v>30520012</v>
-      </c>
-      <c r="C363" s="18" t="s">
-        <v>745</v>
-      </c>
-      <c r="D363" s="17"/>
-      <c r="E363" s="15" t="s">
+        <v>305218</v>
+      </c>
+      <c r="C363" t="s">
+        <v>519</v>
+      </c>
+      <c r="E363" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="364" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B364">
-        <v>305224</v>
+        <v>305219</v>
       </c>
       <c r="C364" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="E364" t="s">
         <v>114</v>
@@ -8256,10 +8443,10 @@
     </row>
     <row r="365" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B365">
-        <v>305225</v>
+        <v>305220</v>
       </c>
       <c r="C365" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="E365" t="s">
         <v>114</v>
@@ -8267,10 +8454,10 @@
     </row>
     <row r="366" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B366">
-        <v>305226</v>
-      </c>
-      <c r="C366" t="s">
-        <v>536</v>
+        <v>305221</v>
+      </c>
+      <c r="C366" s="15" t="s">
+        <v>522</v>
       </c>
       <c r="E366" t="s">
         <v>114</v>
@@ -8278,10 +8465,10 @@
     </row>
     <row r="367" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B367">
-        <v>305300</v>
-      </c>
-      <c r="C367" t="s">
-        <v>537</v>
+        <v>305222</v>
+      </c>
+      <c r="C367" s="15" t="s">
+        <v>523</v>
       </c>
       <c r="E367" t="s">
         <v>114</v>
@@ -8289,10 +8476,10 @@
     </row>
     <row r="368" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B368">
-        <v>305301</v>
+        <v>305223</v>
       </c>
       <c r="C368" t="s">
-        <v>538</v>
+        <v>524</v>
       </c>
       <c r="E368" t="s">
         <v>114</v>
@@ -8300,10 +8487,10 @@
     </row>
     <row r="369" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B369">
-        <v>305302</v>
-      </c>
-      <c r="C369" t="s">
-        <v>539</v>
+        <v>30520001</v>
+      </c>
+      <c r="C369" s="15" t="s">
+        <v>525</v>
       </c>
       <c r="E369" t="s">
         <v>114</v>
@@ -8311,10 +8498,10 @@
     </row>
     <row r="370" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B370">
-        <v>305303</v>
-      </c>
-      <c r="C370" t="s">
-        <v>540</v>
+        <v>30520002</v>
+      </c>
+      <c r="C370" s="15" t="s">
+        <v>526</v>
       </c>
       <c r="E370" t="s">
         <v>114</v>
@@ -8322,10 +8509,10 @@
     </row>
     <row r="371" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B371">
-        <v>305304</v>
-      </c>
-      <c r="C371" t="s">
-        <v>541</v>
+        <v>30520003</v>
+      </c>
+      <c r="C371" s="15" t="s">
+        <v>527</v>
       </c>
       <c r="E371" t="s">
         <v>114</v>
@@ -8333,10 +8520,10 @@
     </row>
     <row r="372" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B372">
-        <v>305305</v>
-      </c>
-      <c r="C372" t="s">
-        <v>542</v>
+        <v>30520004</v>
+      </c>
+      <c r="C372" s="15" t="s">
+        <v>528</v>
       </c>
       <c r="E372" t="s">
         <v>114</v>
@@ -8344,10 +8531,10 @@
     </row>
     <row r="373" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B373">
-        <v>305306</v>
-      </c>
-      <c r="C373" t="s">
-        <v>543</v>
+        <v>30520005</v>
+      </c>
+      <c r="C373" s="15" t="s">
+        <v>529</v>
       </c>
       <c r="E373" t="s">
         <v>114</v>
@@ -8355,10 +8542,10 @@
     </row>
     <row r="374" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B374">
-        <v>305307</v>
-      </c>
-      <c r="C374" t="s">
-        <v>544</v>
+        <v>30520006</v>
+      </c>
+      <c r="C374" s="15" t="s">
+        <v>530</v>
       </c>
       <c r="E374" t="s">
         <v>114</v>
@@ -8366,10 +8553,10 @@
     </row>
     <row r="375" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B375">
-        <v>305308</v>
-      </c>
-      <c r="C375" t="s">
-        <v>545</v>
+        <v>30520007</v>
+      </c>
+      <c r="C375" s="15" t="s">
+        <v>531</v>
       </c>
       <c r="E375" t="s">
         <v>114</v>
@@ -8377,62 +8564,67 @@
     </row>
     <row r="376" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B376">
-        <v>305309</v>
-      </c>
-      <c r="C376" t="s">
-        <v>546</v>
-      </c>
-      <c r="E376" t="s">
+        <v>30520008</v>
+      </c>
+      <c r="C376" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="E376" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="377" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B377">
-        <v>305310</v>
-      </c>
-      <c r="C377" t="s">
-        <v>547</v>
-      </c>
-      <c r="E377" t="s">
+        <v>30520009</v>
+      </c>
+      <c r="C377" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="E377" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="378" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B378">
-        <v>305311</v>
-      </c>
-      <c r="C378" t="s">
-        <v>548</v>
-      </c>
-      <c r="E378" t="s">
+        <v>30520010</v>
+      </c>
+      <c r="C378" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="E378" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="379" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B379">
-        <v>305312</v>
-      </c>
-      <c r="C379" t="s">
-        <v>549</v>
-      </c>
-      <c r="E379" t="s">
+      <c r="B379" s="17">
+        <v>30520011</v>
+      </c>
+      <c r="C379" s="18" t="s">
+        <v>535</v>
+      </c>
+      <c r="D379" s="17"/>
+      <c r="E379" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="380" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B380">
-        <v>305313</v>
-      </c>
-      <c r="C380" t="s">
-        <v>550</v>
-      </c>
-      <c r="E380" t="s">
+        <v>30520012</v>
+      </c>
+      <c r="C380" s="18" t="s">
+        <v>747</v>
+      </c>
+      <c r="D380" s="17"/>
+      <c r="E380" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="381" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B381">
-        <v>305314</v>
+        <v>305224</v>
+      </c>
+      <c r="C381" t="s">
+        <v>536</v>
       </c>
       <c r="E381" t="s">
         <v>114</v>
@@ -8440,10 +8632,10 @@
     </row>
     <row r="382" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B382">
-        <v>305315</v>
+        <v>305225</v>
       </c>
       <c r="C382" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="E382" t="s">
         <v>114</v>
@@ -8451,10 +8643,10 @@
     </row>
     <row r="383" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B383">
-        <v>305316</v>
+        <v>305226</v>
       </c>
       <c r="C383" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="E383" t="s">
         <v>114</v>
@@ -8462,10 +8654,10 @@
     </row>
     <row r="384" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B384">
-        <v>305317</v>
+        <v>305300</v>
       </c>
       <c r="C384" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="E384" t="s">
         <v>114</v>
@@ -8473,10 +8665,10 @@
     </row>
     <row r="385" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B385">
-        <v>305318</v>
+        <v>305301</v>
       </c>
       <c r="C385" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="E385" t="s">
         <v>114</v>
@@ -8484,10 +8676,10 @@
     </row>
     <row r="386" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B386">
-        <v>305319</v>
+        <v>305302</v>
       </c>
       <c r="C386" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="E386" t="s">
         <v>114</v>
@@ -8495,10 +8687,10 @@
     </row>
     <row r="387" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B387">
-        <v>305320</v>
+        <v>305303</v>
       </c>
       <c r="C387" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="E387" t="s">
         <v>114</v>
@@ -8506,10 +8698,10 @@
     </row>
     <row r="388" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B388">
-        <v>305321</v>
-      </c>
-      <c r="C388" s="15" t="s">
-        <v>557</v>
+        <v>305304</v>
+      </c>
+      <c r="C388" t="s">
+        <v>543</v>
       </c>
       <c r="E388" t="s">
         <v>114</v>
@@ -8517,10 +8709,10 @@
     </row>
     <row r="389" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B389">
-        <v>305322</v>
-      </c>
-      <c r="C389" s="15" t="s">
-        <v>558</v>
+        <v>305305</v>
+      </c>
+      <c r="C389" t="s">
+        <v>544</v>
       </c>
       <c r="E389" t="s">
         <v>114</v>
@@ -8528,10 +8720,10 @@
     </row>
     <row r="390" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B390">
-        <v>305323</v>
+        <v>305306</v>
       </c>
       <c r="C390" t="s">
-        <v>559</v>
+        <v>545</v>
       </c>
       <c r="E390" t="s">
         <v>114</v>
@@ -8539,10 +8731,10 @@
     </row>
     <row r="391" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B391">
-        <v>305324</v>
+        <v>305307</v>
       </c>
       <c r="C391" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="E391" t="s">
         <v>114</v>
@@ -8550,10 +8742,10 @@
     </row>
     <row r="392" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B392">
-        <v>305325</v>
+        <v>305308</v>
       </c>
       <c r="C392" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="E392" t="s">
         <v>114</v>
@@ -8561,10 +8753,10 @@
     </row>
     <row r="393" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B393">
-        <v>305326</v>
-      </c>
-      <c r="C393" s="15" t="s">
-        <v>562</v>
+        <v>305309</v>
+      </c>
+      <c r="C393" t="s">
+        <v>548</v>
       </c>
       <c r="E393" t="s">
         <v>114</v>
@@ -8572,10 +8764,10 @@
     </row>
     <row r="394" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B394">
-        <v>30530001</v>
-      </c>
-      <c r="C394" s="15" t="s">
-        <v>563</v>
+        <v>305310</v>
+      </c>
+      <c r="C394" t="s">
+        <v>549</v>
       </c>
       <c r="E394" t="s">
         <v>114</v>
@@ -8583,10 +8775,10 @@
     </row>
     <row r="395" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B395">
-        <v>30530002</v>
+        <v>305311</v>
       </c>
       <c r="C395" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E395" t="s">
         <v>114</v>
@@ -8594,10 +8786,10 @@
     </row>
     <row r="396" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B396">
-        <v>30530003</v>
-      </c>
-      <c r="C396" s="15" t="s">
-        <v>565</v>
+        <v>305312</v>
+      </c>
+      <c r="C396" t="s">
+        <v>551</v>
       </c>
       <c r="E396" t="s">
         <v>114</v>
@@ -8605,10 +8797,10 @@
     </row>
     <row r="397" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B397">
-        <v>30530004</v>
-      </c>
-      <c r="C397" s="15" t="s">
-        <v>566</v>
+        <v>305313</v>
+      </c>
+      <c r="C397" t="s">
+        <v>552</v>
       </c>
       <c r="E397" t="s">
         <v>114</v>
@@ -8616,10 +8808,7 @@
     </row>
     <row r="398" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B398">
-        <v>30530005</v>
-      </c>
-      <c r="C398" s="15" t="s">
-        <v>567</v>
+        <v>305314</v>
       </c>
       <c r="E398" t="s">
         <v>114</v>
@@ -8627,10 +8816,10 @@
     </row>
     <row r="399" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B399">
-        <v>30530006</v>
-      </c>
-      <c r="C399" s="15" t="s">
-        <v>568</v>
+        <v>305315</v>
+      </c>
+      <c r="C399" t="s">
+        <v>553</v>
       </c>
       <c r="E399" t="s">
         <v>114</v>
@@ -8638,78 +8827,76 @@
     </row>
     <row r="400" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B400">
-        <v>30530007</v>
-      </c>
-      <c r="C400" s="15" t="s">
-        <v>569</v>
-      </c>
-      <c r="E400" s="15" t="s">
+        <v>305316</v>
+      </c>
+      <c r="C400" t="s">
+        <v>554</v>
+      </c>
+      <c r="E400" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="401" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B401">
-        <v>30530008</v>
-      </c>
-      <c r="C401" s="15" t="s">
-        <v>570</v>
-      </c>
-      <c r="E401" s="15" t="s">
+        <v>305317</v>
+      </c>
+      <c r="C401" t="s">
+        <v>555</v>
+      </c>
+      <c r="E401" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="402" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B402">
-        <v>30530009</v>
-      </c>
-      <c r="C402" s="15" t="s">
-        <v>571</v>
-      </c>
-      <c r="E402" s="15" t="s">
+        <v>305318</v>
+      </c>
+      <c r="C402" t="s">
+        <v>556</v>
+      </c>
+      <c r="E402" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="403" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B403">
-        <v>30530010</v>
-      </c>
-      <c r="C403" s="15" t="s">
-        <v>572</v>
-      </c>
-      <c r="E403" s="15" t="s">
+        <v>305319</v>
+      </c>
+      <c r="C403" t="s">
+        <v>557</v>
+      </c>
+      <c r="E403" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="404" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B404" s="17">
-        <v>30530011</v>
-      </c>
-      <c r="C404" s="18" t="s">
-        <v>573</v>
-      </c>
-      <c r="D404" s="17"/>
-      <c r="E404" s="18" t="s">
+      <c r="B404">
+        <v>305320</v>
+      </c>
+      <c r="C404" t="s">
+        <v>558</v>
+      </c>
+      <c r="E404" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="405" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B405">
-        <v>30530012</v>
-      </c>
-      <c r="C405" s="18" t="s">
-        <v>744</v>
-      </c>
-      <c r="D405" s="17"/>
-      <c r="E405" s="18" t="s">
+        <v>305321</v>
+      </c>
+      <c r="C405" s="15" t="s">
+        <v>559</v>
+      </c>
+      <c r="E405" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="406" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B406">
-        <v>309205</v>
-      </c>
-      <c r="C406" t="s">
-        <v>574</v>
+        <v>305322</v>
+      </c>
+      <c r="C406" s="15" t="s">
+        <v>560</v>
       </c>
       <c r="E406" t="s">
         <v>114</v>
@@ -8717,10 +8904,10 @@
     </row>
     <row r="407" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B407">
-        <v>308001</v>
+        <v>305323</v>
       </c>
       <c r="C407" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E407" t="s">
         <v>114</v>
@@ -8728,10 +8915,10 @@
     </row>
     <row r="408" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B408">
-        <v>308002</v>
+        <v>305324</v>
       </c>
       <c r="C408" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="E408" t="s">
         <v>114</v>
@@ -8739,10 +8926,10 @@
     </row>
     <row r="409" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B409">
-        <v>308006</v>
+        <v>305325</v>
       </c>
       <c r="C409" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="E409" t="s">
         <v>114</v>
@@ -8750,10 +8937,10 @@
     </row>
     <row r="410" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B410">
-        <v>308007</v>
-      </c>
-      <c r="C410" t="s">
-        <v>578</v>
+        <v>305326</v>
+      </c>
+      <c r="C410" s="15" t="s">
+        <v>564</v>
       </c>
       <c r="E410" t="s">
         <v>114</v>
@@ -8761,10 +8948,10 @@
     </row>
     <row r="411" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B411">
-        <v>308011</v>
-      </c>
-      <c r="C411" t="s">
-        <v>579</v>
+        <v>30530001</v>
+      </c>
+      <c r="C411" s="15" t="s">
+        <v>565</v>
       </c>
       <c r="E411" t="s">
         <v>114</v>
@@ -8772,10 +8959,10 @@
     </row>
     <row r="412" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B412">
-        <v>308012</v>
+        <v>30530002</v>
       </c>
       <c r="C412" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="E412" t="s">
         <v>114</v>
@@ -8783,10 +8970,10 @@
     </row>
     <row r="413" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B413">
-        <v>308016</v>
-      </c>
-      <c r="C413" t="s">
-        <v>581</v>
+        <v>30530003</v>
+      </c>
+      <c r="C413" s="15" t="s">
+        <v>567</v>
       </c>
       <c r="E413" t="s">
         <v>114</v>
@@ -8794,10 +8981,10 @@
     </row>
     <row r="414" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B414">
-        <v>308017</v>
-      </c>
-      <c r="C414" t="s">
-        <v>582</v>
+        <v>30530004</v>
+      </c>
+      <c r="C414" s="15" t="s">
+        <v>568</v>
       </c>
       <c r="E414" t="s">
         <v>114</v>
@@ -8805,10 +8992,10 @@
     </row>
     <row r="415" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B415">
-        <v>308021</v>
+        <v>30530005</v>
       </c>
       <c r="C415" s="15" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
       <c r="E415" t="s">
         <v>114</v>
@@ -8816,10 +9003,10 @@
     </row>
     <row r="416" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B416">
-        <v>308022</v>
+        <v>30530006</v>
       </c>
       <c r="C416" s="15" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="E416" t="s">
         <v>114</v>
@@ -8827,76 +9014,78 @@
     </row>
     <row r="417" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B417">
-        <v>308026</v>
+        <v>30530007</v>
       </c>
       <c r="C417" s="15" t="s">
-        <v>585</v>
-      </c>
-      <c r="E417" t="s">
+        <v>571</v>
+      </c>
+      <c r="E417" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="418" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B418">
-        <v>308027</v>
+        <v>30530008</v>
       </c>
       <c r="C418" s="15" t="s">
-        <v>586</v>
-      </c>
-      <c r="E418" t="s">
+        <v>572</v>
+      </c>
+      <c r="E418" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="419" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B419">
-        <v>308031</v>
+        <v>30530009</v>
       </c>
       <c r="C419" s="15" t="s">
-        <v>587</v>
-      </c>
-      <c r="E419" t="s">
+        <v>573</v>
+      </c>
+      <c r="E419" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="420" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B420">
-        <v>308032</v>
+        <v>30530010</v>
       </c>
       <c r="C420" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="E420" t="s">
+        <v>574</v>
+      </c>
+      <c r="E420" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="421" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B421">
-        <v>308036</v>
-      </c>
-      <c r="C421" s="15" t="s">
-        <v>589</v>
-      </c>
-      <c r="E421" t="s">
+      <c r="B421" s="17">
+        <v>30530011</v>
+      </c>
+      <c r="C421" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="D421" s="17"/>
+      <c r="E421" s="18" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="422" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B422">
-        <v>308037</v>
-      </c>
-      <c r="C422" s="15" t="s">
-        <v>590</v>
-      </c>
-      <c r="E422" t="s">
+        <v>30530012</v>
+      </c>
+      <c r="C422" s="18" t="s">
+        <v>746</v>
+      </c>
+      <c r="D422" s="17"/>
+      <c r="E422" s="18" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="423" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B423">
-        <v>308041</v>
-      </c>
-      <c r="C423" s="15" t="s">
-        <v>591</v>
+        <v>309205</v>
+      </c>
+      <c r="C423" t="s">
+        <v>576</v>
       </c>
       <c r="E423" t="s">
         <v>114</v>
@@ -8904,10 +9093,10 @@
     </row>
     <row r="424" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B424">
-        <v>308042</v>
-      </c>
-      <c r="C424" s="15" t="s">
-        <v>592</v>
+        <v>308001</v>
+      </c>
+      <c r="C424" t="s">
+        <v>577</v>
       </c>
       <c r="E424" t="s">
         <v>114</v>
@@ -8915,10 +9104,10 @@
     </row>
     <row r="425" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B425">
-        <v>308046</v>
-      </c>
-      <c r="C425" s="15" t="s">
-        <v>593</v>
+        <v>308002</v>
+      </c>
+      <c r="C425" t="s">
+        <v>578</v>
       </c>
       <c r="E425" t="s">
         <v>114</v>
@@ -8926,10 +9115,10 @@
     </row>
     <row r="426" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B426">
-        <v>308047</v>
-      </c>
-      <c r="C426" s="15" t="s">
-        <v>594</v>
+        <v>308006</v>
+      </c>
+      <c r="C426" t="s">
+        <v>579</v>
       </c>
       <c r="E426" t="s">
         <v>114</v>
@@ -8937,25 +9126,212 @@
     </row>
     <row r="427" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B427">
-        <v>308048</v>
-      </c>
-      <c r="C427" s="18" t="s">
-        <v>765</v>
-      </c>
-      <c r="D427" s="44"/>
-      <c r="E427" s="17" t="s">
+        <v>308007</v>
+      </c>
+      <c r="C427" t="s">
+        <v>580</v>
+      </c>
+      <c r="E427" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="428" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B428">
+        <v>308011</v>
+      </c>
+      <c r="C428" t="s">
+        <v>581</v>
+      </c>
+      <c r="E428" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="429" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B429">
+        <v>308012</v>
+      </c>
+      <c r="C429" t="s">
+        <v>582</v>
+      </c>
+      <c r="E429" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="430" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B430">
+        <v>308016</v>
+      </c>
+      <c r="C430" t="s">
+        <v>583</v>
+      </c>
+      <c r="E430" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="431" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B431">
+        <v>308017</v>
+      </c>
+      <c r="C431" t="s">
+        <v>584</v>
+      </c>
+      <c r="E431" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="432" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B432">
+        <v>308021</v>
+      </c>
+      <c r="C432" s="15" t="s">
+        <v>585</v>
+      </c>
+      <c r="E432" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="433" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B433">
+        <v>308022</v>
+      </c>
+      <c r="C433" s="15" t="s">
+        <v>586</v>
+      </c>
+      <c r="E433" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="434" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B434">
+        <v>308026</v>
+      </c>
+      <c r="C434" s="15" t="s">
+        <v>587</v>
+      </c>
+      <c r="E434" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="435" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B435">
+        <v>308027</v>
+      </c>
+      <c r="C435" s="15" t="s">
+        <v>588</v>
+      </c>
+      <c r="E435" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="436" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B436">
+        <v>308031</v>
+      </c>
+      <c r="C436" s="15" t="s">
+        <v>589</v>
+      </c>
+      <c r="E436" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="437" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B437">
+        <v>308032</v>
+      </c>
+      <c r="C437" s="15" t="s">
+        <v>590</v>
+      </c>
+      <c r="E437" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="438" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B438">
+        <v>308036</v>
+      </c>
+      <c r="C438" s="15" t="s">
+        <v>591</v>
+      </c>
+      <c r="E438" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="439" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B439">
+        <v>308037</v>
+      </c>
+      <c r="C439" s="15" t="s">
+        <v>592</v>
+      </c>
+      <c r="E439" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="440" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B440">
+        <v>308041</v>
+      </c>
+      <c r="C440" s="15" t="s">
+        <v>593</v>
+      </c>
+      <c r="E440" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="441" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B441">
+        <v>308042</v>
+      </c>
+      <c r="C441" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="E441" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="442" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B442">
+        <v>308046</v>
+      </c>
+      <c r="C442" s="15" t="s">
+        <v>595</v>
+      </c>
+      <c r="E442" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="443" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B443">
+        <v>308047</v>
+      </c>
+      <c r="C443" s="15" t="s">
+        <v>596</v>
+      </c>
+      <c r="E443" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="444" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B444">
+        <v>308048</v>
+      </c>
+      <c r="C444" s="18" t="s">
+        <v>767</v>
+      </c>
+      <c r="D444" s="44"/>
+      <c r="E444" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="445" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B445">
         <v>308049</v>
       </c>
-      <c r="C428" s="18" t="s">
-        <v>766</v>
-      </c>
-      <c r="D428" s="44"/>
-      <c r="E428" s="17" t="s">
+      <c r="C445" s="18" t="s">
+        <v>768</v>
+      </c>
+      <c r="D445" s="44"/>
+      <c r="E445" s="17" t="s">
         <v>114</v>
       </c>
     </row>
@@ -8991,22 +9367,22 @@
         <v>5</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="F1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
@@ -9018,22 +9394,22 @@
         <v>2</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -9043,7 +9419,7 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -9052,10 +9428,10 @@
         <v>13</v>
       </c>
       <c r="K2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
@@ -9124,22 +9500,22 @@
         <v>0</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="I4" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K4" t="s">
         <v>20</v>
@@ -9153,40 +9529,40 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E5" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="I5" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K5" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="Q5">
         <v>306002</v>
@@ -9200,40 +9576,40 @@
         <v>0</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="I6" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="K6" t="s">
         <v>20</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="Q6">
         <v>306003</v>
@@ -9247,40 +9623,40 @@
         <v>0</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="I7" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="K7" t="s">
         <v>20</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="Q7">
         <v>306004</v>
@@ -9294,40 +9670,40 @@
         <v>1</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K8" t="s">
         <v>20</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P8" s="13" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="Q8" s="14">
         <v>306005</v>
@@ -9341,40 +9717,40 @@
         <v>1</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="K9" t="s">
         <v>20</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P9" s="13" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="Q9" s="14">
         <v>306006</v>
@@ -9388,40 +9764,40 @@
         <v>1</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="G10" s="40" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="H10" s="40" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="K10" t="s">
         <v>20</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="Q10" s="14">
         <v>30600001</v>
@@ -9435,40 +9811,40 @@
         <v>0</v>
       </c>
       <c r="D11" s="48" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E11" s="49" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F11" s="47" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="G11" s="50" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="Q11" s="16">
         <v>30600002</v>
@@ -9482,40 +9858,40 @@
         <v>1</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="F12" s="47" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="H12" s="47" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="K12" t="s">
         <v>20</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P12" s="13" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="Q12" s="14">
         <v>30600003</v>
@@ -9529,22 +9905,22 @@
         <v>0</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="H13" s="53" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I13" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="K13" t="s">
         <v>84</v>
@@ -9560,40 +9936,40 @@
         <v>1</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="I14" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="K14" t="s">
         <v>84</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="Q14">
         <v>306102</v>
@@ -9607,40 +9983,40 @@
         <v>1</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="K15" t="s">
         <v>84</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="Q15" s="16">
         <v>306103</v>
@@ -9654,40 +10030,40 @@
         <v>0</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="H16" s="27" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="K16" t="s">
         <v>84</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N16" s="25" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="O16" s="25" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="P16" s="25" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="Q16" s="29">
         <v>306104</v>
@@ -9701,40 +10077,40 @@
         <v>0</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="K17" t="s">
         <v>84</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N17" s="25" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="O17" s="25" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="P17" s="25" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="Q17" s="29">
         <v>306105</v>
@@ -9748,40 +10124,40 @@
         <v>0</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="G18" s="27" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="H18" s="27" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="K18" t="s">
         <v>84</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N18" s="25" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="O18" s="25" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="P18" s="25" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="Q18" s="29">
         <v>306106</v>
@@ -9795,40 +10171,40 @@
         <v>0</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="K19" t="s">
         <v>84</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N19" s="25" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="O19" s="25" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="P19" s="25" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="Q19" s="29">
         <v>306107</v>
@@ -9842,40 +10218,40 @@
         <v>1</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="F20" s="33" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="G20" s="27" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="H20" s="28" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="K20" t="s">
         <v>84</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N20" s="25" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="O20" s="25" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="P20" s="25" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="Q20" s="16">
         <v>30610001</v>
@@ -9889,40 +10265,40 @@
         <v>1</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E21" s="34" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="F21" s="35" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="G21" s="36" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="H21" s="36" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="K21" t="s">
         <v>84</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P21" s="13" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="Q21" s="16">
         <v>30610002</v>
@@ -9936,40 +10312,40 @@
         <v>1</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F22" s="40" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G22" s="40" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="H22" s="40" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="K22" t="s">
         <v>84</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P22" s="13" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="Q22" s="16">
         <v>30610003</v>
@@ -9983,40 +10359,40 @@
         <v>1</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="H23" s="42" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="K23" t="s">
         <v>84</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P23" s="13" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="Q23" s="16">
         <v>30610004</v>
@@ -10030,40 +10406,40 @@
         <v>1</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="H24" s="43" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="K24" t="s">
         <v>84</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P24" s="13" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="Q24" s="16">
         <v>30610005</v>
@@ -10077,40 +10453,40 @@
         <v>1</v>
       </c>
       <c r="D25" s="45" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E25" s="45" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F25" s="46" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="G25" s="47" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="H25" s="47" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="K25" t="s">
         <v>84</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N25" s="25" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="O25" s="25" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="P25" s="25" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="Q25" s="16">
         <v>30610006</v>

--- a/source/bin/excel/audio.xlsx
+++ b/source/bin/excel/audio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165C1F02-B5B5-4979-B394-B414A42557CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD5AB40-063B-402B-9DDB-A7B726BD9AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="826">
   <si>
     <t>sheet</t>
   </si>
@@ -2588,6 +2588,14 @@
   </si>
   <si>
     <t>ui/activity/extend/2606dp/main/audio/2606dp_event</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2606斗牌主活动bgm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui/activity/extend/2606dp/main/audio/2606dp_bgm</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -3352,7 +3360,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E445"/>
+  <dimension ref="A1:E446"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.875" customWidth="1"/>
@@ -8099,28 +8107,29 @@
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B336">
-        <v>305032</v>
-      </c>
-      <c r="C336" t="s">
-        <v>493</v>
-      </c>
-      <c r="D336">
-        <v>1314</v>
-      </c>
+      <c r="A336" s="52" t="s">
+        <v>824</v>
+      </c>
+      <c r="B336" s="54">
+        <v>10415</v>
+      </c>
+      <c r="C336" s="15" t="s">
+        <v>825</v>
+      </c>
+      <c r="D336" s="15"/>
       <c r="E336" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="337" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B337">
-        <v>305033</v>
+        <v>305032</v>
       </c>
       <c r="C337" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D337">
-        <v>1445</v>
+        <v>1314</v>
       </c>
       <c r="E337" t="s">
         <v>114</v>
@@ -8128,13 +8137,13 @@
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B338">
-        <v>305034</v>
+        <v>305033</v>
       </c>
       <c r="C338" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D338">
-        <v>2098</v>
+        <v>1445</v>
       </c>
       <c r="E338" t="s">
         <v>114</v>
@@ -8142,13 +8151,13 @@
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B339">
-        <v>305035</v>
+        <v>305034</v>
       </c>
       <c r="C339" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D339">
-        <v>1523</v>
+        <v>2098</v>
       </c>
       <c r="E339" t="s">
         <v>114</v>
@@ -8156,13 +8165,13 @@
     </row>
     <row r="340" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B340">
-        <v>305036</v>
-      </c>
-      <c r="C340" s="15" t="s">
-        <v>497</v>
+        <v>305035</v>
+      </c>
+      <c r="C340" t="s">
+        <v>496</v>
       </c>
       <c r="D340">
-        <v>1915</v>
+        <v>1523</v>
       </c>
       <c r="E340" t="s">
         <v>114</v>
@@ -8170,13 +8179,13 @@
     </row>
     <row r="341" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B341">
-        <v>305037</v>
-      </c>
-      <c r="C341" t="s">
-        <v>498</v>
+        <v>305036</v>
+      </c>
+      <c r="C341" s="15" t="s">
+        <v>497</v>
       </c>
       <c r="D341">
-        <v>1200</v>
+        <v>1915</v>
       </c>
       <c r="E341" t="s">
         <v>114</v>
@@ -8184,13 +8193,13 @@
     </row>
     <row r="342" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B342">
-        <v>305038</v>
+        <v>305037</v>
       </c>
       <c r="C342" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D342">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="E342" t="s">
         <v>114</v>
@@ -8198,13 +8207,13 @@
     </row>
     <row r="343" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B343">
-        <v>305039</v>
+        <v>305038</v>
       </c>
       <c r="C343" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D343">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="E343" t="s">
         <v>114</v>
@@ -8212,13 +8221,13 @@
     </row>
     <row r="344" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B344">
-        <v>305040</v>
+        <v>305039</v>
       </c>
       <c r="C344" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D344">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="E344" t="s">
         <v>114</v>
@@ -8226,10 +8235,13 @@
     </row>
     <row r="345" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B345">
-        <v>305200</v>
+        <v>305040</v>
       </c>
       <c r="C345" t="s">
-        <v>502</v>
+        <v>501</v>
+      </c>
+      <c r="D345">
+        <v>2500</v>
       </c>
       <c r="E345" t="s">
         <v>114</v>
@@ -8237,10 +8249,10 @@
     </row>
     <row r="346" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B346">
-        <v>305201</v>
+        <v>305200</v>
       </c>
       <c r="C346" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E346" t="s">
         <v>114</v>
@@ -8248,10 +8260,10 @@
     </row>
     <row r="347" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B347">
-        <v>305202</v>
+        <v>305201</v>
       </c>
       <c r="C347" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E347" t="s">
         <v>114</v>
@@ -8259,10 +8271,10 @@
     </row>
     <row r="348" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B348">
-        <v>305203</v>
+        <v>305202</v>
       </c>
       <c r="C348" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E348" t="s">
         <v>114</v>
@@ -8270,10 +8282,10 @@
     </row>
     <row r="349" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B349">
-        <v>305204</v>
+        <v>305203</v>
       </c>
       <c r="C349" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E349" t="s">
         <v>114</v>
@@ -8281,10 +8293,10 @@
     </row>
     <row r="350" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B350">
-        <v>305205</v>
+        <v>305204</v>
       </c>
       <c r="C350" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E350" t="s">
         <v>114</v>
@@ -8292,10 +8304,10 @@
     </row>
     <row r="351" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B351">
-        <v>305206</v>
+        <v>305205</v>
       </c>
       <c r="C351" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E351" t="s">
         <v>114</v>
@@ -8303,10 +8315,10 @@
     </row>
     <row r="352" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B352">
-        <v>305207</v>
+        <v>305206</v>
       </c>
       <c r="C352" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E352" t="s">
         <v>114</v>
@@ -8314,10 +8326,10 @@
     </row>
     <row r="353" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B353">
-        <v>305208</v>
+        <v>305207</v>
       </c>
       <c r="C353" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E353" t="s">
         <v>114</v>
@@ -8325,10 +8337,10 @@
     </row>
     <row r="354" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B354">
-        <v>305209</v>
+        <v>305208</v>
       </c>
       <c r="C354" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E354" t="s">
         <v>114</v>
@@ -8336,10 +8348,10 @@
     </row>
     <row r="355" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B355">
-        <v>305210</v>
+        <v>305209</v>
       </c>
       <c r="C355" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E355" t="s">
         <v>114</v>
@@ -8347,10 +8359,10 @@
     </row>
     <row r="356" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B356">
-        <v>305211</v>
+        <v>305210</v>
       </c>
       <c r="C356" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E356" t="s">
         <v>114</v>
@@ -8358,10 +8370,10 @@
     </row>
     <row r="357" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B357">
-        <v>305212</v>
+        <v>305211</v>
       </c>
       <c r="C357" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E357" t="s">
         <v>114</v>
@@ -8369,10 +8381,10 @@
     </row>
     <row r="358" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B358">
-        <v>305213</v>
+        <v>305212</v>
       </c>
       <c r="C358" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E358" t="s">
         <v>114</v>
@@ -8380,7 +8392,10 @@
     </row>
     <row r="359" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B359">
-        <v>305214</v>
+        <v>305213</v>
+      </c>
+      <c r="C359" t="s">
+        <v>515</v>
       </c>
       <c r="E359" t="s">
         <v>114</v>
@@ -8388,10 +8403,7 @@
     </row>
     <row r="360" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B360">
-        <v>305215</v>
-      </c>
-      <c r="C360" t="s">
-        <v>516</v>
+        <v>305214</v>
       </c>
       <c r="E360" t="s">
         <v>114</v>
@@ -8399,10 +8411,10 @@
     </row>
     <row r="361" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B361">
-        <v>305216</v>
+        <v>305215</v>
       </c>
       <c r="C361" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E361" t="s">
         <v>114</v>
@@ -8410,10 +8422,10 @@
     </row>
     <row r="362" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B362">
-        <v>305217</v>
+        <v>305216</v>
       </c>
       <c r="C362" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E362" t="s">
         <v>114</v>
@@ -8421,10 +8433,10 @@
     </row>
     <row r="363" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B363">
-        <v>305218</v>
+        <v>305217</v>
       </c>
       <c r="C363" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E363" t="s">
         <v>114</v>
@@ -8432,10 +8444,10 @@
     </row>
     <row r="364" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B364">
-        <v>305219</v>
+        <v>305218</v>
       </c>
       <c r="C364" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E364" t="s">
         <v>114</v>
@@ -8443,10 +8455,10 @@
     </row>
     <row r="365" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B365">
-        <v>305220</v>
+        <v>305219</v>
       </c>
       <c r="C365" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E365" t="s">
         <v>114</v>
@@ -8454,10 +8466,10 @@
     </row>
     <row r="366" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B366">
-        <v>305221</v>
-      </c>
-      <c r="C366" s="15" t="s">
-        <v>522</v>
+        <v>305220</v>
+      </c>
+      <c r="C366" t="s">
+        <v>521</v>
       </c>
       <c r="E366" t="s">
         <v>114</v>
@@ -8465,10 +8477,10 @@
     </row>
     <row r="367" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B367">
-        <v>305222</v>
+        <v>305221</v>
       </c>
       <c r="C367" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E367" t="s">
         <v>114</v>
@@ -8476,10 +8488,10 @@
     </row>
     <row r="368" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B368">
-        <v>305223</v>
-      </c>
-      <c r="C368" t="s">
-        <v>524</v>
+        <v>305222</v>
+      </c>
+      <c r="C368" s="15" t="s">
+        <v>523</v>
       </c>
       <c r="E368" t="s">
         <v>114</v>
@@ -8487,10 +8499,10 @@
     </row>
     <row r="369" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B369">
-        <v>30520001</v>
-      </c>
-      <c r="C369" s="15" t="s">
-        <v>525</v>
+        <v>305223</v>
+      </c>
+      <c r="C369" t="s">
+        <v>524</v>
       </c>
       <c r="E369" t="s">
         <v>114</v>
@@ -8498,10 +8510,10 @@
     </row>
     <row r="370" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B370">
-        <v>30520002</v>
+        <v>30520001</v>
       </c>
       <c r="C370" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E370" t="s">
         <v>114</v>
@@ -8509,10 +8521,10 @@
     </row>
     <row r="371" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B371">
-        <v>30520003</v>
+        <v>30520002</v>
       </c>
       <c r="C371" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E371" t="s">
         <v>114</v>
@@ -8520,10 +8532,10 @@
     </row>
     <row r="372" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B372">
-        <v>30520004</v>
+        <v>30520003</v>
       </c>
       <c r="C372" s="15" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E372" t="s">
         <v>114</v>
@@ -8531,10 +8543,10 @@
     </row>
     <row r="373" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B373">
-        <v>30520005</v>
+        <v>30520004</v>
       </c>
       <c r="C373" s="15" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E373" t="s">
         <v>114</v>
@@ -8542,10 +8554,10 @@
     </row>
     <row r="374" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B374">
-        <v>30520006</v>
+        <v>30520005</v>
       </c>
       <c r="C374" s="15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E374" t="s">
         <v>114</v>
@@ -8553,10 +8565,10 @@
     </row>
     <row r="375" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B375">
-        <v>30520007</v>
+        <v>30520006</v>
       </c>
       <c r="C375" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E375" t="s">
         <v>114</v>
@@ -8564,21 +8576,21 @@
     </row>
     <row r="376" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B376">
-        <v>30520008</v>
+        <v>30520007</v>
       </c>
       <c r="C376" s="15" t="s">
-        <v>532</v>
-      </c>
-      <c r="E376" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="E376" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="377" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B377">
-        <v>30520009</v>
+        <v>30520008</v>
       </c>
       <c r="C377" s="15" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E377" s="15" t="s">
         <v>114</v>
@@ -8586,33 +8598,32 @@
     </row>
     <row r="378" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B378">
+        <v>30520009</v>
+      </c>
+      <c r="C378" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="E378" s="15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="379" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B379">
         <v>30520010</v>
       </c>
-      <c r="C378" s="15" t="s">
+      <c r="C379" s="15" t="s">
         <v>534</v>
       </c>
-      <c r="E378" s="15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="379" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B379" s="17">
+      <c r="E379" s="15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="380" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B380" s="17">
         <v>30520011</v>
       </c>
-      <c r="C379" s="18" t="s">
+      <c r="C380" s="18" t="s">
         <v>535</v>
-      </c>
-      <c r="D379" s="17"/>
-      <c r="E379" s="15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="380" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B380">
-        <v>30520012</v>
-      </c>
-      <c r="C380" s="18" t="s">
-        <v>747</v>
       </c>
       <c r="D380" s="17"/>
       <c r="E380" s="15" t="s">
@@ -8621,21 +8632,22 @@
     </row>
     <row r="381" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B381">
-        <v>305224</v>
-      </c>
-      <c r="C381" t="s">
-        <v>536</v>
-      </c>
-      <c r="E381" t="s">
+        <v>30520012</v>
+      </c>
+      <c r="C381" s="18" t="s">
+        <v>747</v>
+      </c>
+      <c r="D381" s="17"/>
+      <c r="E381" s="15" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="382" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B382">
-        <v>305225</v>
+        <v>305224</v>
       </c>
       <c r="C382" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E382" t="s">
         <v>114</v>
@@ -8643,10 +8655,10 @@
     </row>
     <row r="383" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B383">
-        <v>305226</v>
+        <v>305225</v>
       </c>
       <c r="C383" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E383" t="s">
         <v>114</v>
@@ -8654,10 +8666,10 @@
     </row>
     <row r="384" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B384">
-        <v>305300</v>
+        <v>305226</v>
       </c>
       <c r="C384" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E384" t="s">
         <v>114</v>
@@ -8665,10 +8677,10 @@
     </row>
     <row r="385" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B385">
-        <v>305301</v>
+        <v>305300</v>
       </c>
       <c r="C385" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E385" t="s">
         <v>114</v>
@@ -8676,10 +8688,10 @@
     </row>
     <row r="386" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B386">
-        <v>305302</v>
+        <v>305301</v>
       </c>
       <c r="C386" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E386" t="s">
         <v>114</v>
@@ -8687,10 +8699,10 @@
     </row>
     <row r="387" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B387">
-        <v>305303</v>
+        <v>305302</v>
       </c>
       <c r="C387" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E387" t="s">
         <v>114</v>
@@ -8698,10 +8710,10 @@
     </row>
     <row r="388" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B388">
-        <v>305304</v>
+        <v>305303</v>
       </c>
       <c r="C388" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E388" t="s">
         <v>114</v>
@@ -8709,10 +8721,10 @@
     </row>
     <row r="389" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B389">
-        <v>305305</v>
+        <v>305304</v>
       </c>
       <c r="C389" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E389" t="s">
         <v>114</v>
@@ -8720,10 +8732,10 @@
     </row>
     <row r="390" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B390">
-        <v>305306</v>
+        <v>305305</v>
       </c>
       <c r="C390" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E390" t="s">
         <v>114</v>
@@ -8731,10 +8743,10 @@
     </row>
     <row r="391" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B391">
-        <v>305307</v>
+        <v>305306</v>
       </c>
       <c r="C391" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E391" t="s">
         <v>114</v>
@@ -8742,10 +8754,10 @@
     </row>
     <row r="392" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B392">
-        <v>305308</v>
+        <v>305307</v>
       </c>
       <c r="C392" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E392" t="s">
         <v>114</v>
@@ -8753,10 +8765,10 @@
     </row>
     <row r="393" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B393">
-        <v>305309</v>
+        <v>305308</v>
       </c>
       <c r="C393" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E393" t="s">
         <v>114</v>
@@ -8764,10 +8776,10 @@
     </row>
     <row r="394" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B394">
-        <v>305310</v>
+        <v>305309</v>
       </c>
       <c r="C394" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E394" t="s">
         <v>114</v>
@@ -8775,10 +8787,10 @@
     </row>
     <row r="395" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B395">
-        <v>305311</v>
+        <v>305310</v>
       </c>
       <c r="C395" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E395" t="s">
         <v>114</v>
@@ -8786,10 +8798,10 @@
     </row>
     <row r="396" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B396">
-        <v>305312</v>
+        <v>305311</v>
       </c>
       <c r="C396" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E396" t="s">
         <v>114</v>
@@ -8797,10 +8809,10 @@
     </row>
     <row r="397" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B397">
-        <v>305313</v>
+        <v>305312</v>
       </c>
       <c r="C397" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E397" t="s">
         <v>114</v>
@@ -8808,7 +8820,10 @@
     </row>
     <row r="398" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B398">
-        <v>305314</v>
+        <v>305313</v>
+      </c>
+      <c r="C398" t="s">
+        <v>552</v>
       </c>
       <c r="E398" t="s">
         <v>114</v>
@@ -8816,10 +8831,7 @@
     </row>
     <row r="399" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B399">
-        <v>305315</v>
-      </c>
-      <c r="C399" t="s">
-        <v>553</v>
+        <v>305314</v>
       </c>
       <c r="E399" t="s">
         <v>114</v>
@@ -8827,10 +8839,10 @@
     </row>
     <row r="400" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B400">
-        <v>305316</v>
+        <v>305315</v>
       </c>
       <c r="C400" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E400" t="s">
         <v>114</v>
@@ -8838,10 +8850,10 @@
     </row>
     <row r="401" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B401">
-        <v>305317</v>
+        <v>305316</v>
       </c>
       <c r="C401" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E401" t="s">
         <v>114</v>
@@ -8849,10 +8861,10 @@
     </row>
     <row r="402" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B402">
-        <v>305318</v>
+        <v>305317</v>
       </c>
       <c r="C402" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E402" t="s">
         <v>114</v>
@@ -8860,10 +8872,10 @@
     </row>
     <row r="403" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B403">
-        <v>305319</v>
+        <v>305318</v>
       </c>
       <c r="C403" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E403" t="s">
         <v>114</v>
@@ -8871,10 +8883,10 @@
     </row>
     <row r="404" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B404">
-        <v>305320</v>
+        <v>305319</v>
       </c>
       <c r="C404" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E404" t="s">
         <v>114</v>
@@ -8882,10 +8894,10 @@
     </row>
     <row r="405" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B405">
-        <v>305321</v>
-      </c>
-      <c r="C405" s="15" t="s">
-        <v>559</v>
+        <v>305320</v>
+      </c>
+      <c r="C405" t="s">
+        <v>558</v>
       </c>
       <c r="E405" t="s">
         <v>114</v>
@@ -8893,10 +8905,10 @@
     </row>
     <row r="406" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B406">
-        <v>305322</v>
+        <v>305321</v>
       </c>
       <c r="C406" s="15" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E406" t="s">
         <v>114</v>
@@ -8904,10 +8916,10 @@
     </row>
     <row r="407" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B407">
-        <v>305323</v>
-      </c>
-      <c r="C407" t="s">
-        <v>561</v>
+        <v>305322</v>
+      </c>
+      <c r="C407" s="15" t="s">
+        <v>560</v>
       </c>
       <c r="E407" t="s">
         <v>114</v>
@@ -8915,10 +8927,10 @@
     </row>
     <row r="408" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B408">
-        <v>305324</v>
+        <v>305323</v>
       </c>
       <c r="C408" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E408" t="s">
         <v>114</v>
@@ -8926,10 +8938,10 @@
     </row>
     <row r="409" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B409">
-        <v>305325</v>
+        <v>305324</v>
       </c>
       <c r="C409" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E409" t="s">
         <v>114</v>
@@ -8937,10 +8949,10 @@
     </row>
     <row r="410" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B410">
-        <v>305326</v>
-      </c>
-      <c r="C410" s="15" t="s">
-        <v>564</v>
+        <v>305325</v>
+      </c>
+      <c r="C410" t="s">
+        <v>563</v>
       </c>
       <c r="E410" t="s">
         <v>114</v>
@@ -8948,10 +8960,10 @@
     </row>
     <row r="411" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B411">
-        <v>30530001</v>
+        <v>305326</v>
       </c>
       <c r="C411" s="15" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E411" t="s">
         <v>114</v>
@@ -8959,10 +8971,10 @@
     </row>
     <row r="412" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B412">
-        <v>30530002</v>
-      </c>
-      <c r="C412" t="s">
-        <v>566</v>
+        <v>30530001</v>
+      </c>
+      <c r="C412" s="15" t="s">
+        <v>565</v>
       </c>
       <c r="E412" t="s">
         <v>114</v>
@@ -8970,10 +8982,10 @@
     </row>
     <row r="413" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B413">
-        <v>30530003</v>
-      </c>
-      <c r="C413" s="15" t="s">
-        <v>567</v>
+        <v>30530002</v>
+      </c>
+      <c r="C413" t="s">
+        <v>566</v>
       </c>
       <c r="E413" t="s">
         <v>114</v>
@@ -8981,10 +8993,10 @@
     </row>
     <row r="414" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B414">
-        <v>30530004</v>
+        <v>30530003</v>
       </c>
       <c r="C414" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E414" t="s">
         <v>114</v>
@@ -8992,10 +9004,10 @@
     </row>
     <row r="415" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B415">
-        <v>30530005</v>
+        <v>30530004</v>
       </c>
       <c r="C415" s="15" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E415" t="s">
         <v>114</v>
@@ -9003,10 +9015,10 @@
     </row>
     <row r="416" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B416">
-        <v>30530006</v>
+        <v>30530005</v>
       </c>
       <c r="C416" s="15" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E416" t="s">
         <v>114</v>
@@ -9014,21 +9026,21 @@
     </row>
     <row r="417" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B417">
-        <v>30530007</v>
+        <v>30530006</v>
       </c>
       <c r="C417" s="15" t="s">
-        <v>571</v>
-      </c>
-      <c r="E417" s="15" t="s">
+        <v>570</v>
+      </c>
+      <c r="E417" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="418" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B418">
-        <v>30530008</v>
+        <v>30530007</v>
       </c>
       <c r="C418" s="15" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E418" s="15" t="s">
         <v>114</v>
@@ -9036,10 +9048,10 @@
     </row>
     <row r="419" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B419">
-        <v>30530009</v>
+        <v>30530008</v>
       </c>
       <c r="C419" s="15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E419" s="15" t="s">
         <v>114</v>
@@ -9047,33 +9059,32 @@
     </row>
     <row r="420" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B420">
+        <v>30530009</v>
+      </c>
+      <c r="C420" s="15" t="s">
+        <v>573</v>
+      </c>
+      <c r="E420" s="15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="421" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B421">
         <v>30530010</v>
       </c>
-      <c r="C420" s="15" t="s">
+      <c r="C421" s="15" t="s">
         <v>574</v>
       </c>
-      <c r="E420" s="15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="421" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B421" s="17">
+      <c r="E421" s="15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="422" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B422" s="17">
         <v>30530011</v>
       </c>
-      <c r="C421" s="18" t="s">
+      <c r="C422" s="18" t="s">
         <v>575</v>
-      </c>
-      <c r="D421" s="17"/>
-      <c r="E421" s="18" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="422" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B422">
-        <v>30530012</v>
-      </c>
-      <c r="C422" s="18" t="s">
-        <v>746</v>
       </c>
       <c r="D422" s="17"/>
       <c r="E422" s="18" t="s">
@@ -9082,21 +9093,22 @@
     </row>
     <row r="423" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B423">
-        <v>309205</v>
-      </c>
-      <c r="C423" t="s">
-        <v>576</v>
-      </c>
-      <c r="E423" t="s">
+        <v>30530012</v>
+      </c>
+      <c r="C423" s="18" t="s">
+        <v>746</v>
+      </c>
+      <c r="D423" s="17"/>
+      <c r="E423" s="18" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="424" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B424">
-        <v>308001</v>
+        <v>309205</v>
       </c>
       <c r="C424" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E424" t="s">
         <v>114</v>
@@ -9104,10 +9116,10 @@
     </row>
     <row r="425" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B425">
-        <v>308002</v>
+        <v>308001</v>
       </c>
       <c r="C425" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E425" t="s">
         <v>114</v>
@@ -9115,10 +9127,10 @@
     </row>
     <row r="426" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B426">
-        <v>308006</v>
+        <v>308002</v>
       </c>
       <c r="C426" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E426" t="s">
         <v>114</v>
@@ -9126,10 +9138,10 @@
     </row>
     <row r="427" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B427">
-        <v>308007</v>
+        <v>308006</v>
       </c>
       <c r="C427" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E427" t="s">
         <v>114</v>
@@ -9137,10 +9149,10 @@
     </row>
     <row r="428" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B428">
-        <v>308011</v>
+        <v>308007</v>
       </c>
       <c r="C428" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E428" t="s">
         <v>114</v>
@@ -9148,10 +9160,10 @@
     </row>
     <row r="429" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B429">
-        <v>308012</v>
+        <v>308011</v>
       </c>
       <c r="C429" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E429" t="s">
         <v>114</v>
@@ -9159,10 +9171,10 @@
     </row>
     <row r="430" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B430">
-        <v>308016</v>
+        <v>308012</v>
       </c>
       <c r="C430" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E430" t="s">
         <v>114</v>
@@ -9170,10 +9182,10 @@
     </row>
     <row r="431" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B431">
-        <v>308017</v>
+        <v>308016</v>
       </c>
       <c r="C431" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E431" t="s">
         <v>114</v>
@@ -9181,10 +9193,10 @@
     </row>
     <row r="432" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B432">
-        <v>308021</v>
-      </c>
-      <c r="C432" s="15" t="s">
-        <v>585</v>
+        <v>308017</v>
+      </c>
+      <c r="C432" t="s">
+        <v>584</v>
       </c>
       <c r="E432" t="s">
         <v>114</v>
@@ -9192,10 +9204,10 @@
     </row>
     <row r="433" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B433">
-        <v>308022</v>
+        <v>308021</v>
       </c>
       <c r="C433" s="15" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E433" t="s">
         <v>114</v>
@@ -9203,10 +9215,10 @@
     </row>
     <row r="434" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B434">
-        <v>308026</v>
+        <v>308022</v>
       </c>
       <c r="C434" s="15" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E434" t="s">
         <v>114</v>
@@ -9214,10 +9226,10 @@
     </row>
     <row r="435" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B435">
-        <v>308027</v>
+        <v>308026</v>
       </c>
       <c r="C435" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E435" t="s">
         <v>114</v>
@@ -9225,10 +9237,10 @@
     </row>
     <row r="436" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B436">
-        <v>308031</v>
+        <v>308027</v>
       </c>
       <c r="C436" s="15" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E436" t="s">
         <v>114</v>
@@ -9236,10 +9248,10 @@
     </row>
     <row r="437" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B437">
-        <v>308032</v>
+        <v>308031</v>
       </c>
       <c r="C437" s="15" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E437" t="s">
         <v>114</v>
@@ -9247,10 +9259,10 @@
     </row>
     <row r="438" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B438">
-        <v>308036</v>
+        <v>308032</v>
       </c>
       <c r="C438" s="15" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E438" t="s">
         <v>114</v>
@@ -9258,10 +9270,10 @@
     </row>
     <row r="439" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B439">
-        <v>308037</v>
+        <v>308036</v>
       </c>
       <c r="C439" s="15" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E439" t="s">
         <v>114</v>
@@ -9269,10 +9281,10 @@
     </row>
     <row r="440" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B440">
-        <v>308041</v>
+        <v>308037</v>
       </c>
       <c r="C440" s="15" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E440" t="s">
         <v>114</v>
@@ -9280,10 +9292,10 @@
     </row>
     <row r="441" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B441">
-        <v>308042</v>
+        <v>308041</v>
       </c>
       <c r="C441" s="15" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E441" t="s">
         <v>114</v>
@@ -9291,10 +9303,10 @@
     </row>
     <row r="442" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B442">
-        <v>308046</v>
+        <v>308042</v>
       </c>
       <c r="C442" s="15" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E442" t="s">
         <v>114</v>
@@ -9302,10 +9314,10 @@
     </row>
     <row r="443" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B443">
-        <v>308047</v>
+        <v>308046</v>
       </c>
       <c r="C443" s="15" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E443" t="s">
         <v>114</v>
@@ -9313,25 +9325,36 @@
     </row>
     <row r="444" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B444">
-        <v>308048</v>
-      </c>
-      <c r="C444" s="18" t="s">
-        <v>767</v>
-      </c>
-      <c r="D444" s="44"/>
-      <c r="E444" s="17" t="s">
+        <v>308047</v>
+      </c>
+      <c r="C444" s="15" t="s">
+        <v>596</v>
+      </c>
+      <c r="E444" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="445" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B445">
-        <v>308049</v>
+        <v>308048</v>
       </c>
       <c r="C445" s="18" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D445" s="44"/>
       <c r="E445" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="446" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B446">
+        <v>308049</v>
+      </c>
+      <c r="C446" s="18" t="s">
+        <v>768</v>
+      </c>
+      <c r="D446" s="44"/>
+      <c r="E446" s="17" t="s">
         <v>114</v>
       </c>
     </row>
